--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 16-Apr-2026  16:34</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 17-Apr-2026  16:46</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -687,10 +687,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.867</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.9556999999999999</v>
+        <v>0.9777</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>7</v>
@@ -715,13 +715,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.583</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.75</v>
+        <v>0.7776999999999999</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -737,22 +737,22 @@
         <v>15</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.8</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.711</v>
+        <v>0.7776999999999999</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -768,270 +768,270 @@
         <v>14</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>0.9329999999999999</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.6</v>
+        <v>0.733</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.467</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0.9</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.6333</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.6333</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.55</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>0.6</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.65</v>
+        <v>0.333</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.6</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.525</v>
+        <v>0.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.575</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="I13" s="11" t="n">
         <v>0.6</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>0.5667</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.467</v>
+        <v>0.7</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.489</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.6</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.3777</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1078,7 +1078,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>3</v>
@@ -1087,13 +1087,13 @@
         <v>0.333</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.25</v>
+        <v>0.2777</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2045.3</v>
+        <v>2105.7</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2005.69</v>
+        <v>2015.22</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2019.71</v>
+        <v>2023.09</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1879.04</v>
+        <v>1883.08</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1039.9</v>
+        <v>1039</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>950.1799999999999</v>
+        <v>958.64</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>930.89</v>
+        <v>935.13</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>836.11</v>
+        <v>838.1</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>563.75</v>
+        <v>569.6</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>518.9</v>
+        <v>523.73</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>520.76</v>
+        <v>522.6799999999999</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>421.82</v>
+        <v>423.35</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>592.5</v>
+        <v>592.3</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>552.78</v>
+        <v>556.55</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>565.66</v>
+        <v>566.71</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>532.45</v>
+        <v>533.1799999999999</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1228.3</v>
+        <v>1270</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1182.19</v>
+        <v>1190.55</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1162.13</v>
+        <v>1166.36</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1068.98</v>
+        <v>1073.28</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>789.45</v>
+        <v>788.2</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>747.52</v>
+        <v>751.39</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>753.13</v>
+        <v>754.51</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>738.1799999999999</v>
+        <v>738.91</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1214.9</v>
+        <v>1240.3</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1182.45</v>
+        <v>1187.96</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1185.53</v>
+        <v>1187.67</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1141.4</v>
+        <v>1142.2</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>432.7</v>
+        <v>438.75</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>399.84</v>
+        <v>403.55</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>377.64</v>
+        <v>380.03</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>292.95</v>
+        <v>294.53</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>87.16</v>
+        <v>89.78</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>81.97</v>
+        <v>82.72</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>80.33</v>
+        <v>80.7</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>75.31999999999999</v>
+        <v>75.48</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>171.32</v>
+        <v>2461.3</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>159.91</v>
+        <v>2315.7</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>155.76</v>
+        <v>2298.99</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>141.92</v>
+        <v>2380.76</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,23 +1509,23 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>210.69</v>
+        <v>173.33</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>200.68</v>
+        <v>161.18</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>197.05</v>
+        <v>156.44</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>179.18</v>
+        <v>142.12</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,23 +1537,23 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>782.85</v>
+        <v>212.12</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>712.01</v>
+        <v>201.77</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>683.5599999999999</v>
+        <v>197.64</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>570.4</v>
+        <v>179.53</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VEDL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,79 +1565,79 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>719.2</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>687.63</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>572.67</v>
+      </c>
+      <c r="G15" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VEDL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
-        <v>1077.1</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>906.23</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>852.6900000000001</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>835.62</v>
-      </c>
-      <c r="G15" s="15">
+      <c r="C16" s="14" t="n">
+        <v>1077.15</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>922.51</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>861.49</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>836.52</v>
+      </c>
+      <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>CANBK</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
-        <v>141.03</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>137.02</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>140.62</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>133.04</v>
-      </c>
-      <c r="G16" s="19">
+      <c r="C17" s="18" t="n">
+        <v>142.37</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>137.53</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>140.69</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>133.23</v>
+      </c>
+      <c r="G17" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANBK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>940.05</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>918.5700000000001</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>903.05</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>806.14</v>
-      </c>
-      <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,23 +1649,23 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>71.25</v>
+        <v>939.45</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>67.75</v>
+        <v>920.5599999999999</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>66.43000000000001</v>
+        <v>904.48</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>60.24</v>
+        <v>808.04</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,107 +1677,107 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>68.23</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>1080.25</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>1061.75</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>1071.76</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>979.8099999999999</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
           <t>UNIONBANK</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n">
-        <v>188.49</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>181.17</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>178.98</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>159.89</v>
-      </c>
-      <c r="G19" s="19">
+      <c r="C21" s="18" t="n">
+        <v>188.91</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>179.36</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>160.13</v>
+      </c>
+      <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
-        <v>7714.5</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>6984.03</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>6967.07</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>7040.91</v>
-      </c>
-      <c r="G20" s="15">
+      <c r="C22" s="14" t="n">
+        <v>7958.5</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>7076.84</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>7005.95</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>7045.14</v>
+      </c>
+      <c r="G22" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>1849.3</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>1719.43</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>1773.33</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>1826.06</v>
-      </c>
-      <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>1170.2</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>1031.16</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>994.47</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>1015.81</v>
-      </c>
-      <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>4461.4</v>
+        <v>1866.1</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>4273.29</v>
+        <v>1733.39</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>4186.6</v>
+        <v>1776.97</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>3894.56</v>
+        <v>1823.3</v>
       </c>
       <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,135 +1817,135 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
+          <t>CENTURYPLY</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>762.15</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>722.39</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>728.85</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>752.0599999999999</v>
+      </c>
+      <c r="G24" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>1178.35</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>1045.18</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>1001.68</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>1019.2</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>4525.9</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>4297.35</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>4199.91</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>3905.47</v>
+      </c>
+      <c r="G26" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
           <t>VOLTAS</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
-        <v>1408.8</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>1341.8</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>1379.13</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>1374.37</v>
-      </c>
-      <c r="G24" s="15">
+      <c r="C27" s="14" t="n">
+        <v>1440.1</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>1351.16</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>1381.52</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>1375.67</v>
+      </c>
+      <c r="G27" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n">
-        <v>9825</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>9380.15</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>9377.98</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>9040.120000000001</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="C28" s="18" t="n">
+        <v>9773.5</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>9417.610000000001</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>9393.49</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>9052.030000000001</v>
+      </c>
+      <c r="G28" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>1855.8</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>1756.02</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>1705.26</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>1465.64</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>37440</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>34067.49</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>34066.45</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>34816.47</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>122.82</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>116.45</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>117.53</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>110.81</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1957,443 +1957,443 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>1860.5</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>1765.97</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>1711.35</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>1470.67</v>
+      </c>
+      <c r="G29" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>37505</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>34394.88</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>34201.3</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>34854.37</v>
+      </c>
+      <c r="G30" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>7189.5</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>7054.81</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>7170.75</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>6845.43</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>125.03</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>117.27</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>117.83</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>111.02</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
           <t>TVSMOTOR</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n">
-        <v>3757.2</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>3620.96</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>3627.67</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>3437.34</v>
-      </c>
-      <c r="G29" s="19">
+      <c r="C33" s="18" t="n">
+        <v>3735.8</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>3631.89</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>3631.92</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>3445.74</v>
+      </c>
+      <c r="G33" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>1349.6</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>1285.8</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>1285.27</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>1243.28</v>
-      </c>
-      <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>HDFCAMC</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>2662.2</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>2492.35</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>2526.46</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>2561.79</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>ICICIGI</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>1886.7</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>1792.98</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>1829.67</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>1881.88</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIGI","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>2862.2</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>2600.44</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>2490.39</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>2066.92</v>
-      </c>
-      <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>DISHTV</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>3578</v>
+        <v>4.08</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>3410.71</v>
+        <v>2.94</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>3453.89</v>
+        <v>2.96</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>3252.43</v>
+        <v>3.93</v>
       </c>
       <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DISHTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>458.9</v>
+        <v>273.34</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>418.8</v>
+        <v>248.74</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>405.17</v>
+        <v>252.04</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>390.35</v>
+        <v>265.25</v>
       </c>
       <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>364.2</v>
+        <v>643.25</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>338.94</v>
+        <v>603.5599999999999</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>340.84</v>
+        <v>590.15</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>356.69</v>
+        <v>580.51</v>
       </c>
       <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>1974.7</v>
+        <v>585.55</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>1903.22</v>
+        <v>538.04</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>1937.26</v>
+        <v>533.1</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1904.65</v>
+        <v>554.11</v>
       </c>
       <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBILIFE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>1022.75</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>980.73</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>982.89</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>863.75</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>5582</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>5402.97</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>5444.86</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>5391.28</v>
+      </c>
+      <c r="G38" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
-        <v>632.2</v>
+        <v>1386</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>599.39</v>
+        <v>1326.98</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>587.98</v>
+        <v>1274.22</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>581.15</v>
+        <v>1196.8</v>
       </c>
       <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>574.5</v>
+        <v>6229</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>533.04</v>
+        <v>6081.21</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>530.96</v>
+        <v>6142.67</v>
       </c>
       <c r="F40" s="18" t="n">
-        <v>554</v>
+        <v>6213.36</v>
       </c>
       <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>91.48</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>77.26000000000001</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>73.28</v>
-      </c>
-      <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>1797.4</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>1722.58</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>1729.74</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>1743.73</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>7776</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>7065.62</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>7070.03</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>7666.11</v>
-      </c>
-      <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>2249.5</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>2169.77</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>2117.46</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>1948.93</v>
+      </c>
+      <c r="G42" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>5500.5</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>5195.06</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>5266.06</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>5495.39</v>
-      </c>
-      <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>655.7</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>625.28</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>603.9400000000001</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>559.52</v>
+      </c>
+      <c r="G43" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>5570</v>
+        <v>1135.75</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>5384.13</v>
+        <v>1064.13</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>5439.27</v>
+        <v>1039.32</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>5389.73</v>
+        <v>945.71</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2405,23 +2405,23 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>1386.5</v>
+        <v>2326.1</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>1320.76</v>
+        <v>2309.3</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>1269.65</v>
+        <v>2272.36</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>1191.64</v>
+        <v>2124.04</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>6293.5</v>
+        <v>1119.7</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>6065.65</v>
+        <v>1043.34</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>6139.15</v>
+        <v>982.9400000000001</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>6222.8</v>
+        <v>906.25</v>
       </c>
       <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2461,23 +2461,23 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>2249.5</v>
+        <v>4179.5</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>2161.38</v>
+        <v>4170.88</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>2112.07</v>
+        <v>4153.44</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>1947.13</v>
+        <v>3836.77</v>
       </c>
       <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2489,947 +2489,1339 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>651</v>
+        <v>943.95</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>622.08</v>
+        <v>905.64</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>601.8200000000001</v>
+        <v>903.72</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>558.1799999999999</v>
+        <v>916.91</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="n">
-        <v>1128.35</v>
-      </c>
-      <c r="D49" s="18" t="n">
-        <v>1056.59</v>
-      </c>
-      <c r="E49" s="18" t="n">
-        <v>1035.39</v>
-      </c>
-      <c r="F49" s="18" t="n">
-        <v>943.7</v>
-      </c>
-      <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>1359.1</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>1292.78</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>1288.17</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>1246.9</v>
+      </c>
+      <c r="G49" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="n">
-        <v>2327</v>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>2307.53</v>
-      </c>
-      <c r="E50" s="18" t="n">
-        <v>2270.17</v>
-      </c>
-      <c r="F50" s="18" t="n">
-        <v>2121.76</v>
-      </c>
-      <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>2792.4</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>2520.92</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>2536.89</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>2567.7</v>
+      </c>
+      <c r="G50" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>NATCOPHARM</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="n">
-        <v>1086.8</v>
-      </c>
-      <c r="D51" s="18" t="n">
-        <v>1035.3</v>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>977.36</v>
-      </c>
-      <c r="F51" s="18" t="n">
-        <v>904.02</v>
-      </c>
-      <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="n">
+        <v>1891.6</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>1802.37</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>1832.09</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>1880.45</v>
+      </c>
+      <c r="G51" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIGI","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="n">
-        <v>939.1</v>
-      </c>
-      <c r="D52" s="18" t="n">
-        <v>901.6</v>
-      </c>
-      <c r="E52" s="18" t="n">
-        <v>902.0700000000001</v>
-      </c>
-      <c r="F52" s="18" t="n">
-        <v>915.85</v>
-      </c>
-      <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="n">
+        <v>2856.1</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>2624.79</v>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>2504.73</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>2075.45</v>
+      </c>
+      <c r="G52" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C53" s="14" t="n">
-        <v>6883.5</v>
+        <v>3571.3</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>6428.35</v>
+        <v>3400.13</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>6095.69</v>
+        <v>3430.67</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>5600.74</v>
+        <v>3231.14</v>
       </c>
       <c r="G53" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>1222.6</v>
+        <v>464.85</v>
       </c>
       <c r="D54" s="14" t="n">
-        <v>1058.91</v>
+        <v>423.19</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>1017.76</v>
+        <v>407.51</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>957.29</v>
+        <v>391.08</v>
       </c>
       <c r="G54" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>1118.9</v>
+        <v>373.3</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>968.14</v>
+        <v>342.21</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>941.27</v>
+        <v>342.11</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>966.54</v>
+        <v>357.15</v>
       </c>
       <c r="G55" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="C56" s="14" t="n">
-        <v>193.19</v>
+        <v>1970.9</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>165.24</v>
+        <v>1909.66</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>154.91</v>
+        <v>1938.58</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>141.1</v>
+        <v>1908.89</v>
       </c>
       <c r="G56" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBILIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C57" s="14" t="n">
-        <v>309.26</v>
+        <v>1036.95</v>
       </c>
       <c r="D57" s="14" t="n">
-        <v>269.93</v>
+        <v>986.09</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>265.13</v>
+        <v>985.01</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>257.25</v>
+        <v>866.78</v>
       </c>
       <c r="G57" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>170.48</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>157.1</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>156.33</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>159.56</v>
-      </c>
-      <c r="G58" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>486</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>483.16</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>474.3</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>484.96</v>
+      </c>
+      <c r="G58" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n">
-        <v>755.9</v>
-      </c>
-      <c r="D59" s="14" t="n">
-        <v>708.84</v>
-      </c>
-      <c r="E59" s="14" t="n">
-        <v>692.59</v>
-      </c>
-      <c r="F59" s="14" t="n">
-        <v>677.53</v>
-      </c>
-      <c r="G59" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>757.3</v>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>753.33</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>755.9299999999999</v>
+      </c>
+      <c r="F59" s="18" t="n">
+        <v>739.63</v>
+      </c>
+      <c r="G59" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="n">
-        <v>4074.2</v>
-      </c>
-      <c r="D60" s="14" t="n">
-        <v>3842.46</v>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v>3653.68</v>
-      </c>
-      <c r="F60" s="14" t="n">
-        <v>3047.67</v>
-      </c>
-      <c r="G60" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>1285.6</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>1231.22</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>1241.83</v>
+      </c>
+      <c r="F60" s="18" t="n">
+        <v>1235.2</v>
+      </c>
+      <c r="G60" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>JPPOWER</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="D61" s="14" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="E61" s="14" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="F61" s="14" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="G61" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>3186.9</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>2802.35</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>2797.92</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>2847.52</v>
+      </c>
+      <c r="G61" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
-        <v>535.95</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>500.14</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>493.59</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>498.98</v>
-      </c>
-      <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>473.9</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>426.58</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>433.53</v>
+      </c>
+      <c r="F62" s="18" t="n">
+        <v>465.38</v>
+      </c>
+      <c r="G62" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="C63" s="14" t="n">
-        <v>81.38</v>
+        <v>390.7</v>
       </c>
       <c r="D63" s="14" t="n">
-        <v>77.01000000000001</v>
+        <v>370.01</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>76.54000000000001</v>
+        <v>378.99</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>78.88</v>
+        <v>389.39</v>
       </c>
       <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BSOFT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C64" s="14" t="n">
-        <v>297.75</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="D64" s="14" t="n">
-        <v>270.7</v>
+        <v>79</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>263.71</v>
+        <v>73.98</v>
       </c>
       <c r="F64" s="14" t="n">
-        <v>252.02</v>
+        <v>73.58</v>
       </c>
       <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="n">
+        <v>7992.5</v>
+      </c>
+      <c r="D65" s="14" t="n">
+        <v>7153.9</v>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>7106.21</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>7674.75</v>
+      </c>
+      <c r="G65" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="n">
-        <v>390.8</v>
-      </c>
-      <c r="D65" s="14" t="n">
-        <v>378.04</v>
-      </c>
-      <c r="E65" s="14" t="n">
-        <v>370.35</v>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>349.36</v>
-      </c>
-      <c r="G65" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>7029.5</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>6485.6</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>6132.32</v>
+      </c>
+      <c r="F66" s="18" t="n">
+        <v>5630.9</v>
+      </c>
+      <c r="G66" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="n">
-        <v>312.25</v>
-      </c>
-      <c r="D66" s="14" t="n">
-        <v>299.78</v>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>293.12</v>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>283.32</v>
-      </c>
-      <c r="G66" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n">
+        <v>1259.8</v>
+      </c>
+      <c r="D67" s="18" t="n">
+        <v>1078.04</v>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>1027.25</v>
+      </c>
+      <c r="F67" s="18" t="n">
+        <v>961.91</v>
+      </c>
+      <c r="G67" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>POWERINDIA</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="n">
-        <v>28255</v>
-      </c>
-      <c r="D67" s="14" t="n">
-        <v>26149.29</v>
-      </c>
-      <c r="E67" s="14" t="n">
-        <v>24299.48</v>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>20544.54</v>
-      </c>
-      <c r="G67" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>1127.3</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>983.3</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>948.5700000000001</v>
+      </c>
+      <c r="F68" s="18" t="n">
+        <v>968.27</v>
+      </c>
+      <c r="G68" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>SCHNEIDER</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="n">
-        <v>998.25</v>
-      </c>
-      <c r="D68" s="14" t="n">
-        <v>936.4400000000001</v>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v>877.66</v>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>798.8099999999999</v>
-      </c>
-      <c r="G68" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="16" t="inlineStr">
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n">
+        <v>198.5</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>168.41</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>156.61</v>
+      </c>
+      <c r="F69" s="18" t="n">
+        <v>141.74</v>
+      </c>
+      <c r="G69" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="n">
-        <v>3563.8</v>
-      </c>
-      <c r="D69" s="14" t="n">
-        <v>3240.44</v>
-      </c>
-      <c r="E69" s="14" t="n">
-        <v>3190.25</v>
-      </c>
-      <c r="F69" s="14" t="n">
-        <v>3128.6</v>
-      </c>
-      <c r="G69" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>316.79</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>274.39</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>267.16</v>
+      </c>
+      <c r="F70" s="18" t="n">
+        <v>257.96</v>
+      </c>
+      <c r="G70" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="n">
-        <v>426.6</v>
-      </c>
-      <c r="D70" s="14" t="n">
-        <v>396.68</v>
-      </c>
-      <c r="E70" s="14" t="n">
-        <v>387.56</v>
-      </c>
-      <c r="F70" s="14" t="n">
-        <v>384.47</v>
-      </c>
-      <c r="G70" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="16" t="inlineStr">
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n">
+        <v>171.49</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>158.47</v>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>156.92</v>
+      </c>
+      <c r="F71" s="18" t="n">
+        <v>159.72</v>
+      </c>
+      <c r="G71" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C71" s="14" t="n">
-        <v>4126.4</v>
-      </c>
-      <c r="D71" s="14" t="n">
-        <v>3480.31</v>
-      </c>
-      <c r="E71" s="14" t="n">
-        <v>3266.35</v>
-      </c>
-      <c r="F71" s="14" t="n">
-        <v>3190.43</v>
-      </c>
-      <c r="G71" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="16" t="inlineStr">
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="n">
+        <v>774.8</v>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>715.12</v>
+      </c>
+      <c r="E72" s="18" t="n">
+        <v>695.8099999999999</v>
+      </c>
+      <c r="F72" s="18" t="n">
+        <v>680.26</v>
+      </c>
+      <c r="G72" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="n">
-        <v>1521.6</v>
-      </c>
-      <c r="D72" s="14" t="n">
-        <v>1438.71</v>
-      </c>
-      <c r="E72" s="14" t="n">
-        <v>1423.79</v>
-      </c>
-      <c r="F72" s="14" t="n">
-        <v>1386.69</v>
-      </c>
-      <c r="G72" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C73" s="18" t="n">
-        <v>1710.4</v>
+        <v>4138.2</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>1573.19</v>
+        <v>3870.63</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>1548.37</v>
+        <v>3672.68</v>
       </c>
       <c r="F73" s="18" t="n">
-        <v>1608.91</v>
+        <v>3057</v>
       </c>
       <c r="G73" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="C74" s="18" t="n">
-        <v>1782.3</v>
+        <v>19.2</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>1653.11</v>
+        <v>16.49</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>1660.66</v>
+        <v>15.83</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>1665.03</v>
+        <v>16.65</v>
       </c>
       <c r="G74" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B75" s="13" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="n">
-        <v>597.6</v>
-      </c>
-      <c r="D75" s="14" t="n">
-        <v>547.62</v>
-      </c>
-      <c r="E75" s="14" t="n">
-        <v>540.89</v>
-      </c>
-      <c r="F75" s="14" t="n">
-        <v>575.72</v>
-      </c>
-      <c r="G75" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="n">
+        <v>538.05</v>
+      </c>
+      <c r="D75" s="18" t="n">
+        <v>503.75</v>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>495.33</v>
+      </c>
+      <c r="F75" s="18" t="n">
+        <v>499.22</v>
+      </c>
+      <c r="G75" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="C76" s="14" t="n">
-        <v>282.75</v>
-      </c>
-      <c r="D76" s="14" t="n">
-        <v>280.59</v>
-      </c>
-      <c r="E76" s="14" t="n">
-        <v>271.23</v>
-      </c>
-      <c r="F76" s="14" t="n">
-        <v>249.11</v>
-      </c>
-      <c r="G76" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+      <c r="A76" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>77.63</v>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="F76" s="18" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="G76" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
+      <c r="A77" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C77" s="18" t="n">
-        <v>1257.4</v>
+        <v>300.65</v>
       </c>
       <c r="D77" s="18" t="n">
-        <v>1225.5</v>
+        <v>273.55</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>1240.04</v>
+        <v>265.15</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>1233.3</v>
+        <v>252.44</v>
       </c>
       <c r="G77" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C78" s="18" t="n">
-        <v>3036.4</v>
+        <v>393.6</v>
       </c>
       <c r="D78" s="18" t="n">
-        <v>2761.87</v>
+        <v>379.52</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>2782.04</v>
+        <v>371.26</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>2842.21</v>
+        <v>350.19</v>
       </c>
       <c r="G78" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
-        </is>
-      </c>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="n">
-        <v>1491</v>
-      </c>
-      <c r="D79" s="14" t="n">
-        <v>1433.37</v>
-      </c>
-      <c r="E79" s="14" t="n">
-        <v>1454</v>
-      </c>
-      <c r="F79" s="14" t="n">
-        <v>1479.66</v>
-      </c>
-      <c r="G79" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+      <c r="A79" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="n">
+        <v>318.1</v>
+      </c>
+      <c r="D79" s="18" t="n">
+        <v>301.52</v>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>294.1</v>
+      </c>
+      <c r="F79" s="18" t="n">
+        <v>283.93</v>
+      </c>
+      <c r="G79" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C80" s="18" t="n">
-        <v>983.95</v>
+        <v>28925</v>
       </c>
       <c r="D80" s="18" t="n">
-        <v>934.8</v>
+        <v>26413.64</v>
       </c>
       <c r="E80" s="18" t="n">
-        <v>940.33</v>
+        <v>24480.9</v>
       </c>
       <c r="F80" s="18" t="n">
-        <v>874.9400000000001</v>
+        <v>20670.71</v>
       </c>
       <c r="G80" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="20" t="inlineStr">
         <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="n">
+        <v>1036.05</v>
+      </c>
+      <c r="D81" s="18" t="n">
+        <v>945.9299999999999</v>
+      </c>
+      <c r="E81" s="18" t="n">
+        <v>883.87</v>
+      </c>
+      <c r="F81" s="18" t="n">
+        <v>800.98</v>
+      </c>
+      <c r="G81" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="n">
+        <v>3707.9</v>
+      </c>
+      <c r="D82" s="18" t="n">
+        <v>3284.96</v>
+      </c>
+      <c r="E82" s="18" t="n">
+        <v>3210.55</v>
+      </c>
+      <c r="F82" s="18" t="n">
+        <v>3134.24</v>
+      </c>
+      <c r="G82" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="D83" s="18" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="E83" s="18" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="F83" s="18" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="G83" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>427.6</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>399.62</v>
+      </c>
+      <c r="E84" s="18" t="n">
+        <v>389.13</v>
+      </c>
+      <c r="F84" s="18" t="n">
+        <v>384.93</v>
+      </c>
+      <c r="G84" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="n">
+        <v>4141.4</v>
+      </c>
+      <c r="D85" s="18" t="n">
+        <v>3543.27</v>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>3300.67</v>
+      </c>
+      <c r="F85" s="18" t="n">
+        <v>3202.25</v>
+      </c>
+      <c r="G85" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="n">
+        <v>1565</v>
+      </c>
+      <c r="D86" s="18" t="n">
+        <v>1450.74</v>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>1429.33</v>
+      </c>
+      <c r="F86" s="18" t="n">
+        <v>1387.29</v>
+      </c>
+      <c r="G86" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>TRITURBINE</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>515.45</v>
+      </c>
+      <c r="D87" s="18" t="n">
+        <v>467.92</v>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>475.52</v>
+      </c>
+      <c r="F87" s="18" t="n">
+        <v>508.31</v>
+      </c>
+      <c r="G87" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="n">
+        <v>1710.6</v>
+      </c>
+      <c r="D88" s="14" t="n">
+        <v>1586.27</v>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v>1554.73</v>
+      </c>
+      <c r="F88" s="14" t="n">
+        <v>1609.87</v>
+      </c>
+      <c r="G88" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="n">
+        <v>1792.2</v>
+      </c>
+      <c r="D89" s="14" t="n">
+        <v>1666.36</v>
+      </c>
+      <c r="E89" s="14" t="n">
+        <v>1665.82</v>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>1667.65</v>
+      </c>
+      <c r="G89" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="n">
+        <v>632.9</v>
+      </c>
+      <c r="D90" s="18" t="n">
+        <v>555.74</v>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>544.5</v>
+      </c>
+      <c r="F90" s="18" t="n">
+        <v>576.3099999999999</v>
+      </c>
+      <c r="G90" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="n">
+        <v>284.05</v>
+      </c>
+      <c r="D91" s="18" t="n">
+        <v>280.92</v>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>271.73</v>
+      </c>
+      <c r="F91" s="18" t="n">
+        <v>249.64</v>
+      </c>
+      <c r="G91" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="n">
+        <v>1511.4</v>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>1440.8</v>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v>1456.25</v>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>1479.82</v>
+      </c>
+      <c r="G92" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B81" s="17" t="inlineStr">
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>990.6</v>
+      </c>
+      <c r="D93" s="18" t="n">
+        <v>940.11</v>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>942.3</v>
+      </c>
+      <c r="F93" s="18" t="n">
+        <v>876.4400000000001</v>
+      </c>
+      <c r="G93" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C81" s="18" t="n">
-        <v>284.4</v>
-      </c>
-      <c r="D81" s="18" t="n">
-        <v>277.87</v>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>275.82</v>
-      </c>
-      <c r="F81" s="18" t="n">
-        <v>248.65</v>
-      </c>
-      <c r="G81" s="19">
+      <c r="C94" s="18" t="n">
+        <v>293.75</v>
+      </c>
+      <c r="D94" s="18" t="n">
+        <v>279.38</v>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>276.52</v>
+      </c>
+      <c r="F94" s="18" t="n">
+        <v>249.09</v>
+      </c>
+      <c r="G94" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="n">
+        <v>853.9</v>
+      </c>
+      <c r="D95" s="18" t="n">
+        <v>828.3200000000001</v>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>851.02</v>
+      </c>
+      <c r="F95" s="18" t="n">
+        <v>841.6</v>
+      </c>
+      <c r="G95" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 17-Apr-2026  16:46</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 18-Apr-2026  15:37</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 18-Apr-2026  15:37</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 19-Apr-2026  15:37</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 19-Apr-2026  15:37</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 20-Apr-2026  17:02</t>
         </is>
       </c>
     </row>
@@ -696,63 +696,63 @@
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.75</v>
+        <v>0.867</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.583</v>
+        <v>0.333</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.9329999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.583</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -765,25 +765,25 @@
         <v>15</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>8</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.9329999999999999</v>
+        <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>0.5329999999999999</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.733</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -799,19 +799,19 @@
         <v>9</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0.9</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.7</v>
@@ -820,122 +820,122 @@
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.65</v>
+        <v>0.667</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.7</v>
+        <v>0.267</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.6446999999999999</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.45</v>
+        <v>0.333</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.65</v>
+        <v>0.6443000000000001</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="F11" s="10" t="n">
-        <v>0.9329999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>0.6</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.7</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.622</v>
+        <v>0.6333</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.6167</v>
@@ -1006,32 +1006,32 @@
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>10</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.9329999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1047,7 +1047,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>1</v>
@@ -1056,13 +1056,13 @@
         <v>0.6</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2105.7</v>
+        <v>2143.9</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2015.22</v>
+        <v>2027.47</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2023.09</v>
+        <v>2027.83</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1883.08</v>
+        <v>1886.51</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1039</v>
+        <v>1015.25</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>958.64</v>
+        <v>964.03</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>935.13</v>
+        <v>938.27</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>838.1</v>
+        <v>840.9</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>569.6</v>
+        <v>556.6</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>523.73</v>
+        <v>526.86</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>522.6799999999999</v>
+        <v>524.01</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>423.35</v>
+        <v>425.51</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>592.3</v>
+        <v>590.3</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>556.55</v>
+        <v>559.76</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>566.71</v>
+        <v>567.63</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>533.1799999999999</v>
+        <v>534.8</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1270</v>
+        <v>1287.7</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1190.55</v>
+        <v>1199.81</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1166.36</v>
+        <v>1171.12</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1073.28</v>
+        <v>1077.47</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>788.2</v>
+        <v>789.9</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>751.39</v>
+        <v>755.0599999999999</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>754.51</v>
+        <v>755.9</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>738.91</v>
+        <v>740.0700000000001</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1240.3</v>
+        <v>1274.5</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1187.96</v>
+        <v>1196.2</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1187.67</v>
+        <v>1191.08</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1142.2</v>
+        <v>1145.76</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>438.75</v>
+        <v>426.65</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>403.55</v>
+        <v>405.75</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>380.03</v>
+        <v>381.86</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>294.53</v>
+        <v>296.53</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>89.78</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>82.72</v>
+        <v>83.3</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>80.7</v>
+        <v>81.02</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>75.48</v>
+        <v>75.77</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2461.3</v>
+        <v>2427.2</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2315.7</v>
+        <v>2326.32</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2298.99</v>
+        <v>2304.02</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2380.76</v>
+        <v>2383.96</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>173.33</v>
+        <v>172.71</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>161.18</v>
+        <v>162.28</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>156.44</v>
+        <v>157.08</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>142.12</v>
+        <v>142.59</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>212.12</v>
+        <v>211.72</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>201.77</v>
+        <v>202.72</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>197.64</v>
+        <v>198.19</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>179.53</v>
+        <v>180.01</v>
       </c>
       <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>787.5</v>
+        <v>771</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>719.2</v>
+        <v>724.14</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>687.63</v>
+        <v>690.9</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>572.67</v>
+        <v>575.5700000000001</v>
       </c>
       <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VEDL","Chart 📈")</f>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>1077.15</v>
+        <v>1076.65</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>922.51</v>
+        <v>937.1900000000001</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>861.49</v>
+        <v>869.9299999999999</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>836.52</v>
+        <v>839.55</v>
       </c>
       <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
@@ -1616,336 +1616,336 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>142.37</v>
+        <v>7980.5</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>137.53</v>
+        <v>7162.9</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>140.69</v>
+        <v>7044.17</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>133.23</v>
+        <v>7059.89</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANBK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>939.45</v>
+        <v>1889</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>920.5599999999999</v>
+        <v>1748.21</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>904.48</v>
+        <v>1781.36</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>808.04</v>
+        <v>1825.18</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>72.73</v>
+        <v>1187.2</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>68.23</v>
+        <v>1058.71</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>66.68000000000001</v>
+        <v>1008.95</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>60.43</v>
+        <v>1021.45</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>1080.25</v>
+        <v>4513</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>1061.75</v>
+        <v>4317.88</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>1071.76</v>
+        <v>4212.19</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>979.8099999999999</v>
+        <v>3912.23</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>188.91</v>
+        <v>1438</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>181.9</v>
+        <v>1359.43</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>179.36</v>
+        <v>1383.74</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>160.13</v>
+        <v>1379.05</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>7958.5</v>
+        <v>142.74</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>7076.84</v>
+        <v>138.02</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>7005.95</v>
+        <v>140.77</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>7045.14</v>
+        <v>133.57</v>
       </c>
       <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANBK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>1866.1</v>
+        <v>928.3</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>1733.39</v>
+        <v>921.3</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>1776.97</v>
+        <v>905.41</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>1823.3</v>
+        <v>809.4299999999999</v>
       </c>
       <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>762.15</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>722.39</v>
+        <v>68.92</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>728.85</v>
+        <v>67.03</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>752.0599999999999</v>
+        <v>60.78</v>
       </c>
       <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>1178.35</v>
+        <v>1107.85</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>1045.18</v>
+        <v>1066.14</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>1001.68</v>
+        <v>1073.17</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>1019.2</v>
+        <v>982.66</v>
       </c>
       <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>4525.9</v>
+        <v>189.29</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>4297.35</v>
+        <v>182.61</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>4199.91</v>
+        <v>179.75</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>3905.47</v>
+        <v>160.58</v>
       </c>
       <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>1440.1</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>1351.16</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>1381.52</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>1375.67</v>
-      </c>
-      <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>9803</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>9454.309999999999</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>9409.559999999999</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>9078.25</v>
+      </c>
+      <c r="G27" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>9773.5</v>
+        <v>1866.2</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>9417.610000000001</v>
+        <v>1775.51</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>9393.49</v>
+        <v>1717.42</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>9052.030000000001</v>
+        <v>1476.8</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1957,23 +1957,23 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>1860.5</v>
+        <v>37790</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>1765.97</v>
+        <v>34718.22</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>1711.35</v>
+        <v>34342.05</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>1470.67</v>
+        <v>34907.95</v>
       </c>
       <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1985,23 +1985,23 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>37505</v>
+        <v>7243</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>34394.88</v>
+        <v>7072.73</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>34201.3</v>
+        <v>7173.59</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>34854.37</v>
+        <v>6860.3</v>
       </c>
       <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>7189.5</v>
+        <v>123.19</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>7054.81</v>
+        <v>117.83</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>7170.75</v>
+        <v>118.04</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>6845.43</v>
+        <v>111.3</v>
       </c>
       <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2041,79 +2041,79 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>125.03</v>
+        <v>3761.9</v>
       </c>
       <c r="D32" s="18" t="n">
-        <v>117.27</v>
+        <v>3644.28</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>117.83</v>
+        <v>3637.02</v>
       </c>
       <c r="F32" s="18" t="n">
-        <v>111.02</v>
+        <v>3453.58</v>
       </c>
       <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>3735.8</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>3631.89</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>3631.92</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>3445.74</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>270.08</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>250.77</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>252.75</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>265.21</v>
+      </c>
+      <c r="G33" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>DISHTV</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>4.08</v>
+        <v>648.45</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>2.94</v>
+        <v>607.84</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>2.96</v>
+        <v>592.4299999999999</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>3.93</v>
+        <v>580.2</v>
       </c>
       <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DISHTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2125,303 +2125,303 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>273.34</v>
+        <v>574.15</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>248.74</v>
+        <v>541.48</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>252.04</v>
+        <v>534.71</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>265.25</v>
+        <v>554.1900000000001</v>
       </c>
       <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>SUNTV</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>643.25</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>603.5599999999999</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>580.51</v>
-      </c>
-      <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>740.5</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>642.75</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>654.49</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>714.37</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>585.55</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>538.04</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>533.1</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>554.11</v>
-      </c>
-      <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>620.35</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>561.9</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>547.47</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>578.09</v>
+      </c>
+      <c r="G37" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
-        <v>5582</v>
+        <v>471.7</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>5402.97</v>
+        <v>471.35</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>5444.86</v>
+        <v>466.96</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>5391.28</v>
+        <v>436.64</v>
       </c>
       <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>283.35</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>281.15</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>272.18</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>250.48</v>
+      </c>
+      <c r="G39" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>515.7</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>486.26</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>475.93</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>486.25</v>
+      </c>
+      <c r="G40" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>760.7</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>754.03</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>756.12</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>738.22</v>
+      </c>
+      <c r="G41" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>1286.4</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>1236.48</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>1243.57</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G42" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>3340.1</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>2853.56</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>2819.18</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>2850.39</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>466.55</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>430.39</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>434.82</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>464.56</v>
+      </c>
+      <c r="G44" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>1386</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>1326.98</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>1274.22</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>1196.8</v>
-      </c>
-      <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="n">
-        <v>6229</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>6081.21</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>6142.67</v>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>6213.36</v>
-      </c>
-      <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>1797.4</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>1722.58</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>1729.74</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>1743.73</v>
-      </c>
-      <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>GLENMARK</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>2249.5</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>2169.77</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>2117.46</v>
-      </c>
-      <c r="F42" s="18" t="n">
-        <v>1948.93</v>
-      </c>
-      <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>655.7</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>625.28</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>603.9400000000001</v>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>559.52</v>
-      </c>
-      <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>1135.75</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>1064.13</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>1039.32</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>945.71</v>
-      </c>
-      <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>2326.1</v>
+        <v>5642</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>2309.3</v>
+        <v>5425.74</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>2272.36</v>
+        <v>5452.6</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>2124.04</v>
+        <v>5397.72</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>1119.7</v>
+        <v>1367.8</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>1043.34</v>
+        <v>1330.86</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>982.9400000000001</v>
+        <v>1277.89</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>906.25</v>
+        <v>1200.99</v>
       </c>
       <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2461,23 +2461,23 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>4179.5</v>
+        <v>6280</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>4170.88</v>
+        <v>6100.14</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>4153.44</v>
+        <v>6148.07</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>3836.77</v>
+        <v>6234.99</v>
       </c>
       <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2489,247 +2489,247 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>1794.6</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>1729.44</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>1732.28</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <v>1745.5</v>
+      </c>
+      <c r="G48" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>2230.7</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>2175.57</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>2121.9</v>
+      </c>
+      <c r="F49" s="18" t="n">
+        <v>1953.94</v>
+      </c>
+      <c r="G49" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>664.45</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>629.01</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>606.3099999999999</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>561.64</v>
+      </c>
+      <c r="G50" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>1129.5</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>1070.36</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>1042.86</v>
+      </c>
+      <c r="F51" s="18" t="n">
+        <v>948.5700000000001</v>
+      </c>
+      <c r="G51" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>2328.7</v>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>2311.15</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>2274.58</v>
+      </c>
+      <c r="F52" s="18" t="n">
+        <v>2132.07</v>
+      </c>
+      <c r="G52" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>1100.05</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>1048.74</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>987.53</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <v>908.36</v>
+      </c>
+      <c r="G53" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>4191.2</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>4172.81</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>4154.92</v>
+      </c>
+      <c r="F54" s="18" t="n">
+        <v>3840.28</v>
+      </c>
+      <c r="G54" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C48" s="18" t="n">
-        <v>943.95</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>905.64</v>
-      </c>
-      <c r="E48" s="18" t="n">
-        <v>903.72</v>
-      </c>
-      <c r="F48" s="18" t="n">
-        <v>916.91</v>
-      </c>
-      <c r="G48" s="19">
+      <c r="C55" s="18" t="n">
+        <v>936.5</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>908.5700000000001</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>905</v>
+      </c>
+      <c r="F55" s="18" t="n">
+        <v>918.25</v>
+      </c>
+      <c r="G55" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
       </c>
-      <c r="C49" s="14" t="n">
-        <v>1359.1</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>1292.78</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>1288.17</v>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>1246.9</v>
-      </c>
-      <c r="G49" s="15">
+      <c r="C56" s="14" t="n">
+        <v>1354.7</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>1298.68</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>1290.78</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>1250.67</v>
+      </c>
+      <c r="G56" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>HDFCAMC</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n">
-        <v>2792.4</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>2520.92</v>
-      </c>
-      <c r="E50" s="14" t="n">
-        <v>2536.89</v>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>2567.7</v>
-      </c>
-      <c r="G50" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>ICICIGI</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n">
-        <v>1891.6</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>1802.37</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>1832.09</v>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>1880.45</v>
-      </c>
-      <c r="G51" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIGI","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="n">
-        <v>2856.1</v>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>2624.79</v>
-      </c>
-      <c r="E52" s="14" t="n">
-        <v>2504.73</v>
-      </c>
-      <c r="F52" s="14" t="n">
-        <v>2075.45</v>
-      </c>
-      <c r="G52" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>MUTHOOTFIN</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="n">
-        <v>3571.3</v>
-      </c>
-      <c r="D53" s="14" t="n">
-        <v>3400.13</v>
-      </c>
-      <c r="E53" s="14" t="n">
-        <v>3430.67</v>
-      </c>
-      <c r="F53" s="14" t="n">
-        <v>3231.14</v>
-      </c>
-      <c r="G53" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>PFC</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n">
-        <v>464.85</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>423.19</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>407.51</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>391.08</v>
-      </c>
-      <c r="G54" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="n">
-        <v>373.3</v>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>342.21</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>342.11</v>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>357.15</v>
-      </c>
-      <c r="G55" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>SBILIFE</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="n">
-        <v>1970.9</v>
-      </c>
-      <c r="D56" s="14" t="n">
-        <v>1909.66</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>1938.58</v>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>1908.89</v>
-      </c>
-      <c r="G56" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBILIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2741,275 +2741,275 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>2768.2</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>2544.47</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>2545.97</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>2579.63</v>
+      </c>
+      <c r="G57" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="n">
+        <v>2859.1</v>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>2647.1</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>2518.63</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>2087.81</v>
+      </c>
+      <c r="G58" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="n">
+        <v>3531.2</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>3412.62</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>3434.62</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>3241.67</v>
+      </c>
+      <c r="G59" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="n">
+        <v>472.85</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>427.92</v>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>410.08</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>392.9</v>
+      </c>
+      <c r="G60" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>382.7</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>346.07</v>
+      </c>
+      <c r="E61" s="14" t="n">
+        <v>343.7</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="G61" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>1982.5</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>1916.6</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>1940.3</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>1911.32</v>
+      </c>
+      <c r="G62" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBILIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
           <t>SHRIRAMFIN</t>
         </is>
       </c>
-      <c r="C57" s="14" t="n">
-        <v>1036.95</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>986.09</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>985.01</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>866.78</v>
-      </c>
-      <c r="G57" s="15">
+      <c r="C63" s="14" t="n">
+        <v>1045.15</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>991.71</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>987.37</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>869.49</v>
+      </c>
+      <c r="G63" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n">
-        <v>486</v>
-      </c>
-      <c r="D58" s="18" t="n">
-        <v>483.16</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>474.3</v>
-      </c>
-      <c r="F58" s="18" t="n">
-        <v>484.96</v>
-      </c>
-      <c r="G58" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="n">
-        <v>757.3</v>
-      </c>
-      <c r="D59" s="18" t="n">
-        <v>753.33</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>755.9299999999999</v>
-      </c>
-      <c r="F59" s="18" t="n">
-        <v>739.63</v>
-      </c>
-      <c r="G59" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="n">
-        <v>1285.6</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>1231.22</v>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>1241.83</v>
-      </c>
-      <c r="F60" s="18" t="n">
-        <v>1235.2</v>
-      </c>
-      <c r="G60" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n">
-        <v>3186.9</v>
-      </c>
-      <c r="D61" s="18" t="n">
-        <v>2802.35</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>2797.92</v>
-      </c>
-      <c r="F61" s="18" t="n">
-        <v>2847.52</v>
-      </c>
-      <c r="G61" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="n">
-        <v>473.9</v>
-      </c>
-      <c r="D62" s="18" t="n">
-        <v>426.58</v>
-      </c>
-      <c r="E62" s="18" t="n">
-        <v>433.53</v>
-      </c>
-      <c r="F62" s="18" t="n">
-        <v>465.38</v>
-      </c>
-      <c r="G62" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>BSOFT</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n">
-        <v>390.7</v>
-      </c>
-      <c r="D63" s="14" t="n">
-        <v>370.01</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>378.99</v>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>389.39</v>
-      </c>
-      <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BSOFT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>95.48999999999999</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>79</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>73.98</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>73.58</v>
-      </c>
-      <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>7158</v>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>6549.64</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>6172.54</v>
+      </c>
+      <c r="F64" s="18" t="n">
+        <v>5650.88</v>
+      </c>
+      <c r="G64" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="n">
-        <v>7992.5</v>
-      </c>
-      <c r="D65" s="14" t="n">
-        <v>7153.9</v>
-      </c>
-      <c r="E65" s="14" t="n">
-        <v>7106.21</v>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>7674.75</v>
-      </c>
-      <c r="G65" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>1259.4</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>1095.32</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>1036.36</v>
+      </c>
+      <c r="F65" s="18" t="n">
+        <v>966.84</v>
+      </c>
+      <c r="G65" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C66" s="18" t="n">
-        <v>7029.5</v>
+        <v>1152.7</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>6485.6</v>
+        <v>999.4299999999999</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>6132.32</v>
+        <v>956.5700000000001</v>
       </c>
       <c r="F66" s="18" t="n">
-        <v>5630.9</v>
+        <v>970.86</v>
       </c>
       <c r="G66" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3021,23 +3021,23 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C67" s="18" t="n">
-        <v>1259.8</v>
+        <v>200.83</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>1078.04</v>
+        <v>171.5</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>1027.25</v>
+        <v>158.35</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>961.91</v>
+        <v>142.65</v>
       </c>
       <c r="G67" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3049,23 +3049,23 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C68" s="18" t="n">
-        <v>1127.3</v>
+        <v>325.63</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>983.3</v>
+        <v>279.27</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>948.5700000000001</v>
+        <v>269.45</v>
       </c>
       <c r="F68" s="18" t="n">
-        <v>968.27</v>
+        <v>258.62</v>
       </c>
       <c r="G68" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3077,23 +3077,23 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="C69" s="18" t="n">
-        <v>198.5</v>
+        <v>179.42</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>168.41</v>
+        <v>160.47</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>156.61</v>
+        <v>157.81</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>141.74</v>
+        <v>160.22</v>
       </c>
       <c r="G69" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C70" s="18" t="n">
-        <v>316.79</v>
+        <v>795.7</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>274.39</v>
+        <v>722.79</v>
       </c>
       <c r="E70" s="18" t="n">
-        <v>267.16</v>
+        <v>699.73</v>
       </c>
       <c r="F70" s="18" t="n">
-        <v>257.96</v>
+        <v>683.98</v>
       </c>
       <c r="G70" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3133,23 +3133,23 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C71" s="18" t="n">
-        <v>171.49</v>
+        <v>4232.3</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>158.47</v>
+        <v>3905.07</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>156.92</v>
+        <v>3694.63</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>159.72</v>
+        <v>3073.11</v>
       </c>
       <c r="G71" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3161,23 +3161,23 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="C72" s="18" t="n">
-        <v>774.8</v>
+        <v>19.08</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>715.12</v>
+        <v>16.73</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>695.8099999999999</v>
+        <v>15.96</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>680.26</v>
+        <v>16.71</v>
       </c>
       <c r="G72" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C73" s="18" t="n">
-        <v>4138.2</v>
+        <v>543.05</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>3870.63</v>
+        <v>507.49</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>3672.68</v>
+        <v>497.2</v>
       </c>
       <c r="F73" s="18" t="n">
-        <v>3057</v>
+        <v>500.78</v>
       </c>
       <c r="G73" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3217,23 +3217,23 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C74" s="18" t="n">
-        <v>19.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>16.49</v>
+        <v>78.16</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>15.83</v>
+        <v>77.06</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>16.65</v>
+        <v>79.17</v>
       </c>
       <c r="G74" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3245,23 +3245,23 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C75" s="18" t="n">
-        <v>538.05</v>
+        <v>304.35</v>
       </c>
       <c r="D75" s="18" t="n">
-        <v>503.75</v>
+        <v>276.48</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>495.33</v>
+        <v>266.69</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>499.22</v>
+        <v>253.46</v>
       </c>
       <c r="G75" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3273,23 +3273,23 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C76" s="18" t="n">
-        <v>83.56</v>
+        <v>398</v>
       </c>
       <c r="D76" s="18" t="n">
-        <v>77.63</v>
+        <v>381.28</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>76.81999999999999</v>
+        <v>372.31</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>78.90000000000001</v>
+        <v>350.71</v>
       </c>
       <c r="G76" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3301,23 +3301,23 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C77" s="18" t="n">
-        <v>300.65</v>
+        <v>319.7</v>
       </c>
       <c r="D77" s="18" t="n">
-        <v>273.55</v>
+        <v>303.25</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>265.15</v>
+        <v>295.11</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>252.44</v>
+        <v>285.18</v>
       </c>
       <c r="G77" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3329,23 +3329,23 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C78" s="18" t="n">
-        <v>393.6</v>
+        <v>29645</v>
       </c>
       <c r="D78" s="18" t="n">
-        <v>379.52</v>
+        <v>26721.39</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>371.26</v>
+        <v>24683.43</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>350.19</v>
+        <v>20780.69</v>
       </c>
       <c r="G78" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3357,23 +3357,23 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C79" s="18" t="n">
-        <v>318.1</v>
+        <v>1087.85</v>
       </c>
       <c r="D79" s="18" t="n">
-        <v>301.52</v>
+        <v>959.4400000000001</v>
       </c>
       <c r="E79" s="18" t="n">
-        <v>294.1</v>
+        <v>891.87</v>
       </c>
       <c r="F79" s="18" t="n">
-        <v>283.93</v>
+        <v>805.64</v>
       </c>
       <c r="G79" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3385,23 +3385,23 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C80" s="18" t="n">
-        <v>28925</v>
+        <v>3709</v>
       </c>
       <c r="D80" s="18" t="n">
-        <v>26413.64</v>
+        <v>3325.34</v>
       </c>
       <c r="E80" s="18" t="n">
-        <v>24480.9</v>
+        <v>3230.1</v>
       </c>
       <c r="F80" s="18" t="n">
-        <v>20670.71</v>
+        <v>3141.39</v>
       </c>
       <c r="G80" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3413,23 +3413,23 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>1036.05</v>
+        <v>52.5</v>
       </c>
       <c r="D81" s="18" t="n">
-        <v>945.9299999999999</v>
+        <v>45.55</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>883.87</v>
+        <v>45.11</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>800.98</v>
+        <v>51.4</v>
       </c>
       <c r="G81" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3441,23 +3441,23 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>3707.9</v>
+        <v>433.6</v>
       </c>
       <c r="D82" s="18" t="n">
-        <v>3284.96</v>
+        <v>402.86</v>
       </c>
       <c r="E82" s="18" t="n">
-        <v>3210.55</v>
+        <v>390.87</v>
       </c>
       <c r="F82" s="18" t="n">
-        <v>3134.24</v>
+        <v>386.18</v>
       </c>
       <c r="G82" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3469,23 +3469,23 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>52.93</v>
+        <v>4185.2</v>
       </c>
       <c r="D83" s="18" t="n">
-        <v>44.82</v>
+        <v>3604.41</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>44.81</v>
+        <v>3335.36</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>50.95</v>
+        <v>3214.32</v>
       </c>
       <c r="G83" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>427.6</v>
+        <v>1606.3</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>399.62</v>
+        <v>1465.56</v>
       </c>
       <c r="E84" s="18" t="n">
-        <v>389.13</v>
+        <v>1436.27</v>
       </c>
       <c r="F84" s="18" t="n">
-        <v>384.93</v>
+        <v>1389.59</v>
       </c>
       <c r="G84" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3525,302 +3525,246 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C85" s="18" t="n">
-        <v>4141.4</v>
+        <v>576.2</v>
       </c>
       <c r="D85" s="18" t="n">
-        <v>3543.27</v>
+        <v>478.23</v>
       </c>
       <c r="E85" s="18" t="n">
-        <v>3300.67</v>
+        <v>479.47</v>
       </c>
       <c r="F85" s="18" t="n">
-        <v>3202.25</v>
+        <v>509.21</v>
       </c>
       <c r="G85" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="C86" s="18" t="n">
-        <v>1565</v>
-      </c>
-      <c r="D86" s="18" t="n">
-        <v>1450.74</v>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>1429.33</v>
-      </c>
-      <c r="F86" s="18" t="n">
-        <v>1387.29</v>
-      </c>
-      <c r="G86" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="n">
+        <v>1694.9</v>
+      </c>
+      <c r="D86" s="14" t="n">
+        <v>1596.62</v>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v>1560.23</v>
+      </c>
+      <c r="F86" s="14" t="n">
+        <v>1612</v>
+      </c>
+      <c r="G86" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="n">
-        <v>515.45</v>
-      </c>
-      <c r="D87" s="18" t="n">
-        <v>467.92</v>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>475.52</v>
-      </c>
-      <c r="F87" s="18" t="n">
-        <v>508.31</v>
-      </c>
-      <c r="G87" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="n">
+        <v>1767.9</v>
+      </c>
+      <c r="D87" s="14" t="n">
+        <v>1676.03</v>
+      </c>
+      <c r="E87" s="14" t="n">
+        <v>1669.82</v>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>1668.2</v>
+      </c>
+      <c r="G87" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="n">
-        <v>1710.6</v>
-      </c>
-      <c r="D88" s="14" t="n">
-        <v>1586.27</v>
-      </c>
-      <c r="E88" s="14" t="n">
-        <v>1554.73</v>
-      </c>
-      <c r="F88" s="14" t="n">
-        <v>1609.87</v>
-      </c>
-      <c r="G88" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="D88" s="18" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="E88" s="18" t="n">
+        <v>74.73999999999999</v>
+      </c>
+      <c r="F88" s="18" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="G88" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="n">
-        <v>1792.2</v>
-      </c>
-      <c r="D89" s="14" t="n">
-        <v>1666.36</v>
-      </c>
-      <c r="E89" s="14" t="n">
-        <v>1665.82</v>
-      </c>
-      <c r="F89" s="14" t="n">
-        <v>1667.65</v>
-      </c>
-      <c r="G89" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>8082.5</v>
+      </c>
+      <c r="D89" s="18" t="n">
+        <v>7242.34</v>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>7144.5</v>
+      </c>
+      <c r="F89" s="18" t="n">
+        <v>7693.39</v>
+      </c>
+      <c r="G89" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="n">
-        <v>632.9</v>
-      </c>
-      <c r="D90" s="18" t="n">
-        <v>555.74</v>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>544.5</v>
-      </c>
-      <c r="F90" s="18" t="n">
-        <v>576.3099999999999</v>
-      </c>
-      <c r="G90" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="n">
+        <v>1504.4</v>
+      </c>
+      <c r="D90" s="14" t="n">
+        <v>1446.86</v>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v>1458.14</v>
+      </c>
+      <c r="F90" s="14" t="n">
+        <v>1485.5</v>
+      </c>
+      <c r="G90" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C91" s="18" t="n">
-        <v>284.05</v>
+        <v>997.65</v>
       </c>
       <c r="D91" s="18" t="n">
-        <v>280.92</v>
+        <v>945.59</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>271.73</v>
+        <v>944.47</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>249.64</v>
+        <v>880.74</v>
       </c>
       <c r="G91" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
-        </is>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="n">
-        <v>1511.4</v>
-      </c>
-      <c r="D92" s="14" t="n">
-        <v>1440.8</v>
-      </c>
-      <c r="E92" s="14" t="n">
-        <v>1456.25</v>
-      </c>
-      <c r="F92" s="14" t="n">
-        <v>1479.82</v>
-      </c>
-      <c r="G92" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>294.35</v>
+      </c>
+      <c r="D92" s="18" t="n">
+        <v>280.81</v>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>277.22</v>
+      </c>
+      <c r="F92" s="18" t="n">
+        <v>250.14</v>
+      </c>
+      <c r="G92" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="A93" s="20" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="C93" s="18" t="n">
-        <v>990.6</v>
+        <v>851.95</v>
       </c>
       <c r="D93" s="18" t="n">
-        <v>940.11</v>
+        <v>830.5700000000001</v>
       </c>
       <c r="E93" s="18" t="n">
-        <v>942.3</v>
+        <v>851.0599999999999</v>
       </c>
       <c r="F93" s="18" t="n">
-        <v>876.4400000000001</v>
+        <v>844.51</v>
       </c>
       <c r="G93" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="n">
-        <v>293.75</v>
-      </c>
-      <c r="D94" s="18" t="n">
-        <v>279.38</v>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>276.52</v>
-      </c>
-      <c r="F94" s="18" t="n">
-        <v>249.09</v>
-      </c>
-      <c r="G94" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C95" s="18" t="n">
-        <v>853.9</v>
-      </c>
-      <c r="D95" s="18" t="n">
-        <v>828.3200000000001</v>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>851.02</v>
-      </c>
-      <c r="F95" s="18" t="n">
-        <v>841.6</v>
-      </c>
-      <c r="G95" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 20-Apr-2026  17:02</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 22-Apr-2026  05:00</t>
         </is>
       </c>
     </row>
@@ -696,187 +696,187 @@
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.867</v>
+        <v>0.833</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.333</v>
+        <v>0.583</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.7333</v>
+        <v>0.8053</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.583</v>
+        <v>0.867</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.583</v>
+        <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.722</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>9</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.711</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.9</v>
+        <v>0.667</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.7</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.267</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.6446999999999999</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>9</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -889,7 +889,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>12</v>
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>0.6</v>
@@ -907,100 +907,100 @@
         <v>0.7</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.6333</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.8</v>
+        <v>0.625</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.65</v>
+        <v>0.625</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.4</v>
+        <v>0.575</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.6167</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.625</v>
+        <v>0.55</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.575</v>
+        <v>0.45</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.6</v>
+        <v>0.5832999999999999</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.6</v>
+        <v>0.578</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1013,87 +1013,87 @@
         <v>20</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>10</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.6</v>
+        <v>0.333</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2777</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.2777</v>
+        <v>0.1333</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2143.9</v>
+        <v>2119.9</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2027.47</v>
+        <v>2043.09</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2027.83</v>
+        <v>2034.41</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1886.51</v>
+        <v>1892.83</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1015.25</v>
+        <v>1029.95</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>964.03</v>
+        <v>975.28</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>938.27</v>
+        <v>945.01</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>840.9</v>
+        <v>844.4</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>556.6</v>
+        <v>554.9</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>526.86</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>524.01</v>
+        <v>526.27</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>425.51</v>
+        <v>428.38</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>590.3</v>
+        <v>588.65</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>559.76</v>
+        <v>564.99</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>567.63</v>
+        <v>569.24</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>534.8</v>
+        <v>535.3200000000001</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1287.7</v>
+        <v>1285.5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1199.81</v>
+        <v>1215.64</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1171.12</v>
+        <v>1180.04</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1077.47</v>
+        <v>1082.32</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>789.9</v>
+        <v>787.2</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>755.0599999999999</v>
+        <v>761.08</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>755.9</v>
+        <v>758.39</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>740.0700000000001</v>
+        <v>742</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1274.5</v>
+        <v>1267.4</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1196.2</v>
+        <v>1210.17</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1191.08</v>
+        <v>1197.41</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1145.76</v>
+        <v>1149.13</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>426.65</v>
+        <v>431.2</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>405.75</v>
+        <v>409.65</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>381.86</v>
+        <v>385.35</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>296.53</v>
+        <v>298.91</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>88.90000000000001</v>
+        <v>89.28</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>83.3</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>81.02</v>
+        <v>81.63</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>75.77</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2427.2</v>
+        <v>2399</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2326.32</v>
+        <v>2340.53</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2304.02</v>
+        <v>2311.77</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2383.96</v>
+        <v>2385.23</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>172.71</v>
+        <v>176.59</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>162.28</v>
+        <v>164.75</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>157.08</v>
+        <v>158.52</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>142.59</v>
+        <v>143.25</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>211.72</v>
+        <v>212.72</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>202.72</v>
+        <v>204.47</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>198.19</v>
+        <v>199.28</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>180.01</v>
+        <v>180.57</v>
       </c>
       <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>771</v>
+        <v>764.45</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>724.14</v>
+        <v>731.65</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>690.9</v>
+        <v>696.65</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>575.5700000000001</v>
+        <v>579.42</v>
       </c>
       <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VEDL","Chart 📈")</f>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>1076.65</v>
+        <v>1129.6</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>937.1900000000001</v>
+        <v>969.59</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>869.9299999999999</v>
+        <v>888.8099999999999</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>839.55</v>
+        <v>844.25</v>
       </c>
       <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
@@ -1616,896 +1616,896 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>7980.5</v>
+        <v>283.31</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>7162.9</v>
+        <v>276.77</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>7044.17</v>
+        <v>282.13</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>7059.89</v>
+        <v>275.38</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BANKBARODA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>1889</v>
+        <v>145</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1748.21</v>
+        <v>139.22</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>1781.36</v>
+        <v>141.07</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>1825.18</v>
+        <v>133.92</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANBK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>1187.2</v>
+        <v>924.45</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>1058.71</v>
+        <v>921.58</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>1008.95</v>
+        <v>906.75</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>1021.45</v>
+        <v>812.1</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>4513</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>4317.88</v>
+        <v>71.11</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>4212.19</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>3912.23</v>
+        <v>61.15</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="20" t="inlineStr">
         <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>1102.25</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>1073.52</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>1075.77</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>985.59</v>
+      </c>
+      <c r="G21" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>194.53</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>180.77</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>161.17</v>
+      </c>
+      <c r="G22" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>1438</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>1359.43</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>1383.74</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>1379.05</v>
-      </c>
-      <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>142.74</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>138.02</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>140.77</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>133.57</v>
-      </c>
-      <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANBK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>928.3</v>
+        <v>7857</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>921.3</v>
+        <v>7288.94</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>905.41</v>
+        <v>7106.72</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>809.4299999999999</v>
+        <v>7066.07</v>
       </c>
       <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>75.54000000000001</v>
+        <v>1881.6</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>68.92</v>
+        <v>1771.39</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>67.03</v>
+        <v>1788.63</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>60.78</v>
+        <v>1827.19</v>
       </c>
       <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>1107.85</v>
+        <v>767.5</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>1066.14</v>
+        <v>732.45</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>1073.17</v>
+        <v>732.46</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>982.66</v>
+        <v>753.83</v>
       </c>
       <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>189.29</v>
+        <v>1201.8</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>182.61</v>
+        <v>1084</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>179.75</v>
+        <v>1023.49</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>160.58</v>
+        <v>1024.51</v>
       </c>
       <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>9803</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>9454.309999999999</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>9409.559999999999</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>9078.25</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>4463.1</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>4345.66</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>4232.11</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>3923.41</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>1866.2</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>1775.51</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>1717.42</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>1476.8</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>1487.6</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>1380.06</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>1390.58</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>1383.09</v>
+      </c>
+      <c r="G28" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>37790</v>
+        <v>273.62</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>34718.22</v>
+        <v>255.1</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>34342.05</v>
+        <v>254.44</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>34907.95</v>
+        <v>266.21</v>
       </c>
       <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>7243</v>
+        <v>643.7</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>7072.73</v>
+        <v>614.46</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>7173.59</v>
+        <v>596.42</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>6860.3</v>
+        <v>581.25</v>
       </c>
       <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>604.4</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>552.5599999999999</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>539.92</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>557.33</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>123.19</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>117.83</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>118.04</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>111.3</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>9769</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>9513.469999999999</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>9438.1</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>9083.549999999999</v>
+      </c>
+      <c r="G32" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>3761.9</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>3644.28</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>3637.02</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>3453.58</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>270.08</v>
+        <v>1918</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>250.77</v>
+        <v>1799.45</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>252.75</v>
+        <v>1732.01</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>265.21</v>
+        <v>1486.1</v>
       </c>
       <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>648.45</v>
+        <v>38170</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>607.84</v>
+        <v>35338.36</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>592.4299999999999</v>
+        <v>34633.76</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>580.2</v>
+        <v>34989.85</v>
       </c>
       <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>574.15</v>
+        <v>7181.5</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>541.48</v>
+        <v>7097.55</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>534.71</v>
+        <v>7176.42</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>554.1900000000001</v>
+        <v>6865.07</v>
       </c>
       <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>740.5</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>642.75</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>654.49</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>714.37</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>119.35</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>118.66</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>111.64</v>
+      </c>
+      <c r="G36" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>620.35</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>561.9</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>547.47</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>578.09</v>
-      </c>
-      <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>3756.6</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>3664.32</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>3646.07</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>3459.78</v>
+      </c>
+      <c r="G37" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
-        <v>471.7</v>
+        <v>519.8</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>471.35</v>
+        <v>491.4</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>466.96</v>
+        <v>478.89</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>436.64</v>
+        <v>488.91</v>
       </c>
       <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
-        <v>283.35</v>
+        <v>2354.7</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>281.15</v>
+        <v>2187.67</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>272.18</v>
+        <v>2217.71</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>250.48</v>
+        <v>2332.3</v>
       </c>
       <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>515.7</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>486.26</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>475.93</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>486.25</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>765.45</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>755.85</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>756.72</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>739.87</v>
+      </c>
+      <c r="G40" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>760.7</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>754.03</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>756.12</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>738.22</v>
-      </c>
-      <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>1420.8</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>1266.39</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>1255.66</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>1238.6</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>1286.4</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>1236.48</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>1243.57</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>1235</v>
-      </c>
-      <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>3258.1</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>2926.18</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>2852.6</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>2864.71</v>
+      </c>
+      <c r="G42" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>3340.1</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>2853.56</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>2819.18</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>2850.39</v>
-      </c>
-      <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>1169.2</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>1097.07</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>1104.87</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>1126.25</v>
+      </c>
+      <c r="G43" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>1294.99</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>1317.82</v>
+      </c>
+      <c r="F44" s="18" t="n">
+        <v>1373.59</v>
+      </c>
+      <c r="G44" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>VBL</t>
         </is>
       </c>
-      <c r="C44" s="14" t="n">
-        <v>466.55</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>430.39</v>
-      </c>
-      <c r="E44" s="14" t="n">
-        <v>434.82</v>
-      </c>
-      <c r="F44" s="14" t="n">
-        <v>464.56</v>
-      </c>
-      <c r="G44" s="15">
+      <c r="C45" s="18" t="n">
+        <v>489.65</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>440.75</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>438.87</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>465.23</v>
+      </c>
+      <c r="G45" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>1743.2</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>1621.55</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>1573.57</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>1618</v>
+      </c>
+      <c r="G46" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>1807.4</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>1699.83</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>1680.39</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>1677.04</v>
+      </c>
+      <c r="G47" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>ALKEM</t>
         </is>
       </c>
-      <c r="C45" s="18" t="n">
-        <v>5642</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>5425.74</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>5452.6</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>5397.72</v>
-      </c>
-      <c r="G45" s="19">
+      <c r="C48" s="18" t="n">
+        <v>5697.5</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>5474.95</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>5471.39</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <v>5404.74</v>
+      </c>
+      <c r="G48" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>1367.8</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>1330.86</v>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>1277.89</v>
-      </c>
-      <c r="F46" s="18" t="n">
-        <v>1200.99</v>
-      </c>
-      <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>6280</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>6100.14</v>
-      </c>
-      <c r="E47" s="18" t="n">
-        <v>6148.07</v>
-      </c>
-      <c r="F47" s="18" t="n">
-        <v>6234.99</v>
-      </c>
-      <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="n">
-        <v>1794.6</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>1729.44</v>
-      </c>
-      <c r="E48" s="18" t="n">
-        <v>1732.28</v>
-      </c>
-      <c r="F48" s="18" t="n">
-        <v>1745.5</v>
-      </c>
-      <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2517,23 +2517,23 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
-        <v>2230.7</v>
+        <v>1397.5</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>2175.57</v>
+        <v>1342.45</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>2121.9</v>
+        <v>1286.87</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>1953.94</v>
+        <v>1203.7</v>
       </c>
       <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2545,23 +2545,23 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>664.45</v>
+        <v>6314</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>629.01</v>
+        <v>6136.52</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>606.3099999999999</v>
+        <v>6159.78</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>561.64</v>
+        <v>6237.93</v>
       </c>
       <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2573,23 +2573,23 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>1129.5</v>
+        <v>1795</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>1070.36</v>
+        <v>1740.13</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>1042.86</v>
+        <v>1736.58</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>948.5700000000001</v>
+        <v>1745.22</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2601,23 +2601,23 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>2328.7</v>
+        <v>2222.8</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>2311.15</v>
+        <v>2185.03</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>2274.58</v>
+        <v>2130.05</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>2132.07</v>
+        <v>1961.19</v>
       </c>
       <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2629,23 +2629,23 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
-        <v>1100.05</v>
+        <v>685.4</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>1048.74</v>
+        <v>637.72</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>987.53</v>
+        <v>611.73</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>908.36</v>
+        <v>563.9</v>
       </c>
       <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2657,23 +2657,23 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>4191.2</v>
+        <v>1491</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>4172.81</v>
+        <v>1485.87</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>4154.92</v>
+        <v>1488.88</v>
       </c>
       <c r="F54" s="18" t="n">
-        <v>3840.28</v>
+        <v>1446.21</v>
       </c>
       <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2685,1086 +2685,1170 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>1114</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>1078.3</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>1048.35</v>
+      </c>
+      <c r="F55" s="18" t="n">
+        <v>952.78</v>
+      </c>
+      <c r="G55" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>1069.1</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>1051.27</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>993.3</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <v>912.1900000000001</v>
+      </c>
+      <c r="G56" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C55" s="18" t="n">
-        <v>936.5</v>
-      </c>
-      <c r="D55" s="18" t="n">
-        <v>908.5700000000001</v>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>905</v>
-      </c>
-      <c r="F55" s="18" t="n">
-        <v>918.25</v>
-      </c>
-      <c r="G55" s="19">
+      <c r="C57" s="18" t="n">
+        <v>927.95</v>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>912.15</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>906.79</v>
+      </c>
+      <c r="F57" s="18" t="n">
+        <v>919.05</v>
+      </c>
+      <c r="G57" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="n">
-        <v>1354.7</v>
-      </c>
-      <c r="D56" s="14" t="n">
-        <v>1298.68</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>1290.78</v>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>1250.67</v>
-      </c>
-      <c r="G56" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>HDFCAMC</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="n">
-        <v>2768.2</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>2544.47</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>2545.97</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>2579.63</v>
-      </c>
-      <c r="G57" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C58" s="14" t="n">
-        <v>2859.1</v>
+        <v>7693</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>2647.1</v>
+        <v>6719.31</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>2518.63</v>
+        <v>6272.95</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>2087.81</v>
+        <v>5691.4</v>
       </c>
       <c r="G58" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C59" s="14" t="n">
-        <v>3531.2</v>
+        <v>1297.45</v>
       </c>
       <c r="D59" s="14" t="n">
-        <v>3412.62</v>
+        <v>1129.21</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>3434.62</v>
+        <v>1055.22</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>3241.67</v>
+        <v>972.41</v>
       </c>
       <c r="G59" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C60" s="14" t="n">
-        <v>472.85</v>
+        <v>1177.1</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>427.92</v>
+        <v>1029.33</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>410.08</v>
+        <v>972.51</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>392.9</v>
+        <v>973.61</v>
       </c>
       <c r="G60" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C61" s="14" t="n">
-        <v>382.7</v>
+        <v>212.4</v>
       </c>
       <c r="D61" s="14" t="n">
-        <v>346.07</v>
+        <v>178.11</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>343.7</v>
+        <v>162.15</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>358.52</v>
+        <v>144.01</v>
       </c>
       <c r="G61" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C62" s="14" t="n">
-        <v>1982.5</v>
+        <v>334.7</v>
       </c>
       <c r="D62" s="14" t="n">
-        <v>1916.6</v>
+        <v>289.15</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>1940.3</v>
+        <v>274.39</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>1911.32</v>
+        <v>260.2</v>
       </c>
       <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBILIFE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>181.59</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>164.06</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>159.53</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>160.41</v>
+      </c>
+      <c r="G63" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="n">
+        <v>823.3</v>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>739.47</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>708.55</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>686.12</v>
+      </c>
+      <c r="G64" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="n">
+        <v>446.55</v>
+      </c>
+      <c r="D65" s="14" t="n">
+        <v>444.41</v>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>438.52</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>405.97</v>
+      </c>
+      <c r="G65" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="n">
+        <v>4242.6</v>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>3967.12</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>3737.12</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>3096.86</v>
+      </c>
+      <c r="G66" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>JPPOWER</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="G67" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>515.23</v>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v>501.26</v>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>500.75</v>
+      </c>
+      <c r="G68" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="D69" s="14" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="E69" s="14" t="n">
+        <v>77.52</v>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>79.42</v>
+      </c>
+      <c r="G69" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="n">
+        <v>305.55</v>
+      </c>
+      <c r="D70" s="14" t="n">
+        <v>281.28</v>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>269.47</v>
+      </c>
+      <c r="F70" s="14" t="n">
+        <v>254.31</v>
+      </c>
+      <c r="G70" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="n">
+        <v>403.75</v>
+      </c>
+      <c r="D71" s="14" t="n">
+        <v>384.71</v>
+      </c>
+      <c r="E71" s="14" t="n">
+        <v>374.44</v>
+      </c>
+      <c r="F71" s="14" t="n">
+        <v>351.34</v>
+      </c>
+      <c r="G71" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="n">
+        <v>319.8</v>
+      </c>
+      <c r="D72" s="14" t="n">
+        <v>306.21</v>
+      </c>
+      <c r="E72" s="14" t="n">
+        <v>296.99</v>
+      </c>
+      <c r="F72" s="14" t="n">
+        <v>285.26</v>
+      </c>
+      <c r="G72" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="n">
+        <v>30170</v>
+      </c>
+      <c r="D73" s="14" t="n">
+        <v>27322.86</v>
+      </c>
+      <c r="E73" s="14" t="n">
+        <v>25094.78</v>
+      </c>
+      <c r="F73" s="14" t="n">
+        <v>20992.78</v>
+      </c>
+      <c r="G73" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="n">
+        <v>1089</v>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>980.34</v>
+      </c>
+      <c r="E74" s="14" t="n">
+        <v>905.89</v>
+      </c>
+      <c r="F74" s="14" t="n">
+        <v>810.45</v>
+      </c>
+      <c r="G74" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="n">
+        <v>3840.5</v>
+      </c>
+      <c r="D75" s="14" t="n">
+        <v>3408.56</v>
+      </c>
+      <c r="E75" s="14" t="n">
+        <v>3272.56</v>
+      </c>
+      <c r="F75" s="14" t="n">
+        <v>3156.54</v>
+      </c>
+      <c r="G75" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D76" s="14" t="n">
+        <v>46.94</v>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v>45.73</v>
+      </c>
+      <c r="F76" s="14" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="G76" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="n">
+        <v>439.85</v>
+      </c>
+      <c r="D77" s="14" t="n">
+        <v>409.24</v>
+      </c>
+      <c r="E77" s="14" t="n">
+        <v>394.5</v>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>387.02</v>
+      </c>
+      <c r="G77" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="n">
+        <v>4125</v>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>3698.85</v>
+      </c>
+      <c r="E78" s="14" t="n">
+        <v>3396.08</v>
+      </c>
+      <c r="F78" s="14" t="n">
+        <v>3234.63</v>
+      </c>
+      <c r="G78" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="n">
+        <v>1655.1</v>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>1497.05</v>
+      </c>
+      <c r="E79" s="14" t="n">
+        <v>1451.83</v>
+      </c>
+      <c r="F79" s="14" t="n">
+        <v>1394.27</v>
+      </c>
+      <c r="G79" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>TRITURBINE</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="n">
+        <v>573.85</v>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>495.25</v>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v>486.58</v>
+      </c>
+      <c r="F80" s="14" t="n">
+        <v>510.21</v>
+      </c>
+      <c r="G80" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n">
-        <v>1045.15</v>
-      </c>
-      <c r="D63" s="14" t="n">
-        <v>991.71</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>987.37</v>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>869.49</v>
-      </c>
-      <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="n">
-        <v>7158</v>
-      </c>
-      <c r="D64" s="18" t="n">
-        <v>6549.64</v>
-      </c>
-      <c r="E64" s="18" t="n">
-        <v>6172.54</v>
-      </c>
-      <c r="F64" s="18" t="n">
-        <v>5650.88</v>
-      </c>
-      <c r="G64" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="n">
-        <v>1259.4</v>
-      </c>
-      <c r="D65" s="18" t="n">
-        <v>1095.32</v>
-      </c>
-      <c r="E65" s="18" t="n">
-        <v>1036.36</v>
-      </c>
-      <c r="F65" s="18" t="n">
-        <v>966.84</v>
-      </c>
-      <c r="G65" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="C66" s="18" t="n">
-        <v>1152.7</v>
-      </c>
-      <c r="D66" s="18" t="n">
-        <v>999.4299999999999</v>
-      </c>
-      <c r="E66" s="18" t="n">
-        <v>956.5700000000001</v>
-      </c>
-      <c r="F66" s="18" t="n">
-        <v>970.86</v>
-      </c>
-      <c r="G66" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>ADANIPOWER</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="n">
-        <v>200.83</v>
-      </c>
-      <c r="D67" s="18" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="E67" s="18" t="n">
-        <v>158.35</v>
-      </c>
-      <c r="F67" s="18" t="n">
-        <v>142.65</v>
-      </c>
-      <c r="G67" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="n">
-        <v>325.63</v>
-      </c>
-      <c r="D68" s="18" t="n">
-        <v>279.27</v>
-      </c>
-      <c r="E68" s="18" t="n">
-        <v>269.45</v>
-      </c>
-      <c r="F68" s="18" t="n">
-        <v>258.62</v>
-      </c>
-      <c r="G68" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="n">
-        <v>179.42</v>
-      </c>
-      <c r="D69" s="18" t="n">
-        <v>160.47</v>
-      </c>
-      <c r="E69" s="18" t="n">
-        <v>157.81</v>
-      </c>
-      <c r="F69" s="18" t="n">
-        <v>160.22</v>
-      </c>
-      <c r="G69" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="n">
-        <v>795.7</v>
-      </c>
-      <c r="D70" s="18" t="n">
-        <v>722.79</v>
-      </c>
-      <c r="E70" s="18" t="n">
-        <v>699.73</v>
-      </c>
-      <c r="F70" s="18" t="n">
-        <v>683.98</v>
-      </c>
-      <c r="G70" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="n">
-        <v>4232.3</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>3905.07</v>
-      </c>
-      <c r="E71" s="18" t="n">
-        <v>3694.63</v>
-      </c>
-      <c r="F71" s="18" t="n">
-        <v>3073.11</v>
-      </c>
-      <c r="G71" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>JPPOWER</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="n">
-        <v>19.08</v>
-      </c>
-      <c r="D72" s="18" t="n">
-        <v>16.73</v>
-      </c>
-      <c r="E72" s="18" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="F72" s="18" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="G72" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="n">
-        <v>543.05</v>
-      </c>
-      <c r="D73" s="18" t="n">
-        <v>507.49</v>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>497.2</v>
-      </c>
-      <c r="F73" s="18" t="n">
-        <v>500.78</v>
-      </c>
-      <c r="G73" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>NHPC</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="D74" s="18" t="n">
-        <v>78.16</v>
-      </c>
-      <c r="E74" s="18" t="n">
-        <v>77.06</v>
-      </c>
-      <c r="F74" s="18" t="n">
-        <v>79.17</v>
-      </c>
-      <c r="G74" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>NLCINDIA</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="n">
-        <v>304.35</v>
-      </c>
-      <c r="D75" s="18" t="n">
-        <v>276.48</v>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>266.69</v>
-      </c>
-      <c r="F75" s="18" t="n">
-        <v>253.46</v>
-      </c>
-      <c r="G75" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B76" s="17" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="n">
-        <v>398</v>
-      </c>
-      <c r="D76" s="18" t="n">
-        <v>381.28</v>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>372.31</v>
-      </c>
-      <c r="F76" s="18" t="n">
-        <v>350.71</v>
-      </c>
-      <c r="G76" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="C77" s="18" t="n">
-        <v>319.7</v>
-      </c>
-      <c r="D77" s="18" t="n">
-        <v>303.25</v>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>295.11</v>
-      </c>
-      <c r="F77" s="18" t="n">
-        <v>285.18</v>
-      </c>
-      <c r="G77" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>POWERINDIA</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="n">
-        <v>29645</v>
-      </c>
-      <c r="D78" s="18" t="n">
-        <v>26721.39</v>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>24683.43</v>
-      </c>
-      <c r="F78" s="18" t="n">
-        <v>20780.69</v>
-      </c>
-      <c r="G78" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>SCHNEIDER</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="n">
-        <v>1087.85</v>
-      </c>
-      <c r="D79" s="18" t="n">
-        <v>959.4400000000001</v>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>891.87</v>
-      </c>
-      <c r="F79" s="18" t="n">
-        <v>805.64</v>
-      </c>
-      <c r="G79" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B80" s="17" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C80" s="18" t="n">
-        <v>3709</v>
-      </c>
-      <c r="D80" s="18" t="n">
-        <v>3325.34</v>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>3230.1</v>
-      </c>
-      <c r="F80" s="18" t="n">
-        <v>3141.39</v>
-      </c>
-      <c r="G80" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>52.5</v>
+        <v>1369.5</v>
       </c>
       <c r="D81" s="18" t="n">
-        <v>45.55</v>
+        <v>1312.23</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>45.11</v>
+        <v>1297.14</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>51.4</v>
+        <v>1252.59</v>
       </c>
       <c r="G81" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>433.6</v>
+        <v>2766.9</v>
       </c>
       <c r="D82" s="18" t="n">
-        <v>402.86</v>
+        <v>2587.16</v>
       </c>
       <c r="E82" s="18" t="n">
-        <v>390.87</v>
+        <v>2563.98</v>
       </c>
       <c r="F82" s="18" t="n">
-        <v>386.18</v>
+        <v>2585.63</v>
       </c>
       <c r="G82" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>4185.2</v>
+        <v>1368.6</v>
       </c>
       <c r="D83" s="18" t="n">
-        <v>3604.41</v>
+        <v>1317.33</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>3335.36</v>
+        <v>1322.86</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>3214.32</v>
+        <v>1365.47</v>
       </c>
       <c r="G83" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>1606.3</v>
+        <v>557.9</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>1465.56</v>
+        <v>527.74</v>
       </c>
       <c r="E84" s="18" t="n">
-        <v>1436.27</v>
+        <v>521.55</v>
       </c>
       <c r="F84" s="18" t="n">
-        <v>1389.59</v>
+        <v>544.25</v>
       </c>
       <c r="G84" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>TRITURBINE</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C85" s="18" t="n">
-        <v>576.2</v>
+        <v>2785</v>
       </c>
       <c r="D85" s="18" t="n">
-        <v>478.23</v>
+        <v>2675.61</v>
       </c>
       <c r="E85" s="18" t="n">
-        <v>479.47</v>
+        <v>2540.64</v>
       </c>
       <c r="F85" s="18" t="n">
-        <v>509.21</v>
+        <v>2102.6</v>
       </c>
       <c r="G85" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C86" s="14" t="n">
-        <v>1694.9</v>
-      </c>
-      <c r="D86" s="14" t="n">
-        <v>1596.62</v>
-      </c>
-      <c r="E86" s="14" t="n">
-        <v>1560.23</v>
-      </c>
-      <c r="F86" s="14" t="n">
-        <v>1612</v>
-      </c>
-      <c r="G86" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="n">
+        <v>3586.5</v>
+      </c>
+      <c r="D86" s="18" t="n">
+        <v>3446.2</v>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>3447.2</v>
+      </c>
+      <c r="F86" s="18" t="n">
+        <v>3254.34</v>
+      </c>
+      <c r="G86" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B87" s="13" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C87" s="14" t="n">
-        <v>1767.9</v>
-      </c>
-      <c r="D87" s="14" t="n">
-        <v>1676.03</v>
-      </c>
-      <c r="E87" s="14" t="n">
-        <v>1669.82</v>
-      </c>
-      <c r="F87" s="14" t="n">
-        <v>1668.2</v>
-      </c>
-      <c r="G87" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>472.85</v>
+      </c>
+      <c r="D87" s="18" t="n">
+        <v>435.92</v>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>414.84</v>
+      </c>
+      <c r="F87" s="18" t="n">
+        <v>394.62</v>
+      </c>
+      <c r="G87" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C88" s="18" t="n">
-        <v>93.3</v>
+        <v>383.85</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>80.36</v>
+        <v>352.88</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>74.73999999999999</v>
+        <v>346.77</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>73.98999999999999</v>
+        <v>358.84</v>
       </c>
       <c r="G88" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C89" s="18" t="n">
-        <v>8082.5</v>
+        <v>1030</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>7242.34</v>
+        <v>999.98</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>7144.5</v>
+        <v>991.22</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>7693.39</v>
+        <v>872.86</v>
       </c>
       <c r="G89" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="C90" s="14" t="n">
-        <v>1504.4</v>
+        <v>627.35</v>
       </c>
       <c r="D90" s="14" t="n">
-        <v>1446.86</v>
+        <v>572.6799999999999</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>1458.14</v>
+        <v>553.14</v>
       </c>
       <c r="F90" s="14" t="n">
-        <v>1485.5</v>
+        <v>578.66</v>
       </c>
       <c r="G90" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>AUBANK</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="n">
-        <v>997.65</v>
-      </c>
-      <c r="D91" s="18" t="n">
-        <v>945.59</v>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>944.47</v>
-      </c>
-      <c r="F91" s="18" t="n">
-        <v>880.74</v>
-      </c>
-      <c r="G91" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="n">
+        <v>284.45</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>281.63</v>
+      </c>
+      <c r="E91" s="14" t="n">
+        <v>273.08</v>
+      </c>
+      <c r="F91" s="14" t="n">
+        <v>250.98</v>
+      </c>
+      <c r="G91" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C92" s="18" t="n">
-        <v>294.35</v>
+        <v>99.58</v>
       </c>
       <c r="D92" s="18" t="n">
-        <v>280.81</v>
+        <v>83.7</v>
       </c>
       <c r="E92" s="18" t="n">
-        <v>277.22</v>
+        <v>76.58</v>
       </c>
       <c r="F92" s="18" t="n">
-        <v>250.14</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="G92" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="20" t="inlineStr">
         <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>8040</v>
+      </c>
+      <c r="D93" s="18" t="n">
+        <v>7377.64</v>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>7209.26</v>
+      </c>
+      <c r="F93" s="18" t="n">
+        <v>7703.18</v>
+      </c>
+      <c r="G93" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B93" s="17" t="inlineStr">
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="n">
+        <v>1044.85</v>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>963</v>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v>951.9299999999999</v>
+      </c>
+      <c r="F94" s="14" t="n">
+        <v>883.11</v>
+      </c>
+      <c r="G94" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="n">
+        <v>297.05</v>
+      </c>
+      <c r="D95" s="14" t="n">
+        <v>283.64</v>
+      </c>
+      <c r="E95" s="14" t="n">
+        <v>278.7</v>
+      </c>
+      <c r="F95" s="14" t="n">
+        <v>251.02</v>
+      </c>
+      <c r="G95" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="C93" s="18" t="n">
-        <v>851.95</v>
-      </c>
-      <c r="D93" s="18" t="n">
-        <v>830.5700000000001</v>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>851.0599999999999</v>
-      </c>
-      <c r="F93" s="18" t="n">
-        <v>844.51</v>
-      </c>
-      <c r="G93" s="19">
+      <c r="C96" s="14" t="n">
+        <v>858</v>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>835.41</v>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v>851.53</v>
+      </c>
+      <c r="F96" s="14" t="n">
+        <v>841.39</v>
+      </c>
+      <c r="G96" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 22-Apr-2026  05:00</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 22-Apr-2026  16:57</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -687,10 +687,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.9329999999999999</v>
+        <v>1</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.9777</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -706,146 +706,146 @@
         <v>12</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.833</v>
+        <v>0.917</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.583</v>
+        <v>0.667</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.8053</v>
+        <v>0.8613</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.9329999999999999</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.7333</v>
+        <v>0.7667</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.7333</v>
+        <v>0.7556999999999999</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0.5329999999999999</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.7333</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>8</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.9329999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.733</v>
+        <v>0.667</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>0.5329999999999999</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.733</v>
+        <v>0.6890000000000001</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -882,125 +882,125 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>12</v>
-      </c>
       <c r="E11" s="9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.55</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.6</v>
+        <v>0.733</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.7</v>
+        <v>0.267</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.6167</v>
+        <v>0.6443000000000001</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.625</v>
+        <v>0.55</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.575</v>
+        <v>0.7</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.6083</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.55</v>
+        <v>0.625</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.5832999999999999</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>13</v>
-      </c>
       <c r="D14" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.867</v>
+        <v>0.75</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.578</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1016,7 +1016,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>3</v>
@@ -1025,13 +1025,13 @@
         <v>0.75</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.15</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.4667</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1075,25 +1075,25 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.1333</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1229,23 +1229,23 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2119.9</v>
+        <v>2260.8</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2043.09</v>
+        <v>2085.12</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2034.41</v>
+        <v>2075.27</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1892.83</v>
+        <v>2237.38</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1029.95</v>
+        <v>2121.9</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>975.28</v>
+        <v>2043.28</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>945.01</v>
+        <v>2034.48</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>844.4</v>
+        <v>1892.85</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>554.9</v>
+        <v>1039.9</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>531.6799999999999</v>
+        <v>976.22</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>526.27</v>
+        <v>945.4</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>428.38</v>
+        <v>844.5</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>588.65</v>
+        <v>556.95</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>564.99</v>
+        <v>531.88</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>569.24</v>
+        <v>526.35</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>535.3200000000001</v>
+        <v>428.4</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1285.5</v>
+        <v>604.75</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1215.64</v>
+        <v>566.52</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1180.04</v>
+        <v>569.87</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1082.32</v>
+        <v>535.48</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>787.2</v>
+        <v>1278.6</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>761.08</v>
+        <v>1214.98</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>758.39</v>
+        <v>1179.77</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>742</v>
+        <v>1082.25</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1267.4</v>
+        <v>784.5</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1210.17</v>
+        <v>760.8200000000001</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1197.41</v>
+        <v>758.28</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1149.13</v>
+        <v>741.97</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>431.2</v>
+        <v>1263.4</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>409.65</v>
+        <v>1209.79</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>385.35</v>
+        <v>1197.25</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>298.91</v>
+        <v>1149.09</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>89.28</v>
+        <v>435.95</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>84.31999999999999</v>
+        <v>410.11</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>81.63</v>
+        <v>385.53</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>76.04000000000001</v>
+        <v>298.96</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2399</v>
+        <v>88.59</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2340.53</v>
+        <v>84.25</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2311.77</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2385.23</v>
+        <v>76.03</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,23 +1509,23 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>176.59</v>
+        <v>2454.3</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>164.75</v>
+        <v>2345.8</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>158.52</v>
+        <v>2313.94</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>143.25</v>
+        <v>2385.78</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,23 +1537,23 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>212.72</v>
+        <v>176.23</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>204.47</v>
+        <v>164.71</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>199.28</v>
+        <v>158.51</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>180.57</v>
+        <v>143.25</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>764.45</v>
+        <v>213.03</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>731.65</v>
+        <v>204.5</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>696.65</v>
+        <v>199.29</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>579.42</v>
+        <v>180.57</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VEDL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,79 +1593,79 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>757</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>730.9400000000001</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>696.35</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>579.34</v>
+      </c>
+      <c r="G16" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VEDL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n">
-        <v>1129.6</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>969.59</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>888.8099999999999</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>844.25</v>
-      </c>
-      <c r="G16" s="15">
+      <c r="C17" s="14" t="n">
+        <v>1139.2</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>970.51</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>889.1799999999999</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>844.34</v>
+      </c>
+      <c r="G17" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>BANKBARODA</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
-        <v>283.31</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>276.77</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>282.13</v>
-      </c>
-      <c r="F17" s="18" t="n">
+      <c r="C18" s="18" t="n">
+        <v>282.77</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>276.72</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>282.11</v>
+      </c>
+      <c r="F18" s="18" t="n">
         <v>275.38</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G18" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BANKBARODA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>145</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>139.22</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>141.07</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>133.92</v>
-      </c>
-      <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANBK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,23 +1677,23 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>924.45</v>
+        <v>152.92</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>921.58</v>
+        <v>148.37</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>906.75</v>
+        <v>151.49</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>812.1</v>
+        <v>141.6</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BANKINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1705,23 +1705,23 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>81.70999999999999</v>
+        <v>145.23</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>71.11</v>
+        <v>139.25</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>68.09999999999999</v>
+        <v>141.08</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>61.15</v>
+        <v>133.92</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANBK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1733,23 +1733,23 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>1102.25</v>
+        <v>36.93</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>1073.52</v>
+        <v>35.38</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>1075.77</v>
+        <v>35.83</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>985.59</v>
+        <v>36.78</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTRALBK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,2094 +1761,2290 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>925.35</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>921.66</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>906.78</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>812.11</v>
+      </c>
+      <c r="G22" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>1103.3</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1073.62</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1075.81</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>985.6</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
           <t>UNIONBANK</t>
         </is>
       </c>
-      <c r="C22" s="18" t="n">
-        <v>194.53</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>180.77</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>161.17</v>
-      </c>
-      <c r="G22" s="19">
+      <c r="C25" s="18" t="n">
+        <v>194.05</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>184.45</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>161.16</v>
+      </c>
+      <c r="G25" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>7857</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>7288.94</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>7106.72</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>7066.07</v>
-      </c>
-      <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>1881.6</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>1771.39</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>1788.63</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>1827.19</v>
-      </c>
-      <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>CENTURYPLY</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>767.5</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>732.45</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>732.46</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>753.83</v>
-      </c>
-      <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>1201.8</v>
+        <v>271.56</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>1084</v>
+        <v>254.91</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>1023.49</v>
+        <v>254.36</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>1024.51</v>
+        <v>266.19</v>
       </c>
       <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>4463.1</v>
+        <v>652.45</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>4345.66</v>
+        <v>615.29</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>4232.11</v>
+        <v>596.77</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>3923.41</v>
+        <v>581.33</v>
       </c>
       <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>1487.6</v>
+        <v>599.6</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>1380.06</v>
+        <v>552.1</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>1390.58</v>
+        <v>539.73</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1383.09</v>
+        <v>557.28</v>
       </c>
       <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>273.62</v>
+        <v>7803.5</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>255.1</v>
+        <v>7283.85</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>254.44</v>
+        <v>7104.62</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>266.21</v>
+        <v>7065.54</v>
       </c>
       <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>643.7</v>
+        <v>1888.6</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>614.46</v>
+        <v>1772.06</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>596.42</v>
+        <v>1788.9</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>581.25</v>
+        <v>1827.26</v>
       </c>
       <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>604.4</v>
+        <v>777.9</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>552.5599999999999</v>
+        <v>733.4400000000001</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>539.92</v>
+        <v>732.86</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>557.33</v>
+        <v>753.9299999999999</v>
       </c>
       <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>9769</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>9513.469999999999</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>9438.1</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>9083.549999999999</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>5488.9</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>5078.61</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>5009.25</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>5443.43</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>1918</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>1799.45</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>1732.01</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>1486.1</v>
-      </c>
-      <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>1202.7</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>1084.09</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>1023.53</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>1024.52</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>38170</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>35338.36</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>34633.76</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>34989.85</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>4454.6</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>4344.85</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>4231.77</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>3923.33</v>
+      </c>
+      <c r="G34" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>7181.5</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>7097.55</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>7176.42</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>6865.07</v>
-      </c>
-      <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>1481.6</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>1379.49</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>1390.35</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>1383.03</v>
+      </c>
+      <c r="G35" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>127.55</v>
+        <v>541.55</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>119.35</v>
+        <v>493.47</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>118.66</v>
+        <v>479.74</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>111.64</v>
+        <v>489.13</v>
       </c>
       <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>2368.8</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>2189.01</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>2218.26</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>2332.44</v>
+      </c>
+      <c r="G37" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>772.5</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>756.52</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>757</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>739.9400000000001</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>1395.8</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>1264.01</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>1254.68</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>1238.35</v>
+      </c>
+      <c r="G39" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>3243</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>2924.74</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>2852.01</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>2864.56</v>
+      </c>
+      <c r="G40" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>1178.6</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>1097.96</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>1105.24</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>1126.34</v>
+      </c>
+      <c r="G41" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>1392.8</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>1296.69</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>1318.52</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>1373.77</v>
+      </c>
+      <c r="G42" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>494.95</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>441.25</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>439.08</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>465.29</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>3756.6</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>3664.32</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>3646.07</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>3459.78</v>
-      </c>
-      <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="n">
-        <v>519.8</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>491.4</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>478.89</v>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>488.91</v>
-      </c>
-      <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>2354.7</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>2187.67</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>2217.71</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>2332.3</v>
-      </c>
-      <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="n">
-        <v>765.45</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>755.85</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>756.72</v>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>739.87</v>
-      </c>
-      <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>1420.8</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>1266.39</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>1255.66</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>1238.6</v>
-      </c>
-      <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>3258.1</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>2926.18</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>2852.6</v>
-      </c>
-      <c r="F42" s="18" t="n">
-        <v>2864.71</v>
-      </c>
-      <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>1169.2</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>1097.07</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>1104.87</v>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>1126.25</v>
-      </c>
-      <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>1375</v>
+        <v>178.97</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>1294.99</v>
+        <v>172.98</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1317.82</v>
+        <v>177.8</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>1373.59</v>
+        <v>161.25</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ASHOKLEY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>489.65</v>
+        <v>9602</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>440.75</v>
+        <v>9497.559999999999</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>438.87</v>
+        <v>9431.549999999999</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>465.23</v>
+        <v>9081.889999999999</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="n">
-        <v>1743.2</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>1621.55</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>1573.57</v>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>1618</v>
-      </c>
-      <c r="G46" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>1903.2</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>1798.04</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>1731.43</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>1485.95</v>
+      </c>
+      <c r="G46" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="n">
-        <v>1807.4</v>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>1699.83</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>1680.39</v>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>1677.04</v>
-      </c>
-      <c r="G47" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>37885</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>35311.22</v>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>34622.59</v>
+      </c>
+      <c r="F47" s="18" t="n">
+        <v>34987.02</v>
+      </c>
+      <c r="G47" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>5697.5</v>
+        <v>7230</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>5474.95</v>
+        <v>7102.17</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>5471.39</v>
+        <v>7178.32</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>5404.74</v>
+        <v>6865.56</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
-        <v>1397.5</v>
+        <v>354.55</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>1342.45</v>
+        <v>321.36</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>1286.87</v>
+        <v>322.89</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>1203.7</v>
+        <v>352.6</v>
       </c>
       <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>6314</v>
+        <v>131.76</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>6136.52</v>
+        <v>119.75</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>6159.78</v>
+        <v>118.83</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>6237.93</v>
+        <v>111.68</v>
       </c>
       <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>1795</v>
+        <v>3660.7</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>1740.13</v>
+        <v>3655.18</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>1736.58</v>
+        <v>3642.31</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>1745.22</v>
+        <v>3458.83</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>GLENMARK</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="n">
-        <v>2222.8</v>
-      </c>
-      <c r="D52" s="18" t="n">
-        <v>2185.03</v>
-      </c>
-      <c r="E52" s="18" t="n">
-        <v>2130.05</v>
-      </c>
-      <c r="F52" s="18" t="n">
-        <v>1961.19</v>
-      </c>
-      <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="n">
+        <v>1733.6</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>1620.63</v>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>1573.2</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>1617.91</v>
+      </c>
+      <c r="G52" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="n">
-        <v>685.4</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>637.72</v>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>611.73</v>
-      </c>
-      <c r="F53" s="18" t="n">
-        <v>563.9</v>
-      </c>
-      <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="n">
+        <v>1809.4</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>1700.02</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>1680.47</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>1677.06</v>
+      </c>
+      <c r="G53" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>1491</v>
+        <v>629.1</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>1485.87</v>
+        <v>572.84</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>1488.88</v>
+        <v>553.21</v>
       </c>
       <c r="F54" s="18" t="n">
-        <v>1446.21</v>
+        <v>578.67</v>
       </c>
       <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C55" s="18" t="n">
-        <v>1114</v>
+        <v>166.12</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>1078.3</v>
+        <v>153.55</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>1048.35</v>
+        <v>154.47</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>952.78</v>
+        <v>165.25</v>
       </c>
       <c r="G55" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="20" t="inlineStr">
         <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>283.65</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>281.56</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>273.05</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <v>250.97</v>
+      </c>
+      <c r="G56" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>NATCOPHARM</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="n">
-        <v>1069.1</v>
-      </c>
-      <c r="D56" s="18" t="n">
-        <v>1051.27</v>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>993.3</v>
-      </c>
-      <c r="F56" s="18" t="n">
-        <v>912.1900000000001</v>
-      </c>
-      <c r="G56" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>5627</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>5468.23</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>5468.63</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>5404.04</v>
+      </c>
+      <c r="G57" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="n">
-        <v>927.95</v>
-      </c>
-      <c r="D57" s="18" t="n">
-        <v>912.15</v>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>906.79</v>
-      </c>
-      <c r="F57" s="18" t="n">
-        <v>919.05</v>
-      </c>
-      <c r="G57" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C58" s="14" t="n">
-        <v>7693</v>
+        <v>1421.2</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>6719.31</v>
+        <v>1344.71</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>6272.95</v>
+        <v>1287.8</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>5691.4</v>
+        <v>1203.94</v>
       </c>
       <c r="G58" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C59" s="14" t="n">
-        <v>1297.45</v>
+        <v>6285.5</v>
       </c>
       <c r="D59" s="14" t="n">
-        <v>1129.21</v>
+        <v>6133.81</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>1055.22</v>
+        <v>6158.66</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>972.41</v>
+        <v>6237.65</v>
       </c>
       <c r="G59" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C60" s="14" t="n">
-        <v>1177.1</v>
+        <v>1800.6</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>1029.33</v>
+        <v>1740.66</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>972.51</v>
+        <v>1736.8</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>973.61</v>
+        <v>1745.27</v>
       </c>
       <c r="G60" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C61" s="14" t="n">
-        <v>212.4</v>
+        <v>2240</v>
       </c>
       <c r="D61" s="14" t="n">
-        <v>178.11</v>
+        <v>2186.67</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>162.15</v>
+        <v>2130.72</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>144.01</v>
+        <v>1961.36</v>
       </c>
       <c r="G61" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C62" s="14" t="n">
-        <v>334.7</v>
+        <v>672.75</v>
       </c>
       <c r="D62" s="14" t="n">
-        <v>289.15</v>
+        <v>636.52</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>274.39</v>
+        <v>611.23</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>260.2</v>
+        <v>563.78</v>
       </c>
       <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C63" s="14" t="n">
-        <v>181.59</v>
+        <v>1494.8</v>
       </c>
       <c r="D63" s="14" t="n">
-        <v>164.06</v>
+        <v>1486.23</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>159.53</v>
+        <v>1489.03</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>160.41</v>
+        <v>1446.25</v>
       </c>
       <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C64" s="14" t="n">
-        <v>823.3</v>
+        <v>1096.1</v>
       </c>
       <c r="D64" s="14" t="n">
-        <v>739.47</v>
+        <v>1076.6</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>708.55</v>
+        <v>1047.64</v>
       </c>
       <c r="F64" s="14" t="n">
-        <v>686.12</v>
+        <v>952.61</v>
       </c>
       <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C65" s="14" t="n">
-        <v>446.55</v>
+        <v>1071</v>
       </c>
       <c r="D65" s="14" t="n">
-        <v>444.41</v>
+        <v>1051.45</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>438.52</v>
+        <v>993.37</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>405.97</v>
+        <v>912.21</v>
       </c>
       <c r="G65" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="n">
+        <v>929.9</v>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>912.33</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>906.87</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>919.0700000000001</v>
+      </c>
+      <c r="G66" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n">
+        <v>7587</v>
+      </c>
+      <c r="D67" s="18" t="n">
+        <v>6709.21</v>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>6268.8</v>
+      </c>
+      <c r="F67" s="18" t="n">
+        <v>5690.34</v>
+      </c>
+      <c r="G67" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>1368.1</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>1135.94</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>1057.99</v>
+      </c>
+      <c r="F68" s="18" t="n">
+        <v>973.11</v>
+      </c>
+      <c r="G68" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n">
+        <v>1198.95</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>1031.41</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>973.37</v>
+      </c>
+      <c r="F69" s="18" t="n">
+        <v>973.8200000000001</v>
+      </c>
+      <c r="G69" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>215.65</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>178.42</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>162.28</v>
+      </c>
+      <c r="F70" s="18" t="n">
+        <v>144.04</v>
+      </c>
+      <c r="G70" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n">
+        <v>333.64</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>289.05</v>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>274.35</v>
+      </c>
+      <c r="F71" s="18" t="n">
+        <v>260.19</v>
+      </c>
+      <c r="G71" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="n">
+        <v>180.27</v>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>163.94</v>
+      </c>
+      <c r="E72" s="18" t="n">
+        <v>159.48</v>
+      </c>
+      <c r="F72" s="18" t="n">
+        <v>160.39</v>
+      </c>
+      <c r="G72" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>824.35</v>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>739.5700000000001</v>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>708.59</v>
+      </c>
+      <c r="F73" s="18" t="n">
+        <v>686.13</v>
+      </c>
+      <c r="G73" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
         <is>
           <t>GVT&amp;D</t>
         </is>
       </c>
-      <c r="C66" s="14" t="n">
-        <v>4242.6</v>
-      </c>
-      <c r="D66" s="14" t="n">
-        <v>3967.12</v>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>3737.12</v>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>3096.86</v>
-      </c>
-      <c r="G66" s="15">
+      <c r="C74" s="18" t="n">
+        <v>4239.4</v>
+      </c>
+      <c r="D74" s="18" t="n">
+        <v>3966.82</v>
+      </c>
+      <c r="E74" s="18" t="n">
+        <v>3737</v>
+      </c>
+      <c r="F74" s="18" t="n">
+        <v>3096.83</v>
+      </c>
+      <c r="G74" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B75" s="17" t="inlineStr">
         <is>
           <t>JPPOWER</t>
         </is>
       </c>
-      <c r="C67" s="14" t="n">
-        <v>20.02</v>
-      </c>
-      <c r="D67" s="14" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="E67" s="14" t="n">
-        <v>16.23</v>
-      </c>
-      <c r="F67" s="14" t="n">
+      <c r="C75" s="18" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="D75" s="18" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="F75" s="18" t="n">
         <v>16.77</v>
       </c>
-      <c r="G67" s="15">
+      <c r="G75" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B76" s="17" t="inlineStr">
         <is>
           <t>JSWENERGY</t>
         </is>
       </c>
-      <c r="C68" s="14" t="n">
-        <v>553.3</v>
-      </c>
-      <c r="D68" s="14" t="n">
-        <v>515.23</v>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v>501.26</v>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>500.75</v>
-      </c>
-      <c r="G68" s="15">
+      <c r="C76" s="18" t="n">
+        <v>560.55</v>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>515.92</v>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>501.55</v>
+      </c>
+      <c r="F76" s="18" t="n">
+        <v>500.82</v>
+      </c>
+      <c r="G76" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="16" t="inlineStr">
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B77" s="17" t="inlineStr">
         <is>
           <t>NHPC</t>
         </is>
       </c>
-      <c r="C69" s="14" t="n">
-        <v>83.37</v>
-      </c>
-      <c r="D69" s="14" t="n">
-        <v>79.04000000000001</v>
-      </c>
-      <c r="E69" s="14" t="n">
-        <v>77.52</v>
-      </c>
-      <c r="F69" s="14" t="n">
-        <v>79.42</v>
-      </c>
-      <c r="G69" s="15">
+      <c r="C77" s="18" t="n">
+        <v>82.63</v>
+      </c>
+      <c r="D77" s="18" t="n">
+        <v>78.97</v>
+      </c>
+      <c r="E77" s="18" t="n">
+        <v>77.48999999999999</v>
+      </c>
+      <c r="F77" s="18" t="n">
+        <v>79.41</v>
+      </c>
+      <c r="G77" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B78" s="17" t="inlineStr">
         <is>
           <t>NLCINDIA</t>
         </is>
       </c>
-      <c r="C70" s="14" t="n">
-        <v>305.55</v>
-      </c>
-      <c r="D70" s="14" t="n">
-        <v>281.28</v>
-      </c>
-      <c r="E70" s="14" t="n">
-        <v>269.47</v>
-      </c>
-      <c r="F70" s="14" t="n">
-        <v>254.31</v>
-      </c>
-      <c r="G70" s="15">
+      <c r="C78" s="18" t="n">
+        <v>301.15</v>
+      </c>
+      <c r="D78" s="18" t="n">
+        <v>280.86</v>
+      </c>
+      <c r="E78" s="18" t="n">
+        <v>269.3</v>
+      </c>
+      <c r="F78" s="18" t="n">
+        <v>254.27</v>
+      </c>
+      <c r="G78" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="16" t="inlineStr">
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B79" s="17" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
       </c>
-      <c r="C71" s="14" t="n">
-        <v>403.75</v>
-      </c>
-      <c r="D71" s="14" t="n">
-        <v>384.71</v>
-      </c>
-      <c r="E71" s="14" t="n">
-        <v>374.44</v>
-      </c>
-      <c r="F71" s="14" t="n">
-        <v>351.34</v>
-      </c>
-      <c r="G71" s="15">
+      <c r="C79" s="18" t="n">
+        <v>405.4</v>
+      </c>
+      <c r="D79" s="18" t="n">
+        <v>384.86</v>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>374.51</v>
+      </c>
+      <c r="F79" s="18" t="n">
+        <v>351.35</v>
+      </c>
+      <c r="G79" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="16" t="inlineStr">
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B80" s="17" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
       </c>
-      <c r="C72" s="14" t="n">
-        <v>319.8</v>
-      </c>
-      <c r="D72" s="14" t="n">
+      <c r="C80" s="18" t="n">
+        <v>319.75</v>
+      </c>
+      <c r="D80" s="18" t="n">
         <v>306.21</v>
       </c>
-      <c r="E72" s="14" t="n">
+      <c r="E80" s="18" t="n">
         <v>296.99</v>
       </c>
-      <c r="F72" s="14" t="n">
+      <c r="F80" s="18" t="n">
         <v>285.26</v>
       </c>
-      <c r="G72" s="15">
+      <c r="G80" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="16" t="inlineStr">
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B81" s="17" t="inlineStr">
         <is>
           <t>POWERINDIA</t>
         </is>
       </c>
-      <c r="C73" s="14" t="n">
-        <v>30170</v>
-      </c>
-      <c r="D73" s="14" t="n">
-        <v>27322.86</v>
-      </c>
-      <c r="E73" s="14" t="n">
-        <v>25094.78</v>
-      </c>
-      <c r="F73" s="14" t="n">
-        <v>20992.78</v>
-      </c>
-      <c r="G73" s="15">
+      <c r="C81" s="18" t="n">
+        <v>30335</v>
+      </c>
+      <c r="D81" s="18" t="n">
+        <v>27338.58</v>
+      </c>
+      <c r="E81" s="18" t="n">
+        <v>25101.25</v>
+      </c>
+      <c r="F81" s="18" t="n">
+        <v>20994.42</v>
+      </c>
+      <c r="G81" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
-        <is>
-          <t>SCHNEIDER</t>
-        </is>
-      </c>
-      <c r="C74" s="14" t="n">
-        <v>1089</v>
-      </c>
-      <c r="D74" s="14" t="n">
-        <v>980.34</v>
-      </c>
-      <c r="E74" s="14" t="n">
-        <v>905.89</v>
-      </c>
-      <c r="F74" s="14" t="n">
-        <v>810.45</v>
-      </c>
-      <c r="G74" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B75" s="13" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="n">
-        <v>3840.5</v>
-      </c>
-      <c r="D75" s="14" t="n">
-        <v>3408.56</v>
-      </c>
-      <c r="E75" s="14" t="n">
-        <v>3272.56</v>
-      </c>
-      <c r="F75" s="14" t="n">
-        <v>3156.54</v>
-      </c>
-      <c r="G75" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="C76" s="14" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="D76" s="14" t="n">
-        <v>46.94</v>
-      </c>
-      <c r="E76" s="14" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="F76" s="14" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="G76" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="n">
-        <v>439.85</v>
-      </c>
-      <c r="D77" s="14" t="n">
-        <v>409.24</v>
-      </c>
-      <c r="E77" s="14" t="n">
-        <v>394.5</v>
-      </c>
-      <c r="F77" s="14" t="n">
-        <v>387.02</v>
-      </c>
-      <c r="G77" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C78" s="14" t="n">
-        <v>4125</v>
-      </c>
-      <c r="D78" s="14" t="n">
-        <v>3698.85</v>
-      </c>
-      <c r="E78" s="14" t="n">
-        <v>3396.08</v>
-      </c>
-      <c r="F78" s="14" t="n">
-        <v>3234.63</v>
-      </c>
-      <c r="G78" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="n">
-        <v>1655.1</v>
-      </c>
-      <c r="D79" s="14" t="n">
-        <v>1497.05</v>
-      </c>
-      <c r="E79" s="14" t="n">
-        <v>1451.83</v>
-      </c>
-      <c r="F79" s="14" t="n">
-        <v>1394.27</v>
-      </c>
-      <c r="G79" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C80" s="14" t="n">
-        <v>573.85</v>
-      </c>
-      <c r="D80" s="14" t="n">
-        <v>495.25</v>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v>486.58</v>
-      </c>
-      <c r="F80" s="14" t="n">
-        <v>510.21</v>
-      </c>
-      <c r="G80" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="C81" s="18" t="n">
-        <v>1369.5</v>
-      </c>
-      <c r="D81" s="18" t="n">
-        <v>1312.23</v>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>1297.14</v>
-      </c>
-      <c r="F81" s="18" t="n">
-        <v>1252.59</v>
-      </c>
-      <c r="G81" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>2766.9</v>
+        <v>1111.7</v>
       </c>
       <c r="D82" s="18" t="n">
-        <v>2587.16</v>
+        <v>982.51</v>
       </c>
       <c r="E82" s="18" t="n">
-        <v>2563.98</v>
+        <v>906.78</v>
       </c>
       <c r="F82" s="18" t="n">
-        <v>2585.63</v>
+        <v>810.6799999999999</v>
       </c>
       <c r="G82" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>1368.6</v>
+        <v>3844.3</v>
       </c>
       <c r="D83" s="18" t="n">
-        <v>1317.33</v>
+        <v>3408.92</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>1322.86</v>
+        <v>3272.71</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>1365.47</v>
+        <v>3156.57</v>
       </c>
       <c r="G83" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>557.9</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>527.74</v>
+        <v>73.22</v>
       </c>
       <c r="E84" s="18" t="n">
-        <v>521.55</v>
+        <v>72.47</v>
       </c>
       <c r="F84" s="18" t="n">
-        <v>544.25</v>
+        <v>79.92</v>
       </c>
       <c r="G84" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SJVN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C85" s="18" t="n">
-        <v>2785</v>
+        <v>54.57</v>
       </c>
       <c r="D85" s="18" t="n">
-        <v>2675.61</v>
+        <v>47.06</v>
       </c>
       <c r="E85" s="18" t="n">
-        <v>2540.64</v>
+        <v>45.78</v>
       </c>
       <c r="F85" s="18" t="n">
-        <v>2102.6</v>
+        <v>51.36</v>
       </c>
       <c r="G85" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>3586.5</v>
+        <v>436.05</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>3446.2</v>
+        <v>408.88</v>
       </c>
       <c r="E86" s="18" t="n">
-        <v>3447.2</v>
+        <v>394.35</v>
       </c>
       <c r="F86" s="18" t="n">
-        <v>3254.34</v>
+        <v>386.98</v>
       </c>
       <c r="G86" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>472.85</v>
+        <v>4053.1</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>435.92</v>
+        <v>3692.01</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>414.84</v>
+        <v>3393.26</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>394.62</v>
+        <v>3233.92</v>
       </c>
       <c r="G87" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C88" s="18" t="n">
-        <v>383.85</v>
+        <v>1657.4</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>352.88</v>
+        <v>1497.26</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>346.77</v>
+        <v>1451.92</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>358.84</v>
+        <v>1394.3</v>
       </c>
       <c r="G88" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C89" s="18" t="n">
-        <v>1030</v>
+        <v>570.9</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>999.98</v>
+        <v>494.97</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>991.22</v>
+        <v>486.47</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>872.86</v>
+        <v>510.18</v>
       </c>
       <c r="G89" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C90" s="14" t="n">
-        <v>627.35</v>
+        <v>1379.6</v>
       </c>
       <c r="D90" s="14" t="n">
-        <v>572.6799999999999</v>
+        <v>1313.2</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>553.14</v>
+        <v>1297.54</v>
       </c>
       <c r="F90" s="14" t="n">
-        <v>578.66</v>
+        <v>1252.69</v>
       </c>
       <c r="G90" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="C91" s="14" t="n">
-        <v>284.45</v>
+        <v>2766.4</v>
       </c>
       <c r="D91" s="14" t="n">
-        <v>281.63</v>
+        <v>2587.11</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>273.08</v>
+        <v>2563.96</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>250.98</v>
+        <v>2585.63</v>
       </c>
       <c r="G91" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="n">
-        <v>99.58</v>
-      </c>
-      <c r="D92" s="18" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>76.58</v>
-      </c>
-      <c r="F92" s="18" t="n">
-        <v>74.45999999999999</v>
-      </c>
-      <c r="G92" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="n">
+        <v>1367.6</v>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>1317.23</v>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v>1322.82</v>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>1365.46</v>
+      </c>
+      <c r="G92" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C93" s="18" t="n">
-        <v>8040</v>
-      </c>
-      <c r="D93" s="18" t="n">
-        <v>7377.64</v>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>7209.26</v>
-      </c>
-      <c r="F93" s="18" t="n">
-        <v>7703.18</v>
-      </c>
-      <c r="G93" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="n">
+        <v>559.05</v>
+      </c>
+      <c r="D93" s="14" t="n">
+        <v>527.85</v>
+      </c>
+      <c r="E93" s="14" t="n">
+        <v>521.59</v>
+      </c>
+      <c r="F93" s="14" t="n">
+        <v>544.26</v>
+      </c>
+      <c r="G93" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C94" s="14" t="n">
-        <v>1044.85</v>
+        <v>2783.2</v>
       </c>
       <c r="D94" s="14" t="n">
-        <v>963</v>
+        <v>2675.44</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>951.9299999999999</v>
+        <v>2540.57</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>883.11</v>
+        <v>2102.58</v>
       </c>
       <c r="G94" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C95" s="14" t="n">
-        <v>297.05</v>
+        <v>3586.9</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>283.64</v>
+        <v>3446.24</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>278.7</v>
+        <v>3447.21</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>251.02</v>
+        <v>3254.35</v>
       </c>
       <c r="G95" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="16" t="inlineStr">
         <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="n">
+        <v>470.3</v>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>435.67</v>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v>414.74</v>
+      </c>
+      <c r="F96" s="14" t="n">
+        <v>394.59</v>
+      </c>
+      <c r="G96" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="n">
+        <v>383.35</v>
+      </c>
+      <c r="D97" s="14" t="n">
+        <v>352.83</v>
+      </c>
+      <c r="E97" s="14" t="n">
+        <v>346.75</v>
+      </c>
+      <c r="F97" s="14" t="n">
+        <v>358.84</v>
+      </c>
+      <c r="G97" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="n">
+        <v>1044.55</v>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>1001.36</v>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v>991.8</v>
+      </c>
+      <c r="F98" s="14" t="n">
+        <v>873</v>
+      </c>
+      <c r="G98" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="n">
+        <v>100.37</v>
+      </c>
+      <c r="D99" s="18" t="n">
+        <v>83.77</v>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>76.61</v>
+      </c>
+      <c r="F99" s="18" t="n">
+        <v>74.47</v>
+      </c>
+      <c r="G99" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="n">
+        <v>8126.5</v>
+      </c>
+      <c r="D100" s="18" t="n">
+        <v>7385.88</v>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>7212.65</v>
+      </c>
+      <c r="F100" s="18" t="n">
+        <v>7704.04</v>
+      </c>
+      <c r="G100" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B96" s="13" t="inlineStr">
+      <c r="B101" s="13" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="n">
+        <v>1043.2</v>
+      </c>
+      <c r="D101" s="14" t="n">
+        <v>962.84</v>
+      </c>
+      <c r="E101" s="14" t="n">
+        <v>951.86</v>
+      </c>
+      <c r="F101" s="14" t="n">
+        <v>883.1</v>
+      </c>
+      <c r="G101" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="n">
+        <v>296.45</v>
+      </c>
+      <c r="D102" s="14" t="n">
+        <v>283.59</v>
+      </c>
+      <c r="E102" s="14" t="n">
+        <v>278.67</v>
+      </c>
+      <c r="F102" s="14" t="n">
+        <v>251.02</v>
+      </c>
+      <c r="G102" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="C96" s="14" t="n">
-        <v>858</v>
-      </c>
-      <c r="D96" s="14" t="n">
-        <v>835.41</v>
-      </c>
-      <c r="E96" s="14" t="n">
-        <v>851.53</v>
-      </c>
-      <c r="F96" s="14" t="n">
-        <v>841.39</v>
-      </c>
-      <c r="G96" s="15">
+      <c r="C103" s="14" t="n">
+        <v>870.1</v>
+      </c>
+      <c r="D103" s="14" t="n">
+        <v>836.5599999999999</v>
+      </c>
+      <c r="E103" s="14" t="n">
+        <v>852</v>
+      </c>
+      <c r="F103" s="14" t="n">
+        <v>841.51</v>
+      </c>
+      <c r="G103" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 22-Apr-2026  16:57</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 23-Apr-2026  18:13</t>
         </is>
       </c>
     </row>
@@ -672,84 +672,84 @@
         <v>15</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>15</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1</v>
+        <v>0.9553</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.917</v>
+        <v>1</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.8613</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.7667</v>
@@ -765,7 +765,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>13</v>
@@ -774,7 +774,7 @@
         <v>7</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.9329999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.867</v>
@@ -783,7 +783,7 @@
         <v>0.467</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.7556999999999999</v>
+        <v>0.7337</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -820,32 +820,32 @@
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.867</v>
+        <v>0.75</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.667</v>
+        <v>0.583</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.6890000000000001</v>
+        <v>0.6386999999999999</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -861,7 +861,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>2</v>
@@ -870,137 +870,137 @@
         <v>0.9</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.6333</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.9329999999999999</v>
+        <v>0.625</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.733</v>
+        <v>0.625</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.267</v>
+        <v>0.575</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.55</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G12" s="6" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I12" s="7" t="n">
         <v>0.6</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0.6167</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.6083</v>
+        <v>0.4833</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.75</v>
+        <v>0.467</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.45</v>
+        <v>0.467</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.6</v>
+        <v>0.4447</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1013,25 +1013,25 @@
         <v>20</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.15</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.4333</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1075,25 +1075,25 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.2</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2260.8</v>
+        <v>2300</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2085.12</v>
+        <v>2105.58</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2075.27</v>
+        <v>2084.09</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2237.38</v>
+        <v>2238.67</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>2121.9</v>
+        <v>1041.35</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>2043.28</v>
+        <v>982.4299999999999</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>2034.48</v>
+        <v>949.16</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1892.85</v>
+        <v>847.2</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1039.9</v>
+        <v>549.45</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>976.22</v>
+        <v>533.55</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>945.4</v>
+        <v>527.26</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>844.5</v>
+        <v>429.67</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>556.95</v>
+        <v>592.1</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>531.88</v>
+        <v>568.96</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>526.35</v>
+        <v>570.75</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>428.4</v>
+        <v>536.3099999999999</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>604.75</v>
+        <v>1254.5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>566.52</v>
+        <v>1218.74</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>569.87</v>
+        <v>1182.7</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>535.48</v>
+        <v>1084.32</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1278.6</v>
+        <v>775.8</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1214.98</v>
+        <v>762.25</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1179.77</v>
+        <v>758.97</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1082.25</v>
+        <v>741.84</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>784.5</v>
+        <v>1257</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>760.8200000000001</v>
+        <v>1214.28</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>758.28</v>
+        <v>1199.59</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>741.97</v>
+        <v>1149.75</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>1263.4</v>
+        <v>439.25</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>1209.79</v>
+        <v>412.88</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>1197.25</v>
+        <v>387.64</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1149.09</v>
+        <v>300.61</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>435.95</v>
+        <v>87.31</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>410.11</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>385.53</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>298.96</v>
+        <v>76.16</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>88.59</v>
+        <v>2459.8</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>84.25</v>
+        <v>2356.66</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>81.59999999999999</v>
+        <v>2319.66</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>76.03</v>
+        <v>2385.37</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,23 +1509,23 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>2454.3</v>
+        <v>176.45</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>2345.8</v>
+        <v>165.83</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>2313.94</v>
+        <v>159.21</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>2385.78</v>
+        <v>143.64</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,23 +1537,23 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>176.23</v>
+        <v>210.91</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>164.71</v>
+        <v>205.11</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>158.51</v>
+        <v>199.75</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>143.25</v>
+        <v>181.12</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>213.03</v>
+        <v>735.6</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>204.5</v>
+        <v>731.39</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>199.29</v>
+        <v>697.89</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>180.57</v>
+        <v>581.3</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VEDL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,751 +1593,751 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>757</v>
+        <v>1204.1</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>730.9400000000001</v>
+        <v>992.76</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>696.35</v>
+        <v>901.53</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>579.34</v>
+        <v>847.21</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VEDL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>1139.2</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>970.51</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>889.1799999999999</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>844.34</v>
-      </c>
-      <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>DISHTV</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="G17" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DISHTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>282.77</v>
+        <v>272.16</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>276.72</v>
+        <v>256.55</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>282.11</v>
+        <v>255.05</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>275.38</v>
+        <v>266.3</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BANKBARODA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>152.92</v>
+        <v>625.85</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>148.37</v>
+        <v>616.3</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>151.49</v>
+        <v>597.91</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>141.6</v>
+        <v>582.0700000000001</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BANKINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>145.23</v>
+        <v>647.7</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>139.25</v>
+        <v>561.21</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>141.08</v>
+        <v>543.97</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>133.92</v>
+        <v>555.99</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANBK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>CENTRALBK</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>36.93</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>35.38</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>36.78</v>
-      </c>
-      <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTRALBK","Chart 📈")</f>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>5520.5</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>5473.21</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>5470.67</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>5423.4</v>
+      </c>
+      <c r="G21" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="n">
-        <v>925.35</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>921.66</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>906.78</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>812.11</v>
-      </c>
-      <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1435.4</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1353.35</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>1293.59</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>1211.17</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>79.76000000000001</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>70.93000000000001</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>68.02</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>61.13</v>
-      </c>
-      <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>6378.5</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>6157.11</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>6167.28</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>6240.12</v>
+      </c>
+      <c r="G23" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>1103.3</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>1073.62</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>1075.81</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>985.6</v>
-      </c>
-      <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>1331</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>1244.99</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>1253.31</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>1248.7</v>
+      </c>
+      <c r="G24" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>194.05</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>184.45</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>180.75</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>161.16</v>
-      </c>
-      <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>1795.4</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>1745.87</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>1739.1</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>1748.08</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>271.56</v>
+        <v>2335</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>254.91</v>
+        <v>2200.79</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>254.36</v>
+        <v>2138.74</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>266.19</v>
+        <v>1966.87</v>
       </c>
       <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>652.45</v>
+        <v>686.95</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>615.29</v>
+        <v>641.3200000000001</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>596.77</v>
+        <v>614.2</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>581.33</v>
+        <v>565.41</v>
       </c>
       <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>599.6</v>
+        <v>1526.1</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>552.1</v>
+        <v>1490.03</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>539.73</v>
+        <v>1490.49</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>557.28</v>
+        <v>1449.33</v>
       </c>
       <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>JBCHEPHARM</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>2011.5</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>2005.13</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>1994.22</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>1844.78</v>
+      </c>
+      <c r="G29" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>1129</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>1081.59</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>1050.83</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>954.28</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>2341.4</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>2313.78</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>2279.79</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>2144.22</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>2292.9</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>2123.1</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>2117.09</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>2254.23</v>
+      </c>
+      <c r="G32" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1071.45</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>1053.36</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>996.4299999999999</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>914.22</v>
+      </c>
+      <c r="G33" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>946.35</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>915.5700000000001</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>908.42</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>920.6</v>
+      </c>
+      <c r="G34" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n">
-        <v>7803.5</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>7283.85</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>7104.62</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>7065.54</v>
-      </c>
-      <c r="G29" s="19">
+      <c r="C35" s="18" t="n">
+        <v>7795</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>7332.53</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>7131.7</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>7070.39</v>
+      </c>
+      <c r="G35" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>BLUESTARCO</t>
         </is>
       </c>
-      <c r="C30" s="18" t="n">
-        <v>1888.6</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>1772.06</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>1788.9</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>1827.26</v>
-      </c>
-      <c r="G30" s="19">
+      <c r="C36" s="18" t="n">
+        <v>1829.8</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>1777.56</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>1790.5</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>1817.64</v>
+      </c>
+      <c r="G36" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>CENTURYPLY</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n">
-        <v>777.9</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>733.4400000000001</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>732.86</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>753.9299999999999</v>
-      </c>
-      <c r="G31" s="19">
+      <c r="C37" s="18" t="n">
+        <v>787.2</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>738.5599999999999</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>734.99</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>753.52</v>
+      </c>
+      <c r="G37" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>CERA</t>
         </is>
       </c>
-      <c r="C32" s="18" t="n">
-        <v>5488.9</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>5078.61</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>5009.25</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>5443.43</v>
-      </c>
-      <c r="G32" s="19">
+      <c r="C38" s="18" t="n">
+        <v>5469.8</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>5115.86</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>5027.3</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>5434.57</v>
+      </c>
+      <c r="G38" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>KAJARIACER</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n">
-        <v>1202.7</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>1084.09</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>1023.53</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>1024.52</v>
-      </c>
-      <c r="G33" s="19">
+      <c r="C39" s="18" t="n">
+        <v>1191.9</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>1094.36</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>1030.13</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>1026.02</v>
+      </c>
+      <c r="G39" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="C34" s="18" t="n">
-        <v>4454.6</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>4344.85</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>4231.77</v>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>3923.33</v>
-      </c>
-      <c r="G34" s="19">
+      <c r="C40" s="18" t="n">
+        <v>4456.5</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>4355.48</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>4240.59</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>3930.28</v>
+      </c>
+      <c r="G40" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>VOLTAS</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n">
-        <v>1481.6</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>1379.49</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>1390.35</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>1383.03</v>
-      </c>
-      <c r="G35" s="19">
+      <c r="C41" s="18" t="n">
+        <v>1445.5</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>1385.78</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>1392.51</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>1379.9</v>
+      </c>
+      <c r="G41" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>BALRAMCHIN</t>
         </is>
       </c>
-      <c r="C36" s="14" t="n">
-        <v>541.55</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>493.47</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>479.74</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>489.13</v>
-      </c>
-      <c r="G36" s="15">
+      <c r="C42" s="14" t="n">
+        <v>540.3</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>497.93</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>482.12</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>489.48</v>
+      </c>
+      <c r="G42" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>2368.8</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>2189.01</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>2218.26</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>2332.44</v>
-      </c>
-      <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>772.5</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>756.52</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>757</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>739.9400000000001</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n">
-        <v>1395.8</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>1264.01</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>1254.68</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>1238.35</v>
-      </c>
-      <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>3243</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>2924.74</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>2852.01</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>2864.56</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>1178.6</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>1097.96</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>1105.24</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>1126.34</v>
-      </c>
-      <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>UNITDSPR</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>1392.8</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>1296.69</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>1318.52</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>1373.77</v>
-      </c>
-      <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2349,247 +2349,247 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>2366.4</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>2205.9</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>2224.07</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>2334.82</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>778.9</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>758.65</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>757.86</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>740.9400000000001</v>
+      </c>
+      <c r="G44" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>1410.5</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>1277.96</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>1260.79</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>1241.13</v>
+      </c>
+      <c r="G45" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>3199.2</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>2950.88</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>2865.62</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>2866.12</v>
+      </c>
+      <c r="G46" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>1184.4</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>1106.2</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>1108.34</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>1128.02</v>
+      </c>
+      <c r="G47" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>1382.3</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>1304.84</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>1321.02</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>1375.74</v>
+      </c>
+      <c r="G48" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
           <t>VBL</t>
         </is>
       </c>
-      <c r="C43" s="14" t="n">
-        <v>494.95</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>441.25</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>439.08</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>465.29</v>
-      </c>
-      <c r="G43" s="15">
+      <c r="C49" s="14" t="n">
+        <v>484.25</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>445.35</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>440.85</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>465.45</v>
+      </c>
+      <c r="G49" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>ASHOKLEY</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>178.97</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>172.98</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>177.8</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>161.25</v>
-      </c>
-      <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ASHOKLEY","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>9602</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>9497.559999999999</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>9431.549999999999</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>9081.889999999999</v>
-      </c>
-      <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>1903.2</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>1798.04</v>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>1731.43</v>
-      </c>
-      <c r="F46" s="18" t="n">
-        <v>1485.95</v>
-      </c>
-      <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>37885</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>35311.22</v>
-      </c>
-      <c r="E47" s="18" t="n">
-        <v>34622.59</v>
-      </c>
-      <c r="F47" s="18" t="n">
-        <v>34987.02</v>
-      </c>
-      <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="n">
-        <v>7230</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>7102.17</v>
-      </c>
-      <c r="E48" s="18" t="n">
-        <v>7178.32</v>
-      </c>
-      <c r="F48" s="18" t="n">
-        <v>6865.56</v>
-      </c>
-      <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>EXIDEIND</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="n">
-        <v>354.55</v>
-      </c>
-      <c r="D49" s="18" t="n">
-        <v>321.36</v>
-      </c>
-      <c r="E49" s="18" t="n">
-        <v>322.89</v>
-      </c>
-      <c r="F49" s="18" t="n">
-        <v>352.6</v>
-      </c>
-      <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>131.76</v>
+        <v>77.31</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>119.75</v>
+        <v>71.53</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>118.83</v>
+        <v>68.39</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>111.68</v>
+        <v>61.32</v>
       </c>
       <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>3660.7</v>
+        <v>1094.25</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>3655.18</v>
+        <v>1075.58</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>3642.31</v>
+        <v>1076.53</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>3458.83</v>
+        <v>985.95</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2605,16 +2605,16 @@
         </is>
       </c>
       <c r="C52" s="14" t="n">
-        <v>1733.6</v>
+        <v>1707.7</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>1620.63</v>
+        <v>1628.93</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>1573.2</v>
+        <v>1578.47</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>1617.91</v>
+        <v>1619.32</v>
       </c>
       <c r="G52" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
@@ -2633,16 +2633,16 @@
         </is>
       </c>
       <c r="C53" s="14" t="n">
-        <v>1809.4</v>
+        <v>1785.3</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>1700.02</v>
+        <v>1708.14</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>1680.47</v>
+        <v>1684.58</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>1677.06</v>
+        <v>1677.45</v>
       </c>
       <c r="G53" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
@@ -2652,392 +2652,392 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>629.1</v>
+        <v>7575.5</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>572.84</v>
+        <v>6791.72</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>553.21</v>
+        <v>6320.04</v>
       </c>
       <c r="F54" s="18" t="n">
-        <v>578.67</v>
+        <v>5711.61</v>
       </c>
       <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C55" s="18" t="n">
-        <v>166.12</v>
+        <v>1361.25</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>153.55</v>
+        <v>1157.4</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>154.47</v>
+        <v>1069.88</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>165.25</v>
+        <v>977.75</v>
       </c>
       <c r="G55" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C56" s="18" t="n">
-        <v>283.65</v>
+        <v>1214.15</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>281.56</v>
+        <v>1048.81</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>273.05</v>
+        <v>982.8099999999999</v>
       </c>
       <c r="F56" s="18" t="n">
-        <v>250.97</v>
+        <v>976.98</v>
       </c>
       <c r="G56" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>ALKEM</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="n">
-        <v>5627</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>5468.23</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>5468.63</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>5404.04</v>
-      </c>
-      <c r="G57" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>214.18</v>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>181.82</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>164.31</v>
+      </c>
+      <c r="F57" s="18" t="n">
+        <v>144.84</v>
+      </c>
+      <c r="G57" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>1421.2</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>1344.71</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>1287.8</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>1203.94</v>
-      </c>
-      <c r="G58" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>337.6</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>293.67</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>276.83</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>261.14</v>
+      </c>
+      <c r="G58" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n">
-        <v>6285.5</v>
-      </c>
-      <c r="D59" s="14" t="n">
-        <v>6133.81</v>
-      </c>
-      <c r="E59" s="14" t="n">
-        <v>6158.66</v>
-      </c>
-      <c r="F59" s="14" t="n">
-        <v>6237.65</v>
-      </c>
-      <c r="G59" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>180.18</v>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>165.48</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>160.29</v>
+      </c>
+      <c r="F59" s="18" t="n">
+        <v>160.67</v>
+      </c>
+      <c r="G59" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="n">
-        <v>1800.6</v>
-      </c>
-      <c r="D60" s="14" t="n">
-        <v>1740.66</v>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v>1736.8</v>
-      </c>
-      <c r="F60" s="14" t="n">
-        <v>1745.27</v>
-      </c>
-      <c r="G60" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>837.8</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>748.9299999999999</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>713.66</v>
+      </c>
+      <c r="F60" s="18" t="n">
+        <v>688.87</v>
+      </c>
+      <c r="G60" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>GLENMARK</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="n">
-        <v>2240</v>
-      </c>
-      <c r="D61" s="14" t="n">
-        <v>2186.67</v>
-      </c>
-      <c r="E61" s="14" t="n">
-        <v>2130.72</v>
-      </c>
-      <c r="F61" s="14" t="n">
-        <v>1961.36</v>
-      </c>
-      <c r="G61" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>450.65</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>444.8</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>406.42</v>
+      </c>
+      <c r="G61" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
-        <v>672.75</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>636.52</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>611.23</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>563.78</v>
-      </c>
-      <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>4496.4</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>4017.25</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>3766.78</v>
+      </c>
+      <c r="F62" s="18" t="n">
+        <v>3112.31</v>
+      </c>
+      <c r="G62" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>IPCALAB</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n">
-        <v>1494.8</v>
-      </c>
-      <c r="D63" s="14" t="n">
-        <v>1486.23</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>1489.03</v>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>1446.25</v>
-      </c>
-      <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>JPPOWER</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="F63" s="18" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="G63" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>1096.1</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>1076.6</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>1047.64</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>952.61</v>
-      </c>
-      <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>561.4</v>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>520.25</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>503.9</v>
+      </c>
+      <c r="F64" s="18" t="n">
+        <v>501.39</v>
+      </c>
+      <c r="G64" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>NATCOPHARM</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="n">
-        <v>1071</v>
-      </c>
-      <c r="D65" s="14" t="n">
-        <v>1051.45</v>
-      </c>
-      <c r="E65" s="14" t="n">
-        <v>993.37</v>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>912.21</v>
-      </c>
-      <c r="G65" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>81.45999999999999</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="F65" s="18" t="n">
+        <v>79.47</v>
+      </c>
+      <c r="G65" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="n">
-        <v>929.9</v>
-      </c>
-      <c r="D66" s="14" t="n">
-        <v>912.33</v>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>906.87</v>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>919.0700000000001</v>
-      </c>
-      <c r="G66" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>296.9</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>282.39</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>270.38</v>
+      </c>
+      <c r="F66" s="18" t="n">
+        <v>254.58</v>
+      </c>
+      <c r="G66" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C67" s="18" t="n">
-        <v>7587</v>
+        <v>402.25</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>6709.21</v>
+        <v>386.52</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>6268.8</v>
+        <v>375.59</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>5690.34</v>
+        <v>352.15</v>
       </c>
       <c r="G67" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3049,23 +3049,23 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C68" s="18" t="n">
-        <v>1368.1</v>
+        <v>319.15</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>1135.94</v>
+        <v>307.44</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>1057.99</v>
+        <v>297.86</v>
       </c>
       <c r="F68" s="18" t="n">
-        <v>973.11</v>
+        <v>285.79</v>
       </c>
       <c r="G68" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3077,23 +3077,23 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C69" s="18" t="n">
-        <v>1198.95</v>
+        <v>31720</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>1031.41</v>
+        <v>27755.86</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>973.37</v>
+        <v>25360.81</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>973.8200000000001</v>
+        <v>21110.09</v>
       </c>
       <c r="G69" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C70" s="18" t="n">
-        <v>215.65</v>
+        <v>1127</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>178.42</v>
+        <v>996.27</v>
       </c>
       <c r="E70" s="18" t="n">
-        <v>162.28</v>
+        <v>915.42</v>
       </c>
       <c r="F70" s="18" t="n">
-        <v>144.04</v>
+        <v>813.78</v>
       </c>
       <c r="G70" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3133,23 +3133,23 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C71" s="18" t="n">
-        <v>333.64</v>
+        <v>3864.4</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>289.05</v>
+        <v>3452.3</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>274.35</v>
+        <v>3295.92</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>260.19</v>
+        <v>3164.92</v>
       </c>
       <c r="G71" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3161,23 +3161,23 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C72" s="18" t="n">
-        <v>180.27</v>
+        <v>53.73</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>163.94</v>
+        <v>47.69</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>159.48</v>
+        <v>46.09</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>160.39</v>
+        <v>51.45</v>
       </c>
       <c r="G72" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C73" s="18" t="n">
-        <v>824.35</v>
+        <v>430.3</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>739.5700000000001</v>
+        <v>410.92</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>708.59</v>
+        <v>395.76</v>
       </c>
       <c r="F73" s="18" t="n">
-        <v>686.13</v>
+        <v>387.89</v>
       </c>
       <c r="G73" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3217,23 +3217,23 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C74" s="18" t="n">
-        <v>4239.4</v>
+        <v>4059.7</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>3966.82</v>
+        <v>3727.03</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>3737</v>
+        <v>3419.4</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>3096.83</v>
+        <v>3242.19</v>
       </c>
       <c r="G74" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3245,23 +3245,23 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C75" s="18" t="n">
-        <v>20.13</v>
+        <v>1737</v>
       </c>
       <c r="D75" s="18" t="n">
-        <v>17.25</v>
+        <v>1520.1</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>16.24</v>
+        <v>1463.1</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>16.77</v>
+        <v>1399.35</v>
       </c>
       <c r="G75" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3273,778 +3273,582 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C76" s="18" t="n">
-        <v>560.55</v>
+        <v>579</v>
       </c>
       <c r="D76" s="18" t="n">
-        <v>515.92</v>
+        <v>502.97</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>501.55</v>
+        <v>490.1</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>500.82</v>
+        <v>511.82</v>
       </c>
       <c r="G76" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>NHPC</t>
-        </is>
-      </c>
-      <c r="C77" s="18" t="n">
-        <v>82.63</v>
-      </c>
-      <c r="D77" s="18" t="n">
-        <v>78.97</v>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>77.48999999999999</v>
-      </c>
-      <c r="F77" s="18" t="n">
-        <v>79.41</v>
-      </c>
-      <c r="G77" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="n">
+        <v>621.7</v>
+      </c>
+      <c r="D77" s="14" t="n">
+        <v>577.5</v>
+      </c>
+      <c r="E77" s="14" t="n">
+        <v>555.89</v>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>579.5700000000001</v>
+      </c>
+      <c r="G77" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>NLCINDIA</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="n">
-        <v>301.15</v>
-      </c>
-      <c r="D78" s="18" t="n">
-        <v>280.86</v>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>269.3</v>
-      </c>
-      <c r="F78" s="18" t="n">
-        <v>254.27</v>
-      </c>
-      <c r="G78" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="n">
+        <v>473.9</v>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>470.97</v>
+      </c>
+      <c r="E78" s="14" t="n">
+        <v>467.27</v>
+      </c>
+      <c r="F78" s="14" t="n">
+        <v>438.5</v>
+      </c>
+      <c r="G78" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="n">
-        <v>405.4</v>
-      </c>
-      <c r="D79" s="18" t="n">
-        <v>384.86</v>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>374.51</v>
-      </c>
-      <c r="F79" s="18" t="n">
-        <v>351.35</v>
-      </c>
-      <c r="G79" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>282</v>
+      </c>
+      <c r="E79" s="14" t="n">
+        <v>273.56</v>
+      </c>
+      <c r="F79" s="14" t="n">
+        <v>251.67</v>
+      </c>
+      <c r="G79" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C80" s="18" t="n">
-        <v>319.75</v>
+        <v>1369.6</v>
       </c>
       <c r="D80" s="18" t="n">
-        <v>306.21</v>
+        <v>1318.57</v>
       </c>
       <c r="E80" s="18" t="n">
-        <v>296.99</v>
+        <v>1300.36</v>
       </c>
       <c r="F80" s="18" t="n">
-        <v>285.26</v>
+        <v>1253.04</v>
       </c>
       <c r="G80" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>30335</v>
+        <v>2708.2</v>
       </c>
       <c r="D81" s="18" t="n">
-        <v>27338.58</v>
+        <v>2598.64</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>25101.25</v>
+        <v>2569.62</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>20994.42</v>
+        <v>2588.88</v>
       </c>
       <c r="G81" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C82" s="18" t="n">
-        <v>1111.7</v>
+        <v>545.55</v>
       </c>
       <c r="D82" s="18" t="n">
-        <v>982.51</v>
+        <v>529.53</v>
       </c>
       <c r="E82" s="18" t="n">
-        <v>906.78</v>
+        <v>522.53</v>
       </c>
       <c r="F82" s="18" t="n">
-        <v>810.6799999999999</v>
+        <v>544.66</v>
       </c>
       <c r="G82" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C83" s="18" t="n">
-        <v>3844.3</v>
+        <v>2791.4</v>
       </c>
       <c r="D83" s="18" t="n">
-        <v>3408.92</v>
+        <v>2686.49</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>3272.71</v>
+        <v>2550.41</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>3156.57</v>
+        <v>2112.09</v>
       </c>
       <c r="G83" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C84" s="18" t="n">
-        <v>80.84999999999999</v>
+        <v>3561.4</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>73.22</v>
+        <v>3457.21</v>
       </c>
       <c r="E84" s="18" t="n">
-        <v>72.47</v>
+        <v>3451.69</v>
       </c>
       <c r="F84" s="18" t="n">
-        <v>79.92</v>
+        <v>3250.8</v>
       </c>
       <c r="G84" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SJVN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C85" s="18" t="n">
-        <v>54.57</v>
+        <v>469.8</v>
       </c>
       <c r="D85" s="18" t="n">
-        <v>47.06</v>
+        <v>438.92</v>
       </c>
       <c r="E85" s="18" t="n">
-        <v>45.78</v>
+        <v>416.9</v>
       </c>
       <c r="F85" s="18" t="n">
-        <v>51.36</v>
+        <v>394.94</v>
       </c>
       <c r="G85" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>436.05</v>
+        <v>376.45</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>408.88</v>
+        <v>355.08</v>
       </c>
       <c r="E86" s="18" t="n">
-        <v>394.35</v>
+        <v>347.92</v>
       </c>
       <c r="F86" s="18" t="n">
-        <v>386.98</v>
+        <v>359.05</v>
       </c>
       <c r="G86" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>4053.1</v>
+        <v>1009.3</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>3692.01</v>
+        <v>1002.12</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>3393.26</v>
+        <v>992.48</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>3233.92</v>
+        <v>874.39</v>
       </c>
       <c r="G87" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="C88" s="18" t="n">
-        <v>1657.4</v>
-      </c>
-      <c r="D88" s="18" t="n">
-        <v>1497.26</v>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>1451.92</v>
-      </c>
-      <c r="F88" s="18" t="n">
-        <v>1394.3</v>
-      </c>
-      <c r="G88" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="n">
+        <v>9550.5</v>
+      </c>
+      <c r="D88" s="14" t="n">
+        <v>9502.610000000001</v>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v>9436.219999999999</v>
+      </c>
+      <c r="F88" s="14" t="n">
+        <v>9096.299999999999</v>
+      </c>
+      <c r="G88" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="n">
-        <v>570.9</v>
-      </c>
-      <c r="D89" s="18" t="n">
-        <v>494.97</v>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>486.47</v>
-      </c>
-      <c r="F89" s="18" t="n">
-        <v>510.18</v>
-      </c>
-      <c r="G89" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="n">
+        <v>1874.1</v>
+      </c>
+      <c r="D89" s="14" t="n">
+        <v>1805.28</v>
+      </c>
+      <c r="E89" s="14" t="n">
+        <v>1737.02</v>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>1492.47</v>
+      </c>
+      <c r="G89" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C90" s="14" t="n">
-        <v>1379.6</v>
+        <v>37380</v>
       </c>
       <c r="D90" s="14" t="n">
-        <v>1313.2</v>
+        <v>35508.25</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>1297.54</v>
+        <v>34730.74</v>
       </c>
       <c r="F90" s="14" t="n">
-        <v>1252.69</v>
+        <v>35043.14</v>
       </c>
       <c r="G90" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C91" s="14" t="n">
-        <v>2766.4</v>
+        <v>127.22</v>
       </c>
       <c r="D91" s="14" t="n">
-        <v>2587.11</v>
+        <v>120.46</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>2563.96</v>
+        <v>119.16</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>2585.63</v>
+        <v>111.97</v>
       </c>
       <c r="G91" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="n">
-        <v>1367.6</v>
-      </c>
-      <c r="D92" s="14" t="n">
-        <v>1317.23</v>
-      </c>
-      <c r="E92" s="14" t="n">
-        <v>1322.82</v>
-      </c>
-      <c r="F92" s="14" t="n">
-        <v>1365.46</v>
-      </c>
-      <c r="G92" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="D92" s="18" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>77.44</v>
+      </c>
+      <c r="F92" s="18" t="n">
+        <v>74.70999999999999</v>
+      </c>
+      <c r="G92" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B93" s="13" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="n">
-        <v>559.05</v>
-      </c>
-      <c r="D93" s="14" t="n">
-        <v>527.85</v>
-      </c>
-      <c r="E93" s="14" t="n">
-        <v>521.59</v>
-      </c>
-      <c r="F93" s="14" t="n">
-        <v>544.26</v>
-      </c>
-      <c r="G93" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>8791.5</v>
+      </c>
+      <c r="D93" s="18" t="n">
+        <v>7519.75</v>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>7274.59</v>
+      </c>
+      <c r="F93" s="18" t="n">
+        <v>7749.23</v>
+      </c>
+      <c r="G93" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C94" s="14" t="n">
-        <v>2783.2</v>
+        <v>1056.25</v>
       </c>
       <c r="D94" s="14" t="n">
-        <v>2675.44</v>
+        <v>971.74</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>2540.57</v>
+        <v>955.96</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>2102.58</v>
+        <v>889.1</v>
       </c>
       <c r="G94" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C95" s="14" t="n">
-        <v>3586.9</v>
+        <v>295.4</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>3446.24</v>
+        <v>284.71</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>3447.21</v>
+        <v>279.33</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>3254.35</v>
+        <v>251.3</v>
       </c>
       <c r="G95" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="C96" s="14" t="n">
-        <v>470.3</v>
+        <v>860.35</v>
       </c>
       <c r="D96" s="14" t="n">
-        <v>435.67</v>
+        <v>838.8200000000001</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>414.74</v>
+        <v>852.33</v>
       </c>
       <c r="F96" s="14" t="n">
-        <v>394.59</v>
+        <v>842.25</v>
       </c>
       <c r="G96" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="inlineStr">
-        <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="C97" s="14" t="n">
-        <v>383.35</v>
-      </c>
-      <c r="D97" s="14" t="n">
-        <v>352.83</v>
-      </c>
-      <c r="E97" s="14" t="n">
-        <v>346.75</v>
-      </c>
-      <c r="F97" s="14" t="n">
-        <v>358.84</v>
-      </c>
-      <c r="G97" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="n">
-        <v>1044.55</v>
-      </c>
-      <c r="D98" s="14" t="n">
-        <v>1001.36</v>
-      </c>
-      <c r="E98" s="14" t="n">
-        <v>991.8</v>
-      </c>
-      <c r="F98" s="14" t="n">
-        <v>873</v>
-      </c>
-      <c r="G98" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C99" s="18" t="n">
-        <v>100.37</v>
-      </c>
-      <c r="D99" s="18" t="n">
-        <v>83.77</v>
-      </c>
-      <c r="E99" s="18" t="n">
-        <v>76.61</v>
-      </c>
-      <c r="F99" s="18" t="n">
-        <v>74.47</v>
-      </c>
-      <c r="G99" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="n">
-        <v>8126.5</v>
-      </c>
-      <c r="D100" s="18" t="n">
-        <v>7385.88</v>
-      </c>
-      <c r="E100" s="18" t="n">
-        <v>7212.65</v>
-      </c>
-      <c r="F100" s="18" t="n">
-        <v>7704.04</v>
-      </c>
-      <c r="G100" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>AUBANK</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="n">
-        <v>1043.2</v>
-      </c>
-      <c r="D101" s="14" t="n">
-        <v>962.84</v>
-      </c>
-      <c r="E101" s="14" t="n">
-        <v>951.86</v>
-      </c>
-      <c r="F101" s="14" t="n">
-        <v>883.1</v>
-      </c>
-      <c r="G101" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B102" s="13" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="C102" s="14" t="n">
-        <v>296.45</v>
-      </c>
-      <c r="D102" s="14" t="n">
-        <v>283.59</v>
-      </c>
-      <c r="E102" s="14" t="n">
-        <v>278.67</v>
-      </c>
-      <c r="F102" s="14" t="n">
-        <v>251.02</v>
-      </c>
-      <c r="G102" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B103" s="13" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C103" s="14" t="n">
-        <v>870.1</v>
-      </c>
-      <c r="D103" s="14" t="n">
-        <v>836.5599999999999</v>
-      </c>
-      <c r="E103" s="14" t="n">
-        <v>852</v>
-      </c>
-      <c r="F103" s="14" t="n">
-        <v>841.51</v>
-      </c>
-      <c r="G103" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 24-Apr-2026  16:53</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 25-Apr-2026  16:10</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 25-Apr-2026  16:10</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 26-Apr-2026  16:11</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 26-Apr-2026  16:11</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 27-Apr-2026  18:05</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>14</v>
@@ -681,7 +681,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.867</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0.9329999999999999</v>
@@ -690,224 +690,224 @@
         <v>1</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.9333</v>
+        <v>0.9553</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.7</v>
+        <v>0.8167</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.733</v>
+        <v>0.9</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>13</v>
-      </c>
       <c r="E8" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.6</v>
+        <v>0.867</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.65</v>
+        <v>0.6890000000000001</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.867</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.6223</v>
+        <v>0.6887000000000001</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.625</v>
+        <v>0.733</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.575</v>
+        <v>0.333</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.6083</v>
+        <v>0.6887000000000001</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.9</v>
+        <v>0.625</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.7</v>
+        <v>0.625</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.6</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -923,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>6</v>
@@ -932,137 +932,137 @@
         <v>0.667</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.528</v>
+        <v>0.5557</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.55</v>
+        <v>0.467</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.55</v>
+        <v>0.467</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.35</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.4833</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.467</v>
+        <v>0.35</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.4447</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C15" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="F15" s="10" t="n">
-        <v>0.333</v>
+        <v>0.55</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.167</v>
+        <v>0.3</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.15</v>
+        <v>0.333</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.2333</v>
+        <v>0.3053</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1075,7 +1075,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0</v>
+        <v>0.0333</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2287.6</v>
+        <v>2321.8</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2122.92</v>
+        <v>2141.86</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2092.07</v>
+        <v>2101.07</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2238.24</v>
+        <v>2233.06</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1048.35</v>
+        <v>1061.8</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>988.7</v>
+        <v>995.67</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>953.05</v>
+        <v>957.3099999999999</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>849.14</v>
+        <v>851.29</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>541.5</v>
+        <v>559.35</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>534.3099999999999</v>
+        <v>536.6900000000001</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>527.8099999999999</v>
+        <v>529.05</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>430.69</v>
+        <v>431.47</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>588.5</v>
+        <v>628</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>570.8200000000001</v>
+        <v>576.27</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>571.4400000000001</v>
+        <v>573.66</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>537.67</v>
+        <v>538.01</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1256</v>
+        <v>1278.2</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1222.29</v>
+        <v>1227.62</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1185.57</v>
+        <v>1189.2</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1085.11</v>
+        <v>1087</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>766.3</v>
+        <v>770.4</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>762.63</v>
+        <v>763.37</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>759.26</v>
+        <v>759.6900000000001</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>741.8</v>
+        <v>741.0700000000001</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1255.7</v>
+        <v>1282.7</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1218.23</v>
+        <v>1224.37</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1201.8</v>
+        <v>1204.97</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1151.24</v>
+        <v>1153.39</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>437.05</v>
+        <v>441</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>415.18</v>
+        <v>417.64</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>389.58</v>
+        <v>391.59</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>301.97</v>
+        <v>303.18</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>89.29000000000001</v>
+        <v>90.42</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>85</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>82.12</v>
+        <v>82.44</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>76.28</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2605.8</v>
+        <v>2693.9</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2380.38</v>
+        <v>2410.24</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2330.88</v>
+        <v>2345.12</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2390.81</v>
+        <v>2392.93</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>178.46</v>
+        <v>184.2</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>167.03</v>
+        <v>168.67</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>159.97</v>
+        <v>160.92</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>144.09</v>
+        <v>144.39</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>210.07</v>
+        <v>213.27</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>205.58</v>
+        <v>206.32</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>200.15</v>
+        <v>200.67</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>181.44</v>
+        <v>181.8</v>
       </c>
       <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
@@ -1565,2095 +1565,2375 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>742.5</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>731.54</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>700.51</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>584.12</v>
+      </c>
+      <c r="G15" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VEDL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
-        <v>1207.45</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>1013.2</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>913.53</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>852.2</v>
-      </c>
-      <c r="G15" s="15">
+      <c r="C16" s="14" t="n">
+        <v>1212.45</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>1032.18</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>925.25</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>855.1900000000001</v>
+      </c>
+      <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>270.09</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>257.84</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>255.64</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>266.68</v>
-      </c>
-      <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>665.15</v>
+        <v>1416.7</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>571.11</v>
+        <v>1364.59</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>548.72</v>
+        <v>1302.95</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>556.22</v>
+        <v>1215.26</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>516.1</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>499.66</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>483.45</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>490.64</v>
-      </c>
-      <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>6477</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>6205.19</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>6186.75</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>6251.86</v>
+      </c>
+      <c r="G18" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>2327.3</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>2217.47</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>2228.12</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>2326.73</v>
-      </c>
-      <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>1334.5</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>1259.73</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>1258.9</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>1251.29</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>783.3</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>761</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>758.86</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>741.05</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>1775.5</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>1745.91</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>1739.56</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>1742.55</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>1421.3</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>1291.61</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>1267.09</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>1242.92</v>
-      </c>
-      <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>2325.1</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>2221.14</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>2152.1</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>1973.34</v>
+      </c>
+      <c r="G21" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>3187.2</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>2973.39</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>2878.23</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>2867.56</v>
-      </c>
-      <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>694.9</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>650.5700000000001</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>620.2</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>565.98</v>
+      </c>
+      <c r="G22" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>1174</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>1112.65</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>1110.92</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>1129.4</v>
-      </c>
-      <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>1541.3</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>1500.59</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>1494.94</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>1446.36</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>UNITDSPR</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>1391.9</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>1313.13</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>1323.8</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>1374.28</v>
-      </c>
-      <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>JBCHEPHARM</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>2047.5</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>2009.22</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1996.75</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>1849.61</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>490.45</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>449.64</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>442.79</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>464.31</v>
-      </c>
-      <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>1123.55</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>1088.33</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>1056.04</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>955.53</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>7753.5</v>
+        <v>2324.5</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>7372.62</v>
+        <v>2313.27</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>7156.07</v>
+        <v>2282.16</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>7059.12</v>
+        <v>2148.88</v>
       </c>
       <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>1818.4</v>
+        <v>2268.7</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>1781.45</v>
+        <v>2149.4</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>1791.59</v>
+        <v>2128.7</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>1811.39</v>
+        <v>2255.7</v>
       </c>
       <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>781.95</v>
+        <v>1089.9</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>742.7</v>
+        <v>1060.27</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>736.83</v>
+        <v>1003.75</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>753.62</v>
+        <v>920.95</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>1211.15</v>
+        <v>1733.5</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>1105.48</v>
+        <v>1698.06</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>1037.23</v>
+        <v>1716.15</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>1028.29</v>
+        <v>1715.41</v>
       </c>
       <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>4410</v>
+        <v>4219.8</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>4360.67</v>
+        <v>4161.91</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>4247.23</v>
+        <v>4152.68</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>3937.14</v>
+        <v>3861.53</v>
       </c>
       <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>1464</v>
+        <v>939.65</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>1393.23</v>
+        <v>918.88</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>1395.31</v>
+        <v>910.36</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>1378.84</v>
+        <v>922.38</v>
       </c>
       <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>1413.8</v>
+        <v>270.67</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>1359.1</v>
+        <v>259.06</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>1298.3</v>
+        <v>256.23</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>1214.1</v>
+        <v>266.4</v>
       </c>
       <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>6361.5</v>
+        <v>680.75</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>6176.58</v>
+        <v>581.55</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>6174.91</v>
+        <v>553.89</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>6265.34</v>
+        <v>557.12</v>
       </c>
       <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>DRREDDY</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>1317.1</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>1251.86</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>1255.81</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>1250.58</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>1723.3</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>1642.92</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>1588.24</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>1617.02</v>
+      </c>
+      <c r="G34" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>GLENMARK</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>2299.5</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>2210.19</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>2145.04</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>1970.87</v>
-      </c>
-      <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>1799.7</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>1722.7</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>1692.53</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>1676.36</v>
+      </c>
+      <c r="G35" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>689.45</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>645.9</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>617.15</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>565.8200000000001</v>
-      </c>
-      <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>SOBHA</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>1430.6</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>1336.15</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>1349.75</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>1421.81</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>1555.9</v>
+        <v>8111.5</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>1496.3</v>
+        <v>7442.99</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>1493.05</v>
+        <v>7193.54</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1448.29</v>
+        <v>7069</v>
       </c>
       <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="C38" s="14" t="n">
-        <v>2005.8</v>
+        <v>1916.3</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>2005.19</v>
+        <v>1794.29</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>1994.67</v>
+        <v>1796.48</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1848.32</v>
+        <v>1803.92</v>
       </c>
       <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>1113.45</v>
+        <v>791.5</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>1084.62</v>
+        <v>747.34</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>1053.29</v>
+        <v>738.98</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>955.4299999999999</v>
+        <v>753.88</v>
       </c>
       <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>2267.4</v>
+        <v>1236.25</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>2136.85</v>
+        <v>1117.93</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>2122.99</v>
+        <v>1045.03</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>2258.82</v>
+        <v>1028.99</v>
       </c>
       <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>1093.2</v>
+        <v>4441.8</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>1057.15</v>
+        <v>4368.4</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>1000.23</v>
+        <v>4254.86</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>920.8200000000001</v>
+        <v>3941.05</v>
       </c>
       <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>927.4</v>
+        <v>1515</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>916.7</v>
+        <v>1404.82</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>909.16</v>
+        <v>1400</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>921.67</v>
+        <v>1377.77</v>
       </c>
       <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C43" s="18" t="n">
-        <v>714.5</v>
+        <v>520.5</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>666.41</v>
+        <v>501.64</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>663.41</v>
+        <v>484.9</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>712.48</v>
+        <v>488.93</v>
       </c>
       <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>626.85</v>
+        <v>2328.3</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>582.2</v>
+        <v>2228.02</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>558.67</v>
+        <v>2232.05</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>579.91</v>
+        <v>2326.19</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>165.61</v>
+        <v>787</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>155.68</v>
+        <v>763.47</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>155.3</v>
+        <v>759.96</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>165.25</v>
+        <v>741.73</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>473.7</v>
+        <v>1417.3</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>471.23</v>
+        <v>1303.58</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>467.53</v>
+        <v>1272.98</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>438.5</v>
+        <v>1243.53</v>
       </c>
       <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>3315.4</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>3005.96</v>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>2895.38</v>
+      </c>
+      <c r="F47" s="18" t="n">
+        <v>2871.98</v>
+      </c>
+      <c r="G47" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>1160.5</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>1117.21</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>1112.86</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <v>1129.21</v>
+      </c>
+      <c r="G48" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>1391.6</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>1320.61</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>1326.46</v>
+      </c>
+      <c r="F49" s="18" t="n">
+        <v>1374.11</v>
+      </c>
+      <c r="G49" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>518.85</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>456.23</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>445.77</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>464.93</v>
+      </c>
+      <c r="G50" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>284.8</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>282.27</v>
-      </c>
-      <c r="E47" s="18" t="n">
-        <v>274</v>
-      </c>
-      <c r="F47" s="18" t="n">
-        <v>251.78</v>
-      </c>
-      <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="n">
-        <v>7328.5</v>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>6842.84</v>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>6359.59</v>
-      </c>
-      <c r="F48" s="14" t="n">
-        <v>5725.68</v>
-      </c>
-      <c r="G48" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n">
-        <v>1411.95</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>1181.64</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>1083.3</v>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>983.98</v>
-      </c>
-      <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n">
-        <v>1235.8</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>1066.62</v>
-      </c>
-      <c r="E50" s="14" t="n">
-        <v>992.73</v>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>980.92</v>
-      </c>
-      <c r="G50" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C51" s="14" t="n">
-        <v>212.9</v>
+        <v>722.45</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>184.78</v>
+        <v>671.75</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>166.22</v>
+        <v>665.72</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>145.46</v>
+        <v>713.04</v>
       </c>
       <c r="G51" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="C52" s="14" t="n">
-        <v>337.39</v>
+        <v>635.6</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>297.84</v>
+        <v>587.28</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>279.2</v>
+        <v>561.6900000000001</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>261.9</v>
+        <v>579.8200000000001</v>
       </c>
       <c r="G52" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C53" s="14" t="n">
-        <v>180.58</v>
+        <v>165.74</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>166.92</v>
+        <v>156.64</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>161.09</v>
+        <v>155.71</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>160.73</v>
+        <v>164.95</v>
       </c>
       <c r="G53" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>823.15</v>
+        <v>476.2</v>
       </c>
       <c r="D54" s="14" t="n">
-        <v>756</v>
+        <v>471.7</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>717.95</v>
+        <v>467.87</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>689.04</v>
+        <v>439.09</v>
       </c>
       <c r="G54" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>282.61</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>274.47</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>252.22</v>
+      </c>
+      <c r="G55" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>7430.5</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>6898.81</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>6401.58</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <v>5730.13</v>
+      </c>
+      <c r="G56" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>1435.8</v>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>1205.85</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>1097.12</v>
+      </c>
+      <c r="F57" s="18" t="n">
+        <v>985.4400000000001</v>
+      </c>
+      <c r="G57" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>1229.7</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>1082.15</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>1002.02</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>981.1</v>
+      </c>
+      <c r="G58" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>218.05</v>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>187.95</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>168.25</v>
+      </c>
+      <c r="F59" s="18" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="G59" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>348.58</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>302.67</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>281.92</v>
+      </c>
+      <c r="F60" s="18" t="n">
+        <v>262.75</v>
+      </c>
+      <c r="G60" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>188.01</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>168.93</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>162.14</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>161.06</v>
+      </c>
+      <c r="G61" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>820.3</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>762.12</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>721.97</v>
+      </c>
+      <c r="F62" s="18" t="n">
+        <v>689.3200000000001</v>
+      </c>
+      <c r="G62" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="C55" s="14" t="n">
-        <v>456</v>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>445.86</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>439.57</v>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>406.98</v>
-      </c>
-      <c r="G55" s="15">
+      <c r="C63" s="18" t="n">
+        <v>452.5</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>446.5</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>440.08</v>
+      </c>
+      <c r="F63" s="18" t="n">
+        <v>407.23</v>
+      </c>
+      <c r="G63" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="16" t="inlineStr">
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>GVT&amp;D</t>
         </is>
       </c>
-      <c r="C56" s="14" t="n">
-        <v>4598.3</v>
-      </c>
-      <c r="D56" s="14" t="n">
-        <v>4072.59</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>3799.38</v>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>3126.15</v>
-      </c>
-      <c r="G56" s="15">
+      <c r="C64" s="18" t="n">
+        <v>4556.8</v>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>4118.71</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>3829.09</v>
+      </c>
+      <c r="F64" s="18" t="n">
+        <v>3142.55</v>
+      </c>
+      <c r="G64" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>JPPOWER</t>
         </is>
       </c>
-      <c r="C57" s="14" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="G57" s="15">
+      <c r="C65" s="18" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="F65" s="18" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="G65" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
         <is>
           <t>JSWENERGY</t>
         </is>
       </c>
-      <c r="C58" s="14" t="n">
-        <v>544.95</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>522.6</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>505.51</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>501.41</v>
-      </c>
-      <c r="G58" s="15">
+      <c r="C66" s="18" t="n">
+        <v>573.8</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>527.48</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>508.18</v>
+      </c>
+      <c r="F66" s="18" t="n">
+        <v>499.85</v>
+      </c>
+      <c r="G66" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B67" s="17" t="inlineStr">
         <is>
           <t>NHPC</t>
         </is>
       </c>
-      <c r="C59" s="14" t="n">
-        <v>80.66</v>
-      </c>
-      <c r="D59" s="14" t="n">
-        <v>79.34</v>
-      </c>
-      <c r="E59" s="14" t="n">
-        <v>77.77</v>
-      </c>
-      <c r="F59" s="14" t="n">
-        <v>79.38</v>
-      </c>
-      <c r="G59" s="15">
+      <c r="C67" s="18" t="n">
+        <v>83.23</v>
+      </c>
+      <c r="D67" s="18" t="n">
+        <v>79.70999999999999</v>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>77.98</v>
+      </c>
+      <c r="F67" s="18" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="G67" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>NLCINDIA</t>
         </is>
       </c>
-      <c r="C60" s="14" t="n">
-        <v>299.1</v>
-      </c>
-      <c r="D60" s="14" t="n">
-        <v>283.98</v>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v>271.51</v>
-      </c>
-      <c r="F60" s="14" t="n">
-        <v>255.14</v>
-      </c>
-      <c r="G60" s="15">
+      <c r="C68" s="18" t="n">
+        <v>313.85</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>286.82</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>273.17</v>
+      </c>
+      <c r="F68" s="18" t="n">
+        <v>255.05</v>
+      </c>
+      <c r="G68" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="16" t="inlineStr">
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
       </c>
-      <c r="C61" s="14" t="n">
-        <v>401.85</v>
-      </c>
-      <c r="D61" s="14" t="n">
-        <v>387.98</v>
-      </c>
-      <c r="E61" s="14" t="n">
-        <v>376.62</v>
-      </c>
-      <c r="F61" s="14" t="n">
-        <v>352.59</v>
-      </c>
-      <c r="G61" s="15">
+      <c r="C69" s="18" t="n">
+        <v>410.2</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>390.1</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>377.94</v>
+      </c>
+      <c r="F69" s="18" t="n">
+        <v>353.03</v>
+      </c>
+      <c r="G69" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B70" s="17" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
       </c>
-      <c r="C62" s="14" t="n">
-        <v>316.4</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>308.3</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>298.58</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>286.05</v>
-      </c>
-      <c r="G62" s="15">
+      <c r="C70" s="18" t="n">
+        <v>320.9</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>299.46</v>
+      </c>
+      <c r="F70" s="18" t="n">
+        <v>285.93</v>
+      </c>
+      <c r="G70" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B71" s="17" t="inlineStr">
         <is>
           <t>POWERINDIA</t>
         </is>
       </c>
-      <c r="C63" s="14" t="n">
-        <v>32200</v>
-      </c>
-      <c r="D63" s="14" t="n">
-        <v>28179.11</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>25629.01</v>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>21221.6</v>
-      </c>
-      <c r="G63" s="15">
+      <c r="C71" s="18" t="n">
+        <v>32065</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>28549.19</v>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>25881.41</v>
+      </c>
+      <c r="F71" s="18" t="n">
+        <v>21332.95</v>
+      </c>
+      <c r="G71" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>SCHNEIDER</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>1180.1</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>1013.78</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>925.8</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>817.64</v>
-      </c>
-      <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="n">
-        <v>3808.9</v>
-      </c>
-      <c r="D65" s="14" t="n">
-        <v>3486.26</v>
-      </c>
-      <c r="E65" s="14" t="n">
-        <v>3316.03</v>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>3173.96</v>
-      </c>
-      <c r="G65" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="n">
-        <v>53.91</v>
-      </c>
-      <c r="D66" s="14" t="n">
-        <v>48.29</v>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>51.48</v>
-      </c>
-      <c r="G66" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="n">
-        <v>435</v>
-      </c>
-      <c r="D67" s="14" t="n">
-        <v>413.21</v>
-      </c>
-      <c r="E67" s="14" t="n">
-        <v>397.3</v>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>388.48</v>
-      </c>
-      <c r="G67" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="n">
-        <v>4006.5</v>
-      </c>
-      <c r="D68" s="14" t="n">
-        <v>3753.64</v>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v>3442.43</v>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>3265.36</v>
-      </c>
-      <c r="G68" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="n">
-        <v>1699.5</v>
-      </c>
-      <c r="D69" s="14" t="n">
-        <v>1537.18</v>
-      </c>
-      <c r="E69" s="14" t="n">
-        <v>1472.37</v>
-      </c>
-      <c r="F69" s="14" t="n">
-        <v>1401.61</v>
-      </c>
-      <c r="G69" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="n">
-        <v>569.85</v>
-      </c>
-      <c r="D70" s="14" t="n">
-        <v>509.34</v>
-      </c>
-      <c r="E70" s="14" t="n">
-        <v>493.23</v>
-      </c>
-      <c r="F70" s="14" t="n">
-        <v>512.3</v>
-      </c>
-      <c r="G70" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="n">
-        <v>1687</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>1634.46</v>
-      </c>
-      <c r="E71" s="18" t="n">
-        <v>1582.73</v>
-      </c>
-      <c r="F71" s="18" t="n">
-        <v>1617.76</v>
-      </c>
-      <c r="G71" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C72" s="18" t="n">
-        <v>1775.9</v>
+        <v>1182</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>1714.59</v>
+        <v>1029.8</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>1688.16</v>
+        <v>935.84</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>1678.04</v>
+        <v>819.15</v>
       </c>
       <c r="G72" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B73" s="13" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="D73" s="14" t="n">
-        <v>72.14</v>
-      </c>
-      <c r="E73" s="14" t="n">
-        <v>68.76000000000001</v>
-      </c>
-      <c r="F73" s="14" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="G73" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>3856</v>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>3521.48</v>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>3337.21</v>
+      </c>
+      <c r="F73" s="18" t="n">
+        <v>3181.91</v>
+      </c>
+      <c r="G73" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
-        <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="C74" s="14" t="n">
-        <v>1101.1</v>
-      </c>
-      <c r="D74" s="14" t="n">
-        <v>1078.01</v>
-      </c>
-      <c r="E74" s="14" t="n">
-        <v>1077.5</v>
-      </c>
-      <c r="F74" s="14" t="n">
-        <v>987.09</v>
-      </c>
-      <c r="G74" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n">
+        <v>80.41</v>
+      </c>
+      <c r="D74" s="18" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="E74" s="18" t="n">
+        <v>73.22</v>
+      </c>
+      <c r="F74" s="18" t="n">
+        <v>79.81</v>
+      </c>
+      <c r="G74" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SJVN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C75" s="18" t="n">
-        <v>1365.9</v>
+        <v>56.93</v>
       </c>
       <c r="D75" s="18" t="n">
-        <v>1323.08</v>
+        <v>49.11</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>1302.93</v>
+        <v>46.81</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>1254.17</v>
+        <v>51.34</v>
       </c>
       <c r="G75" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C76" s="18" t="n">
-        <v>2735</v>
+        <v>453.2</v>
       </c>
       <c r="D76" s="18" t="n">
-        <v>2611.63</v>
+        <v>417.02</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>2576.1</v>
+        <v>399.49</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>2589.84</v>
+        <v>389.07</v>
       </c>
       <c r="G76" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C77" s="18" t="n">
-        <v>2760.9</v>
+        <v>4156.3</v>
       </c>
       <c r="D77" s="18" t="n">
-        <v>2693.57</v>
+        <v>3791.99</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>2558.66</v>
+        <v>3470.41</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>2119.99</v>
+        <v>3255.39</v>
       </c>
       <c r="G77" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C78" s="18" t="n">
-        <v>3493.5</v>
+        <v>1772.5</v>
       </c>
       <c r="D78" s="18" t="n">
-        <v>3460.66</v>
+        <v>1559.59</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>3453.32</v>
+        <v>1484.14</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>3249.89</v>
+        <v>1401.74</v>
       </c>
       <c r="G78" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C79" s="18" t="n">
-        <v>469.35</v>
+        <v>580</v>
       </c>
       <c r="D79" s="18" t="n">
-        <v>441.82</v>
+        <v>516.0700000000001</v>
       </c>
       <c r="E79" s="18" t="n">
-        <v>418.95</v>
+        <v>496.63</v>
       </c>
       <c r="F79" s="18" t="n">
-        <v>395.77</v>
+        <v>513.4</v>
       </c>
       <c r="G79" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B80" s="17" t="inlineStr">
-        <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="C80" s="18" t="n">
-        <v>374</v>
-      </c>
-      <c r="D80" s="18" t="n">
-        <v>356.88</v>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>348.94</v>
-      </c>
-      <c r="F80" s="18" t="n">
-        <v>359.13</v>
-      </c>
-      <c r="G80" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="F80" s="14" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="G80" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="C81" s="18" t="n">
-        <v>1011.3</v>
-      </c>
-      <c r="D81" s="18" t="n">
-        <v>1002.99</v>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>993.22</v>
-      </c>
-      <c r="F81" s="18" t="n">
-        <v>875.16</v>
-      </c>
-      <c r="G81" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="n">
+        <v>1111.85</v>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>1081.24</v>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>1078.85</v>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>988.67</v>
+      </c>
+      <c r="G81" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="12" t="inlineStr">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="B82" s="17" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="C82" s="14" t="n">
-        <v>9576</v>
-      </c>
-      <c r="D82" s="14" t="n">
-        <v>9509.6</v>
-      </c>
-      <c r="E82" s="14" t="n">
-        <v>9441.700000000001</v>
-      </c>
-      <c r="F82" s="14" t="n">
-        <v>9096.219999999999</v>
-      </c>
-      <c r="G82" s="15">
+      <c r="C82" s="18" t="n">
+        <v>9662</v>
+      </c>
+      <c r="D82" s="18" t="n">
+        <v>9524.110000000001</v>
+      </c>
+      <c r="E82" s="18" t="n">
+        <v>9450.33</v>
+      </c>
+      <c r="F82" s="18" t="n">
+        <v>9093.370000000001</v>
+      </c>
+      <c r="G82" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="16" t="inlineStr">
+      <c r="A83" s="20" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B83" s="13" t="inlineStr">
+      <c r="B83" s="17" t="inlineStr">
         <is>
           <t>BHARATFORG</t>
         </is>
       </c>
-      <c r="C83" s="14" t="n">
-        <v>1856</v>
-      </c>
-      <c r="D83" s="14" t="n">
-        <v>1810.11</v>
-      </c>
-      <c r="E83" s="14" t="n">
-        <v>1741.69</v>
-      </c>
-      <c r="F83" s="14" t="n">
-        <v>1493.67</v>
-      </c>
-      <c r="G83" s="15">
+      <c r="C83" s="18" t="n">
+        <v>1901.1</v>
+      </c>
+      <c r="D83" s="18" t="n">
+        <v>1818.78</v>
+      </c>
+      <c r="E83" s="18" t="n">
+        <v>1747.94</v>
+      </c>
+      <c r="F83" s="18" t="n">
+        <v>1498.63</v>
+      </c>
+      <c r="G83" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="16" t="inlineStr">
+      <c r="A84" s="20" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="B84" s="17" t="inlineStr">
         <is>
           <t>BOSCHLTD</t>
         </is>
       </c>
-      <c r="C84" s="14" t="n">
-        <v>36690</v>
-      </c>
-      <c r="D84" s="14" t="n">
-        <v>35620.79</v>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v>34807.57</v>
-      </c>
-      <c r="F84" s="14" t="n">
-        <v>35060.75</v>
-      </c>
-      <c r="G84" s="15">
+      <c r="C84" s="18" t="n">
+        <v>37225</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>35773.58</v>
+      </c>
+      <c r="E84" s="18" t="n">
+        <v>34902.37</v>
+      </c>
+      <c r="F84" s="18" t="n">
+        <v>35073.14</v>
+      </c>
+      <c r="G84" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="16" t="inlineStr">
+      <c r="A85" s="20" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B85" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="n">
-        <v>125.7</v>
-      </c>
-      <c r="D85" s="14" t="n">
-        <v>120.96</v>
-      </c>
-      <c r="E85" s="14" t="n">
-        <v>119.41</v>
-      </c>
-      <c r="F85" s="14" t="n">
-        <v>112.13</v>
-      </c>
-      <c r="G85" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="n">
+        <v>7174</v>
+      </c>
+      <c r="D85" s="18" t="n">
+        <v>7109.06</v>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>7172.52</v>
+      </c>
+      <c r="F85" s="18" t="n">
+        <v>6860.18</v>
+      </c>
+      <c r="G85" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="C86" s="18" t="n">
-        <v>1065.65</v>
+        <v>352.35</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>980.6799999999999</v>
+        <v>328.18</v>
       </c>
       <c r="E86" s="18" t="n">
-        <v>960.26</v>
+        <v>325.68</v>
       </c>
       <c r="F86" s="18" t="n">
-        <v>892.15</v>
+        <v>352.15</v>
       </c>
       <c r="G86" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C87" s="18" t="n">
-        <v>293</v>
+        <v>127.93</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>285.5</v>
+        <v>121.62</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>279.86</v>
+        <v>119.75</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>251.89</v>
+        <v>112.22</v>
       </c>
       <c r="G87" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C88" s="14" t="n">
-        <v>100.22</v>
+        <v>1324.2</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>86.54000000000001</v>
+        <v>1323.18</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>78.34</v>
+        <v>1303.77</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>74.93000000000001</v>
+        <v>1253.71</v>
       </c>
       <c r="G88" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
         <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="n">
+        <v>2756</v>
+      </c>
+      <c r="D89" s="14" t="n">
+        <v>2625.38</v>
+      </c>
+      <c r="E89" s="14" t="n">
+        <v>2583.15</v>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>2586.71</v>
+      </c>
+      <c r="G89" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="n">
+        <v>2830</v>
+      </c>
+      <c r="D90" s="14" t="n">
+        <v>2706.57</v>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v>2569.3</v>
+      </c>
+      <c r="F90" s="14" t="n">
+        <v>2126.17</v>
+      </c>
+      <c r="G90" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="n">
+        <v>3493.8</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>3463.82</v>
+      </c>
+      <c r="E91" s="14" t="n">
+        <v>3454.91</v>
+      </c>
+      <c r="F91" s="14" t="n">
+        <v>3253.08</v>
+      </c>
+      <c r="G91" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="n">
+        <v>474.9</v>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>444.97</v>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v>421.15</v>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>395.39</v>
+      </c>
+      <c r="G92" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="D93" s="14" t="n">
+        <v>358.9</v>
+      </c>
+      <c r="E93" s="14" t="n">
+        <v>350.08</v>
+      </c>
+      <c r="F93" s="14" t="n">
+        <v>358.78</v>
+      </c>
+      <c r="G93" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B89" s="13" t="inlineStr">
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="n">
+        <v>106.69</v>
+      </c>
+      <c r="D94" s="18" t="n">
+        <v>88.45999999999999</v>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="F94" s="18" t="n">
+        <v>74.95999999999999</v>
+      </c>
+      <c r="G94" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
         <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="C89" s="14" t="n">
-        <v>8949</v>
-      </c>
-      <c r="D89" s="14" t="n">
-        <v>7655.87</v>
-      </c>
-      <c r="E89" s="14" t="n">
-        <v>7340.26</v>
-      </c>
-      <c r="F89" s="14" t="n">
-        <v>7772.88</v>
-      </c>
-      <c r="G89" s="15">
+      <c r="C95" s="18" t="n">
+        <v>9360</v>
+      </c>
+      <c r="D95" s="18" t="n">
+        <v>7818.17</v>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>7419.46</v>
+      </c>
+      <c r="F95" s="18" t="n">
+        <v>7787.96</v>
+      </c>
+      <c r="G95" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>TANLA</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="n">
+        <v>582.95</v>
+      </c>
+      <c r="D96" s="18" t="n">
+        <v>477.54</v>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>467.49</v>
+      </c>
+      <c r="F96" s="18" t="n">
+        <v>520.13</v>
+      </c>
+      <c r="G96" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="n">
+        <v>1043</v>
+      </c>
+      <c r="D97" s="14" t="n">
+        <v>986.62</v>
+      </c>
+      <c r="E97" s="14" t="n">
+        <v>963.51</v>
+      </c>
+      <c r="F97" s="14" t="n">
+        <v>894.27</v>
+      </c>
+      <c r="G97" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="n">
+        <v>294.05</v>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>286.32</v>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v>280.42</v>
+      </c>
+      <c r="F98" s="14" t="n">
+        <v>252.14</v>
+      </c>
+      <c r="G98" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="n">
+        <v>900.15</v>
+      </c>
+      <c r="D99" s="14" t="n">
+        <v>845.45</v>
+      </c>
+      <c r="E99" s="14" t="n">
+        <v>854.04</v>
+      </c>
+      <c r="F99" s="14" t="n">
+        <v>845.88</v>
+      </c>
+      <c r="G99" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 27-Apr-2026  18:05</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 28-Apr-2026  19:25</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0.9</v>
@@ -749,10 +749,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.7333</v>
+        <v>0.7667</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -864,7 +864,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>1</v>
@@ -873,10 +873,10 @@
         <v>0.733</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.333</v>
+        <v>0.267</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.6887000000000001</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -1016,7 +1016,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>4</v>
@@ -1025,13 +1025,13 @@
         <v>0.55</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.35</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -2069,79 +2069,79 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1051.75</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>980.34</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>987.85</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>1022.36</v>
+      </c>
+      <c r="G33" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
           <t>TIPSMUSIC</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C34" s="14" t="n">
         <v>680.75</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D34" s="14" t="n">
         <v>581.55</v>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E34" s="14" t="n">
         <v>553.89</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F34" s="14" t="n">
         <v>557.12</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G34" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>OBEROIRLTY</t>
         </is>
       </c>
-      <c r="C34" s="18" t="n">
+      <c r="C35" s="18" t="n">
         <v>1723.3</v>
       </c>
-      <c r="D34" s="18" t="n">
+      <c r="D35" s="18" t="n">
         <v>1642.92</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E35" s="18" t="n">
         <v>1588.24</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F35" s="18" t="n">
         <v>1617.02</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G35" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>1799.7</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>1722.7</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>1692.53</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>1676.36</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2153,79 +2153,79 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>1799.7</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>1722.7</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>1692.53</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>1676.36</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
           <t>SOBHA</t>
         </is>
       </c>
-      <c r="C36" s="18" t="n">
+      <c r="C37" s="18" t="n">
         <v>1430.6</v>
       </c>
-      <c r="D36" s="18" t="n">
+      <c r="D37" s="18" t="n">
         <v>1336.15</v>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E37" s="18" t="n">
         <v>1349.75</v>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="F37" s="18" t="n">
         <v>1421.81</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G37" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
-      <c r="C37" s="14" t="n">
+      <c r="C38" s="14" t="n">
         <v>8111.5</v>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D38" s="14" t="n">
         <v>7442.99</v>
       </c>
-      <c r="E37" s="14" t="n">
+      <c r="E38" s="14" t="n">
         <v>7193.54</v>
       </c>
-      <c r="F37" s="14" t="n">
+      <c r="F38" s="14" t="n">
         <v>7069</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G38" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>1916.3</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>1794.29</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>1796.48</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>1803.92</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2237,23 +2237,23 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>791.5</v>
+        <v>1916.3</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>747.34</v>
+        <v>1794.29</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>738.98</v>
+        <v>1796.48</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>753.88</v>
+        <v>1803.92</v>
       </c>
       <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2265,23 +2265,23 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>1236.25</v>
+        <v>791.5</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>1117.93</v>
+        <v>747.34</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>1045.03</v>
+        <v>738.98</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>1028.99</v>
+        <v>753.88</v>
       </c>
       <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2293,23 +2293,23 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>4441.8</v>
+        <v>1236.25</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>4368.4</v>
+        <v>1117.93</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>4254.86</v>
+        <v>1045.03</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>3941.05</v>
+        <v>1028.99</v>
       </c>
       <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2321,79 +2321,79 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>4441.8</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>4368.4</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>4254.86</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>3941.05</v>
+      </c>
+      <c r="G42" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
           <t>VOLTAS</t>
         </is>
       </c>
-      <c r="C42" s="14" t="n">
+      <c r="C43" s="14" t="n">
         <v>1515</v>
       </c>
-      <c r="D42" s="14" t="n">
+      <c r="D43" s="14" t="n">
         <v>1404.82</v>
       </c>
-      <c r="E42" s="14" t="n">
+      <c r="E43" s="14" t="n">
         <v>1400</v>
       </c>
-      <c r="F42" s="14" t="n">
+      <c r="F43" s="14" t="n">
         <v>1377.77</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G43" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>BALRAMCHIN</t>
         </is>
       </c>
-      <c r="C43" s="18" t="n">
+      <c r="C44" s="18" t="n">
         <v>520.5</v>
       </c>
-      <c r="D43" s="18" t="n">
+      <c r="D44" s="18" t="n">
         <v>501.64</v>
       </c>
-      <c r="E43" s="18" t="n">
+      <c r="E44" s="18" t="n">
         <v>484.9</v>
       </c>
-      <c r="F43" s="18" t="n">
+      <c r="F44" s="18" t="n">
         <v>488.93</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G44" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>2328.3</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>2228.02</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>2232.05</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>2326.19</v>
-      </c>
-      <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2405,23 +2405,23 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>787</v>
+        <v>2328.3</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>763.47</v>
+        <v>2228.02</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>759.96</v>
+        <v>2232.05</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>741.73</v>
+        <v>2326.19</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>1417.3</v>
+        <v>787</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>1303.58</v>
+        <v>763.47</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>1272.98</v>
+        <v>759.96</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>1243.53</v>
+        <v>741.73</v>
       </c>
       <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2461,23 +2461,23 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>3315.4</v>
+        <v>1417.3</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>3005.96</v>
+        <v>1303.58</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>2895.38</v>
+        <v>1272.98</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>2871.98</v>
+        <v>1243.53</v>
       </c>
       <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>1160.5</v>
+        <v>3315.4</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1117.21</v>
+        <v>3005.96</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>1112.86</v>
+        <v>2895.38</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>1129.21</v>
+        <v>2871.98</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2517,23 +2517,23 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
-        <v>1391.6</v>
+        <v>1160.5</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>1320.61</v>
+        <v>1117.21</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>1326.46</v>
+        <v>1112.86</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>1374.11</v>
+        <v>1129.21</v>
       </c>
       <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2545,56 +2545,56 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>1374.4</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>1325.73</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>1328.34</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>1374.11</v>
+      </c>
+      <c r="G50" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
           <t>VBL</t>
         </is>
       </c>
-      <c r="C50" s="18" t="n">
+      <c r="C51" s="18" t="n">
         <v>518.85</v>
       </c>
-      <c r="D50" s="18" t="n">
+      <c r="D51" s="18" t="n">
         <v>456.23</v>
       </c>
-      <c r="E50" s="18" t="n">
+      <c r="E51" s="18" t="n">
         <v>445.77</v>
       </c>
-      <c r="F50" s="18" t="n">
+      <c r="F51" s="18" t="n">
         <v>464.93</v>
       </c>
-      <c r="G50" s="19">
+      <c r="G51" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n">
-        <v>722.45</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>671.75</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>665.72</v>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>713.04</v>
-      </c>
-      <c r="G51" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
@@ -2745,16 +2745,16 @@
         </is>
       </c>
       <c r="C57" s="18" t="n">
-        <v>1435.8</v>
+        <v>1435.45</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>1205.85</v>
+        <v>1227.72</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>1097.12</v>
+        <v>1110.39</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>985.4400000000001</v>
+        <v>989.92</v>
       </c>
       <c r="G57" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 28-Apr-2026  19:25</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 30-Apr-2026  16:22</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>15</v>
       </c>
       <c r="C4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>15</v>
-      </c>
       <c r="F4" s="6" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>0.9329999999999999</v>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>0.9329999999999999</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="I4" s="7" t="n">
-        <v>0.9553</v>
+        <v>0.8223</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,69 +703,69 @@
         <v>20</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.8167</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.7667</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
         <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>9</v>
@@ -774,7 +774,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.9</v>
@@ -783,13 +783,13 @@
         <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.7</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -802,7 +802,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0.867</v>
@@ -811,103 +811,103 @@
         <v>0.8</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.6890000000000001</v>
+        <v>0.6446999999999999</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.9329999999999999</v>
+        <v>0.625</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.6</v>
+        <v>0.625</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.6887000000000001</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1</v>
+        <v>0.733</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.267</v>
+        <v>0.4</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.5777</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.625</v>
+        <v>0.733</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.6</v>
+        <v>0.333</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.6167</v>
+        <v>0.5777</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -920,25 +920,25 @@
         <v>12</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.667</v>
+        <v>0.417</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.5557</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -951,25 +951,25 @@
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>8</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0.5329999999999999</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.489</v>
+        <v>0.3997</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -982,25 +982,25 @@
         <v>20</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.35</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.4167</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1013,22 +1013,22 @@
         <v>20</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>0.3333</v>
@@ -1078,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
@@ -1087,13 +1087,13 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0333</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2321.8</v>
+        <v>2408.4</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2141.86</v>
+        <v>2212.81</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2101.07</v>
+        <v>2136.63</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2233.06</v>
+        <v>2232.81</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1061.8</v>
+        <v>1038</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>995.67</v>
+        <v>1011.99</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>957.3099999999999</v>
+        <v>968.85</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>851.29</v>
+        <v>857.12</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>559.35</v>
+        <v>595.95</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>536.6900000000001</v>
+        <v>574.95</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>529.05</v>
+        <v>567.61</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>431.47</v>
+        <v>529.45</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>628</v>
+        <v>767.4</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>576.27</v>
+        <v>766.21</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>573.66</v>
+        <v>761.36</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>538.01</v>
+        <v>743.99</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1278.2</v>
+        <v>1264.5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1227.62</v>
+        <v>1237.42</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1189.2</v>
+        <v>1212.89</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1087</v>
+        <v>1154.97</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>770.4</v>
+        <v>90.37</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>763.37</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>759.6900000000001</v>
+        <v>83.41</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>741.0700000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1282.7</v>
+        <v>2645</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1224.37</v>
+        <v>2475.23</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1204.97</v>
+        <v>2380.89</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1153.39</v>
+        <v>2400.48</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>441</v>
+        <v>184.62</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>417.64</v>
+        <v>173.02</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>391.59</v>
+        <v>163.69</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>303.18</v>
+        <v>145.35</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>90.42</v>
+        <v>211.36</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>85.51000000000001</v>
+        <v>208.3</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>82.44</v>
+        <v>202.18</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>76.23999999999999</v>
+        <v>182.59</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,163 +1481,163 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2693.9</v>
+        <v>1266.75</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2410.24</v>
+        <v>1089.92</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2345.12</v>
+        <v>962.4299999999999</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2392.93</v>
+        <v>866.0599999999999</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>184.2</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>168.67</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>160.92</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>144.39</v>
-      </c>
-      <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>1389.5</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>1374.26</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>1314.21</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>1219.32</v>
+      </c>
+      <c r="G13" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>213.27</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>206.32</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>200.67</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>6502.5</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>6279.56</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>6221.11</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>6263.83</v>
+      </c>
+      <c r="G14" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>VEDL</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>742.5</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>731.54</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>700.51</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>584.12</v>
-      </c>
-      <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VEDL","Chart 📈")</f>
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>1322.9</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>1279.18</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1267.54</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>1252.58</v>
+      </c>
+      <c r="G15" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>1212.45</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>1032.18</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>925.25</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>855.1900000000001</v>
-      </c>
-      <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>1750.8</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>1746.95</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>1740.75</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>1741.69</v>
+      </c>
+      <c r="G16" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>1416.7</v>
+        <v>2406.3</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>1364.59</v>
+        <v>2269.62</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>1302.95</v>
+        <v>2181.04</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>1215.26</v>
+        <v>1984.02</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,23 +1649,23 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>6477</v>
+        <v>699.7</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>6205.19</v>
+        <v>664.16</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>6186.75</v>
+        <v>629.5700000000001</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>6251.86</v>
+        <v>569.5599999999999</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,23 +1677,23 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>1334.5</v>
+        <v>1530.9</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>1259.73</v>
+        <v>1509.89</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>1258.9</v>
+        <v>1499.65</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>1251.29</v>
+        <v>1448.17</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1705,23 +1705,23 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>JBCHEPHARM</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>1775.5</v>
+        <v>2043.4</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>1745.91</v>
+        <v>2019.64</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>1739.56</v>
+        <v>2002.7</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>1742.55</v>
+        <v>1856.51</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1733,23 +1733,23 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>2325.1</v>
+        <v>1100.95</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>2221.14</v>
+        <v>1091.23</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>2152.1</v>
+        <v>1060.93</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>1973.34</v>
+        <v>957.91</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>694.9</v>
+        <v>1095.75</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>650.5700000000001</v>
+        <v>1069.16</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>620.2</v>
+        <v>1014.01</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>565.98</v>
+        <v>923.34</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1541.3</v>
+        <v>1808.3</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1500.59</v>
+        <v>1719.35</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>1494.94</v>
+        <v>1723.25</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>1446.36</v>
+        <v>1716.53</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,2122 +1817,1618 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>2047.5</v>
+        <v>4185.1</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>2009.22</v>
+        <v>4171.75</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>1996.75</v>
+        <v>4158.01</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>1849.61</v>
+        <v>3870.47</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>1123.55</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>1088.33</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>1056.04</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>955.53</v>
-      </c>
-      <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>1669.6</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>1655.66</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>1600.07</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>1618.05</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>2324.5</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>2313.27</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>2282.16</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>2148.88</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>1765</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>1735.61</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>1701.57</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>1681.69</v>
+      </c>
+      <c r="G26" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>2268.7</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>2149.4</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>2128.7</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>2255.7</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>SOBHA</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>1433.4</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>1362.96</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>1359.91</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>1427.06</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>1089.9</v>
+        <v>1068.9</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>1060.27</v>
+        <v>998.45</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>1003.75</v>
+        <v>994.97</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>920.95</v>
+        <v>1020.14</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>1733.5</v>
+        <v>649.7</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>1698.06</v>
+        <v>600.23</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>1716.15</v>
+        <v>565.1900000000001</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>1715.41</v>
+        <v>558.6799999999999</v>
       </c>
       <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>4219.8</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>4161.91</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>4152.68</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>3861.53</v>
-      </c>
-      <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>634.7</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>602.99</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>571.48</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>580.46</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>939.65</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>918.88</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>910.36</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>922.38</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>490.8</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>477.33</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>470.77</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>441.15</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>270.67</v>
+        <v>299.55</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>259.06</v>
+        <v>287.3</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>256.23</v>
+        <v>277.44</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>266.4</v>
+        <v>253.17</v>
       </c>
       <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1051.75</v>
+        <v>1430.8</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>980.34</v>
+        <v>1371.16</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>987.85</v>
+        <v>1385.69</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>1022.36</v>
+        <v>1424.35</v>
       </c>
       <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>680.75</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>581.55</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>553.89</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>557.12</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>7230</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>6966.53</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>6473.35</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>5750.99</v>
+      </c>
+      <c r="G34" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C35" s="18" t="n">
-        <v>1723.3</v>
+        <v>1342.25</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>1642.92</v>
+        <v>1255.03</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>1588.24</v>
+        <v>1131.08</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>1617.02</v>
+        <v>995.5</v>
       </c>
       <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>1799.7</v>
+        <v>1227.15</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>1722.7</v>
+        <v>1123.06</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>1692.53</v>
+        <v>1028.97</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>1676.36</v>
+        <v>985.4400000000001</v>
       </c>
       <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>SOBHA</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
-        <v>1430.6</v>
+        <v>221.85</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>1336.15</v>
+        <v>196.64</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>1349.75</v>
+        <v>174.27</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>1421.81</v>
+        <v>147.69</v>
       </c>
       <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>8111.5</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>7442.99</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>7193.54</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>7069</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>352.41</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>315.07</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>289.68</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>265.06</v>
+      </c>
+      <c r="G38" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n">
-        <v>1916.3</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>1794.29</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>1796.48</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>1803.92</v>
-      </c>
-      <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>187.53</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>173.98</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>165.12</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>161.85</v>
+      </c>
+      <c r="G39" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>CENTURYPLY</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>791.5</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>747.34</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>738.98</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>753.88</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>813.35</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>777.85</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>733.41</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>692.71</v>
+      </c>
+      <c r="G40" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>1236.25</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>1117.93</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>1045.03</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>1028.99</v>
-      </c>
-      <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>481.45</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>454.3</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>444.18</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>408.35</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>4441.8</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>4368.4</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>4254.86</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>3941.05</v>
-      </c>
-      <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>4466.2</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>4214.23</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>3903.62</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>3184.87</v>
+      </c>
+      <c r="G42" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>1515</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>1404.82</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>1377.77</v>
-      </c>
-      <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>JPPOWER</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="G43" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>520.5</v>
+        <v>561.15</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>501.64</v>
+        <v>537.6900000000001</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>484.9</v>
+        <v>514.86</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>488.93</v>
+        <v>502.1</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>2328.3</v>
+        <v>83.2</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>2228.02</v>
+        <v>80.86</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>2232.05</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>2326.19</v>
+        <v>79.3</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>787</v>
+        <v>316.6</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>763.47</v>
+        <v>294.81</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>759.96</v>
+        <v>278.19</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>741.73</v>
+        <v>256.08</v>
       </c>
       <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>1417.3</v>
+        <v>399.15</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>1303.58</v>
+        <v>393.23</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>1272.98</v>
+        <v>380.7</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>1243.53</v>
+        <v>353.93</v>
       </c>
       <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>3315.4</v>
+        <v>318.35</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>3005.96</v>
+        <v>312.02</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>2895.38</v>
+        <v>301.69</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>2871.98</v>
+        <v>286.83</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
-        <v>1160.5</v>
+        <v>33550</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>1117.21</v>
+        <v>29730.86</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>1112.86</v>
+        <v>26696.68</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>1129.21</v>
+        <v>21726.92</v>
       </c>
       <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>1374.4</v>
+        <v>1243.7</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>1325.73</v>
+        <v>1073</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>1328.34</v>
+        <v>965.08</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>1374.11</v>
+        <v>828.3200000000001</v>
       </c>
       <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
         <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>3808.2</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>3594.63</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>3389.98</v>
+      </c>
+      <c r="F51" s="18" t="n">
+        <v>3199.03</v>
+      </c>
+      <c r="G51" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="F52" s="18" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="G52" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>444.55</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>426.11</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>405.47</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <v>390.06</v>
+      </c>
+      <c r="G53" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>4077.6</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>3853.66</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>3533.52</v>
+      </c>
+      <c r="F54" s="18" t="n">
+        <v>3268.32</v>
+      </c>
+      <c r="G54" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>1736</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>1603.87</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>1512.01</v>
+      </c>
+      <c r="F55" s="18" t="n">
+        <v>1410</v>
+      </c>
+      <c r="G55" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>TRITURBINE</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>573.25</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>531.67</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>505.65</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <v>514.86</v>
+      </c>
+      <c r="G56" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>521.05</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>504.78</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>488.13</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>487.58</v>
+      </c>
+      <c r="G57" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="n">
+        <v>775</v>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>767.29</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>762.03</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>742.41</v>
+      </c>
+      <c r="G58" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="n">
+        <v>1458.6</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>1342.94</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>1293.56</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>1249.05</v>
+      </c>
+      <c r="G59" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="n">
+        <v>3423.1</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>3115.34</v>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>2955.53</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>2887.24</v>
+      </c>
+      <c r="G60" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>1144.6</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>1126.57</v>
+      </c>
+      <c r="E61" s="14" t="n">
+        <v>1117.45</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>1130.79</v>
+      </c>
+      <c r="G61" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>VBL</t>
         </is>
       </c>
-      <c r="C51" s="18" t="n">
-        <v>518.85</v>
-      </c>
-      <c r="D51" s="18" t="n">
-        <v>456.23</v>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>445.77</v>
-      </c>
-      <c r="F51" s="18" t="n">
-        <v>464.93</v>
-      </c>
-      <c r="G51" s="19">
+      <c r="C62" s="14" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>471.92</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>453.57</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>465.18</v>
+      </c>
+      <c r="G62" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="n">
-        <v>635.6</v>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>587.28</v>
-      </c>
-      <c r="E52" s="14" t="n">
-        <v>561.6900000000001</v>
-      </c>
-      <c r="F52" s="14" t="n">
-        <v>579.8200000000001</v>
-      </c>
-      <c r="G52" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>GAIL</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="n">
-        <v>165.74</v>
-      </c>
-      <c r="D53" s="14" t="n">
-        <v>156.64</v>
-      </c>
-      <c r="E53" s="14" t="n">
-        <v>155.71</v>
-      </c>
-      <c r="F53" s="14" t="n">
-        <v>164.95</v>
-      </c>
-      <c r="G53" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n">
-        <v>476.2</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>471.7</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>467.87</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>439.09</v>
-      </c>
-      <c r="G54" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="n">
-        <v>285.9</v>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>282.61</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>274.47</v>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>252.22</v>
-      </c>
-      <c r="G55" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="n">
-        <v>7430.5</v>
-      </c>
-      <c r="D56" s="18" t="n">
-        <v>6898.81</v>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>6401.58</v>
-      </c>
-      <c r="F56" s="18" t="n">
-        <v>5730.13</v>
-      </c>
-      <c r="G56" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="n">
-        <v>1435.45</v>
-      </c>
-      <c r="D57" s="18" t="n">
-        <v>1227.72</v>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>1110.39</v>
-      </c>
-      <c r="F57" s="18" t="n">
-        <v>989.92</v>
-      </c>
-      <c r="G57" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n">
-        <v>1229.7</v>
-      </c>
-      <c r="D58" s="18" t="n">
-        <v>1082.15</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>1002.02</v>
-      </c>
-      <c r="F58" s="18" t="n">
-        <v>981.1</v>
-      </c>
-      <c r="G58" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>ADANIPOWER</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="n">
-        <v>218.05</v>
-      </c>
-      <c r="D59" s="18" t="n">
-        <v>187.95</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>168.25</v>
-      </c>
-      <c r="F59" s="18" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="G59" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="n">
-        <v>348.58</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>302.67</v>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>281.92</v>
-      </c>
-      <c r="F60" s="18" t="n">
-        <v>262.75</v>
-      </c>
-      <c r="G60" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n">
-        <v>188.01</v>
-      </c>
-      <c r="D61" s="18" t="n">
-        <v>168.93</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>162.14</v>
-      </c>
-      <c r="F61" s="18" t="n">
-        <v>161.06</v>
-      </c>
-      <c r="G61" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="n">
-        <v>820.3</v>
-      </c>
-      <c r="D62" s="18" t="n">
-        <v>762.12</v>
-      </c>
-      <c r="E62" s="18" t="n">
-        <v>721.97</v>
-      </c>
-      <c r="F62" s="18" t="n">
-        <v>689.3200000000001</v>
-      </c>
-      <c r="G62" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C63" s="18" t="n">
-        <v>452.5</v>
+        <v>8024</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>446.5</v>
+        <v>7612.4</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>440.08</v>
+        <v>7296</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>407.23</v>
+        <v>7080.87</v>
       </c>
       <c r="G63" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>4556.8</v>
+        <v>797.65</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>4118.71</v>
+        <v>761.58</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>3829.09</v>
+        <v>746.11</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>3142.55</v>
+        <v>752.8</v>
       </c>
       <c r="G64" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="C65" s="18" t="n">
-        <v>19.63</v>
+        <v>1187.65</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>17.86</v>
+        <v>1141.4</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>16.62</v>
+        <v>1063.57</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>16.77</v>
+        <v>1034.63</v>
       </c>
       <c r="G65" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="C66" s="18" t="n">
-        <v>573.8</v>
+        <v>4385.2</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>527.48</v>
+        <v>4379.94</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>508.18</v>
+        <v>4272.81</v>
       </c>
       <c r="F66" s="18" t="n">
-        <v>499.85</v>
+        <v>3955.9</v>
       </c>
       <c r="G66" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C67" s="18" t="n">
-        <v>83.23</v>
+        <v>1430.4</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>79.70999999999999</v>
+        <v>1421.58</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>77.98</v>
+        <v>1408.03</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>79.23</v>
+        <v>1379.68</v>
       </c>
       <c r="G67" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>NLCINDIA</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="n">
-        <v>313.85</v>
-      </c>
-      <c r="D68" s="18" t="n">
-        <v>286.82</v>
-      </c>
-      <c r="E68" s="18" t="n">
-        <v>273.17</v>
-      </c>
-      <c r="F68" s="18" t="n">
-        <v>255.05</v>
-      </c>
-      <c r="G68" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="n">
+        <v>78.37</v>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>62.15</v>
+      </c>
+      <c r="G68" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="C69" s="18" t="n">
-        <v>410.2</v>
+        <v>9994</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>390.1</v>
+        <v>9568.299999999999</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>377.94</v>
+        <v>9476.799999999999</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>353.03</v>
+        <v>9105.360000000001</v>
       </c>
       <c r="G69" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C70" s="18" t="n">
-        <v>320.9</v>
+        <v>1881.6</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>309.5</v>
+        <v>1838.36</v>
       </c>
       <c r="E70" s="18" t="n">
-        <v>299.46</v>
+        <v>1764.52</v>
       </c>
       <c r="F70" s="18" t="n">
-        <v>285.93</v>
+        <v>1509.25</v>
       </c>
       <c r="G70" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C71" s="18" t="n">
-        <v>32065</v>
+        <v>35995</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>28549.19</v>
+        <v>35964.46</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>25881.41</v>
+        <v>35087.14</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>21332.95</v>
+        <v>35209.32</v>
       </c>
       <c r="G71" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="C72" s="18" t="n">
-        <v>1182</v>
+        <v>360.55</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>1029.8</v>
+        <v>336.49</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>935.84</v>
+        <v>329.57</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>819.15</v>
+        <v>350.29</v>
       </c>
       <c r="G72" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="n">
-        <v>3856</v>
-      </c>
-      <c r="D73" s="18" t="n">
-        <v>3521.48</v>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>3337.21</v>
-      </c>
-      <c r="F73" s="18" t="n">
-        <v>3181.91</v>
-      </c>
-      <c r="G73" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="n">
+        <v>2712.6</v>
+      </c>
+      <c r="D73" s="14" t="n">
+        <v>2658.2</v>
+      </c>
+      <c r="E73" s="14" t="n">
+        <v>2602.35</v>
+      </c>
+      <c r="F73" s="14" t="n">
+        <v>2589.41</v>
+      </c>
+      <c r="G73" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>SJVN</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="n">
-        <v>80.41</v>
-      </c>
-      <c r="D74" s="18" t="n">
-        <v>74.75</v>
-      </c>
-      <c r="E74" s="18" t="n">
-        <v>73.22</v>
-      </c>
-      <c r="F74" s="18" t="n">
-        <v>79.81</v>
-      </c>
-      <c r="G74" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SJVN","Chart 📈")</f>
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="n">
+        <v>554.7</v>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>538.01</v>
+      </c>
+      <c r="E74" s="14" t="n">
+        <v>527.6</v>
+      </c>
+      <c r="F74" s="14" t="n">
+        <v>543.92</v>
+      </c>
+      <c r="G74" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="n">
-        <v>56.93</v>
-      </c>
-      <c r="D75" s="18" t="n">
-        <v>49.11</v>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="F75" s="18" t="n">
-        <v>51.34</v>
-      </c>
-      <c r="G75" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="n">
+        <v>2971.5</v>
+      </c>
+      <c r="D75" s="14" t="n">
+        <v>2769.28</v>
+      </c>
+      <c r="E75" s="14" t="n">
+        <v>2612.01</v>
+      </c>
+      <c r="F75" s="14" t="n">
+        <v>2149.69</v>
+      </c>
+      <c r="G75" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C76" s="18" t="n">
-        <v>453.2</v>
+        <v>116.03</v>
       </c>
       <c r="D76" s="18" t="n">
-        <v>417.02</v>
+        <v>94.16</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>399.49</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>389.07</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="G76" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C77" s="18" t="n">
-        <v>4156.3</v>
+        <v>10.22</v>
       </c>
       <c r="D77" s="18" t="n">
-        <v>3791.99</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>3470.41</v>
+        <v>9.76</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>3255.39</v>
+        <v>9.42</v>
       </c>
       <c r="G77" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C78" s="18" t="n">
-        <v>1772.5</v>
+        <v>9726.5</v>
       </c>
       <c r="D78" s="18" t="n">
-        <v>1559.59</v>
+        <v>8297.610000000001</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>1484.14</v>
+        <v>7673.26</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>1401.74</v>
+        <v>7840.63</v>
       </c>
       <c r="G78" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="n">
-        <v>580</v>
-      </c>
-      <c r="D79" s="18" t="n">
-        <v>516.0700000000001</v>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>496.63</v>
-      </c>
-      <c r="F79" s="18" t="n">
-        <v>513.4</v>
-      </c>
-      <c r="G79" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="n">
+        <v>1015.95</v>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>994.91</v>
+      </c>
+      <c r="E79" s="14" t="n">
+        <v>969.75</v>
+      </c>
+      <c r="F79" s="14" t="n">
+        <v>897.12</v>
+      </c>
+      <c r="G79" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C80" s="14" t="n">
-        <v>79.75</v>
+        <v>286.95</v>
       </c>
       <c r="D80" s="14" t="n">
-        <v>72.87</v>
+        <v>286.57</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>69.19</v>
+        <v>281.21</v>
       </c>
       <c r="F80" s="14" t="n">
-        <v>61.67</v>
+        <v>252.92</v>
       </c>
       <c r="G80" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="C81" s="14" t="n">
-        <v>1111.85</v>
+        <v>916.05</v>
       </c>
       <c r="D81" s="14" t="n">
-        <v>1081.24</v>
+        <v>861.1900000000001</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>1078.85</v>
+        <v>859.87</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>988.67</v>
+        <v>848.28</v>
       </c>
       <c r="G81" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C82" s="18" t="n">
-        <v>9662</v>
-      </c>
-      <c r="D82" s="18" t="n">
-        <v>9524.110000000001</v>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>9450.33</v>
-      </c>
-      <c r="F82" s="18" t="n">
-        <v>9093.370000000001</v>
-      </c>
-      <c r="G82" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C83" s="18" t="n">
-        <v>1901.1</v>
-      </c>
-      <c r="D83" s="18" t="n">
-        <v>1818.78</v>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>1747.94</v>
-      </c>
-      <c r="F83" s="18" t="n">
-        <v>1498.63</v>
-      </c>
-      <c r="G83" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B84" s="17" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C84" s="18" t="n">
-        <v>37225</v>
-      </c>
-      <c r="D84" s="18" t="n">
-        <v>35773.58</v>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>34902.37</v>
-      </c>
-      <c r="F84" s="18" t="n">
-        <v>35073.14</v>
-      </c>
-      <c r="G84" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="C85" s="18" t="n">
-        <v>7174</v>
-      </c>
-      <c r="D85" s="18" t="n">
-        <v>7109.06</v>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>7172.52</v>
-      </c>
-      <c r="F85" s="18" t="n">
-        <v>6860.18</v>
-      </c>
-      <c r="G85" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>EXIDEIND</t>
-        </is>
-      </c>
-      <c r="C86" s="18" t="n">
-        <v>352.35</v>
-      </c>
-      <c r="D86" s="18" t="n">
-        <v>328.18</v>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>325.68</v>
-      </c>
-      <c r="F86" s="18" t="n">
-        <v>352.15</v>
-      </c>
-      <c r="G86" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="n">
-        <v>127.93</v>
-      </c>
-      <c r="D87" s="18" t="n">
-        <v>121.62</v>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>119.75</v>
-      </c>
-      <c r="F87" s="18" t="n">
-        <v>112.22</v>
-      </c>
-      <c r="G87" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="n">
-        <v>1324.2</v>
-      </c>
-      <c r="D88" s="14" t="n">
-        <v>1323.18</v>
-      </c>
-      <c r="E88" s="14" t="n">
-        <v>1303.77</v>
-      </c>
-      <c r="F88" s="14" t="n">
-        <v>1253.71</v>
-      </c>
-      <c r="G88" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>HDFCAMC</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="n">
-        <v>2756</v>
-      </c>
-      <c r="D89" s="14" t="n">
-        <v>2625.38</v>
-      </c>
-      <c r="E89" s="14" t="n">
-        <v>2583.15</v>
-      </c>
-      <c r="F89" s="14" t="n">
-        <v>2586.71</v>
-      </c>
-      <c r="G89" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="n">
-        <v>2830</v>
-      </c>
-      <c r="D90" s="14" t="n">
-        <v>2706.57</v>
-      </c>
-      <c r="E90" s="14" t="n">
-        <v>2569.3</v>
-      </c>
-      <c r="F90" s="14" t="n">
-        <v>2126.17</v>
-      </c>
-      <c r="G90" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B91" s="13" t="inlineStr">
-        <is>
-          <t>MUTHOOTFIN</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="n">
-        <v>3493.8</v>
-      </c>
-      <c r="D91" s="14" t="n">
-        <v>3463.82</v>
-      </c>
-      <c r="E91" s="14" t="n">
-        <v>3454.91</v>
-      </c>
-      <c r="F91" s="14" t="n">
-        <v>3253.08</v>
-      </c>
-      <c r="G91" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
-        <is>
-          <t>PFC</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="n">
-        <v>474.9</v>
-      </c>
-      <c r="D92" s="14" t="n">
-        <v>444.97</v>
-      </c>
-      <c r="E92" s="14" t="n">
-        <v>421.15</v>
-      </c>
-      <c r="F92" s="14" t="n">
-        <v>395.39</v>
-      </c>
-      <c r="G92" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B93" s="13" t="inlineStr">
-        <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="n">
-        <v>378.05</v>
-      </c>
-      <c r="D93" s="14" t="n">
-        <v>358.9</v>
-      </c>
-      <c r="E93" s="14" t="n">
-        <v>350.08</v>
-      </c>
-      <c r="F93" s="14" t="n">
-        <v>358.78</v>
-      </c>
-      <c r="G93" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="n">
-        <v>106.69</v>
-      </c>
-      <c r="D94" s="18" t="n">
-        <v>88.45999999999999</v>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>79.45</v>
-      </c>
-      <c r="F94" s="18" t="n">
-        <v>74.95999999999999</v>
-      </c>
-      <c r="G94" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C95" s="18" t="n">
-        <v>9360</v>
-      </c>
-      <c r="D95" s="18" t="n">
-        <v>7818.17</v>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>7419.46</v>
-      </c>
-      <c r="F95" s="18" t="n">
-        <v>7787.96</v>
-      </c>
-      <c r="G95" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>TANLA</t>
-        </is>
-      </c>
-      <c r="C96" s="18" t="n">
-        <v>582.95</v>
-      </c>
-      <c r="D96" s="18" t="n">
-        <v>477.54</v>
-      </c>
-      <c r="E96" s="18" t="n">
-        <v>467.49</v>
-      </c>
-      <c r="F96" s="18" t="n">
-        <v>520.13</v>
-      </c>
-      <c r="G96" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="inlineStr">
-        <is>
-          <t>AUBANK</t>
-        </is>
-      </c>
-      <c r="C97" s="14" t="n">
-        <v>1043</v>
-      </c>
-      <c r="D97" s="14" t="n">
-        <v>986.62</v>
-      </c>
-      <c r="E97" s="14" t="n">
-        <v>963.51</v>
-      </c>
-      <c r="F97" s="14" t="n">
-        <v>894.27</v>
-      </c>
-      <c r="G97" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="n">
-        <v>294.05</v>
-      </c>
-      <c r="D98" s="14" t="n">
-        <v>286.32</v>
-      </c>
-      <c r="E98" s="14" t="n">
-        <v>280.42</v>
-      </c>
-      <c r="F98" s="14" t="n">
-        <v>252.14</v>
-      </c>
-      <c r="G98" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B99" s="13" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C99" s="14" t="n">
-        <v>900.15</v>
-      </c>
-      <c r="D99" s="14" t="n">
-        <v>845.45</v>
-      </c>
-      <c r="E99" s="14" t="n">
-        <v>854.04</v>
-      </c>
-      <c r="F99" s="14" t="n">
-        <v>845.88</v>
-      </c>
-      <c r="G99" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 30-Apr-2026  16:22</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 01-May-2026  14:53</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>0.8</v>
@@ -718,10 +718,10 @@
         <v>0.75</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.75</v>
+        <v>0.7667</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -851,7 +851,7 @@
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -861,7 +861,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>6</v>
@@ -870,19 +870,19 @@
         <v>0.733</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.5777</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
@@ -892,19 +892,19 @@
         <v>11</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0.733</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="I11" s="11" t="n">
         <v>0.5777</v>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1242,7 +1242,7 @@
         <v>2136.63</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2232.81</v>
+        <v>2232.62</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1270,7 +1270,7 @@
         <v>968.85</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>857.12</v>
+        <v>857.61</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1298,7 +1298,7 @@
         <v>567.61</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>529.45</v>
+        <v>528.6</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1354,7 +1354,7 @@
         <v>1212.89</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1154.97</v>
+        <v>1149.77</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
@@ -1382,7 +1382,7 @@
         <v>83.41</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>76.59999999999999</v>
+        <v>76.63</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
@@ -1410,7 +1410,7 @@
         <v>2380.89</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>2400.48</v>
+        <v>2396.01</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
@@ -1438,7 +1438,7 @@
         <v>163.69</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>145.35</v>
+        <v>145.3</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
@@ -1466,7 +1466,7 @@
         <v>202.18</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>182.59</v>
+        <v>182.7</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
@@ -1494,7 +1494,7 @@
         <v>962.4299999999999</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>866.0599999999999</v>
+        <v>865.51</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
@@ -1522,7 +1522,7 @@
         <v>1314.21</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>1219.32</v>
+        <v>1217.48</v>
       </c>
       <c r="G13" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1550,7 +1550,7 @@
         <v>6221.11</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>6263.83</v>
+        <v>6263.2</v>
       </c>
       <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1578,7 +1578,7 @@
         <v>1267.54</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>1252.58</v>
+        <v>1252.08</v>
       </c>
       <c r="G15" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
@@ -1606,7 +1606,7 @@
         <v>1740.75</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>1741.69</v>
+        <v>1742.02</v>
       </c>
       <c r="G16" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1634,7 +1634,7 @@
         <v>2181.04</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>1984.02</v>
+        <v>1983.08</v>
       </c>
       <c r="G17" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
@@ -1662,7 +1662,7 @@
         <v>629.5700000000001</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>569.5599999999999</v>
+        <v>569.34</v>
       </c>
       <c r="G18" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
@@ -1690,7 +1690,7 @@
         <v>1499.65</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>1448.17</v>
+        <v>1446.33</v>
       </c>
       <c r="G19" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
@@ -1718,7 +1718,7 @@
         <v>2002.7</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>1856.51</v>
+        <v>1853.52</v>
       </c>
       <c r="G20" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
@@ -1743,10 +1743,10 @@
         <v>1091.23</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>1060.93</v>
+        <v>1060.94</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>957.91</v>
+        <v>959.2</v>
       </c>
       <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1095.75</v>
+        <v>2246.7</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1069.16</v>
+        <v>2176.89</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>1014.01</v>
+        <v>2143.06</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>923.34</v>
+        <v>2240.73</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1808.3</v>
+        <v>1095.75</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1719.35</v>
+        <v>1069.16</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>1723.25</v>
+        <v>1014.01</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>1716.53</v>
+        <v>922.71</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,79 +1817,79 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>1808.3</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1719.35</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1723.25</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>1715.89</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
           <t>TORNTPHARM</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C25" s="18" t="n">
         <v>4185.1</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D25" s="18" t="n">
         <v>4171.75</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E25" s="18" t="n">
         <v>4158.01</v>
       </c>
-      <c r="F24" s="18" t="n">
-        <v>3870.47</v>
-      </c>
-      <c r="G24" s="19">
+      <c r="F25" s="18" t="n">
+        <v>3863.05</v>
+      </c>
+      <c r="G25" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>OBEROIRLTY</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C26" s="14" t="n">
         <v>1669.6</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D26" s="14" t="n">
         <v>1655.66</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E26" s="14" t="n">
         <v>1600.07</v>
       </c>
-      <c r="F25" s="14" t="n">
-        <v>1618.05</v>
-      </c>
-      <c r="G25" s="15">
+      <c r="F26" s="14" t="n">
+        <v>1614.9</v>
+      </c>
+      <c r="G26" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>1765</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>1735.61</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>1701.57</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>1681.69</v>
-      </c>
-      <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1901,135 +1901,135 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>1765</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>1735.61</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>1701.56</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>1670.92</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
           <t>SOBHA</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C28" s="14" t="n">
         <v>1433.4</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D28" s="14" t="n">
         <v>1362.96</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E28" s="14" t="n">
         <v>1359.91</v>
       </c>
-      <c r="F27" s="14" t="n">
-        <v>1427.06</v>
-      </c>
-      <c r="G27" s="15">
+      <c r="F28" s="14" t="n">
+        <v>1426.47</v>
+      </c>
+      <c r="G28" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>PVRINOX</t>
         </is>
       </c>
-      <c r="C28" s="18" t="n">
+      <c r="C29" s="18" t="n">
         <v>1068.9</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D29" s="18" t="n">
         <v>998.45</v>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E29" s="18" t="n">
         <v>994.97</v>
       </c>
-      <c r="F28" s="18" t="n">
-        <v>1020.14</v>
-      </c>
-      <c r="G28" s="19">
+      <c r="F29" s="18" t="n">
+        <v>1021.25</v>
+      </c>
+      <c r="G29" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>TIPSMUSIC</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n">
+      <c r="C30" s="18" t="n">
         <v>649.7</v>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D30" s="18" t="n">
         <v>600.23</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E30" s="18" t="n">
         <v>565.1900000000001</v>
       </c>
-      <c r="F29" s="18" t="n">
-        <v>558.6799999999999</v>
-      </c>
-      <c r="G29" s="19">
+      <c r="F30" s="18" t="n">
+        <v>558.96</v>
+      </c>
+      <c r="G30" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>ATGL</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C31" s="14" t="n">
         <v>634.7</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D31" s="14" t="n">
         <v>602.99</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E31" s="14" t="n">
         <v>571.48</v>
       </c>
-      <c r="F30" s="14" t="n">
-        <v>580.46</v>
-      </c>
-      <c r="G30" s="15">
+      <c r="F31" s="14" t="n">
+        <v>580.4299999999999</v>
+      </c>
+      <c r="G31" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>490.8</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>477.33</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>470.77</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>441.15</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2041,23 +2041,23 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>299.55</v>
+        <v>490.8</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>287.3</v>
+        <v>477.33</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>277.44</v>
+        <v>470.77</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>253.17</v>
+        <v>440.76</v>
       </c>
       <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2069,79 +2069,79 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>299.55</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>287.3</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>277.44</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>253.04</v>
+      </c>
+      <c r="G33" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
           <t>RELIANCE</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C34" s="14" t="n">
         <v>1430.8</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D34" s="14" t="n">
         <v>1371.16</v>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E34" s="14" t="n">
         <v>1385.69</v>
       </c>
-      <c r="F33" s="14" t="n">
-        <v>1424.35</v>
-      </c>
-      <c r="G33" s="15">
+      <c r="F34" s="14" t="n">
+        <v>1425.58</v>
+      </c>
+      <c r="G34" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="C34" s="18" t="n">
+      <c r="C35" s="18" t="n">
         <v>7230</v>
       </c>
-      <c r="D34" s="18" t="n">
+      <c r="D35" s="18" t="n">
         <v>6966.53</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E35" s="18" t="n">
         <v>6473.35</v>
       </c>
-      <c r="F34" s="18" t="n">
-        <v>5750.99</v>
-      </c>
-      <c r="G34" s="19">
+      <c r="F35" s="18" t="n">
+        <v>5747</v>
+      </c>
+      <c r="G35" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>1342.25</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>1255.03</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>1131.08</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>995.5</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2153,23 +2153,23 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>1227.15</v>
+        <v>1342.25</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>1123.06</v>
+        <v>1255.03</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>1028.97</v>
+        <v>1131.08</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>985.4400000000001</v>
+        <v>996.14</v>
       </c>
       <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2181,23 +2181,23 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
-        <v>221.85</v>
+        <v>1227.15</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>196.64</v>
+        <v>1123.06</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>174.27</v>
+        <v>1028.97</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>147.69</v>
+        <v>985.86</v>
       </c>
       <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2209,23 +2209,23 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
-        <v>352.41</v>
+        <v>221.85</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>315.07</v>
+        <v>196.64</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>289.68</v>
+        <v>174.27</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>265.06</v>
+        <v>147.6</v>
       </c>
       <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2237,23 +2237,23 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
-        <v>187.53</v>
+        <v>352.41</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>173.98</v>
+        <v>315.07</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>165.12</v>
+        <v>289.68</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>161.85</v>
+        <v>264.89</v>
       </c>
       <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2265,23 +2265,23 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>813.35</v>
+        <v>187.53</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>777.85</v>
+        <v>173.98</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>733.41</v>
+        <v>165.12</v>
       </c>
       <c r="F40" s="18" t="n">
-        <v>692.71</v>
+        <v>161.82</v>
       </c>
       <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2293,23 +2293,23 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C41" s="18" t="n">
-        <v>481.45</v>
+        <v>813.35</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>454.3</v>
+        <v>777.85</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>444.18</v>
+        <v>733.41</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>408.35</v>
+        <v>692.1900000000001</v>
       </c>
       <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2321,23 +2321,23 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>4466.2</v>
+        <v>481.45</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>4214.23</v>
+        <v>454.3</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>3903.62</v>
+        <v>444.18</v>
       </c>
       <c r="F42" s="18" t="n">
-        <v>3184.87</v>
+        <v>408.21</v>
       </c>
       <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2349,23 +2349,23 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C43" s="18" t="n">
-        <v>19.72</v>
+        <v>4466.2</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>18.4</v>
+        <v>4214.23</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>16.99</v>
+        <v>3903.62</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>16.84</v>
+        <v>3183.41</v>
       </c>
       <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2377,23 +2377,23 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>561.15</v>
+        <v>19.72</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>537.6900000000001</v>
+        <v>18.4</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>514.86</v>
+        <v>16.99</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>502.1</v>
+        <v>16.81</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2405,23 +2405,23 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>83.2</v>
+        <v>561.15</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>80.86</v>
+        <v>537.6900000000001</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>78.68000000000001</v>
+        <v>514.86</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>79.3</v>
+        <v>501.27</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>316.6</v>
+        <v>83.2</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>294.81</v>
+        <v>80.86</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>278.19</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>256.08</v>
+        <v>79.23</v>
       </c>
       <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2461,23 +2461,23 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>399.15</v>
+        <v>316.6</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>393.23</v>
+        <v>294.81</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>380.7</v>
+        <v>278.19</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>353.93</v>
+        <v>255.87</v>
       </c>
       <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>318.35</v>
+        <v>399.15</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>312.02</v>
+        <v>393.23</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>301.69</v>
+        <v>380.7</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>286.83</v>
+        <v>353.46</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2517,23 +2517,23 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
-        <v>33550</v>
+        <v>318.35</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>29730.86</v>
+        <v>312.02</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>26696.68</v>
+        <v>301.69</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>21726.92</v>
+        <v>286.47</v>
       </c>
       <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2545,23 +2545,23 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>1243.7</v>
+        <v>33550</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>1073</v>
+        <v>29730.86</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>965.08</v>
+        <v>26696.69</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>828.3200000000001</v>
+        <v>21742.83</v>
       </c>
       <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2573,23 +2573,23 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>3808.2</v>
+        <v>1243.7</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>3594.63</v>
+        <v>1073</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>3389.98</v>
+        <v>965.08</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>3199.03</v>
+        <v>828.35</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2601,23 +2601,23 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>55.58</v>
+        <v>3808.2</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>51.03</v>
+        <v>3594.63</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>47.91</v>
+        <v>3389.98</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>51.38</v>
+        <v>3199.96</v>
       </c>
       <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2629,23 +2629,23 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
-        <v>444.55</v>
+        <v>55.58</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>426.11</v>
+        <v>51.03</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>405.47</v>
+        <v>47.91</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>390.06</v>
+        <v>51.36</v>
       </c>
       <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2657,23 +2657,23 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>4077.6</v>
+        <v>444.55</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>3853.66</v>
+        <v>426.11</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>3533.52</v>
+        <v>405.47</v>
       </c>
       <c r="F54" s="18" t="n">
-        <v>3268.32</v>
+        <v>389.8</v>
       </c>
       <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2685,23 +2685,23 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C55" s="18" t="n">
-        <v>1736</v>
+        <v>4077.6</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>1603.87</v>
+        <v>3853.66</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>1512.01</v>
+        <v>3533.52</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>1410</v>
+        <v>3263.39</v>
       </c>
       <c r="G55" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2713,443 +2713,443 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>1736</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>1603.87</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>1512.01</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <v>1405.94</v>
+      </c>
+      <c r="G56" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
           <t>TRITURBINE</t>
         </is>
       </c>
-      <c r="C56" s="18" t="n">
+      <c r="C57" s="18" t="n">
         <v>573.25</v>
       </c>
-      <c r="D56" s="18" t="n">
+      <c r="D57" s="18" t="n">
         <v>531.67</v>
       </c>
-      <c r="E56" s="18" t="n">
+      <c r="E57" s="18" t="n">
         <v>505.65</v>
       </c>
-      <c r="F56" s="18" t="n">
-        <v>514.86</v>
-      </c>
-      <c r="G56" s="19">
+      <c r="F57" s="18" t="n">
+        <v>513.96</v>
+      </c>
+      <c r="G57" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="n">
-        <v>521.05</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>504.78</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>488.13</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>487.58</v>
-      </c>
-      <c r="G57" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C58" s="14" t="n">
-        <v>775</v>
+        <v>8024</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>767.29</v>
+        <v>7612.4</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>762.03</v>
+        <v>7296.01</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>742.41</v>
+        <v>7083.59</v>
       </c>
       <c r="G58" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="C59" s="14" t="n">
-        <v>1458.6</v>
+        <v>797.65</v>
       </c>
       <c r="D59" s="14" t="n">
-        <v>1342.94</v>
+        <v>761.58</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>1293.56</v>
+        <v>746.11</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>1249.05</v>
+        <v>752.34</v>
       </c>
       <c r="G59" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="C60" s="14" t="n">
-        <v>3423.1</v>
+        <v>272.36</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>3115.34</v>
+        <v>256.02</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>2955.53</v>
+        <v>251.91</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>2887.24</v>
+        <v>272.19</v>
       </c>
       <c r="G60" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="C61" s="14" t="n">
-        <v>1144.6</v>
+        <v>1187.65</v>
       </c>
       <c r="D61" s="14" t="n">
-        <v>1126.57</v>
+        <v>1141.4</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>1117.45</v>
+        <v>1063.57</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>1130.79</v>
+        <v>1034.21</v>
       </c>
       <c r="G61" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>4385.2</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>4379.94</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>4272.81</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>3952.75</v>
+      </c>
+      <c r="G62" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>1430.4</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>1421.58</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>1408.03</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>1376.98</v>
+      </c>
+      <c r="G63" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
-        <v>513.7</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>471.92</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>453.57</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>465.18</v>
-      </c>
-      <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="n">
-        <v>8024</v>
-      </c>
-      <c r="D63" s="18" t="n">
-        <v>7612.4</v>
-      </c>
-      <c r="E63" s="18" t="n">
-        <v>7296</v>
-      </c>
-      <c r="F63" s="18" t="n">
-        <v>7080.87</v>
-      </c>
-      <c r="G63" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>797.65</v>
+        <v>521.05</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>761.58</v>
+        <v>504.78</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>746.11</v>
+        <v>488.13</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>752.8</v>
+        <v>487.27</v>
       </c>
       <c r="G64" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C65" s="18" t="n">
-        <v>1187.65</v>
+        <v>775</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>1141.4</v>
+        <v>767.29</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>1063.57</v>
+        <v>762.03</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>1034.63</v>
+        <v>741.4400000000001</v>
       </c>
       <c r="G65" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C66" s="18" t="n">
-        <v>4385.2</v>
+        <v>1458.6</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>4379.94</v>
+        <v>1342.94</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>4272.81</v>
+        <v>1293.56</v>
       </c>
       <c r="F66" s="18" t="n">
-        <v>3955.9</v>
+        <v>1246.71</v>
       </c>
       <c r="G66" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C67" s="18" t="n">
-        <v>1430.4</v>
+        <v>3423.1</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>1421.58</v>
+        <v>3115.34</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>1408.03</v>
+        <v>2955.53</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>1379.68</v>
+        <v>2886.68</v>
       </c>
       <c r="G67" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="12" t="inlineStr">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>1144.6</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>1126.57</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>1117.45</v>
+      </c>
+      <c r="F68" s="18" t="n">
+        <v>1129.87</v>
+      </c>
+      <c r="G68" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>471.92</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>453.57</v>
+      </c>
+      <c r="F69" s="18" t="n">
+        <v>465.14</v>
+      </c>
+      <c r="G69" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>MAHABANK</t>
         </is>
       </c>
-      <c r="C68" s="14" t="n">
+      <c r="C70" s="14" t="n">
         <v>78.37</v>
       </c>
-      <c r="D68" s="14" t="n">
+      <c r="D70" s="14" t="n">
         <v>74.34999999999999</v>
       </c>
-      <c r="E68" s="14" t="n">
+      <c r="E70" s="14" t="n">
         <v>70.25</v>
       </c>
-      <c r="F68" s="14" t="n">
-        <v>62.15</v>
-      </c>
-      <c r="G68" s="15">
+      <c r="F70" s="14" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="G70" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B69" s="17" t="inlineStr">
+      <c r="B71" s="17" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="C69" s="18" t="n">
+      <c r="C71" s="18" t="n">
         <v>9994</v>
       </c>
-      <c r="D69" s="18" t="n">
+      <c r="D71" s="18" t="n">
         <v>9568.299999999999</v>
       </c>
-      <c r="E69" s="18" t="n">
-        <v>9476.799999999999</v>
-      </c>
-      <c r="F69" s="18" t="n">
-        <v>9105.360000000001</v>
-      </c>
-      <c r="G69" s="19">
+      <c r="E71" s="18" t="n">
+        <v>9476.790000000001</v>
+      </c>
+      <c r="F71" s="18" t="n">
+        <v>9088.25</v>
+      </c>
+      <c r="G71" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="n">
-        <v>1881.6</v>
-      </c>
-      <c r="D70" s="18" t="n">
-        <v>1838.36</v>
-      </c>
-      <c r="E70" s="18" t="n">
-        <v>1764.52</v>
-      </c>
-      <c r="F70" s="18" t="n">
-        <v>1509.25</v>
-      </c>
-      <c r="G70" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="n">
-        <v>35995</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>35964.46</v>
-      </c>
-      <c r="E71" s="18" t="n">
-        <v>35087.14</v>
-      </c>
-      <c r="F71" s="18" t="n">
-        <v>35209.32</v>
-      </c>
-      <c r="G71" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3161,274 +3161,330 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="n">
+        <v>1881.6</v>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>1838.36</v>
+      </c>
+      <c r="E72" s="18" t="n">
+        <v>1764.52</v>
+      </c>
+      <c r="F72" s="18" t="n">
+        <v>1509.26</v>
+      </c>
+      <c r="G72" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>35995</v>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>35964.46</v>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>35087.14</v>
+      </c>
+      <c r="F73" s="18" t="n">
+        <v>35208.49</v>
+      </c>
+      <c r="G73" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
           <t>EXIDEIND</t>
         </is>
       </c>
-      <c r="C72" s="18" t="n">
+      <c r="C74" s="18" t="n">
         <v>360.55</v>
       </c>
-      <c r="D72" s="18" t="n">
+      <c r="D74" s="18" t="n">
         <v>336.49</v>
       </c>
-      <c r="E72" s="18" t="n">
-        <v>329.57</v>
-      </c>
-      <c r="F72" s="18" t="n">
-        <v>350.29</v>
-      </c>
-      <c r="G72" s="19">
+      <c r="E74" s="18" t="n">
+        <v>329.58</v>
+      </c>
+      <c r="F74" s="18" t="n">
+        <v>350.56</v>
+      </c>
+      <c r="G74" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="12" t="inlineStr">
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B75" s="13" t="inlineStr">
         <is>
           <t>HDFCAMC</t>
         </is>
       </c>
-      <c r="C73" s="14" t="n">
+      <c r="C75" s="14" t="n">
         <v>2712.6</v>
       </c>
-      <c r="D73" s="14" t="n">
+      <c r="D75" s="14" t="n">
         <v>2658.2</v>
       </c>
-      <c r="E73" s="14" t="n">
+      <c r="E75" s="14" t="n">
         <v>2602.35</v>
       </c>
-      <c r="F73" s="14" t="n">
-        <v>2589.41</v>
-      </c>
-      <c r="G73" s="15">
+      <c r="F75" s="14" t="n">
+        <v>2590.1</v>
+      </c>
+      <c r="G75" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="16" t="inlineStr">
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>LICHSGFIN</t>
         </is>
       </c>
-      <c r="C74" s="14" t="n">
+      <c r="C76" s="14" t="n">
         <v>554.7</v>
       </c>
-      <c r="D74" s="14" t="n">
+      <c r="D76" s="14" t="n">
         <v>538.01</v>
       </c>
-      <c r="E74" s="14" t="n">
+      <c r="E76" s="14" t="n">
         <v>527.6</v>
       </c>
-      <c r="F74" s="14" t="n">
-        <v>543.92</v>
-      </c>
-      <c r="G74" s="15">
+      <c r="F76" s="14" t="n">
+        <v>543.96</v>
+      </c>
+      <c r="G76" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="16" t="inlineStr">
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="16" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B75" s="13" t="inlineStr">
+      <c r="B77" s="13" t="inlineStr">
         <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C75" s="14" t="n">
+      <c r="C77" s="14" t="n">
         <v>2971.5</v>
       </c>
-      <c r="D75" s="14" t="n">
+      <c r="D77" s="14" t="n">
         <v>2769.28</v>
       </c>
-      <c r="E75" s="14" t="n">
+      <c r="E77" s="14" t="n">
         <v>2612.01</v>
       </c>
-      <c r="F75" s="14" t="n">
-        <v>2149.69</v>
-      </c>
-      <c r="G75" s="15">
+      <c r="F77" s="14" t="n">
+        <v>2152.27</v>
+      </c>
+      <c r="G77" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B76" s="17" t="inlineStr">
+      <c r="B78" s="17" t="inlineStr">
         <is>
           <t>HFCL</t>
         </is>
       </c>
-      <c r="C76" s="18" t="n">
+      <c r="C78" s="18" t="n">
         <v>116.03</v>
       </c>
-      <c r="D76" s="18" t="n">
+      <c r="D78" s="18" t="n">
         <v>94.16</v>
       </c>
-      <c r="E76" s="18" t="n">
+      <c r="E78" s="18" t="n">
         <v>82.93000000000001</v>
       </c>
-      <c r="F76" s="18" t="n">
-        <v>75.79000000000001</v>
-      </c>
-      <c r="G76" s="19">
+      <c r="F78" s="18" t="n">
+        <v>75.68000000000001</v>
+      </c>
+      <c r="G78" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="20" t="inlineStr">
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B77" s="17" t="inlineStr">
+      <c r="B79" s="17" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="C77" s="18" t="n">
+      <c r="C79" s="18" t="n">
         <v>10.22</v>
       </c>
-      <c r="D77" s="18" t="n">
+      <c r="D79" s="18" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="E77" s="18" t="n">
+      <c r="E79" s="18" t="n">
         <v>9.76</v>
       </c>
-      <c r="F77" s="18" t="n">
+      <c r="F79" s="18" t="n">
         <v>9.42</v>
       </c>
-      <c r="G77" s="19">
+      <c r="G79" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="20" t="inlineStr">
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B78" s="17" t="inlineStr">
+      <c r="B80" s="17" t="inlineStr">
         <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="C78" s="18" t="n">
+      <c r="C80" s="18" t="n">
         <v>9726.5</v>
       </c>
-      <c r="D78" s="18" t="n">
+      <c r="D80" s="18" t="n">
         <v>8297.610000000001</v>
       </c>
-      <c r="E78" s="18" t="n">
-        <v>7673.26</v>
-      </c>
-      <c r="F78" s="18" t="n">
-        <v>7840.63</v>
-      </c>
-      <c r="G78" s="19">
+      <c r="E80" s="18" t="n">
+        <v>7673.25</v>
+      </c>
+      <c r="F80" s="18" t="n">
+        <v>7837</v>
+      </c>
+      <c r="G80" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="12" t="inlineStr">
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="12" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B79" s="13" t="inlineStr">
+      <c r="B81" s="13" t="inlineStr">
         <is>
           <t>AUBANK</t>
         </is>
       </c>
-      <c r="C79" s="14" t="n">
+      <c r="C81" s="14" t="n">
         <v>1015.95</v>
       </c>
-      <c r="D79" s="14" t="n">
+      <c r="D81" s="14" t="n">
         <v>994.91</v>
       </c>
-      <c r="E79" s="14" t="n">
+      <c r="E81" s="14" t="n">
         <v>969.75</v>
       </c>
-      <c r="F79" s="14" t="n">
-        <v>897.12</v>
-      </c>
-      <c r="G79" s="15">
+      <c r="F81" s="14" t="n">
+        <v>897.28</v>
+      </c>
+      <c r="G81" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="16" t="inlineStr">
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="16" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C80" s="14" t="n">
+      <c r="C82" s="14" t="n">
         <v>286.95</v>
       </c>
-      <c r="D80" s="14" t="n">
+      <c r="D82" s="14" t="n">
         <v>286.57</v>
       </c>
-      <c r="E80" s="14" t="n">
+      <c r="E82" s="14" t="n">
         <v>281.21</v>
       </c>
-      <c r="F80" s="14" t="n">
-        <v>252.92</v>
-      </c>
-      <c r="G80" s="15">
+      <c r="F82" s="14" t="n">
+        <v>252.33</v>
+      </c>
+      <c r="G82" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="16" t="inlineStr">
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="16" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B81" s="13" t="inlineStr">
+      <c r="B83" s="13" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="C81" s="14" t="n">
+      <c r="C83" s="14" t="n">
         <v>916.05</v>
       </c>
-      <c r="D81" s="14" t="n">
+      <c r="D83" s="14" t="n">
         <v>861.1900000000001</v>
       </c>
-      <c r="E81" s="14" t="n">
+      <c r="E83" s="14" t="n">
         <v>859.87</v>
       </c>
-      <c r="F81" s="14" t="n">
-        <v>848.28</v>
-      </c>
-      <c r="G81" s="15">
+      <c r="F83" s="14" t="n">
+        <v>849.79</v>
+      </c>
+      <c r="G83" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 01-May-2026  14:53</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 04-May-2026  17:29</t>
         </is>
       </c>
     </row>
@@ -672,22 +672,22 @@
         <v>15</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>13</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0.867</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.9329999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>0.8223</v>
@@ -703,25 +703,25 @@
         <v>20</v>
       </c>
       <c r="C5" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="D5" s="9" t="n">
         <v>16</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>15</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G5" s="10" t="n">
         <v>0.8</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>0.75</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.75</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.7667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -737,7 +737,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3</v>
@@ -746,41 +746,41 @@
         <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.7</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="E7" s="9" t="n">
         <v>8</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.9</v>
+        <v>0.667</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I7" s="11" t="n">
         <v>0.6667000000000001</v>
@@ -796,25 +796,25 @@
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>12</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.6446999999999999</v>
+        <v>0.6443000000000001</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -833,7 +833,7 @@
         <v>25</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0.625</v>
@@ -842,10 +842,10 @@
         <v>0.625</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.575</v>
+        <v>0.6</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.6083</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -858,22 +858,22 @@
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="E10" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G10" s="6" t="n">
         <v>0.733</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>0.667</v>
-      </c>
       <c r="H10" s="6" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.6</v>
@@ -882,63 +882,63 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.5777</v>
+        <v>0.5667</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.417</v>
+        <v>0.55</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.417</v>
+        <v>0.45</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.417</v>
+        <v>0.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.417</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -954,22 +954,22 @@
         <v>5</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0.333</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.467</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.3997</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -985,50 +985,50 @@
         <v>6</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.3833</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.45</v>
+        <v>0.333</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.15</v>
+        <v>0.417</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>0.3333</v>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2408.4</v>
+        <v>2485.7</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2212.81</v>
+        <v>2238.8</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2136.63</v>
+        <v>2150.33</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2232.62</v>
+        <v>2248.23</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1038</v>
+        <v>1042.7</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1011.99</v>
+        <v>1014.92</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>968.85</v>
+        <v>971.75</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>857.61</v>
+        <v>859.6900000000001</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>595.95</v>
+        <v>605.55</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>574.95</v>
+        <v>577.86</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>567.61</v>
+        <v>569.1</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>528.6</v>
+        <v>529.33</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>767.4</v>
+        <v>1261.4</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>766.21</v>
+        <v>1233.15</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>761.36</v>
+        <v>1197.37</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>743.99</v>
+        <v>1092.9</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1264.5</v>
+        <v>778.4</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1237.42</v>
+        <v>767.37</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1212.89</v>
+        <v>762.03</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1149.77</v>
+        <v>744.5700000000001</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>90.37</v>
+        <v>1266.6</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>86.93000000000001</v>
+        <v>1240.2</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>83.41</v>
+        <v>1214.99</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>76.63</v>
+        <v>1149.93</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2645</v>
+        <v>89.09</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>2475.23</v>
+        <v>87.14</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>2380.89</v>
+        <v>83.63</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>2396.01</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>184.62</v>
+        <v>2710</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>173.02</v>
+        <v>2497.59</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>163.69</v>
+        <v>2393.79</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>145.3</v>
+        <v>2396.61</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>211.36</v>
+        <v>186.15</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>208.3</v>
+        <v>174.27</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>202.18</v>
+        <v>164.57</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>182.7</v>
+        <v>145.85</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,79 +1481,79 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>212.24</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>208.68</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>202.58</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>183.05</v>
+      </c>
+      <c r="G12" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
-        <v>1266.75</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>1089.92</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>962.4299999999999</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>865.51</v>
-      </c>
-      <c r="G12" s="15">
+      <c r="C13" s="14" t="n">
+        <v>1238.9</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>1104.11</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>973.27</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>869.75</v>
+      </c>
+      <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="n">
-        <v>1389.5</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>1374.26</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>1314.21</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>1217.48</v>
-      </c>
-      <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>6502.5</v>
+        <v>2900.7</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>6279.56</v>
+        <v>2818.74</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>6221.11</v>
+        <v>2834.56</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>6263.2</v>
+        <v>2721.82</v>
       </c>
       <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>1322.9</v>
+        <v>1376</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>1279.18</v>
+        <v>1374.43</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>1267.54</v>
+        <v>1316.63</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>1252.08</v>
+        <v>1221.99</v>
       </c>
       <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>1750.8</v>
+        <v>6619.5</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>1746.95</v>
+        <v>6311.93</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>1740.75</v>
+        <v>6236.74</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>1742.02</v>
+        <v>6270.5</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>2406.3</v>
+        <v>1287.2</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>2269.62</v>
+        <v>1279.94</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>2181.04</v>
+        <v>1268.31</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>1983.08</v>
+        <v>1251.88</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,23 +1649,23 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>699.7</v>
+        <v>1815.5</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>664.16</v>
+        <v>1753.48</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>629.5700000000001</v>
+        <v>1743.68</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>569.34</v>
+        <v>1744.04</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,23 +1677,23 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>1530.9</v>
+        <v>2393.7</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>1509.89</v>
+        <v>2281.43</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>1499.65</v>
+        <v>2189.38</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>1446.33</v>
+        <v>1990.21</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1705,23 +1705,23 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>2043.4</v>
+        <v>703.4</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>2019.64</v>
+        <v>667.89</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>2002.7</v>
+        <v>632.46</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>1853.52</v>
+        <v>571.4</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1733,23 +1733,23 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>1100.95</v>
+        <v>1530</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>1091.23</v>
+        <v>1511.81</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>1060.94</v>
+        <v>1500.84</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>959.2</v>
+        <v>1447.9</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>JBCHEPHARM</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>2246.7</v>
+        <v>2082.1</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>2176.89</v>
+        <v>2025.58</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>2143.06</v>
+        <v>2005.81</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>2240.73</v>
+        <v>1855.28</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1095.75</v>
+        <v>1166.4</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1069.16</v>
+        <v>1098.39</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>1014.01</v>
+        <v>1065.07</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>922.71</v>
+        <v>961.14</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,23 +1817,23 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>1808.3</v>
+        <v>2348.8</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1719.35</v>
+        <v>2315.07</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>1723.25</v>
+        <v>2287.41</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>1715.89</v>
+        <v>2153.88</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1845,555 +1845,555 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>2257.8</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>2184.6</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>2147.56</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>2243.82</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>1114.6</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>1073.49</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>1017.95</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>925.67</v>
+      </c>
+      <c r="G26" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>1823.5</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>1729.27</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>1727.18</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>1717.96</v>
+      </c>
+      <c r="G27" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
           <t>TORNTPHARM</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n">
-        <v>4185.1</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>4171.75</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>4158.01</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>3863.05</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="C28" s="18" t="n">
+        <v>4251.8</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>4179.37</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>4161.69</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>3871.28</v>
+      </c>
+      <c r="G28" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>OBEROIRLTY</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
-        <v>1669.6</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>1655.66</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>1600.07</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>1614.9</v>
-      </c>
-      <c r="G26" s="15">
+      <c r="C29" s="14" t="n">
+        <v>1693.7</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>1659.28</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>1603.74</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>1617.63</v>
+      </c>
+      <c r="G29" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>PHOENIXLTD</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
-        <v>1765</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>1735.61</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>1701.56</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>1670.92</v>
-      </c>
-      <c r="G27" s="15">
+      <c r="C30" s="14" t="n">
+        <v>1787.4</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>1740.54</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>1704.93</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>1673.63</v>
+      </c>
+      <c r="G30" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>SOBHA</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
-        <v>1433.4</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>1362.96</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>1359.91</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>1426.47</v>
-      </c>
-      <c r="G28" s="15">
+      <c r="C31" s="14" t="n">
+        <v>1440.4</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>1370.34</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>1363.07</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>1427.29</v>
+      </c>
+      <c r="G31" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>1068.9</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>998.45</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>994.97</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>1021.25</v>
-      </c>
-      <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>649.7</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>600.23</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>565.1900000000001</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>558.96</v>
-      </c>
-      <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>634.7</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>602.99</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>571.48</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>580.4299999999999</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>490.8</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>477.33</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>470.77</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>440.76</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>524.85</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>506.69</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>489.57</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>488.07</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>299.55</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>287.3</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>277.44</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>253.04</v>
-      </c>
-      <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>5792.5</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>5693.39</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>5744.57</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>5778.4</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRITANNIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>RELIANCE</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>1430.8</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>1371.16</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>1385.69</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>1425.58</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>2172.9</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>2066.99</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>2052.68</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>2171.01</v>
+      </c>
+      <c r="G34" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COLPAL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C35" s="18" t="n">
-        <v>7230</v>
+        <v>784.55</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>6966.53</v>
+        <v>768.9299999999999</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>6473.35</v>
+        <v>762.92</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>5747</v>
+        <v>743.85</v>
       </c>
       <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>1342.25</v>
+        <v>1457.1</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>1255.03</v>
+        <v>1353.81</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>1131.08</v>
+        <v>1299.97</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>996.14</v>
+        <v>1248.66</v>
       </c>
       <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
-        <v>1227.15</v>
+        <v>3389.2</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>1123.06</v>
+        <v>3141.42</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>1028.97</v>
+        <v>2972.54</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>985.86</v>
+        <v>2898.74</v>
       </c>
       <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
-        <v>221.85</v>
+        <v>1160.4</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>196.64</v>
+        <v>1129.79</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>174.27</v>
+        <v>1119.13</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>147.6</v>
+        <v>1130.73</v>
       </c>
       <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>506.75</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>475.24</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>455.66</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>466.96</v>
+      </c>
+      <c r="G39" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>718.4</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>684.47</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>672.3</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>713.91</v>
+      </c>
+      <c r="G40" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>643.15</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>606.8200000000001</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>574.29</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>586.5599999999999</v>
+      </c>
+      <c r="G41" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>292.9</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>287.84</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>278.05</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>253.15</v>
+      </c>
+      <c r="G42" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>1463.1</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>1379.92</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>1388.72</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>1426.91</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>352.41</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>315.07</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>289.68</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>264.89</v>
-      </c>
-      <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="n">
-        <v>187.53</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>173.98</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>165.12</v>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>161.82</v>
-      </c>
-      <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>813.35</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>777.85</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>733.41</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>692.1900000000001</v>
-      </c>
-      <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>481.45</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>454.3</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>444.18</v>
-      </c>
-      <c r="F42" s="18" t="n">
-        <v>408.21</v>
-      </c>
-      <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>4466.2</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>4214.23</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>3903.62</v>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>3183.41</v>
-      </c>
-      <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>19.72</v>
+        <v>7236.5</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>18.4</v>
+        <v>6992.24</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>16.99</v>
+        <v>6503.28</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>16.81</v>
+        <v>5765.69</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2405,23 +2405,23 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>561.15</v>
+        <v>1398.4</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>537.6900000000001</v>
+        <v>1268.69</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>514.86</v>
+        <v>1141.56</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>501.27</v>
+        <v>1002.68</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>83.2</v>
+        <v>1290.7</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>80.86</v>
+        <v>1139.02</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>78.68000000000001</v>
+        <v>1039.24</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>79.23</v>
+        <v>993.92</v>
       </c>
       <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2461,23 +2461,23 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>316.6</v>
+        <v>227.3</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>294.81</v>
+        <v>199.56</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>278.19</v>
+        <v>176.35</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>255.87</v>
+        <v>148.9</v>
       </c>
       <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>399.15</v>
+        <v>377.05</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>393.23</v>
+        <v>320.97</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>380.7</v>
+        <v>293.11</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>353.46</v>
+        <v>266.33</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2517,23 +2517,23 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
-        <v>318.35</v>
+        <v>198.72</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>312.02</v>
+        <v>176.34</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>301.69</v>
+        <v>166.44</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>286.47</v>
+        <v>162.7</v>
       </c>
       <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2545,23 +2545,23 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>33550</v>
+        <v>802.3</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>29730.86</v>
+        <v>780.1799999999999</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>26696.69</v>
+        <v>736.11</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>21742.83</v>
+        <v>694.5</v>
       </c>
       <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2573,23 +2573,23 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>1243.7</v>
+        <v>479.95</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>1073</v>
+        <v>456.74</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>965.08</v>
+        <v>445.58</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>828.35</v>
+        <v>409.09</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2601,23 +2601,23 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>3808.2</v>
+        <v>4486.6</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>3594.63</v>
+        <v>4240.17</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>3389.98</v>
+        <v>3926.48</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>3199.96</v>
+        <v>3200.92</v>
       </c>
       <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2629,23 +2629,23 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
-        <v>55.58</v>
+        <v>19.06</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>51.03</v>
+        <v>18.46</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>47.91</v>
+        <v>17.08</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>51.36</v>
+        <v>16.82</v>
       </c>
       <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2657,23 +2657,23 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>444.55</v>
+        <v>562.3</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>426.11</v>
+        <v>540.03</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>405.47</v>
+        <v>516.72</v>
       </c>
       <c r="F54" s="18" t="n">
-        <v>389.8</v>
+        <v>502.87</v>
       </c>
       <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2685,23 +2685,23 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C55" s="18" t="n">
-        <v>4077.6</v>
+        <v>83.28</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>3853.66</v>
+        <v>81.09</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>3533.52</v>
+        <v>78.86</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>3263.39</v>
+        <v>79.25</v>
       </c>
       <c r="G55" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2713,23 +2713,23 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C56" s="18" t="n">
-        <v>1736</v>
+        <v>320.4</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>1603.87</v>
+        <v>297.24</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>1512.01</v>
+        <v>279.85</v>
       </c>
       <c r="F56" s="18" t="n">
-        <v>1405.94</v>
+        <v>256.53</v>
       </c>
       <c r="G56" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2741,750 +2741,1002 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>TRITURBINE</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C57" s="18" t="n">
-        <v>573.25</v>
+        <v>400.05</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>531.67</v>
+        <v>393.88</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>505.65</v>
+        <v>381.46</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>513.96</v>
+        <v>353.91</v>
       </c>
       <c r="G57" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>8024</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>7612.4</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>7296.01</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>7083.59</v>
-      </c>
-      <c r="G58" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>319.05</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>312.69</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>302.38</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>287.21</v>
+      </c>
+      <c r="G58" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>CENTURYPLY</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n">
-        <v>797.65</v>
-      </c>
-      <c r="D59" s="14" t="n">
-        <v>761.58</v>
-      </c>
-      <c r="E59" s="14" t="n">
-        <v>746.11</v>
-      </c>
-      <c r="F59" s="14" t="n">
-        <v>752.34</v>
-      </c>
-      <c r="G59" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>33730</v>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>30111.73</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>26972.5</v>
+      </c>
+      <c r="F59" s="18" t="n">
+        <v>21849.97</v>
+      </c>
+      <c r="G59" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="n">
-        <v>272.36</v>
-      </c>
-      <c r="D60" s="14" t="n">
-        <v>256.02</v>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v>251.91</v>
-      </c>
-      <c r="F60" s="14" t="n">
-        <v>272.19</v>
-      </c>
-      <c r="G60" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>1305.8</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>1095.17</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>978.4400000000001</v>
+      </c>
+      <c r="F60" s="18" t="n">
+        <v>833.9400000000001</v>
+      </c>
+      <c r="G60" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="n">
-        <v>1187.65</v>
-      </c>
-      <c r="D61" s="14" t="n">
-        <v>1141.4</v>
-      </c>
-      <c r="E61" s="14" t="n">
-        <v>1063.57</v>
-      </c>
-      <c r="F61" s="14" t="n">
-        <v>1034.21</v>
-      </c>
-      <c r="G61" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>3834.1</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>3617.43</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>3407.4</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>3209.58</v>
+      </c>
+      <c r="G61" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
-        <v>4385.2</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>4379.94</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>4272.81</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>3952.75</v>
-      </c>
-      <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>74.27</v>
+      </c>
+      <c r="F62" s="18" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="G62" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SJVN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n">
-        <v>1430.4</v>
-      </c>
-      <c r="D63" s="14" t="n">
-        <v>1421.58</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>1408.03</v>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>1376.98</v>
-      </c>
-      <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>48.19</v>
+      </c>
+      <c r="F63" s="18" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="G63" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>521.05</v>
+        <v>441.4</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>504.78</v>
+        <v>427.56</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>488.13</v>
+        <v>406.88</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>487.27</v>
+        <v>390.97</v>
       </c>
       <c r="G64" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C65" s="18" t="n">
-        <v>775</v>
+        <v>4179.8</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>767.29</v>
+        <v>3884.72</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>762.03</v>
+        <v>3558.86</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>741.4400000000001</v>
+        <v>3273.93</v>
       </c>
       <c r="G65" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C66" s="18" t="n">
-        <v>1458.6</v>
+        <v>1724</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>1342.94</v>
+        <v>1615.31</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>1293.56</v>
+        <v>1520.32</v>
       </c>
       <c r="F66" s="18" t="n">
-        <v>1246.71</v>
+        <v>1408.11</v>
       </c>
       <c r="G66" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C67" s="18" t="n">
-        <v>3423.1</v>
+        <v>570</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>3115.34</v>
+        <v>535.3200000000001</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>2955.53</v>
+        <v>508.17</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>2886.68</v>
+        <v>515.9400000000001</v>
       </c>
       <c r="G67" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="n">
-        <v>1144.6</v>
-      </c>
-      <c r="D68" s="18" t="n">
-        <v>1126.57</v>
-      </c>
-      <c r="E68" s="18" t="n">
-        <v>1117.45</v>
-      </c>
-      <c r="F68" s="18" t="n">
-        <v>1129.87</v>
-      </c>
-      <c r="G68" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="n">
+        <v>8007</v>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>7649.99</v>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v>7323.88</v>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>7085.2</v>
+      </c>
+      <c r="G68" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="n">
-        <v>513.7</v>
-      </c>
-      <c r="D69" s="18" t="n">
-        <v>471.92</v>
-      </c>
-      <c r="E69" s="18" t="n">
-        <v>453.57</v>
-      </c>
-      <c r="F69" s="18" t="n">
-        <v>465.14</v>
-      </c>
-      <c r="G69" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>CENTURYPLY</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="n">
+        <v>815.9</v>
+      </c>
+      <c r="D69" s="14" t="n">
+        <v>766.76</v>
+      </c>
+      <c r="E69" s="14" t="n">
+        <v>748.84</v>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>754.14</v>
+      </c>
+      <c r="G69" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="C70" s="14" t="n">
-        <v>78.37</v>
+        <v>277.95</v>
       </c>
       <c r="D70" s="14" t="n">
-        <v>74.34999999999999</v>
+        <v>258.11</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>70.25</v>
+        <v>252.93</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>62.14</v>
+        <v>273.3</v>
       </c>
       <c r="G70" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="n">
-        <v>9994</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>9568.299999999999</v>
-      </c>
-      <c r="E71" s="18" t="n">
-        <v>9476.790000000001</v>
-      </c>
-      <c r="F71" s="18" t="n">
-        <v>9088.25</v>
-      </c>
-      <c r="G71" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="n">
+        <v>1454.2</v>
+      </c>
+      <c r="D71" s="14" t="n">
+        <v>1424.68</v>
+      </c>
+      <c r="E71" s="14" t="n">
+        <v>1409.84</v>
+      </c>
+      <c r="F71" s="14" t="n">
+        <v>1380.8</v>
+      </c>
+      <c r="G71" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C72" s="18" t="n">
-        <v>1881.6</v>
+        <v>267.3</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>1838.36</v>
+        <v>261.45</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>1764.52</v>
+        <v>257.73</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>1509.26</v>
+        <v>266.1</v>
       </c>
       <c r="G72" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C73" s="18" t="n">
-        <v>35995</v>
+        <v>1059.1</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>35964.46</v>
+        <v>1004.22</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>35087.14</v>
+        <v>997.48</v>
       </c>
       <c r="F73" s="18" t="n">
-        <v>35208.49</v>
+        <v>1021.17</v>
       </c>
       <c r="G73" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C74" s="18" t="n">
-        <v>360.55</v>
+        <v>645.5</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>336.49</v>
+        <v>604.54</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>329.58</v>
+        <v>568.34</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>350.56</v>
+        <v>560.84</v>
       </c>
       <c r="G74" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C75" s="14" t="n">
-        <v>2712.6</v>
+        <v>126.04</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>2658.2</v>
+        <v>97.19</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>2602.35</v>
+        <v>84.62</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>2590.1</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G75" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C76" s="14" t="n">
-        <v>554.7</v>
+        <v>10.52</v>
       </c>
       <c r="D76" s="14" t="n">
-        <v>538.01</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>527.6</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>543.96</v>
+        <v>9.44</v>
       </c>
       <c r="G76" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C77" s="14" t="n">
-        <v>2971.5</v>
+        <v>9730</v>
       </c>
       <c r="D77" s="14" t="n">
-        <v>2769.28</v>
+        <v>8434.030000000001</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>2612.01</v>
+        <v>7753.91</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>2152.27</v>
+        <v>7852.52</v>
       </c>
       <c r="G77" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="8" t="inlineStr">
+      <c r="A78" s="16" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="n">
-        <v>116.03</v>
-      </c>
-      <c r="D78" s="18" t="n">
-        <v>94.16</v>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>82.93000000000001</v>
-      </c>
-      <c r="F78" s="18" t="n">
-        <v>75.68000000000001</v>
-      </c>
-      <c r="G78" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>TANLA</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="n">
+        <v>526.9</v>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>491.39</v>
+      </c>
+      <c r="E78" s="14" t="n">
+        <v>472.46</v>
+      </c>
+      <c r="F78" s="14" t="n">
+        <v>516.74</v>
+      </c>
+      <c r="G78" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="C79" s="18" t="n">
-        <v>10.22</v>
+        <v>10132</v>
       </c>
       <c r="D79" s="18" t="n">
-        <v>9.609999999999999</v>
+        <v>9621.99</v>
       </c>
       <c r="E79" s="18" t="n">
-        <v>9.76</v>
+        <v>9502.49</v>
       </c>
       <c r="F79" s="18" t="n">
-        <v>9.42</v>
+        <v>9106.809999999999</v>
       </c>
       <c r="G79" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C80" s="18" t="n">
-        <v>9726.5</v>
+        <v>1845.8</v>
       </c>
       <c r="D80" s="18" t="n">
-        <v>8297.610000000001</v>
+        <v>1839.07</v>
       </c>
       <c r="E80" s="18" t="n">
-        <v>7673.25</v>
+        <v>1767.71</v>
       </c>
       <c r="F80" s="18" t="n">
-        <v>7837</v>
+        <v>1513.89</v>
       </c>
       <c r="G80" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="12" t="inlineStr">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="n">
+        <v>7329</v>
+      </c>
+      <c r="D81" s="18" t="n">
+        <v>7133.62</v>
+      </c>
+      <c r="E81" s="18" t="n">
+        <v>7173.36</v>
+      </c>
+      <c r="F81" s="18" t="n">
+        <v>6859.43</v>
+      </c>
+      <c r="G81" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="n">
+        <v>359.05</v>
+      </c>
+      <c r="D82" s="18" t="n">
+        <v>338.64</v>
+      </c>
+      <c r="E82" s="18" t="n">
+        <v>330.73</v>
+      </c>
+      <c r="F82" s="18" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="G82" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="n">
+        <v>950.2</v>
+      </c>
+      <c r="D83" s="14" t="n">
+        <v>915.54</v>
+      </c>
+      <c r="E83" s="14" t="n">
+        <v>919.04</v>
+      </c>
+      <c r="F83" s="14" t="n">
+        <v>945.0599999999999</v>
+      </c>
+      <c r="G83" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="n">
+        <v>1639.5</v>
+      </c>
+      <c r="D84" s="14" t="n">
+        <v>1550.14</v>
+      </c>
+      <c r="E84" s="14" t="n">
+        <v>1565.31</v>
+      </c>
+      <c r="F84" s="14" t="n">
+        <v>1604.97</v>
+      </c>
+      <c r="G84" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="n">
+        <v>2753.6</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>2667.29</v>
+      </c>
+      <c r="E85" s="14" t="n">
+        <v>2608.29</v>
+      </c>
+      <c r="F85" s="14" t="n">
+        <v>2594.76</v>
+      </c>
+      <c r="G85" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="n">
+        <v>557</v>
+      </c>
+      <c r="D86" s="14" t="n">
+        <v>539.8200000000001</v>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v>528.76</v>
+      </c>
+      <c r="F86" s="14" t="n">
+        <v>544.67</v>
+      </c>
+      <c r="G86" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="n">
+        <v>2912.9</v>
+      </c>
+      <c r="D87" s="14" t="n">
+        <v>2782.95</v>
+      </c>
+      <c r="E87" s="14" t="n">
+        <v>2623.81</v>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>2159.54</v>
+      </c>
+      <c r="G87" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="n">
+        <v>3487.7</v>
+      </c>
+      <c r="D88" s="14" t="n">
+        <v>3464.74</v>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v>3456.7</v>
+      </c>
+      <c r="F88" s="14" t="n">
+        <v>3267.23</v>
+      </c>
+      <c r="G88" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="D89" s="18" t="n">
+        <v>74.81999999999999</v>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="F89" s="18" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="G89" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="12" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B81" s="13" t="inlineStr">
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>AUBANK</t>
         </is>
       </c>
-      <c r="C81" s="14" t="n">
-        <v>1015.95</v>
-      </c>
-      <c r="D81" s="14" t="n">
-        <v>994.91</v>
-      </c>
-      <c r="E81" s="14" t="n">
-        <v>969.75</v>
-      </c>
-      <c r="F81" s="14" t="n">
-        <v>897.28</v>
-      </c>
-      <c r="G81" s="15">
+      <c r="C90" s="14" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D90" s="14" t="n">
+        <v>996.8200000000001</v>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v>971.52</v>
+      </c>
+      <c r="F90" s="14" t="n">
+        <v>898.29</v>
+      </c>
+      <c r="G90" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="16" t="inlineStr">
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="16" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C82" s="14" t="n">
-        <v>286.95</v>
-      </c>
-      <c r="D82" s="14" t="n">
-        <v>286.57</v>
-      </c>
-      <c r="E82" s="14" t="n">
-        <v>281.21</v>
-      </c>
-      <c r="F82" s="14" t="n">
-        <v>252.33</v>
-      </c>
-      <c r="G82" s="15">
+      <c r="C91" s="14" t="n">
+        <v>289.15</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>286.82</v>
+      </c>
+      <c r="E91" s="14" t="n">
+        <v>281.52</v>
+      </c>
+      <c r="F91" s="14" t="n">
+        <v>252.86</v>
+      </c>
+      <c r="G91" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="16" t="inlineStr">
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B83" s="13" t="inlineStr">
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="C83" s="14" t="n">
-        <v>916.05</v>
-      </c>
-      <c r="D83" s="14" t="n">
-        <v>861.1900000000001</v>
-      </c>
-      <c r="E83" s="14" t="n">
-        <v>859.87</v>
-      </c>
-      <c r="F83" s="14" t="n">
-        <v>849.79</v>
-      </c>
-      <c r="G83" s="15">
+      <c r="C92" s="14" t="n">
+        <v>913.9</v>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>866.21</v>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v>861.99</v>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>849.62</v>
+      </c>
+      <c r="G92" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 04-May-2026  17:29</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 05-May-2026  16:43</t>
         </is>
       </c>
     </row>
@@ -703,87 +703,87 @@
         <v>20</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.75</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.8</v>
+        <v>0.8167</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F6" s="6" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.7333</v>
+        <v>0.7556999999999999</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.667</v>
+        <v>0.9</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -833,7 +833,7 @@
         <v>25</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0.625</v>
@@ -842,134 +842,134 @@
         <v>0.625</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.6</v>
+        <v>0.575</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.6167</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.467</v>
+        <v>0.2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.6</v>
+        <v>0.5667</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.5667</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.45</v>
+        <v>0.467</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.467</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.4</v>
+        <v>0.4447</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.333</v>
+        <v>0.55</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.467</v>
+        <v>0.2</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.4</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -982,25 +982,25 @@
         <v>20</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>9</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.45</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.3833</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1016,7 +1016,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>5</v>
@@ -1025,13 +1025,13 @@
         <v>0.333</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.417</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.417</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.3333</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1047,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>3</v>
@@ -1056,13 +1056,13 @@
         <v>0.333</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.3053</v>
+        <v>0.2777</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1078,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
@@ -1087,13 +1087,13 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0667</v>
+        <v>0.0333</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2485.7</v>
+        <v>2462</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2238.8</v>
+        <v>2260.06</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2150.33</v>
+        <v>2162.55</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2248.23</v>
+        <v>2250.36</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1042.7</v>
+        <v>1054.7</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1014.92</v>
+        <v>1020.73</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>971.75</v>
+        <v>977.51</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>859.6900000000001</v>
+        <v>863.39</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>605.55</v>
+        <v>611.25</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>577.86</v>
+        <v>582.6799999999999</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>569.1</v>
+        <v>571.78</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>529.33</v>
+        <v>530.8099999999999</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1261.4</v>
+        <v>1261.2</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1233.15</v>
+        <v>1235.27</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1197.37</v>
+        <v>1200.9</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1092.9</v>
+        <v>1095.86</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>778.4</v>
+        <v>779.4</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>767.37</v>
+        <v>768.61</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>762.03</v>
+        <v>762.9299999999999</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>744.5700000000001</v>
+        <v>745.14</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1266.6</v>
+        <v>1252.4</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1240.2</v>
+        <v>1241.36</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1214.99</v>
+        <v>1216.46</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1149.93</v>
+        <v>1150.95</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>89.09</v>
+        <v>88.83</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>87.14</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>83.63</v>
+        <v>84.09</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>76.81999999999999</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2710</v>
+        <v>2742.1</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2497.59</v>
+        <v>2520.87</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2393.79</v>
+        <v>2407.45</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>2396.61</v>
+        <v>2400.05</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>186.15</v>
+        <v>187.31</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>174.27</v>
+        <v>176.41</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>164.57</v>
+        <v>166.22</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>145.85</v>
+        <v>146.64</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>212.24</v>
+        <v>211.32</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>208.68</v>
+        <v>209.17</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>202.58</v>
+        <v>203.25</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>183.05</v>
+        <v>183.61</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1238.9</v>
+        <v>1254</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1104.11</v>
+        <v>1132.17</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>973.27</v>
+        <v>995.3</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>869.75</v>
+        <v>877.49</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>2900.7</v>
+        <v>2897.6</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>2818.74</v>
+        <v>2826.25</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>2834.56</v>
+        <v>2837.04</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>2721.82</v>
+        <v>2723.57</v>
       </c>
       <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>1376</v>
+        <v>1428.1</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>1374.43</v>
+        <v>1379.54</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>1316.63</v>
+        <v>1321</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>1221.99</v>
+        <v>1224.04</v>
       </c>
       <c r="G15" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>6619.5</v>
+        <v>6651</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>6311.93</v>
+        <v>6344.23</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>6236.74</v>
+        <v>6252.98</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>6270.5</v>
+        <v>6274.28</v>
       </c>
       <c r="G16" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>1287.2</v>
+        <v>1773.3</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>1279.94</v>
+        <v>1755.36</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>1268.31</v>
+        <v>1744.84</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>1251.88</v>
+        <v>1744.33</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,23 +1649,23 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>1815.5</v>
+        <v>2417.9</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1753.48</v>
+        <v>2305.09</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>1743.68</v>
+        <v>2206.5</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>1744.04</v>
+        <v>1998.56</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,23 +1677,23 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>2393.7</v>
+        <v>711.8</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>2281.43</v>
+        <v>672.0700000000001</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>2189.38</v>
+        <v>635.58</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>1990.21</v>
+        <v>572.79</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1705,23 +1705,23 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>703.4</v>
+        <v>1541.8</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>667.89</v>
+        <v>1514.66</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>632.46</v>
+        <v>1502.45</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>571.4</v>
+        <v>1448.84</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1733,23 +1733,23 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>JBCHEPHARM</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>1530</v>
+        <v>2094.6</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>1511.81</v>
+        <v>2034.01</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>1500.84</v>
+        <v>2010.77</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>1447.9</v>
+        <v>1859.51</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>2082.1</v>
+        <v>1164.1</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>2025.58</v>
+        <v>1105.4</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>2005.81</v>
+        <v>1070.4</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>1855.28</v>
+        <v>964.54</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1166.4</v>
+        <v>2343.3</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1098.39</v>
+        <v>2317.76</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>1065.07</v>
+        <v>2289.61</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>961.14</v>
+        <v>2155.77</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,23 +1817,23 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>2348.8</v>
+        <v>2319.5</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>2315.07</v>
+        <v>2197.44</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>2287.41</v>
+        <v>2154.3</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>2153.88</v>
+        <v>2244.57</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1845,23 +1845,23 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>2257.8</v>
+        <v>1125</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>2184.6</v>
+        <v>1078.39</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>2147.56</v>
+        <v>1022.15</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>2243.82</v>
+        <v>927.65</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1873,23 +1873,23 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>1114.6</v>
+        <v>1820.8</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1073.49</v>
+        <v>1737.98</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>1017.95</v>
+        <v>1730.85</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>925.67</v>
+        <v>1718.98</v>
       </c>
       <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1901,359 +1901,359 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>1823.5</v>
+        <v>4275.1</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>1729.27</v>
+        <v>4189.53</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>1727.18</v>
+        <v>4167.12</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>1717.96</v>
+        <v>3878.4</v>
       </c>
       <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>4251.8</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>4179.37</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>4161.69</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>3871.28</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>531</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>510.27</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>492.39</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>488.82</v>
+      </c>
+      <c r="G28" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>1693.7</v>
+        <v>5834.5</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>1659.28</v>
+        <v>5706.83</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>1603.74</v>
+        <v>5748.09</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>1617.63</v>
+        <v>5778.96</v>
       </c>
       <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRITANNIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>1787.4</v>
+        <v>2178.9</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>1740.54</v>
+        <v>2080.8</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>1704.93</v>
+        <v>2059.38</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>1673.63</v>
+        <v>2170.36</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COLPAL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>2327.4</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>2256.95</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>2244.63</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>2326.51</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>807.2</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>772.58</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>764.65</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>744.48</v>
+      </c>
+      <c r="G32" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1477.8</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>1365.62</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>1306.94</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>1250.94</v>
+      </c>
+      <c r="G33" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>3338.9</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>3184.22</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>3003.83</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>2908.28</v>
+      </c>
+      <c r="G34" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1153.5</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>1133.46</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>1121.46</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>1131.1</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>511.7</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>481.97</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>460.03</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>467.87</v>
+      </c>
+      <c r="G36" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>SOBHA</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>1440.4</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>1370.34</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>1363.07</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>1427.29</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>524.85</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>506.69</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>489.57</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>488.07</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>5792.5</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>5693.39</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>5744.57</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>5778.4</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRITANNIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>COLPAL</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>2172.9</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>2066.99</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>2052.68</v>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>2171.01</v>
-      </c>
-      <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COLPAL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>784.55</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>768.9299999999999</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>762.92</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>743.85</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>1457.1</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>1353.81</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>1299.97</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>1248.66</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
-        <v>3389.2</v>
+        <v>1666.3</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>3141.42</v>
+        <v>1659.95</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>2972.54</v>
+        <v>1606.19</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>2898.74</v>
+        <v>1618.12</v>
       </c>
       <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
-        <v>1160.4</v>
+        <v>1793.9</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>1129.79</v>
+        <v>1745.62</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>1119.13</v>
+        <v>1708.42</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>1130.73</v>
+        <v>1674.83</v>
       </c>
       <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>SOBHA</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
-        <v>506.75</v>
+        <v>1446.3</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>475.24</v>
+        <v>1377.57</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>455.66</v>
+        <v>1366.33</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>466.96</v>
+        <v>1427.48</v>
       </c>
       <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2265,23 +2265,23 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>718.4</v>
+        <v>647.2</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>684.47</v>
+        <v>613.13</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>672.3</v>
+        <v>579.4400000000001</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>713.91</v>
+        <v>587.64</v>
       </c>
       <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2293,23 +2293,23 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>643.15</v>
+        <v>289.95</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>606.8200000000001</v>
+        <v>288.04</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>574.29</v>
+        <v>278.51</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>586.5599999999999</v>
+        <v>253.52</v>
       </c>
       <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2321,23 +2321,23 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>292.9</v>
+        <v>282.55</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>287.84</v>
+        <v>275</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>278.05</v>
+        <v>276.6</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>253.15</v>
+        <v>281.77</v>
       </c>
       <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2353,16 +2353,16 @@
         </is>
       </c>
       <c r="C43" s="14" t="n">
-        <v>1463.1</v>
+        <v>1463.6</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>1379.92</v>
+        <v>1392.54</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>1388.72</v>
+        <v>1393.29</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>1426.91</v>
+        <v>1427.32</v>
       </c>
       <c r="G43" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>7236.5</v>
+        <v>7328</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>6992.24</v>
+        <v>7024.21</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>6503.28</v>
+        <v>6535.62</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>5765.69</v>
+        <v>5781.23</v>
       </c>
       <c r="G44" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>1398.4</v>
+        <v>1409.6</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>1268.69</v>
+        <v>1282.11</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>1141.56</v>
+        <v>1152.07</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>1002.68</v>
+        <v>1006.73</v>
       </c>
       <c r="G45" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>1290.7</v>
+        <v>1331.4</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>1139.02</v>
+        <v>1157.35</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>1039.24</v>
+        <v>1050.7</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>993.92</v>
+        <v>997.28</v>
       </c>
       <c r="G46" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
@@ -2465,16 +2465,16 @@
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>227.3</v>
+        <v>229.96</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>199.56</v>
+        <v>204.42</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>176.35</v>
+        <v>180.17</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>148.9</v>
+        <v>150.42</v>
       </c>
       <c r="G47" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
@@ -2493,16 +2493,16 @@
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>377.05</v>
+        <v>374.95</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>320.97</v>
+        <v>329.02</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>293.11</v>
+        <v>298.59</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>266.33</v>
+        <v>268.26</v>
       </c>
       <c r="G48" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
@@ -2521,16 +2521,16 @@
         </is>
       </c>
       <c r="C49" s="18" t="n">
-        <v>198.72</v>
+        <v>186.88</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>176.34</v>
+        <v>178.4</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>166.44</v>
+        <v>168.05</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>162.7</v>
+        <v>163.19</v>
       </c>
       <c r="G49" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
@@ -2549,16 +2549,16 @@
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>802.3</v>
+        <v>826.9</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>780.1799999999999</v>
+        <v>787.4</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>736.11</v>
+        <v>742.5700000000001</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>694.5</v>
+        <v>696.99</v>
       </c>
       <c r="G50" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
@@ -2577,16 +2577,16 @@
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>479.95</v>
+        <v>472.6</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>456.74</v>
+        <v>460.37</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>445.58</v>
+        <v>447.99</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>409.09</v>
+        <v>410.43</v>
       </c>
       <c r="G51" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
@@ -2605,16 +2605,16 @@
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>4486.6</v>
+        <v>4578.9</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>4240.17</v>
+        <v>4292.07</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>3926.48</v>
+        <v>3972.43</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>3200.92</v>
+        <v>3227.09</v>
       </c>
       <c r="G52" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
@@ -2633,16 +2633,16 @@
         </is>
       </c>
       <c r="C53" s="18" t="n">
-        <v>19.06</v>
+        <v>19.26</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>18.46</v>
+        <v>18.64</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>17.08</v>
+        <v>17.26</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>16.82</v>
+        <v>16.87</v>
       </c>
       <c r="G53" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
@@ -2661,16 +2661,16 @@
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>562.3</v>
+        <v>561.95</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>540.03</v>
+        <v>543.95</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>516.72</v>
+        <v>520.17</v>
       </c>
       <c r="F54" s="18" t="n">
-        <v>502.87</v>
+        <v>504.04</v>
       </c>
       <c r="G54" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
@@ -2689,16 +2689,16 @@
         </is>
       </c>
       <c r="C55" s="18" t="n">
-        <v>83.28</v>
+        <v>83.17</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>81.09</v>
+        <v>81.47</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>78.86</v>
+        <v>79.2</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>79.25</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="G55" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
@@ -2717,16 +2717,16 @@
         </is>
       </c>
       <c r="C56" s="18" t="n">
-        <v>320.4</v>
+        <v>316.45</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>297.24</v>
+        <v>300.77</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>279.85</v>
+        <v>282.68</v>
       </c>
       <c r="F56" s="18" t="n">
-        <v>256.53</v>
+        <v>257.72</v>
       </c>
       <c r="G56" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
@@ -2745,16 +2745,16 @@
         </is>
       </c>
       <c r="C57" s="18" t="n">
-        <v>400.05</v>
+        <v>398.65</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>393.88</v>
+        <v>394.8</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>381.46</v>
+        <v>382.8</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>353.91</v>
+        <v>354.8</v>
       </c>
       <c r="G57" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
@@ -2773,16 +2773,16 @@
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>319.05</v>
+        <v>319.45</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>312.69</v>
+        <v>313.82</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>302.38</v>
+        <v>303.65</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>287.21</v>
+        <v>287.84</v>
       </c>
       <c r="G58" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
@@ -2801,16 +2801,16 @@
         </is>
       </c>
       <c r="C59" s="18" t="n">
-        <v>33730</v>
+        <v>34255</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>30111.73</v>
+        <v>30506.32</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>26972.5</v>
+        <v>27258.09</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>21849.97</v>
+        <v>21973.4</v>
       </c>
       <c r="G59" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
@@ -2829,16 +2829,16 @@
         </is>
       </c>
       <c r="C60" s="18" t="n">
-        <v>1305.8</v>
+        <v>1349.9</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>1095.17</v>
+        <v>1119.43</v>
       </c>
       <c r="E60" s="18" t="n">
-        <v>978.4400000000001</v>
+        <v>993.01</v>
       </c>
       <c r="F60" s="18" t="n">
-        <v>833.9400000000001</v>
+        <v>839.0700000000001</v>
       </c>
       <c r="G60" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
@@ -2857,16 +2857,16 @@
         </is>
       </c>
       <c r="C61" s="18" t="n">
-        <v>3834.1</v>
+        <v>3846.6</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>3617.43</v>
+        <v>3655.91</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>3407.4</v>
+        <v>3439.77</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>3209.58</v>
+        <v>3221.82</v>
       </c>
       <c r="G61" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
@@ -2881,23 +2881,23 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C62" s="18" t="n">
-        <v>79.86</v>
+        <v>54.85</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>76.56</v>
+        <v>52.09</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>74.27</v>
+        <v>48.73</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>79.52</v>
+        <v>51.54</v>
       </c>
       <c r="G62" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SJVN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2909,23 +2909,23 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C63" s="18" t="n">
-        <v>54.96</v>
+        <v>442.65</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>51.4</v>
+        <v>430.44</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>48.19</v>
+        <v>409.7</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>51.46</v>
+        <v>392.01</v>
       </c>
       <c r="G63" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2937,23 +2937,23 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>441.4</v>
+        <v>4113.6</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>427.56</v>
+        <v>3923.98</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>406.88</v>
+        <v>3600.31</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>390.97</v>
+        <v>3290.21</v>
       </c>
       <c r="G64" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2965,23 +2965,23 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C65" s="18" t="n">
-        <v>4179.8</v>
+        <v>1734.7</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>3884.72</v>
+        <v>1636.98</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>3558.86</v>
+        <v>1536.84</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>3273.93</v>
+        <v>1414.59</v>
       </c>
       <c r="G65" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2993,499 +2993,499 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C66" s="18" t="n">
-        <v>1724</v>
+        <v>556.45</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>1615.31</v>
+        <v>540.58</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>1520.32</v>
+        <v>512.51</v>
       </c>
       <c r="F66" s="18" t="n">
-        <v>1408.11</v>
+        <v>516.91</v>
       </c>
       <c r="G66" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="n">
-        <v>570</v>
-      </c>
-      <c r="D67" s="18" t="n">
-        <v>535.3200000000001</v>
-      </c>
-      <c r="E67" s="18" t="n">
-        <v>508.17</v>
-      </c>
-      <c r="F67" s="18" t="n">
-        <v>515.9400000000001</v>
-      </c>
-      <c r="G67" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="n">
+        <v>1063.1</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>1009.83</v>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>1000.06</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>1021.58</v>
+      </c>
+      <c r="G67" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="12" t="inlineStr">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="n">
+        <v>645.65</v>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>608.46</v>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v>571.37</v>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>561.6900000000001</v>
+      </c>
+      <c r="G68" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
-      <c r="C68" s="14" t="n">
-        <v>8007</v>
-      </c>
-      <c r="D68" s="14" t="n">
-        <v>7649.99</v>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v>7323.88</v>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>7085.2</v>
-      </c>
-      <c r="G68" s="15">
+      <c r="C69" s="18" t="n">
+        <v>8204</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>7702.75</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>7358.4</v>
+      </c>
+      <c r="F69" s="18" t="n">
+        <v>7096.33</v>
+      </c>
+      <c r="G69" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="16" t="inlineStr">
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>1802.3</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>1802.13</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>1800.24</v>
+      </c>
+      <c r="F70" s="18" t="n">
+        <v>1799.42</v>
+      </c>
+      <c r="G70" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
         <is>
           <t>CENTURYPLY</t>
         </is>
       </c>
-      <c r="C69" s="14" t="n">
-        <v>815.9</v>
-      </c>
-      <c r="D69" s="14" t="n">
-        <v>766.76</v>
-      </c>
-      <c r="E69" s="14" t="n">
-        <v>748.84</v>
-      </c>
-      <c r="F69" s="14" t="n">
-        <v>754.14</v>
-      </c>
-      <c r="G69" s="15">
+      <c r="C71" s="18" t="n">
+        <v>792.95</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>769.25</v>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>750.5700000000001</v>
+      </c>
+      <c r="F71" s="18" t="n">
+        <v>754.52</v>
+      </c>
+      <c r="G71" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B72" s="17" t="inlineStr">
         <is>
           <t>CROMPTON</t>
         </is>
       </c>
-      <c r="C70" s="14" t="n">
-        <v>277.95</v>
-      </c>
-      <c r="D70" s="14" t="n">
-        <v>258.11</v>
-      </c>
-      <c r="E70" s="14" t="n">
-        <v>252.93</v>
-      </c>
-      <c r="F70" s="14" t="n">
-        <v>273.3</v>
-      </c>
-      <c r="G70" s="15">
+      <c r="C72" s="18" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>259.76</v>
+      </c>
+      <c r="E72" s="18" t="n">
+        <v>253.82</v>
+      </c>
+      <c r="F72" s="18" t="n">
+        <v>273.33</v>
+      </c>
+      <c r="G72" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-      <c r="C71" s="14" t="n">
-        <v>1454.2</v>
-      </c>
-      <c r="D71" s="14" t="n">
-        <v>1424.68</v>
-      </c>
-      <c r="E71" s="14" t="n">
-        <v>1409.84</v>
-      </c>
-      <c r="F71" s="14" t="n">
-        <v>1380.8</v>
-      </c>
-      <c r="G71" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VOLTAS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="n">
-        <v>267.3</v>
-      </c>
-      <c r="D72" s="18" t="n">
-        <v>261.45</v>
-      </c>
-      <c r="E72" s="18" t="n">
-        <v>257.73</v>
-      </c>
-      <c r="F72" s="18" t="n">
-        <v>266.1</v>
-      </c>
-      <c r="G72" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="n">
-        <v>1059.1</v>
-      </c>
-      <c r="D73" s="18" t="n">
-        <v>1004.22</v>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>997.48</v>
-      </c>
-      <c r="F73" s="18" t="n">
-        <v>1021.17</v>
-      </c>
-      <c r="G73" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="n">
+        <v>10046</v>
+      </c>
+      <c r="D73" s="14" t="n">
+        <v>9662.370000000001</v>
+      </c>
+      <c r="E73" s="14" t="n">
+        <v>9523.799999999999</v>
+      </c>
+      <c r="F73" s="14" t="n">
+        <v>9116.15</v>
+      </c>
+      <c r="G73" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="n">
-        <v>645.5</v>
-      </c>
-      <c r="D74" s="18" t="n">
-        <v>604.54</v>
-      </c>
-      <c r="E74" s="18" t="n">
-        <v>568.34</v>
-      </c>
-      <c r="F74" s="18" t="n">
-        <v>560.84</v>
-      </c>
-      <c r="G74" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="n">
+        <v>1866.6</v>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>1845.06</v>
+      </c>
+      <c r="E74" s="14" t="n">
+        <v>1775.83</v>
+      </c>
+      <c r="F74" s="14" t="n">
+        <v>1521.02</v>
+      </c>
+      <c r="G74" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C75" s="14" t="n">
-        <v>126.04</v>
+        <v>7301.5</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>97.19</v>
+        <v>7149.29</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>84.62</v>
+        <v>7176.28</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>76.40000000000001</v>
+        <v>6866.31</v>
       </c>
       <c r="G75" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="n">
+        <v>361.15</v>
+      </c>
+      <c r="D76" s="14" t="n">
+        <v>342.66</v>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v>333.05</v>
+      </c>
+      <c r="F76" s="14" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="G76" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="n">
+        <v>128.77</v>
+      </c>
+      <c r="D77" s="18" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="E77" s="18" t="n">
+        <v>87.55</v>
+      </c>
+      <c r="F77" s="18" t="n">
+        <v>77.31</v>
+      </c>
+      <c r="G77" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="C76" s="14" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="D76" s="14" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="E76" s="14" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="F76" s="14" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="G76" s="15">
+      <c r="C78" s="18" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D78" s="18" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="E78" s="18" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="F78" s="18" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="G78" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="16" t="inlineStr">
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B77" s="13" t="inlineStr">
+      <c r="B79" s="17" t="inlineStr">
         <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="C77" s="14" t="n">
-        <v>9730</v>
-      </c>
-      <c r="D77" s="14" t="n">
-        <v>8434.030000000001</v>
-      </c>
-      <c r="E77" s="14" t="n">
-        <v>7753.91</v>
-      </c>
-      <c r="F77" s="14" t="n">
-        <v>7852.52</v>
-      </c>
-      <c r="G77" s="15">
+      <c r="C79" s="18" t="n">
+        <v>9707</v>
+      </c>
+      <c r="D79" s="18" t="n">
+        <v>8666.66</v>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>7904.83</v>
+      </c>
+      <c r="F79" s="18" t="n">
+        <v>7889.43</v>
+      </c>
+      <c r="G79" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>TANLA</t>
-        </is>
-      </c>
-      <c r="C78" s="14" t="n">
-        <v>526.9</v>
-      </c>
-      <c r="D78" s="14" t="n">
-        <v>491.39</v>
-      </c>
-      <c r="E78" s="14" t="n">
-        <v>472.46</v>
-      </c>
-      <c r="F78" s="14" t="n">
-        <v>516.74</v>
-      </c>
-      <c r="G78" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="n">
-        <v>10132</v>
-      </c>
-      <c r="D79" s="18" t="n">
-        <v>9621.99</v>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>9502.49</v>
-      </c>
-      <c r="F79" s="18" t="n">
-        <v>9106.809999999999</v>
-      </c>
-      <c r="G79" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="C80" s="18" t="n">
-        <v>1845.8</v>
+        <v>538</v>
       </c>
       <c r="D80" s="18" t="n">
-        <v>1839.07</v>
+        <v>497.72</v>
       </c>
       <c r="E80" s="18" t="n">
-        <v>1767.71</v>
+        <v>476.54</v>
       </c>
       <c r="F80" s="18" t="n">
-        <v>1513.89</v>
+        <v>516.91</v>
       </c>
       <c r="G80" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="C81" s="18" t="n">
-        <v>7329</v>
-      </c>
-      <c r="D81" s="18" t="n">
-        <v>7133.62</v>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>7173.36</v>
-      </c>
-      <c r="F81" s="18" t="n">
-        <v>6859.43</v>
-      </c>
-      <c r="G81" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="n">
+        <v>958.6</v>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>921.6</v>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>921.29</v>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>945.11</v>
+      </c>
+      <c r="G81" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>EXIDEIND</t>
-        </is>
-      </c>
-      <c r="C82" s="18" t="n">
-        <v>359.05</v>
-      </c>
-      <c r="D82" s="18" t="n">
-        <v>338.64</v>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>330.73</v>
-      </c>
-      <c r="F82" s="18" t="n">
-        <v>351.57</v>
-      </c>
-      <c r="G82" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+      <c r="A82" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="n">
+        <v>1657.4</v>
+      </c>
+      <c r="D82" s="14" t="n">
+        <v>1560.36</v>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v>1568.93</v>
+      </c>
+      <c r="F82" s="14" t="n">
+        <v>1605.49</v>
+      </c>
+      <c r="G82" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="12" t="inlineStr">
+      <c r="A83" s="16" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="C83" s="14" t="n">
-        <v>950.2</v>
+        <v>2806.3</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>915.54</v>
+        <v>2684.77</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>919.04</v>
+        <v>2620.04</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>945.0599999999999</v>
+        <v>2598.03</v>
       </c>
       <c r="G83" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C84" s="14" t="n">
-        <v>1639.5</v>
+        <v>558.15</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>1550.14</v>
+        <v>542.87</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>1565.31</v>
+        <v>530.89</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>1604.97</v>
+        <v>544.9</v>
       </c>
       <c r="G84" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3525,23 +3525,23 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C85" s="14" t="n">
-        <v>2753.6</v>
+        <v>2902.5</v>
       </c>
       <c r="D85" s="14" t="n">
-        <v>2667.29</v>
+        <v>2810.11</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>2608.29</v>
+        <v>2647.75</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>2594.76</v>
+        <v>2174.93</v>
       </c>
       <c r="G85" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3553,190 +3553,134 @@
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C86" s="14" t="n">
-        <v>557</v>
+        <v>456.9</v>
       </c>
       <c r="D86" s="14" t="n">
-        <v>539.8200000000001</v>
+        <v>450.26</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>528.76</v>
+        <v>428.9</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>544.67</v>
+        <v>398.34</v>
       </c>
       <c r="G86" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B87" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C87" s="14" t="n">
-        <v>2912.9</v>
-      </c>
-      <c r="D87" s="14" t="n">
-        <v>2782.95</v>
-      </c>
-      <c r="E87" s="14" t="n">
-        <v>2623.81</v>
-      </c>
-      <c r="F87" s="14" t="n">
-        <v>2159.54</v>
-      </c>
-      <c r="G87" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>81.23999999999999</v>
+      </c>
+      <c r="D87" s="18" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>71.31999999999999</v>
+      </c>
+      <c r="F87" s="18" t="n">
+        <v>62.76</v>
+      </c>
+      <c r="G87" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C88" s="14" t="n">
-        <v>3487.7</v>
+        <v>1007.1</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>3464.74</v>
+        <v>997.8</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>3456.7</v>
+        <v>972.92</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>3267.23</v>
+        <v>899.37</v>
       </c>
       <c r="G88" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="D89" s="18" t="n">
-        <v>74.81999999999999</v>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>70.61</v>
-      </c>
-      <c r="F89" s="18" t="n">
-        <v>62.41</v>
-      </c>
-      <c r="G89" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="D89" s="14" t="n">
+        <v>287.4</v>
+      </c>
+      <c r="E89" s="14" t="n">
+        <v>282.16</v>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>253.59</v>
+      </c>
+      <c r="G89" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="12" t="inlineStr">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="C90" s="14" t="n">
-        <v>1015</v>
+        <v>910.7</v>
       </c>
       <c r="D90" s="14" t="n">
-        <v>996.8200000000001</v>
+        <v>874.72</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>971.52</v>
+        <v>865.9299999999999</v>
       </c>
       <c r="F90" s="14" t="n">
-        <v>898.29</v>
+        <v>850.88</v>
       </c>
       <c r="G90" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B91" s="13" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="n">
-        <v>289.15</v>
-      </c>
-      <c r="D91" s="14" t="n">
-        <v>286.82</v>
-      </c>
-      <c r="E91" s="14" t="n">
-        <v>281.52</v>
-      </c>
-      <c r="F91" s="14" t="n">
-        <v>252.86</v>
-      </c>
-      <c r="G91" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="n">
-        <v>913.9</v>
-      </c>
-      <c r="D92" s="14" t="n">
-        <v>866.21</v>
-      </c>
-      <c r="E92" s="14" t="n">
-        <v>861.99</v>
-      </c>
-      <c r="F92" s="14" t="n">
-        <v>849.62</v>
-      </c>
-      <c r="G92" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 05-May-2026  16:43</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 06-May-2026  16:38</t>
         </is>
       </c>
     </row>
@@ -665,69 +665,69 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.733</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.8223</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.75</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.8167</v>
+        <v>0.8443000000000001</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -765,7 +765,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>9</v>
@@ -774,7 +774,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.9</v>
@@ -783,100 +783,100 @@
         <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.7</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.625</v>
+        <v>0.8</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.625</v>
+        <v>0.733</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.575</v>
+        <v>0.467</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.6083</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="E10" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.467</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.5667</v>
+        <v>0.6446999999999999</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -889,149 +889,149 @@
         <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>6</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.6</v>
+        <v>0.733</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.6</v>
+        <v>0.733</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.5333</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.4</v>
+        <v>0.625</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.467</v>
+        <v>0.625</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.467</v>
+        <v>0.6</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.4447</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>10</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.4167</v>
+        <v>0.5832999999999999</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="F14" s="6" t="n">
-        <v>0.4</v>
+        <v>0.583</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.45</v>
+        <v>0.583</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.4</v>
+        <v>0.5553</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C15" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="F15" s="10" t="n">
-        <v>0.333</v>
+        <v>0.85</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.417</v>
+        <v>0.55</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.417</v>
+        <v>0.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.389</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1047,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>3</v>
@@ -1056,13 +1056,13 @@
         <v>0.333</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.2777</v>
+        <v>0.3053</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1078,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
@@ -1087,13 +1087,13 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0333</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1224,2463 +1224,2827 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2462</v>
+        <v>3096.3</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2260.06</v>
+        <v>2852.86</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2162.55</v>
+        <v>2846.88</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2250.36</v>
+        <v>2721.23</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1054.7</v>
+        <v>5557</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1020.73</v>
+        <v>5431.78</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>977.51</v>
+        <v>5448.25</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>863.39</v>
+        <v>5403.87</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>611.25</v>
+        <v>1484</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>582.6799999999999</v>
+        <v>1389.49</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>571.78</v>
+        <v>1327.39</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>530.8099999999999</v>
+        <v>1223.96</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1261.2</v>
+        <v>380.6</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1235.27</v>
+        <v>362.39</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1200.9</v>
+        <v>366.58</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1095.86</v>
+        <v>369.4</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>779.4</v>
+        <v>6702</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>768.61</v>
+        <v>6378.3</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>762.9299999999999</v>
+        <v>6270.59</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>745.14</v>
+        <v>6281.55</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1252.4</v>
+        <v>1311</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1241.36</v>
+        <v>1285.23</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1216.46</v>
+        <v>1272.02</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1150.95</v>
+        <v>1252.46</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>88.83</v>
+        <v>1811.5</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>87.56999999999999</v>
+        <v>1760.71</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>84.09</v>
+        <v>1747.46</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>77.06999999999999</v>
+        <v>1744.5</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2742.1</v>
+        <v>2377.6</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2520.87</v>
+        <v>2311.99</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2407.45</v>
+        <v>2213.21</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>2400.05</v>
+        <v>2002.29</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>187.31</v>
+        <v>736</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>176.41</v>
+        <v>678.16</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>166.22</v>
+        <v>639.51</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>146.64</v>
+        <v>573.28</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>211.32</v>
+        <v>1564.4</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>209.17</v>
+        <v>1519.4</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>203.25</v>
+        <v>1504.87</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>183.61</v>
+        <v>1449.55</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>JBCHEPHARM</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>2141.5</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>2044.25</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>2015.89</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>1856.99</v>
+      </c>
+      <c r="G13" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>1177.6</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>1112.28</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>1074.61</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>966.24</v>
+      </c>
+      <c r="G14" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>2442.9</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>2329.23</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>2296.32</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>2157.15</v>
+      </c>
+      <c r="G15" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>2361</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>2213.02</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>2162.41</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>2241.86</v>
+      </c>
+      <c r="G16" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>1150.1</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>1087.1</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>1030.01</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>929.41</v>
+      </c>
+      <c r="G17" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>1850.2</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1748.67</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>1735.53</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>1718.85</v>
+      </c>
+      <c r="G18" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>4358.3</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>4205.6</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>4174.62</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>3881.95</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>938.8</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>916.0700000000001</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>910.66</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>921.26</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>1254</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>1132.17</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>995.3</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>877.49</v>
-      </c>
-      <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>AJANTPHARM</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>2897.6</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>2826.25</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>2837.04</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>2723.57</v>
-      </c>
-      <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>1428.1</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>1379.54</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>1321</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>1224.04</v>
-      </c>
-      <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>6651</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>6344.23</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>6252.98</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>6274.28</v>
-      </c>
-      <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>1773.3</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>1755.36</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>1744.84</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>1744.33</v>
-      </c>
-      <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>GLENMARK</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>2417.9</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>2305.09</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>2206.5</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>1998.56</v>
-      </c>
-      <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>711.8</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>672.0700000000001</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>635.58</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>572.79</v>
-      </c>
-      <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>IPCALAB</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>1541.8</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>1514.66</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>1502.45</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>1448.84</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>2094.6</v>
+        <v>2540.3</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>2034.01</v>
+        <v>2300.54</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>2010.77</v>
+        <v>2186.81</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>1859.51</v>
+        <v>2246.49</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1164.1</v>
+        <v>1045.8</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1105.4</v>
+        <v>1023.12</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>1070.4</v>
+        <v>980.1799999999999</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>964.54</v>
+        <v>864.9299999999999</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>2343.3</v>
+        <v>550.5</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>2317.76</v>
+        <v>539.52</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>2289.61</v>
+        <v>532.39</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>2155.77</v>
+        <v>438.14</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>2319.5</v>
+        <v>634.6</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>2197.44</v>
+        <v>587.62</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>2154.3</v>
+        <v>574.24</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>2244.57</v>
+        <v>530.67</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>1125</v>
+        <v>1264.3</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>1078.39</v>
+        <v>1238.04</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>1022.15</v>
+        <v>1203.39</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>927.65</v>
+        <v>1095.05</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>1820.8</v>
+        <v>1273.3</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1737.98</v>
+        <v>1246.31</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>1730.85</v>
+        <v>1220.49</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>1718.98</v>
+        <v>1154.27</v>
       </c>
       <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>4275.1</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>4189.53</v>
+        <v>87.72</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>4167.12</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>3878.4</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>531</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>510.27</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>492.39</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>488.82</v>
-      </c>
-      <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>RATNAMANI</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>2737</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>2541.46</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>2420.37</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>2401.09</v>
+      </c>
+      <c r="G28" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>5834.5</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>5706.83</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>5748.09</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>5778.96</v>
-      </c>
-      <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRITANNIA","Chart 📈")</f>
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>186.04</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>146.77</v>
+      </c>
+      <c r="G29" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>COLPAL</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>2178.9</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>2080.8</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>2059.38</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>2170.36</v>
-      </c>
-      <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COLPAL","Chart 📈")</f>
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>215.47</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>209.77</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>203.73</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>184.12</v>
+      </c>
+      <c r="G30" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>2327.4</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>2256.95</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>2244.63</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>2326.51</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDUNILVR","Chart 📈")</f>
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>1284.7</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>1146.7</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>1006.65</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>880.8200000000001</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>807.2</v>
+        <v>735.1</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>772.58</v>
+        <v>691.36</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>764.65</v>
+        <v>676.13</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>744.48</v>
+        <v>713.49</v>
       </c>
       <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1477.8</v>
+        <v>651</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>1365.62</v>
+        <v>616.74</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>1306.94</v>
+        <v>582.24</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>1250.94</v>
+        <v>585.59</v>
       </c>
       <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>3338.9</v>
+        <v>165.68</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>3184.22</v>
+        <v>160.6</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>3003.83</v>
+        <v>157.86</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>2908.28</v>
+        <v>164.69</v>
       </c>
       <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>GSPL</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>1153.5</v>
+        <v>296.4</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>1133.46</v>
+        <v>276.21</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>1121.46</v>
+        <v>274.42</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>1131.1</v>
+        <v>292.4</v>
       </c>
       <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GSPL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>511.7</v>
+        <v>1166.8</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>481.97</v>
+        <v>1108.78</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>460.03</v>
+        <v>1085.74</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>467.87</v>
+        <v>1161.69</v>
       </c>
       <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>283.3</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>275.79</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>276.87</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>281.16</v>
+      </c>
+      <c r="G37" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>1437.9</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>1396.86</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>1395.04</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>1426.57</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>OBEROIRLTY</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n">
-        <v>1666.3</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>1659.95</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>1606.19</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>1618.12</v>
-      </c>
-      <c r="G37" s="19">
+      <c r="C39" s="18" t="n">
+        <v>1673.4</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>1661.23</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>1608.83</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>1613.22</v>
+      </c>
+      <c r="G39" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>PHOENIXLTD</t>
         </is>
       </c>
-      <c r="C38" s="18" t="n">
-        <v>1793.9</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>1745.62</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>1708.42</v>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>1674.83</v>
-      </c>
-      <c r="G38" s="19">
+      <c r="C40" s="18" t="n">
+        <v>1839.1</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>1754.53</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>1713.54</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>1671.68</v>
+      </c>
+      <c r="G40" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>SOBHA</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n">
-        <v>1446.3</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>1377.57</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>1366.33</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>1427.48</v>
-      </c>
-      <c r="G39" s="19">
+      <c r="C41" s="18" t="n">
+        <v>1451.8</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>1389.61</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>1372.24</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>1422.81</v>
+      </c>
+      <c r="G41" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>647.2</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>613.13</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>579.4400000000001</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>587.64</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>289.95</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>288.04</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>278.51</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>253.52</v>
-      </c>
-      <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>282.55</v>
+        <v>271.8</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>276.6</v>
+        <v>258.8</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>281.77</v>
+        <v>266.58</v>
       </c>
       <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C43" s="14" t="n">
-        <v>1463.6</v>
+        <v>1068.9</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>1392.54</v>
+        <v>1015.46</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>1393.29</v>
+        <v>1002.75</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>1427.32</v>
+        <v>1021</v>
       </c>
       <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>7328</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>7024.21</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>6535.62</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>5781.23</v>
-      </c>
-      <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>652.7</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>616.16</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>577.5</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>561.7</v>
+      </c>
+      <c r="G44" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>1409.6</v>
+        <v>524.85</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>1282.11</v>
+        <v>511.66</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>1152.07</v>
+        <v>493.66</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>1006.73</v>
+        <v>489.31</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>1331.4</v>
+        <v>5783</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>1157.35</v>
+        <v>5714.09</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>1050.7</v>
+        <v>5749.47</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>997.28</v>
+        <v>5781.82</v>
       </c>
       <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRITANNIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>229.96</v>
+        <v>814.8</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>204.42</v>
+        <v>776.6</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>180.17</v>
+        <v>766.62</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>150.42</v>
+        <v>744.97</v>
       </c>
       <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>374.95</v>
+        <v>1486.1</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>329.02</v>
+        <v>1385.25</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>298.59</v>
+        <v>1319.71</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>268.26</v>
+        <v>1256.48</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
-        <v>186.88</v>
+        <v>3357.2</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>178.4</v>
+        <v>3200.7</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>168.05</v>
+        <v>3017.69</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>163.19</v>
+        <v>2913.13</v>
       </c>
       <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>826.9</v>
+        <v>1152.2</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>787.4</v>
+        <v>1135.24</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>742.5700000000001</v>
+        <v>1122.67</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>696.99</v>
+        <v>1130.8</v>
       </c>
       <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>472.6</v>
+        <v>508.95</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>460.37</v>
+        <v>484.54</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>447.99</v>
+        <v>461.95</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>410.43</v>
+        <v>466.28</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="n">
-        <v>4578.9</v>
-      </c>
-      <c r="D52" s="18" t="n">
-        <v>4292.07</v>
-      </c>
-      <c r="E52" s="18" t="n">
-        <v>3972.43</v>
-      </c>
-      <c r="F52" s="18" t="n">
-        <v>3227.09</v>
-      </c>
-      <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="n">
+        <v>10319</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>9724.91</v>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>9554.99</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>9130.139999999999</v>
+      </c>
+      <c r="G52" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>JPPOWER</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="n">
-        <v>19.26</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>18.64</v>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="F53" s="18" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="n">
+        <v>1873.8</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>1847.8</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>1779.67</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>1521.87</v>
+      </c>
+      <c r="G53" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="n">
-        <v>561.95</v>
-      </c>
-      <c r="D54" s="18" t="n">
-        <v>543.95</v>
-      </c>
-      <c r="E54" s="18" t="n">
-        <v>520.17</v>
-      </c>
-      <c r="F54" s="18" t="n">
-        <v>504.04</v>
-      </c>
-      <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="n">
+        <v>36645</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>36012.21</v>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>35205.37</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>35273.26</v>
+      </c>
+      <c r="G54" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>NHPC</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="n">
-        <v>83.17</v>
-      </c>
-      <c r="D55" s="18" t="n">
-        <v>81.47</v>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="F55" s="18" t="n">
-        <v>79.31999999999999</v>
-      </c>
-      <c r="G55" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="n">
+        <v>7310.5</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>7164.65</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>7181.55</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>6875.15</v>
+      </c>
+      <c r="G55" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>NLCINDIA</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="n">
-        <v>316.45</v>
-      </c>
-      <c r="D56" s="18" t="n">
-        <v>300.77</v>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>282.68</v>
-      </c>
-      <c r="F56" s="18" t="n">
-        <v>257.72</v>
-      </c>
-      <c r="G56" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="n">
+        <v>127.41</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>122.17</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>120.46</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>112.96</v>
+      </c>
+      <c r="G56" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="n">
-        <v>398.65</v>
-      </c>
-      <c r="D57" s="18" t="n">
-        <v>394.8</v>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>382.8</v>
-      </c>
-      <c r="F57" s="18" t="n">
-        <v>354.8</v>
-      </c>
-      <c r="G57" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>3617.9</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>3575.31</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>3603.84</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>3467.85</v>
+      </c>
+      <c r="G57" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>319.45</v>
+        <v>8661.5</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>313.82</v>
+        <v>7823.09</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>303.65</v>
+        <v>7434.81</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>287.84</v>
+        <v>7101.28</v>
       </c>
       <c r="G58" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="C59" s="18" t="n">
-        <v>34255</v>
+        <v>1806.6</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>30506.32</v>
+        <v>1802.55</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>27258.09</v>
+        <v>1800.49</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>21973.4</v>
+        <v>1800.17</v>
       </c>
       <c r="G59" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="C60" s="18" t="n">
-        <v>1349.9</v>
+        <v>798.5</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>1119.43</v>
+        <v>772.04</v>
       </c>
       <c r="E60" s="18" t="n">
-        <v>993.01</v>
+        <v>752.45</v>
       </c>
       <c r="F60" s="18" t="n">
-        <v>839.0700000000001</v>
+        <v>755.09</v>
       </c>
       <c r="G60" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="20" t="inlineStr">
         <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>284.05</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>262.08</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>255</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>272.87</v>
+      </c>
+      <c r="G61" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n">
-        <v>3846.6</v>
-      </c>
-      <c r="D61" s="18" t="n">
-        <v>3655.91</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>3439.77</v>
-      </c>
-      <c r="F61" s="18" t="n">
-        <v>3221.82</v>
-      </c>
-      <c r="G61" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>7182.5</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>7057.87</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>6587.3</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>5796.93</v>
+      </c>
+      <c r="G62" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="n">
-        <v>54.85</v>
-      </c>
-      <c r="D62" s="18" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="E62" s="18" t="n">
-        <v>48.73</v>
-      </c>
-      <c r="F62" s="18" t="n">
-        <v>51.54</v>
-      </c>
-      <c r="G62" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="20" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>1407.3</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>1294.03</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>1162.08</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>1008.22</v>
+      </c>
+      <c r="G63" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="n">
-        <v>442.65</v>
-      </c>
-      <c r="D63" s="18" t="n">
-        <v>430.44</v>
-      </c>
-      <c r="E63" s="18" t="n">
-        <v>409.7</v>
-      </c>
-      <c r="F63" s="18" t="n">
-        <v>392.01</v>
-      </c>
-      <c r="G63" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="20" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="n">
+        <v>1353</v>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>1183.32</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>1069.44</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>999.61</v>
+      </c>
+      <c r="G64" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="n">
-        <v>4113.6</v>
-      </c>
-      <c r="D64" s="18" t="n">
-        <v>3923.98</v>
-      </c>
-      <c r="E64" s="18" t="n">
-        <v>3600.31</v>
-      </c>
-      <c r="F64" s="18" t="n">
-        <v>3290.21</v>
-      </c>
-      <c r="G64" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="20" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="n">
+        <v>229.12</v>
+      </c>
+      <c r="D65" s="14" t="n">
+        <v>206.77</v>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>182.09</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>150.87</v>
+      </c>
+      <c r="G65" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="n">
-        <v>1734.7</v>
-      </c>
-      <c r="D65" s="18" t="n">
-        <v>1636.98</v>
-      </c>
-      <c r="E65" s="18" t="n">
-        <v>1536.84</v>
-      </c>
-      <c r="F65" s="18" t="n">
-        <v>1414.59</v>
-      </c>
-      <c r="G65" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="20" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="n">
+        <v>385.95</v>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>334.44</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>302.01</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>268.53</v>
+      </c>
+      <c r="G66" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C66" s="18" t="n">
-        <v>556.45</v>
-      </c>
-      <c r="D66" s="18" t="n">
-        <v>540.58</v>
-      </c>
-      <c r="E66" s="18" t="n">
-        <v>512.51</v>
-      </c>
-      <c r="F66" s="18" t="n">
-        <v>516.91</v>
-      </c>
-      <c r="G66" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="C67" s="14" t="n">
-        <v>1063.1</v>
+        <v>185.01</v>
       </c>
       <c r="D67" s="14" t="n">
-        <v>1009.83</v>
+        <v>179.03</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>1000.06</v>
+        <v>168.72</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>1021.58</v>
+        <v>163.23</v>
       </c>
       <c r="G67" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C68" s="14" t="n">
-        <v>645.65</v>
+        <v>828.9</v>
       </c>
       <c r="D68" s="14" t="n">
-        <v>608.46</v>
+        <v>791.35</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>571.37</v>
+        <v>745.95</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>561.6900000000001</v>
+        <v>695.3</v>
       </c>
       <c r="G68" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="n">
-        <v>8204</v>
-      </c>
-      <c r="D69" s="18" t="n">
-        <v>7702.75</v>
-      </c>
-      <c r="E69" s="18" t="n">
-        <v>7358.4</v>
-      </c>
-      <c r="F69" s="18" t="n">
-        <v>7096.33</v>
-      </c>
-      <c r="G69" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="n">
+        <v>470.2</v>
+      </c>
+      <c r="D69" s="14" t="n">
+        <v>461.31</v>
+      </c>
+      <c r="E69" s="14" t="n">
+        <v>448.86</v>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>410.46</v>
+      </c>
+      <c r="G69" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="n">
-        <v>1802.3</v>
-      </c>
-      <c r="D70" s="18" t="n">
-        <v>1802.13</v>
-      </c>
-      <c r="E70" s="18" t="n">
-        <v>1800.24</v>
-      </c>
-      <c r="F70" s="18" t="n">
-        <v>1799.42</v>
-      </c>
-      <c r="G70" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="n">
+        <v>4563.1</v>
+      </c>
+      <c r="D70" s="14" t="n">
+        <v>4317.88</v>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>3995.59</v>
+      </c>
+      <c r="F70" s="14" t="n">
+        <v>3235.29</v>
+      </c>
+      <c r="G70" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>CENTURYPLY</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="n">
-        <v>792.95</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>769.25</v>
-      </c>
-      <c r="E71" s="18" t="n">
-        <v>750.5700000000001</v>
-      </c>
-      <c r="F71" s="18" t="n">
-        <v>754.52</v>
-      </c>
-      <c r="G71" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>JPPOWER</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="D71" s="14" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="E71" s="14" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="F71" s="14" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="G71" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="n">
-        <v>275.5</v>
-      </c>
-      <c r="D72" s="18" t="n">
-        <v>259.76</v>
-      </c>
-      <c r="E72" s="18" t="n">
-        <v>253.82</v>
-      </c>
-      <c r="F72" s="18" t="n">
-        <v>273.33</v>
-      </c>
-      <c r="G72" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="n">
+        <v>567.9</v>
+      </c>
+      <c r="D72" s="14" t="n">
+        <v>546.23</v>
+      </c>
+      <c r="E72" s="14" t="n">
+        <v>522.04</v>
+      </c>
+      <c r="F72" s="14" t="n">
+        <v>503.45</v>
+      </c>
+      <c r="G72" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C73" s="14" t="n">
-        <v>10046</v>
+        <v>83.66</v>
       </c>
       <c r="D73" s="14" t="n">
-        <v>9662.370000000001</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>9523.799999999999</v>
+        <v>79.37</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>9116.15</v>
+        <v>79.13</v>
       </c>
       <c r="G73" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C74" s="14" t="n">
-        <v>1866.6</v>
+        <v>322.3</v>
       </c>
       <c r="D74" s="14" t="n">
-        <v>1845.06</v>
+        <v>302.82</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>1775.83</v>
+        <v>284.23</v>
       </c>
       <c r="F74" s="14" t="n">
-        <v>1521.02</v>
+        <v>257.75</v>
       </c>
       <c r="G74" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C75" s="14" t="n">
-        <v>7301.5</v>
+        <v>394.85</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>7149.29</v>
+        <v>394.8</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>7176.28</v>
+        <v>383.27</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>6866.31</v>
+        <v>354.66</v>
       </c>
       <c r="G75" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C76" s="14" t="n">
-        <v>361.15</v>
+        <v>315.95</v>
       </c>
       <c r="D76" s="14" t="n">
-        <v>342.66</v>
+        <v>314.03</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>333.05</v>
+        <v>304.13</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>351.75</v>
+        <v>288.07</v>
       </c>
       <c r="G76" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B77" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C77" s="18" t="n">
-        <v>128.77</v>
-      </c>
-      <c r="D77" s="18" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>87.55</v>
-      </c>
-      <c r="F77" s="18" t="n">
-        <v>77.31</v>
-      </c>
-      <c r="G77" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="n">
+        <v>33380</v>
+      </c>
+      <c r="D77" s="14" t="n">
+        <v>30780.01</v>
+      </c>
+      <c r="E77" s="14" t="n">
+        <v>27498.15</v>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>22073.55</v>
+      </c>
+      <c r="G77" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="D78" s="18" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="F78" s="18" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="G78" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="n">
+        <v>1282.5</v>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>1147</v>
+      </c>
+      <c r="E78" s="14" t="n">
+        <v>1014.05</v>
+      </c>
+      <c r="F78" s="14" t="n">
+        <v>845.6900000000001</v>
+      </c>
+      <c r="G78" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="n">
-        <v>9707</v>
-      </c>
-      <c r="D79" s="18" t="n">
-        <v>8666.66</v>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>7904.83</v>
-      </c>
-      <c r="F79" s="18" t="n">
-        <v>7889.43</v>
-      </c>
-      <c r="G79" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="n">
+        <v>3841.8</v>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>3673.61</v>
+      </c>
+      <c r="E79" s="14" t="n">
+        <v>3455.53</v>
+      </c>
+      <c r="F79" s="14" t="n">
+        <v>3227.11</v>
+      </c>
+      <c r="G79" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B80" s="17" t="inlineStr">
-        <is>
-          <t>TANLA</t>
-        </is>
-      </c>
-      <c r="C80" s="18" t="n">
-        <v>538</v>
-      </c>
-      <c r="D80" s="18" t="n">
-        <v>497.72</v>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>476.54</v>
-      </c>
-      <c r="F80" s="18" t="n">
-        <v>516.91</v>
-      </c>
-      <c r="G80" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v>74.84999999999999</v>
+      </c>
+      <c r="F80" s="14" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="G80" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SJVN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C81" s="14" t="n">
-        <v>958.6</v>
+        <v>54.32</v>
       </c>
       <c r="D81" s="14" t="n">
-        <v>921.6</v>
+        <v>52.3</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>921.29</v>
+        <v>48.95</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>945.11</v>
+        <v>51.3</v>
       </c>
       <c r="G81" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C82" s="14" t="n">
-        <v>1657.4</v>
+        <v>443.25</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>1560.36</v>
+        <v>431.66</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>1568.93</v>
+        <v>411.01</v>
       </c>
       <c r="F82" s="14" t="n">
-        <v>1605.49</v>
+        <v>391.36</v>
       </c>
       <c r="G82" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C83" s="14" t="n">
-        <v>2806.3</v>
+        <v>4076.9</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>2684.77</v>
+        <v>3938.54</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>2620.04</v>
+        <v>3619</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>2598.03</v>
+        <v>3295.54</v>
       </c>
       <c r="G83" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C84" s="14" t="n">
-        <v>558.15</v>
+        <v>1734</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>542.87</v>
+        <v>1646.22</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>530.89</v>
+        <v>1544.57</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>544.9</v>
+        <v>1416.51</v>
       </c>
       <c r="G84" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="16" t="inlineStr">
         <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>TRITURBINE</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="n">
+        <v>557.3</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>542.17</v>
+      </c>
+      <c r="E85" s="14" t="n">
+        <v>514.27</v>
+      </c>
+      <c r="F85" s="14" t="n">
+        <v>515.52</v>
+      </c>
+      <c r="G85" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B85" s="13" t="inlineStr">
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="n">
+        <v>980.75</v>
+      </c>
+      <c r="D86" s="18" t="n">
+        <v>927.23</v>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>923.62</v>
+      </c>
+      <c r="F86" s="18" t="n">
+        <v>944.37</v>
+      </c>
+      <c r="G86" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>1711.9</v>
+      </c>
+      <c r="D87" s="18" t="n">
+        <v>1574.79</v>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>1574.53</v>
+      </c>
+      <c r="F87" s="18" t="n">
+        <v>1604.82</v>
+      </c>
+      <c r="G87" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="n">
+        <v>2815.9</v>
+      </c>
+      <c r="D88" s="18" t="n">
+        <v>2697.26</v>
+      </c>
+      <c r="E88" s="18" t="n">
+        <v>2627.72</v>
+      </c>
+      <c r="F88" s="18" t="n">
+        <v>2595.08</v>
+      </c>
+      <c r="G88" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>582.15</v>
+      </c>
+      <c r="D89" s="18" t="n">
+        <v>546.61</v>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>532.9</v>
+      </c>
+      <c r="F89" s="18" t="n">
+        <v>543.39</v>
+      </c>
+      <c r="G89" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
         <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C85" s="14" t="n">
-        <v>2902.5</v>
-      </c>
-      <c r="D85" s="14" t="n">
-        <v>2810.11</v>
-      </c>
-      <c r="E85" s="14" t="n">
-        <v>2647.75</v>
-      </c>
-      <c r="F85" s="14" t="n">
-        <v>2174.93</v>
-      </c>
-      <c r="G85" s="15">
+      <c r="C90" s="18" t="n">
+        <v>2973.2</v>
+      </c>
+      <c r="D90" s="18" t="n">
+        <v>2825.64</v>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>2660.51</v>
+      </c>
+      <c r="F90" s="18" t="n">
+        <v>2178.54</v>
+      </c>
+      <c r="G90" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="16" t="inlineStr">
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="20" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B86" s="13" t="inlineStr">
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="n">
+        <v>3533.6</v>
+      </c>
+      <c r="D91" s="18" t="n">
+        <v>3467.03</v>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>3458.24</v>
+      </c>
+      <c r="F91" s="18" t="n">
+        <v>3276.82</v>
+      </c>
+      <c r="G91" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
         <is>
           <t>PFC</t>
         </is>
       </c>
-      <c r="C86" s="14" t="n">
-        <v>456.9</v>
-      </c>
-      <c r="D86" s="14" t="n">
-        <v>450.26</v>
-      </c>
-      <c r="E86" s="14" t="n">
-        <v>428.9</v>
-      </c>
-      <c r="F86" s="14" t="n">
-        <v>398.34</v>
-      </c>
-      <c r="G86" s="15">
+      <c r="C92" s="18" t="n">
+        <v>463.9</v>
+      </c>
+      <c r="D92" s="18" t="n">
+        <v>451.56</v>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>430.27</v>
+      </c>
+      <c r="F92" s="18" t="n">
+        <v>397.81</v>
+      </c>
+      <c r="G92" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>1004.1</v>
+      </c>
+      <c r="D93" s="18" t="n">
+        <v>981.03</v>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>984.61</v>
+      </c>
+      <c r="F93" s="18" t="n">
+        <v>876.1799999999999</v>
+      </c>
+      <c r="G93" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B87" s="17" t="inlineStr">
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>CENTRALBK</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="F94" s="14" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="G94" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTRALBK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
         <is>
           <t>MAHABANK</t>
         </is>
       </c>
-      <c r="C87" s="18" t="n">
-        <v>81.23999999999999</v>
-      </c>
-      <c r="D87" s="18" t="n">
-        <v>75.75</v>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>71.31999999999999</v>
-      </c>
-      <c r="F87" s="18" t="n">
-        <v>62.76</v>
-      </c>
-      <c r="G87" s="19">
+      <c r="C95" s="14" t="n">
+        <v>83.63</v>
+      </c>
+      <c r="D95" s="14" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E95" s="14" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="F95" s="14" t="n">
+        <v>62.83</v>
+      </c>
+      <c r="G95" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="12" t="inlineStr">
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="n">
+        <v>1096</v>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>1078.94</v>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v>1078.36</v>
+      </c>
+      <c r="F96" s="14" t="n">
+        <v>991.23</v>
+      </c>
+      <c r="G96" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="n">
+        <v>141.46</v>
+      </c>
+      <c r="D97" s="18" t="n">
+        <v>105.67</v>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="F97" s="18" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="G97" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D98" s="18" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F98" s="18" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="G98" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="n">
+        <v>9694.5</v>
+      </c>
+      <c r="D99" s="18" t="n">
+        <v>8764.549999999999</v>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>7975</v>
+      </c>
+      <c r="F99" s="18" t="n">
+        <v>7887.77</v>
+      </c>
+      <c r="G99" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>TANLA</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="n">
+        <v>562.05</v>
+      </c>
+      <c r="D100" s="18" t="n">
+        <v>503.85</v>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>479.89</v>
+      </c>
+      <c r="F100" s="18" t="n">
+        <v>515.47</v>
+      </c>
+      <c r="G100" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="12" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B88" s="13" t="inlineStr">
+      <c r="B101" s="13" t="inlineStr">
         <is>
           <t>AUBANK</t>
         </is>
       </c>
-      <c r="C88" s="14" t="n">
-        <v>1007.1</v>
-      </c>
-      <c r="D88" s="14" t="n">
-        <v>997.8</v>
-      </c>
-      <c r="E88" s="14" t="n">
-        <v>972.92</v>
-      </c>
-      <c r="F88" s="14" t="n">
-        <v>899.37</v>
-      </c>
-      <c r="G88" s="15">
+      <c r="C101" s="14" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D101" s="14" t="n">
+        <v>1001.78</v>
+      </c>
+      <c r="E101" s="14" t="n">
+        <v>976.53</v>
+      </c>
+      <c r="F101" s="14" t="n">
+        <v>901.2</v>
+      </c>
+      <c r="G101" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="16" t="inlineStr">
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="16" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B89" s="13" t="inlineStr">
+      <c r="B102" s="13" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C89" s="14" t="n">
-        <v>292.6</v>
-      </c>
-      <c r="D89" s="14" t="n">
-        <v>287.4</v>
-      </c>
-      <c r="E89" s="14" t="n">
-        <v>282.16</v>
-      </c>
-      <c r="F89" s="14" t="n">
-        <v>253.59</v>
-      </c>
-      <c r="G89" s="15">
+      <c r="C102" s="14" t="n">
+        <v>293</v>
+      </c>
+      <c r="D102" s="14" t="n">
+        <v>287.93</v>
+      </c>
+      <c r="E102" s="14" t="n">
+        <v>282.59</v>
+      </c>
+      <c r="F102" s="14" t="n">
+        <v>253.64</v>
+      </c>
+      <c r="G102" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="16" t="inlineStr">
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="16" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="B103" s="13" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="C90" s="14" t="n">
-        <v>910.7</v>
-      </c>
-      <c r="D90" s="14" t="n">
-        <v>874.72</v>
-      </c>
-      <c r="E90" s="14" t="n">
-        <v>865.9299999999999</v>
-      </c>
-      <c r="F90" s="14" t="n">
-        <v>850.88</v>
-      </c>
-      <c r="G90" s="15">
+      <c r="C103" s="14" t="n">
+        <v>946.75</v>
+      </c>
+      <c r="D103" s="14" t="n">
+        <v>881.58</v>
+      </c>
+      <c r="E103" s="14" t="n">
+        <v>869.1</v>
+      </c>
+      <c r="F103" s="14" t="n">
+        <v>850.61</v>
+      </c>
+      <c r="G103" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 06-May-2026  16:38</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 07-May-2026  17:37</t>
         </is>
       </c>
     </row>
@@ -727,187 +727,187 @@
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I6" s="7" t="n">
         <v>0.8</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.7556999999999999</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="F7" s="10" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.3</v>
+        <v>0.667</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.7333</v>
+        <v>0.778</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F8" s="6" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.9</v>
+        <v>0.733</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.667</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.7</v>
+        <v>0.7556999999999999</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.733</v>
+        <v>0.9</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.467</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C10" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="E10" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>7</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.6446999999999999</v>
+        <v>0.6333</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.733</v>
+        <v>0.667</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.733</v>
+        <v>0.667</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.622</v>
+        <v>0.6003000000000001</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -920,7 +920,7 @@
         <v>40</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>25</v>
@@ -929,7 +929,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.625</v>
+        <v>0.575</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.625</v>
@@ -938,100 +938,100 @@
         <v>0.6</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.6167</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.5832999999999999</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="E14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="F14" s="6" t="n">
-        <v>0.583</v>
+        <v>0.7</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.583</v>
+        <v>0.3</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.5553</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.5333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1075,25 +1075,25 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3096.3</v>
+        <v>3078.4</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2852.86</v>
+        <v>2874.34</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2846.88</v>
+        <v>2855.96</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2721.23</v>
+        <v>2724.55</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>5557</v>
+        <v>5590.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>5431.78</v>
+        <v>5446.89</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>5448.25</v>
+        <v>5453.83</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>5403.87</v>
+        <v>5406.51</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1484</v>
+        <v>1478.7</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1389.49</v>
+        <v>1397.98</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1327.39</v>
+        <v>1333.33</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1223.96</v>
+        <v>1225.41</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>380.6</v>
+        <v>382.25</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>362.39</v>
+        <v>364.28</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>366.58</v>
+        <v>367.2</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>369.4</v>
+        <v>369.94</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>6702</v>
+        <v>6702.5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6378.3</v>
+        <v>6409.18</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>6270.59</v>
+        <v>6287.53</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>6281.55</v>
+        <v>6284.67</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1311</v>
+        <v>1307.6</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1285.23</v>
+        <v>1287.36</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1272.02</v>
+        <v>1273.41</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1252.46</v>
+        <v>1253.03</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1811.5</v>
+        <v>1870.6</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1760.71</v>
+        <v>1771.42</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1747.46</v>
+        <v>1752.62</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1744.5</v>
+        <v>1745.06</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2377.6</v>
+        <v>2371.6</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2311.99</v>
+        <v>2317.67</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2213.21</v>
+        <v>2219.42</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>2002.29</v>
+        <v>2008.36</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>736</v>
+        <v>743.5</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>678.16</v>
+        <v>686.65</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>639.51</v>
+        <v>645.9400000000001</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>573.28</v>
+        <v>576.7</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>1564.4</v>
+        <v>1560.1</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>1519.4</v>
+        <v>1523.28</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>1504.87</v>
+        <v>1507.04</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1449.55</v>
+        <v>1449.1</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>2141.5</v>
+        <v>2143.2</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>2044.25</v>
+        <v>2053.67</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>2015.89</v>
+        <v>2020.88</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1856.99</v>
+        <v>1862.47</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1177.6</v>
+        <v>1206.5</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>1112.28</v>
+        <v>1121.25</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>1074.61</v>
+        <v>1079.78</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>966.24</v>
+        <v>968.47</v>
       </c>
       <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>2442.9</v>
+        <v>2460.1</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>2329.23</v>
+        <v>2341.69</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>2296.32</v>
+        <v>2302.75</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>2157.15</v>
+        <v>2161.99</v>
       </c>
       <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>2361</v>
+        <v>2375.2</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>2213.02</v>
+        <v>2228.47</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2162.41</v>
+        <v>2170.76</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2241.86</v>
+        <v>2248.47</v>
       </c>
       <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
@@ -1625,16 +1625,16 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1150.1</v>
+        <v>1155.2</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1087.1</v>
+        <v>1093.58</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1030.01</v>
+        <v>1034.92</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>929.41</v>
+        <v>930.29</v>
       </c>
       <c r="G17" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>1850.2</v>
+        <v>1834.4</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>1748.67</v>
+        <v>1756.84</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>1735.53</v>
+        <v>1739.4</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1718.85</v>
+        <v>1716.9</v>
       </c>
       <c r="G18" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
@@ -1681,16 +1681,16 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>4358.3</v>
+        <v>4362.7</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>4205.6</v>
+        <v>4220.57</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>4174.62</v>
+        <v>4181.99</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>3881.95</v>
+        <v>3888.44</v>
       </c>
       <c r="G19" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
@@ -1709,16 +1709,16 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>938.8</v>
+        <v>940.3</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>916.0700000000001</v>
+        <v>916.9</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>910.66</v>
+        <v>911.23</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>921.26</v>
+        <v>921.61</v>
       </c>
       <c r="G20" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>2540.3</v>
+        <v>2513.7</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>2300.54</v>
+        <v>2320.84</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>2186.81</v>
+        <v>2199.63</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>2246.49</v>
+        <v>2249.07</v>
       </c>
       <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1765,16 +1765,16 @@
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1045.8</v>
+        <v>1055.7</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1023.12</v>
+        <v>1026.22</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>980.1799999999999</v>
+        <v>983.15</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>864.9299999999999</v>
+        <v>867.34</v>
       </c>
       <c r="G22" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>550.5</v>
+        <v>568.6</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>539.52</v>
+        <v>542.29</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>532.39</v>
+        <v>533.8099999999999</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>438.14</v>
+        <v>439.82</v>
       </c>
       <c r="G23" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>634.6</v>
+        <v>636.55</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>587.62</v>
+        <v>592.28</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>574.24</v>
+        <v>576.6799999999999</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>530.67</v>
+        <v>532.45</v>
       </c>
       <c r="G24" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>1264.3</v>
+        <v>1258.2</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>1238.04</v>
+        <v>1239.96</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>1203.39</v>
+        <v>1205.54</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>1095.05</v>
+        <v>1097.09</v>
       </c>
       <c r="G25" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
@@ -1877,16 +1877,16 @@
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>1273.3</v>
+        <v>1283.4</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1246.31</v>
+        <v>1249.84</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>1220.49</v>
+        <v>1222.95</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>1154.27</v>
+        <v>1155.44</v>
       </c>
       <c r="G26" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>89.18000000000001</v>
+        <v>90.14</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>87.72</v>
+        <v>87.95</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>84.29000000000001</v>
+        <v>84.52</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>77.06999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="G27" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
@@ -1933,16 +1933,16 @@
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>2737</v>
+        <v>2827.1</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>2541.46</v>
+        <v>2568.66</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>2420.37</v>
+        <v>2436.33</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>2401.09</v>
+        <v>2409.37</v>
       </c>
       <c r="G28" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>186.04</v>
+        <v>187.28</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>177.33</v>
+        <v>178.28</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>167</v>
+        <v>167.8</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>146.77</v>
+        <v>147.35</v>
       </c>
       <c r="G29" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>215.47</v>
+        <v>217.09</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>209.77</v>
+        <v>210.46</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>203.73</v>
+        <v>204.25</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>184.12</v>
+        <v>184.57</v>
       </c>
       <c r="G30" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
@@ -2017,16 +2017,16 @@
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>1284.7</v>
+        <v>1299.2</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>1146.7</v>
+        <v>1161.22</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>1006.65</v>
+        <v>1018.12</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>880.8200000000001</v>
+        <v>885.15</v>
       </c>
       <c r="G31" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
@@ -2036,1148 +2036,1148 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>735.1</v>
+        <v>1675</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>691.36</v>
+        <v>1662.54</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>676.13</v>
+        <v>1611.42</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>713.49</v>
+        <v>1615.68</v>
       </c>
       <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>651</v>
+        <v>1829.5</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>616.74</v>
+        <v>1761.67</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>582.24</v>
+        <v>1718.09</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>585.59</v>
+        <v>1675.63</v>
       </c>
       <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>165.68</v>
+        <v>1483.5</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>160.6</v>
+        <v>1389.4</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>157.86</v>
+        <v>1376.81</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>164.69</v>
+        <v>1473.31</v>
       </c>
       <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PRESTIGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>SOBHA</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1451</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>1395.46</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>1375.33</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>1424.44</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>739.65</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>695.96</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>678.62</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>714.17</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>644.25</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>619.36</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>584.6799999999999</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>585.5599999999999</v>
+      </c>
+      <c r="G37" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>167.26</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>161.23</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>158.23</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>164.93</v>
+      </c>
+      <c r="G38" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>GSPL</t>
         </is>
       </c>
-      <c r="C35" s="14" t="n">
-        <v>296.4</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>276.21</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>274.42</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>292.4</v>
-      </c>
-      <c r="G35" s="15">
+      <c r="C39" s="18" t="n">
+        <v>296.75</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>278.16</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>275.3</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>292.74</v>
+      </c>
+      <c r="G39" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GSPL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>MGL</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>1166.8</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>1108.78</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>1085.74</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>1161.69</v>
-      </c>
-      <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MGL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>283.3</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>275.79</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>276.87</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>281.16</v>
-      </c>
-      <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>RELIANCE</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>1437.9</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>1396.86</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>1395.04</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>1426.57</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>1673.4</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>1661.23</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>1608.83</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>1613.22</v>
-      </c>
-      <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>GUJGASLTD</t>
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>1839.1</v>
+        <v>408.95</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>1754.53</v>
+        <v>375.27</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>1713.54</v>
+        <v>372.74</v>
       </c>
       <c r="F40" s="18" t="n">
-        <v>1671.68</v>
+        <v>401.89</v>
       </c>
       <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GUJGASLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>SOBHA</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C41" s="18" t="n">
-        <v>1451.8</v>
+        <v>1179.8</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>1389.61</v>
+        <v>1115.55</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>1372.24</v>
+        <v>1089.43</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>1422.81</v>
+        <v>1164.54</v>
       </c>
       <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>282.1</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>276.39</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>277.07</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>281.13</v>
+      </c>
+      <c r="G42" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>1436.2</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>1400.6</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>1396.65</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>1425.45</v>
+      </c>
+      <c r="G43" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>10605</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>9835.889999999999</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>9613.440000000001</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>9145.65</v>
+      </c>
+      <c r="G44" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>1992.9</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>1861.62</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>1788.03</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>1530.97</v>
+      </c>
+      <c r="G45" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>37895</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>36191.53</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>35310.87</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>35345.15</v>
+      </c>
+      <c r="G46" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>7327.5</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>7180.16</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>7187.27</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>6877.54</v>
+      </c>
+      <c r="G47" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>364.45</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>345.51</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>334.98</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>352.68</v>
+      </c>
+      <c r="G48" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>5343</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>5167.49</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>5267.94</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>5182.6</v>
+      </c>
+      <c r="G49" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>3370.7</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>3174.21</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>3219.7</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>3346.37</v>
+      </c>
+      <c r="G50" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:M&amp;M","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="n">
+        <v>130.43</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>122.96</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>120.86</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>113.51</v>
+      </c>
+      <c r="G51" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="n">
+        <v>3706.7</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>3587.82</v>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>3607.88</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>3471.76</v>
+      </c>
+      <c r="G52" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>NAZARA</t>
         </is>
       </c>
-      <c r="C42" s="14" t="n">
-        <v>271.8</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>263</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>258.8</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>266.58</v>
-      </c>
-      <c r="G42" s="15">
+      <c r="C53" s="18" t="n">
+        <v>274.35</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>264.08</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>259.41</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <v>267.79</v>
+      </c>
+      <c r="G53" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>PVRINOX</t>
         </is>
       </c>
-      <c r="C43" s="14" t="n">
-        <v>1068.9</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>1015.46</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>1002.75</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>1021</v>
-      </c>
-      <c r="G43" s="15">
+      <c r="C54" s="18" t="n">
+        <v>1066.1</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>1020.28</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>1005.24</v>
+      </c>
+      <c r="F54" s="18" t="n">
+        <v>1021.31</v>
+      </c>
+      <c r="G54" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>TIPSMUSIC</t>
         </is>
       </c>
-      <c r="C44" s="14" t="n">
-        <v>652.7</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>616.16</v>
-      </c>
-      <c r="E44" s="14" t="n">
-        <v>577.5</v>
-      </c>
-      <c r="F44" s="14" t="n">
-        <v>561.7</v>
-      </c>
-      <c r="G44" s="15">
+      <c r="C55" s="18" t="n">
+        <v>643.2</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>618.74</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>580.0700000000001</v>
+      </c>
+      <c r="F55" s="18" t="n">
+        <v>562.97</v>
+      </c>
+      <c r="G55" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>524.85</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>511.66</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>493.66</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>489.31</v>
-      </c>
-      <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>5783</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>5714.09</v>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>5749.47</v>
-      </c>
-      <c r="F46" s="18" t="n">
-        <v>5781.82</v>
-      </c>
-      <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRITANNIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>814.8</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>776.6</v>
-      </c>
-      <c r="E47" s="18" t="n">
-        <v>766.62</v>
-      </c>
-      <c r="F47" s="18" t="n">
-        <v>744.97</v>
-      </c>
-      <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="n">
-        <v>1486.1</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>1385.25</v>
-      </c>
-      <c r="E48" s="18" t="n">
-        <v>1319.71</v>
-      </c>
-      <c r="F48" s="18" t="n">
-        <v>1256.48</v>
-      </c>
-      <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="n">
-        <v>3357.2</v>
-      </c>
-      <c r="D49" s="18" t="n">
-        <v>3200.7</v>
-      </c>
-      <c r="E49" s="18" t="n">
-        <v>3017.69</v>
-      </c>
-      <c r="F49" s="18" t="n">
-        <v>2913.13</v>
-      </c>
-      <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="n">
-        <v>1152.2</v>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>1135.24</v>
-      </c>
-      <c r="E50" s="18" t="n">
-        <v>1122.67</v>
-      </c>
-      <c r="F50" s="18" t="n">
-        <v>1130.8</v>
-      </c>
-      <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="n">
-        <v>508.95</v>
-      </c>
-      <c r="D51" s="18" t="n">
-        <v>484.54</v>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>461.95</v>
-      </c>
-      <c r="F51" s="18" t="n">
-        <v>466.28</v>
-      </c>
-      <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="n">
-        <v>10319</v>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>9724.91</v>
-      </c>
-      <c r="E52" s="14" t="n">
-        <v>9554.99</v>
-      </c>
-      <c r="F52" s="14" t="n">
-        <v>9130.139999999999</v>
-      </c>
-      <c r="G52" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="n">
-        <v>1873.8</v>
-      </c>
-      <c r="D53" s="14" t="n">
-        <v>1847.8</v>
-      </c>
-      <c r="E53" s="14" t="n">
-        <v>1779.67</v>
-      </c>
-      <c r="F53" s="14" t="n">
-        <v>1521.87</v>
-      </c>
-      <c r="G53" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n">
-        <v>36645</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>36012.21</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>35205.37</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>35273.26</v>
-      </c>
-      <c r="G54" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="n">
-        <v>7310.5</v>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>7164.65</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>7181.55</v>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>6875.15</v>
-      </c>
-      <c r="G55" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="C56" s="14" t="n">
-        <v>127.41</v>
+        <v>972.75</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>122.17</v>
+        <v>931.5700000000001</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>120.46</v>
+        <v>925.55</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>112.96</v>
+        <v>946.2</v>
       </c>
       <c r="G56" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="C57" s="14" t="n">
-        <v>3617.9</v>
+        <v>1689.2</v>
       </c>
       <c r="D57" s="14" t="n">
-        <v>3575.31</v>
+        <v>1587.1</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>3603.84</v>
+        <v>1579.05</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>3467.85</v>
+        <v>1608.87</v>
       </c>
       <c r="G57" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n">
-        <v>8661.5</v>
-      </c>
-      <c r="D58" s="18" t="n">
-        <v>7823.09</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>7434.81</v>
-      </c>
-      <c r="F58" s="18" t="n">
-        <v>7101.28</v>
-      </c>
-      <c r="G58" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="n">
+        <v>2834.6</v>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>2710.34</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>2635.83</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>2601.14</v>
+      </c>
+      <c r="G58" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="n">
-        <v>1806.6</v>
-      </c>
-      <c r="D59" s="18" t="n">
-        <v>1802.55</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>1800.49</v>
-      </c>
-      <c r="F59" s="18" t="n">
-        <v>1800.17</v>
-      </c>
-      <c r="G59" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="n">
+        <v>586.35</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>550.39</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>535</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>545.04</v>
+      </c>
+      <c r="G59" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>CENTURYPLY</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="n">
-        <v>798.5</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>772.04</v>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>752.45</v>
-      </c>
-      <c r="F60" s="18" t="n">
-        <v>755.09</v>
-      </c>
-      <c r="G60" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="n">
+        <v>3042.6</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>2846.3</v>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>2675.5</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>2188.07</v>
+      </c>
+      <c r="G60" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n">
-        <v>284.05</v>
-      </c>
-      <c r="D61" s="18" t="n">
-        <v>262.08</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>255</v>
-      </c>
-      <c r="F61" s="18" t="n">
-        <v>272.87</v>
-      </c>
-      <c r="G61" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>3584.3</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>3478.2</v>
+      </c>
+      <c r="E61" s="14" t="n">
+        <v>3463.19</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>3284.78</v>
+      </c>
+      <c r="G61" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C62" s="14" t="n">
-        <v>7182.5</v>
+        <v>457.55</v>
       </c>
       <c r="D62" s="14" t="n">
-        <v>7057.87</v>
+        <v>452.13</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>6587.3</v>
+        <v>431.34</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>5796.93</v>
+        <v>399.1</v>
       </c>
       <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C63" s="14" t="n">
-        <v>1407.3</v>
+        <v>359.75</v>
       </c>
       <c r="D63" s="14" t="n">
-        <v>1294.03</v>
+        <v>358.9</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>1162.08</v>
+        <v>352.6</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1008.22</v>
+        <v>357.17</v>
       </c>
       <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="n">
+        <v>1015.65</v>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>984.33</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>985.83</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>878.64</v>
+      </c>
+      <c r="G64" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>525.5</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>512.98</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>494.91</v>
+      </c>
+      <c r="F65" s="18" t="n">
+        <v>490.05</v>
+      </c>
+      <c r="G65" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>5814</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>5723.6</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>5751.99</v>
+      </c>
+      <c r="F66" s="18" t="n">
+        <v>5778.66</v>
+      </c>
+      <c r="G66" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRITANNIA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n">
+        <v>832.15</v>
+      </c>
+      <c r="D67" s="18" t="n">
+        <v>782.38</v>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>769.62</v>
+      </c>
+      <c r="F67" s="18" t="n">
+        <v>747.46</v>
+      </c>
+      <c r="G67" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>1476</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>1393.9</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>1325.84</v>
+      </c>
+      <c r="F68" s="18" t="n">
+        <v>1257.92</v>
+      </c>
+      <c r="G68" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n">
+        <v>3407</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>3220.34</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>3032.95</v>
+      </c>
+      <c r="F69" s="18" t="n">
+        <v>2910.48</v>
+      </c>
+      <c r="G69" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>1151.7</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>1136.81</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>1123.8</v>
+      </c>
+      <c r="F70" s="18" t="n">
+        <v>1130.25</v>
+      </c>
+      <c r="G70" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>487.02</v>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>463.86</v>
+      </c>
+      <c r="F71" s="18" t="n">
+        <v>466.58</v>
+      </c>
+      <c r="G71" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>1353</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>1183.32</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>1069.44</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>999.61</v>
-      </c>
-      <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>ADANIPOWER</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="n">
-        <v>229.12</v>
-      </c>
-      <c r="D65" s="14" t="n">
-        <v>206.77</v>
-      </c>
-      <c r="E65" s="14" t="n">
-        <v>182.09</v>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>150.87</v>
-      </c>
-      <c r="G65" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="n">
-        <v>385.95</v>
-      </c>
-      <c r="D66" s="14" t="n">
-        <v>334.44</v>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>302.01</v>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>268.53</v>
-      </c>
-      <c r="G66" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="n">
-        <v>185.01</v>
-      </c>
-      <c r="D67" s="14" t="n">
-        <v>179.03</v>
-      </c>
-      <c r="E67" s="14" t="n">
-        <v>168.72</v>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>163.23</v>
-      </c>
-      <c r="G67" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="n">
-        <v>828.9</v>
-      </c>
-      <c r="D68" s="14" t="n">
-        <v>791.35</v>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v>745.95</v>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>695.3</v>
-      </c>
-      <c r="G68" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="n">
-        <v>470.2</v>
-      </c>
-      <c r="D69" s="14" t="n">
-        <v>461.31</v>
-      </c>
-      <c r="E69" s="14" t="n">
-        <v>448.86</v>
-      </c>
-      <c r="F69" s="14" t="n">
-        <v>410.46</v>
-      </c>
-      <c r="G69" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="n">
-        <v>4563.1</v>
-      </c>
-      <c r="D70" s="14" t="n">
-        <v>4317.88</v>
-      </c>
-      <c r="E70" s="14" t="n">
-        <v>3995.59</v>
-      </c>
-      <c r="F70" s="14" t="n">
-        <v>3235.29</v>
-      </c>
-      <c r="G70" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>JPPOWER</t>
-        </is>
-      </c>
-      <c r="C71" s="14" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="D71" s="14" t="n">
-        <v>18.71</v>
-      </c>
-      <c r="E71" s="14" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="F71" s="14" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="G71" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C72" s="14" t="n">
-        <v>567.9</v>
+        <v>7188</v>
       </c>
       <c r="D72" s="14" t="n">
-        <v>546.23</v>
+        <v>7070.27</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>522.04</v>
+        <v>6610.86</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>503.45</v>
+        <v>5815.96</v>
       </c>
       <c r="G72" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C73" s="14" t="n">
-        <v>83.66</v>
+        <v>1387.1</v>
       </c>
       <c r="D73" s="14" t="n">
-        <v>81.68000000000001</v>
+        <v>1302.89</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>79.37</v>
+        <v>1170.9</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>79.13</v>
+        <v>1008.99</v>
       </c>
       <c r="G73" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3217,23 +3217,23 @@
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C74" s="14" t="n">
-        <v>322.3</v>
+        <v>1365</v>
       </c>
       <c r="D74" s="14" t="n">
-        <v>302.82</v>
+        <v>1200.62</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>284.23</v>
+        <v>1081.03</v>
       </c>
       <c r="F74" s="14" t="n">
-        <v>257.75</v>
+        <v>1002.76</v>
       </c>
       <c r="G74" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3245,23 +3245,23 @@
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C75" s="14" t="n">
-        <v>394.85</v>
+        <v>230.19</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>394.8</v>
+        <v>209</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>383.27</v>
+        <v>183.98</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>354.66</v>
+        <v>151.59</v>
       </c>
       <c r="G75" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3273,23 +3273,23 @@
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C76" s="14" t="n">
-        <v>315.95</v>
+        <v>406.45</v>
       </c>
       <c r="D76" s="14" t="n">
-        <v>314.03</v>
+        <v>341.3</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>304.13</v>
+        <v>306.11</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>288.07</v>
+        <v>270.51</v>
       </c>
       <c r="G76" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERGRID","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3301,23 +3301,23 @@
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="C77" s="14" t="n">
-        <v>33380</v>
+        <v>186.61</v>
       </c>
       <c r="D77" s="14" t="n">
-        <v>30780.01</v>
+        <v>179.75</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>27498.15</v>
+        <v>169.42</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>22073.55</v>
+        <v>163.61</v>
       </c>
       <c r="G77" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3329,23 +3329,23 @@
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C78" s="14" t="n">
-        <v>1282.5</v>
+        <v>859.1</v>
       </c>
       <c r="D78" s="14" t="n">
-        <v>1147</v>
+        <v>797.8</v>
       </c>
       <c r="E78" s="14" t="n">
-        <v>1014.05</v>
+        <v>750.39</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>845.6900000000001</v>
+        <v>697.83</v>
       </c>
       <c r="G78" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3357,23 +3357,23 @@
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C79" s="14" t="n">
-        <v>3841.8</v>
+        <v>466.65</v>
       </c>
       <c r="D79" s="14" t="n">
-        <v>3673.61</v>
+        <v>461.82</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>3455.53</v>
+        <v>449.56</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>3227.11</v>
+        <v>411.41</v>
       </c>
       <c r="G79" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3385,23 +3385,23 @@
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C80" s="14" t="n">
-        <v>79.94</v>
+        <v>4768.2</v>
       </c>
       <c r="D80" s="14" t="n">
-        <v>77.31999999999999</v>
+        <v>4360.77</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>74.84999999999999</v>
+        <v>4025.89</v>
       </c>
       <c r="F80" s="14" t="n">
-        <v>79.2</v>
+        <v>3257.19</v>
       </c>
       <c r="G80" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SJVN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3413,23 +3413,23 @@
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="C81" s="14" t="n">
-        <v>54.32</v>
+        <v>19.39</v>
       </c>
       <c r="D81" s="14" t="n">
-        <v>52.3</v>
+        <v>18.77</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>48.95</v>
+        <v>17.42</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>51.3</v>
+        <v>16.89</v>
       </c>
       <c r="G81" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3441,23 +3441,23 @@
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C82" s="14" t="n">
-        <v>443.25</v>
+        <v>575.9</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>431.66</v>
+        <v>549.0599999999999</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>411.01</v>
+        <v>524.15</v>
       </c>
       <c r="F82" s="14" t="n">
-        <v>391.36</v>
+        <v>504.35</v>
       </c>
       <c r="G82" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3469,23 +3469,23 @@
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C83" s="14" t="n">
-        <v>4076.9</v>
+        <v>328.7</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>3938.54</v>
+        <v>305.29</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>3619</v>
+        <v>285.97</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>3295.54</v>
+        <v>258.85</v>
       </c>
       <c r="G83" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C84" s="14" t="n">
-        <v>1734</v>
+        <v>400.35</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>1646.22</v>
+        <v>395.33</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>1544.57</v>
+        <v>383.94</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>1416.51</v>
+        <v>355.13</v>
       </c>
       <c r="G84" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3525,526 +3525,694 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="n">
+        <v>34875</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>31413.74</v>
+      </c>
+      <c r="E85" s="14" t="n">
+        <v>28016.47</v>
+      </c>
+      <c r="F85" s="14" t="n">
+        <v>22335.97</v>
+      </c>
+      <c r="G85" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="D86" s="14" t="n">
+        <v>1165.7</v>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v>1026.97</v>
+      </c>
+      <c r="F86" s="14" t="n">
+        <v>850.9400000000001</v>
+      </c>
+      <c r="G86" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="n">
+        <v>3871.5</v>
+      </c>
+      <c r="D87" s="14" t="n">
+        <v>3692.46</v>
+      </c>
+      <c r="E87" s="14" t="n">
+        <v>3471.85</v>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>3235.69</v>
+      </c>
+      <c r="G87" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="n">
+        <v>79.89</v>
+      </c>
+      <c r="D88" s="14" t="n">
+        <v>77.56</v>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="F88" s="14" t="n">
+        <v>79.34</v>
+      </c>
+      <c r="G88" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SJVN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="D89" s="14" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="E89" s="14" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="G89" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="n">
+        <v>439.25</v>
+      </c>
+      <c r="D90" s="14" t="n">
+        <v>432.38</v>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v>412.12</v>
+      </c>
+      <c r="F90" s="14" t="n">
+        <v>392.04</v>
+      </c>
+      <c r="G90" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="n">
+        <v>4182.3</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>3961.76</v>
+      </c>
+      <c r="E91" s="14" t="n">
+        <v>3641.09</v>
+      </c>
+      <c r="F91" s="14" t="n">
+        <v>3306.32</v>
+      </c>
+      <c r="G91" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="n">
+        <v>1712.5</v>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>1652.53</v>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v>1551.16</v>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>1422.66</v>
+      </c>
+      <c r="G92" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
           <t>TRITURBINE</t>
         </is>
       </c>
-      <c r="C85" s="14" t="n">
-        <v>557.3</v>
-      </c>
-      <c r="D85" s="14" t="n">
-        <v>542.17</v>
-      </c>
-      <c r="E85" s="14" t="n">
-        <v>514.27</v>
-      </c>
-      <c r="F85" s="14" t="n">
-        <v>515.52</v>
-      </c>
-      <c r="G85" s="15">
+      <c r="C93" s="14" t="n">
+        <v>574.1</v>
+      </c>
+      <c r="D93" s="14" t="n">
+        <v>545.21</v>
+      </c>
+      <c r="E93" s="14" t="n">
+        <v>516.62</v>
+      </c>
+      <c r="F93" s="14" t="n">
+        <v>517.12</v>
+      </c>
+      <c r="G93" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>BAJFINANCE</t>
-        </is>
-      </c>
-      <c r="C86" s="18" t="n">
-        <v>980.75</v>
-      </c>
-      <c r="D86" s="18" t="n">
-        <v>927.23</v>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>923.62</v>
-      </c>
-      <c r="F86" s="18" t="n">
-        <v>944.37</v>
-      </c>
-      <c r="G86" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="n">
-        <v>1711.9</v>
-      </c>
-      <c r="D87" s="18" t="n">
-        <v>1574.79</v>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>1574.53</v>
-      </c>
-      <c r="F87" s="18" t="n">
-        <v>1604.82</v>
-      </c>
-      <c r="G87" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>HDFCAMC</t>
-        </is>
-      </c>
-      <c r="C88" s="18" t="n">
-        <v>2815.9</v>
-      </c>
-      <c r="D88" s="18" t="n">
-        <v>2697.26</v>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>2627.72</v>
-      </c>
-      <c r="F88" s="18" t="n">
-        <v>2595.08</v>
-      </c>
-      <c r="G88" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="n">
-        <v>582.15</v>
-      </c>
-      <c r="D89" s="18" t="n">
-        <v>546.61</v>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>532.9</v>
-      </c>
-      <c r="F89" s="18" t="n">
-        <v>543.39</v>
-      </c>
-      <c r="G89" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="n">
-        <v>2973.2</v>
-      </c>
-      <c r="D90" s="18" t="n">
-        <v>2825.64</v>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>2660.51</v>
-      </c>
-      <c r="F90" s="18" t="n">
-        <v>2178.54</v>
-      </c>
-      <c r="G90" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>MUTHOOTFIN</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="n">
-        <v>3533.6</v>
-      </c>
-      <c r="D91" s="18" t="n">
-        <v>3467.03</v>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>3458.24</v>
-      </c>
-      <c r="F91" s="18" t="n">
-        <v>3276.82</v>
-      </c>
-      <c r="G91" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>PFC</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="n">
-        <v>463.9</v>
-      </c>
-      <c r="D92" s="18" t="n">
-        <v>451.56</v>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>430.27</v>
-      </c>
-      <c r="F92" s="18" t="n">
-        <v>397.81</v>
-      </c>
-      <c r="G92" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="C93" s="18" t="n">
-        <v>1004.1</v>
-      </c>
-      <c r="D93" s="18" t="n">
-        <v>981.03</v>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>984.61</v>
-      </c>
-      <c r="F93" s="18" t="n">
-        <v>876.1799999999999</v>
-      </c>
-      <c r="G93" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B94" s="13" t="inlineStr">
-        <is>
-          <t>CENTRALBK</t>
-        </is>
-      </c>
-      <c r="C94" s="14" t="n">
-        <v>36.73</v>
-      </c>
-      <c r="D94" s="14" t="n">
-        <v>35.92</v>
-      </c>
-      <c r="E94" s="14" t="n">
-        <v>35.96</v>
-      </c>
-      <c r="F94" s="14" t="n">
-        <v>36.44</v>
-      </c>
-      <c r="G94" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTRALBK","Chart 📈")</f>
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="n">
+        <v>8842.5</v>
+      </c>
+      <c r="D94" s="18" t="n">
+        <v>7920.18</v>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>7490.02</v>
+      </c>
+      <c r="F94" s="18" t="n">
+        <v>7128.95</v>
+      </c>
+      <c r="G94" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B95" s="13" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C95" s="14" t="n">
-        <v>83.63</v>
-      </c>
-      <c r="D95" s="14" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="E95" s="14" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="F95" s="14" t="n">
-        <v>62.83</v>
-      </c>
-      <c r="G95" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>CENTURYPLY</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="n">
+        <v>799.9</v>
+      </c>
+      <c r="D95" s="18" t="n">
+        <v>774.6900000000001</v>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>754.3099999999999</v>
+      </c>
+      <c r="F95" s="18" t="n">
+        <v>754.98</v>
+      </c>
+      <c r="G95" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="C96" s="14" t="n">
-        <v>1096</v>
-      </c>
-      <c r="D96" s="14" t="n">
-        <v>1078.94</v>
-      </c>
-      <c r="E96" s="14" t="n">
-        <v>1078.36</v>
-      </c>
-      <c r="F96" s="14" t="n">
-        <v>991.23</v>
-      </c>
-      <c r="G96" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="n">
+        <v>5456.5</v>
+      </c>
+      <c r="D96" s="18" t="n">
+        <v>5250.59</v>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>5123.82</v>
+      </c>
+      <c r="F96" s="18" t="n">
+        <v>5401.03</v>
+      </c>
+      <c r="G96" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="n">
+        <v>290.75</v>
+      </c>
+      <c r="D97" s="18" t="n">
+        <v>265.85</v>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>257.09</v>
+      </c>
+      <c r="F97" s="18" t="n">
+        <v>273.46</v>
+      </c>
+      <c r="G97" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="12" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B97" s="17" t="inlineStr">
+      <c r="B98" s="13" t="inlineStr">
         <is>
           <t>HFCL</t>
         </is>
       </c>
-      <c r="C97" s="18" t="n">
-        <v>141.46</v>
-      </c>
-      <c r="D97" s="18" t="n">
-        <v>105.67</v>
-      </c>
-      <c r="E97" s="18" t="n">
-        <v>89.66</v>
-      </c>
-      <c r="F97" s="18" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="G97" s="19">
+      <c r="C98" s="14" t="n">
+        <v>146.24</v>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>109.54</v>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v>91.88</v>
+      </c>
+      <c r="F98" s="14" t="n">
+        <v>78.39</v>
+      </c>
+      <c r="G98" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="20" t="inlineStr">
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B98" s="17" t="inlineStr">
+      <c r="B99" s="13" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="C98" s="18" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="D98" s="18" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E98" s="18" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F98" s="18" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="G98" s="19">
+      <c r="C99" s="14" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="D99" s="14" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E99" s="14" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="F99" s="14" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G99" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="20" t="inlineStr">
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="16" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B99" s="17" t="inlineStr">
+      <c r="B100" s="13" t="inlineStr">
         <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="C99" s="18" t="n">
-        <v>9694.5</v>
-      </c>
-      <c r="D99" s="18" t="n">
-        <v>8764.549999999999</v>
-      </c>
-      <c r="E99" s="18" t="n">
-        <v>7975</v>
-      </c>
-      <c r="F99" s="18" t="n">
-        <v>7887.77</v>
-      </c>
-      <c r="G99" s="19">
+      <c r="C100" s="14" t="n">
+        <v>9498.5</v>
+      </c>
+      <c r="D100" s="14" t="n">
+        <v>8613.6</v>
+      </c>
+      <c r="E100" s="14" t="n">
+        <v>7821.35</v>
+      </c>
+      <c r="F100" s="14" t="n">
+        <v>7697.53</v>
+      </c>
+      <c r="G100" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="20" t="inlineStr">
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="16" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B100" s="17" t="inlineStr">
+      <c r="B101" s="13" t="inlineStr">
         <is>
           <t>TANLA</t>
         </is>
       </c>
-      <c r="C100" s="18" t="n">
-        <v>562.05</v>
-      </c>
-      <c r="D100" s="18" t="n">
-        <v>503.85</v>
-      </c>
-      <c r="E100" s="18" t="n">
-        <v>479.89</v>
-      </c>
-      <c r="F100" s="18" t="n">
-        <v>515.47</v>
-      </c>
-      <c r="G100" s="19">
+      <c r="C101" s="14" t="n">
+        <v>574</v>
+      </c>
+      <c r="D101" s="14" t="n">
+        <v>510.53</v>
+      </c>
+      <c r="E101" s="14" t="n">
+        <v>483.58</v>
+      </c>
+      <c r="F101" s="14" t="n">
+        <v>516.24</v>
+      </c>
+      <c r="G101" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>AUBANK</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="n">
-        <v>1024</v>
-      </c>
-      <c r="D101" s="14" t="n">
-        <v>1001.78</v>
-      </c>
-      <c r="E101" s="14" t="n">
-        <v>976.53</v>
-      </c>
-      <c r="F101" s="14" t="n">
-        <v>901.2</v>
-      </c>
-      <c r="G101" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="16" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="C102" s="14" t="n">
-        <v>293</v>
+        <v>629.25</v>
       </c>
       <c r="D102" s="14" t="n">
-        <v>287.93</v>
+        <v>586.01</v>
       </c>
       <c r="E102" s="14" t="n">
-        <v>282.59</v>
+        <v>582.59</v>
       </c>
       <c r="F102" s="14" t="n">
-        <v>253.64</v>
+        <v>628.76</v>
       </c>
       <c r="G102" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="16" t="inlineStr">
         <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
+        <is>
+          <t>TEJASNET</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="n">
+        <v>533.4</v>
+      </c>
+      <c r="D103" s="14" t="n">
+        <v>433.84</v>
+      </c>
+      <c r="E103" s="14" t="n">
+        <v>422.98</v>
+      </c>
+      <c r="F103" s="14" t="n">
+        <v>482.41</v>
+      </c>
+      <c r="G103" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>CENTRALBK</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="n">
+        <v>37.24</v>
+      </c>
+      <c r="D104" s="18" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="F104" s="18" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="G104" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTRALBK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="n">
+        <v>85.31</v>
+      </c>
+      <c r="D105" s="18" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="F105" s="18" t="n">
+        <v>63.12</v>
+      </c>
+      <c r="G105" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D106" s="18" t="n">
+        <v>1080.18</v>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>1078.89</v>
+      </c>
+      <c r="F106" s="18" t="n">
+        <v>992.39</v>
+      </c>
+      <c r="G106" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B103" s="13" t="inlineStr">
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="n">
+        <v>1032.4</v>
+      </c>
+      <c r="D107" s="14" t="n">
+        <v>1004.69</v>
+      </c>
+      <c r="E107" s="14" t="n">
+        <v>978.72</v>
+      </c>
+      <c r="F107" s="14" t="n">
+        <v>903.8099999999999</v>
+      </c>
+      <c r="G107" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C108" s="14" t="n">
+        <v>297.05</v>
+      </c>
+      <c r="D108" s="14" t="n">
+        <v>288.8</v>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v>283.15</v>
+      </c>
+      <c r="F108" s="14" t="n">
+        <v>254.39</v>
+      </c>
+      <c r="G108" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B109" s="13" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="C103" s="14" t="n">
-        <v>946.75</v>
-      </c>
-      <c r="D103" s="14" t="n">
-        <v>881.58</v>
-      </c>
-      <c r="E103" s="14" t="n">
-        <v>869.1</v>
-      </c>
-      <c r="F103" s="14" t="n">
-        <v>850.61</v>
-      </c>
-      <c r="G103" s="15">
+      <c r="C109" s="14" t="n">
+        <v>946.95</v>
+      </c>
+      <c r="D109" s="14" t="n">
+        <v>887.8099999999999</v>
+      </c>
+      <c r="E109" s="14" t="n">
+        <v>872.15</v>
+      </c>
+      <c r="F109" s="14" t="n">
+        <v>851.73</v>
+      </c>
+      <c r="G109" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 07-May-2026  17:37</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 08-May-2026  16:19</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>14</v>
@@ -715,168 +715,168 @@
         <v>0.733</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.9329999999999999</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8220000000000001</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.8</v>
+        <v>0.7556999999999999</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.778</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>11</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.867</v>
+        <v>0.733</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.733</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.667</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.7556999999999999</v>
+        <v>0.6663</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="F9" s="10" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I10" s="7" t="n">
         <v>0.6</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0.6333</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -889,25 +889,25 @@
         <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.467</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.6003000000000001</v>
+        <v>0.5777</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -920,84 +920,84 @@
         <v>40</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>25</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.575</v>
+        <v>0.525</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.625</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.6</v>
+        <v>0.575</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.6</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C13" s="9" t="n">
-        <v>9</v>
-      </c>
       <c r="D13" s="9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.6</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.5333</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.5333</v>
@@ -1013,25 +1013,25 @@
         <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>6</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.5</v>
+        <v>0.4447</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1075,25 +1075,25 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3078.4</v>
+        <v>3035</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2874.34</v>
+        <v>2889.64</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2855.96</v>
+        <v>2862.98</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2724.55</v>
+        <v>2729.38</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>5590.5</v>
+        <v>5585.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>5446.89</v>
+        <v>5460.09</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>5453.83</v>
+        <v>5458.99</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>5406.51</v>
+        <v>5400.54</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1478.7</v>
+        <v>1487.3</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1397.98</v>
+        <v>1407.37</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1333.33</v>
+        <v>1341.78</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1225.41</v>
+        <v>1226.39</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>382.25</v>
+        <v>380.4</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>364.28</v>
+        <v>365.81</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>367.2</v>
+        <v>367.72</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>369.94</v>
+        <v>369.07</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>6702.5</v>
+        <v>6710.5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6409.18</v>
+        <v>6437.87</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>6287.53</v>
+        <v>6304.11</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>6284.67</v>
+        <v>6273.43</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1307.6</v>
+        <v>1293.9</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1287.36</v>
+        <v>1287.98</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1273.41</v>
+        <v>1274.22</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1253.03</v>
+        <v>1252.4</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1870.6</v>
+        <v>1904.4</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1771.42</v>
+        <v>1784.09</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1752.62</v>
+        <v>1758.57</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1745.06</v>
+        <v>1747.61</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2371.6</v>
+        <v>2366.4</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2317.67</v>
+        <v>2322.31</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2219.42</v>
+        <v>2225.18</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>2008.36</v>
+        <v>2010.6</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>743.5</v>
+        <v>752.95</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>686.65</v>
+        <v>692.97</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>645.9400000000001</v>
+        <v>650.13</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>576.7</v>
+        <v>577.51</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>1560.1</v>
+        <v>1552.6</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>1523.28</v>
+        <v>1527.28</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>1507.04</v>
+        <v>1509.83</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1449.1</v>
+        <v>1449.71</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>2143.2</v>
+        <v>2149.8</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>2053.67</v>
+        <v>2062.83</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>2020.88</v>
+        <v>2025.94</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1862.47</v>
+        <v>1865.91</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1206.5</v>
+        <v>1228.3</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>1121.25</v>
+        <v>1130.44</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>1079.78</v>
+        <v>1084.57</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>968.47</v>
+        <v>968.14</v>
       </c>
       <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>2460.1</v>
+        <v>2379.5</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>2341.69</v>
+        <v>2345.3</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>2302.75</v>
+        <v>2305.75</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>2161.99</v>
+        <v>2159.53</v>
       </c>
       <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LUPIN","Chart 📈")</f>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>2375.2</v>
+        <v>2430.8</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>2228.47</v>
+        <v>2247.74</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2170.76</v>
+        <v>2180.95</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2248.47</v>
+        <v>2250.87</v>
       </c>
       <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
@@ -1625,16 +1625,16 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1155.2</v>
+        <v>1174.7</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1093.58</v>
+        <v>1101.31</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1034.92</v>
+        <v>1040.4</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>930.29</v>
+        <v>931.84</v>
       </c>
       <c r="G17" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>1834.4</v>
+        <v>1847.9</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>1756.84</v>
+        <v>1770.65</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>1739.4</v>
+        <v>1746.39</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1716.9</v>
+        <v>1717.97</v>
       </c>
       <c r="G18" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
@@ -1681,16 +1681,16 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>4362.7</v>
+        <v>4380.8</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>4220.57</v>
+        <v>4235.83</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>4181.99</v>
+        <v>4189.78</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>3888.44</v>
+        <v>3884.77</v>
       </c>
       <c r="G19" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
@@ -1709,16 +1709,16 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>940.3</v>
+        <v>940.05</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>916.9</v>
+        <v>919.1</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>911.23</v>
+        <v>912.36</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>921.61</v>
+        <v>920.78</v>
       </c>
       <c r="G20" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>2513.7</v>
+        <v>2505.9</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>2320.84</v>
+        <v>2338.47</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>2199.63</v>
+        <v>2211.64</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>2249.07</v>
+        <v>2246.07</v>
       </c>
       <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1765,16 +1765,16 @@
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1055.7</v>
+        <v>1044.4</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1026.22</v>
+        <v>1027.95</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>983.15</v>
+        <v>985.55</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>867.34</v>
+        <v>867.79</v>
       </c>
       <c r="G22" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>568.6</v>
+        <v>569.2</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>542.29</v>
+        <v>544.85</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>533.8099999999999</v>
+        <v>535.1900000000001</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>439.82</v>
+        <v>440.5</v>
       </c>
       <c r="G23" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>636.55</v>
+        <v>635.1</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>592.28</v>
+        <v>596.36</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>576.6799999999999</v>
+        <v>578.97</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>532.45</v>
+        <v>532.42</v>
       </c>
       <c r="G24" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>1258.2</v>
+        <v>1248.4</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>1239.96</v>
+        <v>1240.76</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>1205.54</v>
+        <v>1207.22</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>1097.09</v>
+        <v>1096.35</v>
       </c>
       <c r="G25" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
@@ -1877,16 +1877,16 @@
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>1283.4</v>
+        <v>1277.8</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1249.84</v>
+        <v>1252.51</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>1222.95</v>
+        <v>1225.1</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>1155.44</v>
+        <v>1155.6</v>
       </c>
       <c r="G26" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>90.14</v>
+        <v>88.8</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>87.95</v>
+        <v>88.03</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>84.52</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>77.3</v>
+        <v>77.27</v>
       </c>
       <c r="G27" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
@@ -1933,16 +1933,16 @@
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>2827.1</v>
+        <v>2869.4</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>2568.66</v>
+        <v>2597.3</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>2436.33</v>
+        <v>2453.31</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>2409.37</v>
+        <v>2413.8</v>
       </c>
       <c r="G28" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>187.28</v>
+        <v>184.88</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>178.28</v>
+        <v>178.91</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>167.8</v>
+        <v>168.47</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>147.35</v>
+        <v>147.36</v>
       </c>
       <c r="G29" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>217.09</v>
+        <v>214.49</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>210.46</v>
+        <v>210.85</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>204.25</v>
+        <v>204.66</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>184.57</v>
+        <v>184.68</v>
       </c>
       <c r="G30" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
@@ -2017,16 +2017,16 @@
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>1299.2</v>
+        <v>1291.9</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>1161.22</v>
+        <v>1173.67</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>1018.12</v>
+        <v>1028.86</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>885.15</v>
+        <v>888.25</v>
       </c>
       <c r="G31" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
@@ -2036,952 +2036,952 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>1675</v>
+        <v>10711.5</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>1662.54</v>
+        <v>9919.280000000001</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>1611.42</v>
+        <v>9656.5</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>1615.68</v>
+        <v>9151.27</v>
       </c>
       <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1829.5</v>
+        <v>1989.7</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>1761.67</v>
+        <v>1873.82</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>1718.09</v>
+        <v>1795.94</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>1675.63</v>
+        <v>1533.27</v>
       </c>
       <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>1483.5</v>
+        <v>38145</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>1389.4</v>
+        <v>36377.57</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>1376.81</v>
+        <v>35421.99</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>1473.31</v>
+        <v>35334.97</v>
       </c>
       <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PRESTIGE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>7302.5</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>7191.81</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>7191.79</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>6872.33</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>362.25</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>347.11</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>336.05</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>351.54</v>
+      </c>
+      <c r="G36" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>5322</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>5182.2</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>5270.06</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>5178.63</v>
+      </c>
+      <c r="G37" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>132.03</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>123.82</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>121.29</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>3695.2</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>3598.05</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>3611.3</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>3466.08</v>
+      </c>
+      <c r="G39" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>SOBHA</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>1451</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>1395.46</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>1375.33</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>1424.44</v>
-      </c>
-      <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>739.65</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>695.96</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>678.62</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>714.17</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>644.25</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>619.36</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>584.6799999999999</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>585.5599999999999</v>
-      </c>
-      <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>GAIL</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="n">
-        <v>167.26</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>161.23</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>158.23</v>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>164.93</v>
-      </c>
-      <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>GSPL</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>296.75</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>278.16</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>275.3</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>292.74</v>
-      </c>
-      <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GSPL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>GUJGASLTD</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>408.95</v>
+        <v>1703</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>375.27</v>
+        <v>1666.39</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>372.74</v>
+        <v>1615.01</v>
       </c>
       <c r="F40" s="18" t="n">
-        <v>401.89</v>
+        <v>1614.33</v>
       </c>
       <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GUJGASLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="C41" s="18" t="n">
-        <v>1179.8</v>
+        <v>1829.3</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>1115.55</v>
+        <v>1768.11</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>1089.43</v>
+        <v>1722.45</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>1164.54</v>
+        <v>1674.7</v>
       </c>
       <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MGL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>282.1</v>
+        <v>1507.3</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>276.39</v>
+        <v>1404.01</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>277.07</v>
+        <v>1383.58</v>
       </c>
       <c r="F42" s="18" t="n">
-        <v>281.13</v>
+        <v>1471.32</v>
       </c>
       <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PRESTIGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SOBHA</t>
         </is>
       </c>
       <c r="C43" s="18" t="n">
-        <v>1436.2</v>
+        <v>1425.4</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>1400.6</v>
+        <v>1398.31</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>1396.65</v>
+        <v>1377.29</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>1425.45</v>
+        <v>1421.9</v>
       </c>
       <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOBHA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C44" s="14" t="n">
-        <v>10605</v>
+        <v>720.9</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>9835.889999999999</v>
+        <v>698.34</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>9613.440000000001</v>
+        <v>680.28</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>9145.65</v>
+        <v>714.9299999999999</v>
       </c>
       <c r="G44" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="C45" s="14" t="n">
-        <v>1992.9</v>
+        <v>633.05</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>1861.62</v>
+        <v>620.66</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>1788.03</v>
+        <v>586.5700000000001</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>1530.97</v>
+        <v>584.75</v>
       </c>
       <c r="G45" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C46" s="14" t="n">
-        <v>37895</v>
+        <v>166.49</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>36191.53</v>
+        <v>161.73</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>35310.87</v>
+        <v>158.55</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>35345.15</v>
+        <v>164.56</v>
       </c>
       <c r="G46" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C47" s="14" t="n">
-        <v>7327.5</v>
+        <v>1172.9</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>7180.16</v>
+        <v>1121.01</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>7187.27</v>
+        <v>1092.7</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>6877.54</v>
+        <v>1161.3</v>
       </c>
       <c r="G47" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>364.45</v>
+        <v>283.8</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>345.51</v>
+        <v>277.1</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>334.98</v>
+        <v>277.34</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>352.68</v>
+        <v>281.07</v>
       </c>
       <c r="G48" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="C49" s="14" t="n">
-        <v>5343</v>
+        <v>1435.2</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>5167.49</v>
+        <v>1403.9</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>5267.94</v>
+        <v>1398.17</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>5182.6</v>
+        <v>1425.63</v>
       </c>
       <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RELIANCE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>M&amp;M</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n">
-        <v>3370.7</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>3174.21</v>
-      </c>
-      <c r="E50" s="14" t="n">
-        <v>3219.7</v>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>3346.37</v>
-      </c>
-      <c r="G50" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:M&amp;M","Chart 📈")</f>
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>955.35</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>933.83</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>926.72</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>945.03</v>
+      </c>
+      <c r="G50" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n">
-        <v>130.43</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>122.96</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>120.86</v>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>113.51</v>
-      </c>
-      <c r="G51" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>1674.1</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>1595.39</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>1582.78</v>
+      </c>
+      <c r="F51" s="18" t="n">
+        <v>1606</v>
+      </c>
+      <c r="G51" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="n">
-        <v>3706.7</v>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>3587.82</v>
-      </c>
-      <c r="E52" s="14" t="n">
-        <v>3607.88</v>
-      </c>
-      <c r="F52" s="14" t="n">
-        <v>3471.76</v>
-      </c>
-      <c r="G52" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>2854</v>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>2724.02</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>2644.39</v>
+      </c>
+      <c r="F52" s="18" t="n">
+        <v>2597.96</v>
+      </c>
+      <c r="G52" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
-        <v>274.35</v>
+        <v>581.5</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>264.08</v>
+        <v>553.35</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>259.41</v>
+        <v>536.8200000000001</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>267.79</v>
+        <v>543.54</v>
       </c>
       <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>1066.1</v>
+        <v>3097.8</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>1020.28</v>
+        <v>2870.25</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>1005.24</v>
+        <v>2692.06</v>
       </c>
       <c r="F54" s="18" t="n">
-        <v>1021.31</v>
+        <v>2196.26</v>
       </c>
       <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="20" t="inlineStr">
         <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>3528.9</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>3483.03</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>3465.76</v>
+      </c>
+      <c r="F55" s="18" t="n">
+        <v>3280.16</v>
+      </c>
+      <c r="G55" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>461.35</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>453.01</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>432.51</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <v>398.62</v>
+      </c>
+      <c r="G56" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>359.4</v>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>358.95</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>352.87</v>
+      </c>
+      <c r="F57" s="18" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="G57" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>1007.75</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>986.5599999999999</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>986.6900000000001</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>878.23</v>
+      </c>
+      <c r="G58" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="n">
-        <v>643.2</v>
-      </c>
-      <c r="D55" s="18" t="n">
-        <v>618.74</v>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>580.0700000000001</v>
-      </c>
-      <c r="F55" s="18" t="n">
-        <v>562.97</v>
-      </c>
-      <c r="G55" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>BAJFINANCE</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="n">
-        <v>972.75</v>
-      </c>
-      <c r="D56" s="14" t="n">
-        <v>931.5700000000001</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>925.55</v>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>946.2</v>
-      </c>
-      <c r="G56" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJFINANCE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="n">
-        <v>1689.2</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>1587.1</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>1579.05</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>1608.87</v>
-      </c>
-      <c r="G57" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>HDFCAMC</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>2834.6</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>2710.34</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>2635.83</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>2601.14</v>
-      </c>
-      <c r="G58" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C59" s="14" t="n">
-        <v>586.35</v>
+        <v>268.6</v>
       </c>
       <c r="D59" s="14" t="n">
-        <v>550.39</v>
+        <v>264.51</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>535</v>
+        <v>259.77</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>545.04</v>
+        <v>268</v>
       </c>
       <c r="G59" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C60" s="14" t="n">
-        <v>3042.6</v>
+        <v>1073.8</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>2846.3</v>
+        <v>1025.38</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>2675.5</v>
+        <v>1007.93</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>2188.07</v>
+        <v>1021.55</v>
       </c>
       <c r="G60" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C61" s="14" t="n">
-        <v>3584.3</v>
+        <v>648.35</v>
       </c>
       <c r="D61" s="14" t="n">
-        <v>3478.2</v>
+        <v>621.5599999999999</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>3463.19</v>
+        <v>582.75</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>3284.78</v>
+        <v>562.55</v>
       </c>
       <c r="G61" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>PFC</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
-        <v>457.55</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>452.13</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>431.34</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>399.1</v>
-      </c>
-      <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>522.75</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>513.91</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>496</v>
+      </c>
+      <c r="F62" s="18" t="n">
+        <v>488.86</v>
+      </c>
+      <c r="G62" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n">
-        <v>359.75</v>
-      </c>
-      <c r="D63" s="14" t="n">
-        <v>358.9</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>352.6</v>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>357.17</v>
-      </c>
-      <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RECLTD","Chart 📈")</f>
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>2197.4</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>2105.28</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>2072.38</v>
+      </c>
+      <c r="F63" s="18" t="n">
+        <v>2164.8</v>
+      </c>
+      <c r="G63" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COLPAL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>1015.65</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>984.33</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>985.83</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>878.64</v>
-      </c>
-      <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SHRIRAMFIN","Chart 📈")</f>
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>487.7</v>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>453.78</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>458.4</v>
+      </c>
+      <c r="F64" s="18" t="n">
+        <v>482.31</v>
+      </c>
+      <c r="G64" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DABUR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C65" s="18" t="n">
-        <v>525.5</v>
+        <v>831.3</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>512.98</v>
+        <v>787.04</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>494.91</v>
+        <v>772.04</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>490.05</v>
+        <v>746.9299999999999</v>
       </c>
       <c r="G65" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2993,23 +2993,23 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C66" s="18" t="n">
-        <v>5814</v>
+        <v>1482.4</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>5723.6</v>
+        <v>1402.33</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>5751.99</v>
+        <v>1331.98</v>
       </c>
       <c r="F66" s="18" t="n">
-        <v>5778.66</v>
+        <v>1260.25</v>
       </c>
       <c r="G66" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRITANNIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3021,23 +3021,23 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C67" s="18" t="n">
-        <v>832.15</v>
+        <v>3477.2</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>782.38</v>
+        <v>3244.81</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>769.62</v>
+        <v>3050.37</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>747.46</v>
+        <v>2918.5</v>
       </c>
       <c r="G67" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3049,23 +3049,23 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C68" s="18" t="n">
-        <v>1476</v>
+        <v>1176.2</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>1393.9</v>
+        <v>1140.56</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>1325.84</v>
+        <v>1125.86</v>
       </c>
       <c r="F68" s="18" t="n">
-        <v>1257.92</v>
+        <v>1128.27</v>
       </c>
       <c r="G68" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3077,107 +3077,107 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="C69" s="18" t="n">
-        <v>3407</v>
+        <v>508.85</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>3220.34</v>
+        <v>489.1</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>3032.95</v>
+        <v>465.62</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>2910.48</v>
+        <v>465.09</v>
       </c>
       <c r="G69" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="n">
-        <v>1151.7</v>
-      </c>
-      <c r="D70" s="18" t="n">
-        <v>1136.81</v>
-      </c>
-      <c r="E70" s="18" t="n">
-        <v>1123.8</v>
-      </c>
-      <c r="F70" s="18" t="n">
-        <v>1130.25</v>
-      </c>
-      <c r="G70" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="n">
+        <v>1353.6</v>
+      </c>
+      <c r="D70" s="14" t="n">
+        <v>1307.72</v>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>1178.07</v>
+      </c>
+      <c r="F70" s="14" t="n">
+        <v>1009.69</v>
+      </c>
+      <c r="G70" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>487.02</v>
-      </c>
-      <c r="E71" s="18" t="n">
-        <v>463.86</v>
-      </c>
-      <c r="F71" s="18" t="n">
-        <v>466.58</v>
-      </c>
-      <c r="G71" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="n">
+        <v>1355.8</v>
+      </c>
+      <c r="D71" s="14" t="n">
+        <v>1215.4</v>
+      </c>
+      <c r="E71" s="14" t="n">
+        <v>1091.81</v>
+      </c>
+      <c r="F71" s="14" t="n">
+        <v>1003.25</v>
+      </c>
+      <c r="G71" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="12" t="inlineStr">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C72" s="14" t="n">
-        <v>7188</v>
+        <v>225.33</v>
       </c>
       <c r="D72" s="14" t="n">
-        <v>7070.27</v>
+        <v>210.56</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>6610.86</v>
+        <v>185.6</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>5815.96</v>
+        <v>152.13</v>
       </c>
       <c r="G72" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3189,23 +3189,23 @@
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C73" s="14" t="n">
-        <v>1387.1</v>
+        <v>404.6</v>
       </c>
       <c r="D73" s="14" t="n">
-        <v>1302.89</v>
+        <v>347.33</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>1170.9</v>
+        <v>309.97</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>1008.99</v>
+        <v>271.19</v>
       </c>
       <c r="G73" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3217,23 +3217,23 @@
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="C74" s="14" t="n">
-        <v>1365</v>
+        <v>184.41</v>
       </c>
       <c r="D74" s="14" t="n">
-        <v>1200.62</v>
+        <v>180.19</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>1081.03</v>
+        <v>170.01</v>
       </c>
       <c r="F74" s="14" t="n">
-        <v>1002.76</v>
+        <v>163.51</v>
       </c>
       <c r="G74" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3245,23 +3245,23 @@
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C75" s="14" t="n">
-        <v>230.19</v>
+        <v>873.55</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>209</v>
+        <v>805.02</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>183.98</v>
+        <v>755.22</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>151.59</v>
+        <v>699.64</v>
       </c>
       <c r="G75" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3273,23 +3273,23 @@
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C76" s="14" t="n">
-        <v>406.45</v>
+        <v>4625.5</v>
       </c>
       <c r="D76" s="14" t="n">
-        <v>341.3</v>
+        <v>4385.98</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>306.11</v>
+        <v>4049.41</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>270.51</v>
+        <v>3271.8</v>
       </c>
       <c r="G76" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3301,23 +3301,23 @@
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="C77" s="14" t="n">
-        <v>186.61</v>
+        <v>19.08</v>
       </c>
       <c r="D77" s="14" t="n">
-        <v>179.75</v>
+        <v>18.8</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>169.42</v>
+        <v>17.49</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>163.61</v>
+        <v>16.87</v>
       </c>
       <c r="G77" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3329,23 +3329,23 @@
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C78" s="14" t="n">
-        <v>859.1</v>
+        <v>571.2</v>
       </c>
       <c r="D78" s="14" t="n">
-        <v>797.8</v>
+        <v>551.16</v>
       </c>
       <c r="E78" s="14" t="n">
-        <v>750.39</v>
+        <v>526</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>697.83</v>
+        <v>504.6</v>
       </c>
       <c r="G78" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3357,23 +3357,23 @@
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C79" s="14" t="n">
-        <v>466.65</v>
+        <v>328.2</v>
       </c>
       <c r="D79" s="14" t="n">
-        <v>461.82</v>
+        <v>307.47</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>449.56</v>
+        <v>287.63</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>411.41</v>
+        <v>259.37</v>
       </c>
       <c r="G79" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3385,23 +3385,23 @@
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C80" s="14" t="n">
-        <v>4768.2</v>
+        <v>402.15</v>
       </c>
       <c r="D80" s="14" t="n">
-        <v>4360.77</v>
+        <v>395.98</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>4025.89</v>
+        <v>384.66</v>
       </c>
       <c r="F80" s="14" t="n">
-        <v>3257.19</v>
+        <v>355.44</v>
       </c>
       <c r="G80" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3413,23 +3413,23 @@
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C81" s="14" t="n">
-        <v>19.39</v>
+        <v>34005</v>
       </c>
       <c r="D81" s="14" t="n">
-        <v>18.77</v>
+        <v>31660.53</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>17.42</v>
+        <v>28251.31</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>16.89</v>
+        <v>22451.01</v>
       </c>
       <c r="G81" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3441,23 +3441,23 @@
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C82" s="14" t="n">
-        <v>575.9</v>
+        <v>1344.6</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>549.0599999999999</v>
+        <v>1182.74</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>524.15</v>
+        <v>1039.42</v>
       </c>
       <c r="F82" s="14" t="n">
-        <v>504.35</v>
+        <v>854.96</v>
       </c>
       <c r="G82" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3469,23 +3469,23 @@
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C83" s="14" t="n">
-        <v>328.7</v>
+        <v>3822.6</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>305.29</v>
+        <v>3704.85</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>285.97</v>
+        <v>3485.59</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>258.85</v>
+        <v>3230.86</v>
       </c>
       <c r="G83" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C84" s="14" t="n">
-        <v>400.35</v>
+        <v>54.97</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>395.33</v>
+        <v>52.84</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>383.94</v>
+        <v>49.44</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>355.13</v>
+        <v>51.33</v>
       </c>
       <c r="G84" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3525,23 +3525,23 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C85" s="14" t="n">
-        <v>34875</v>
+        <v>436</v>
       </c>
       <c r="D85" s="14" t="n">
-        <v>31413.74</v>
+        <v>432.72</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>28016.47</v>
+        <v>413.06</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>22335.97</v>
+        <v>391.89</v>
       </c>
       <c r="G85" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3553,23 +3553,23 @@
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C86" s="14" t="n">
-        <v>1343.4</v>
+        <v>4677.5</v>
       </c>
       <c r="D86" s="14" t="n">
-        <v>1165.7</v>
+        <v>4029.92</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>1026.97</v>
+        <v>3681.73</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>850.9400000000001</v>
+        <v>3312.78</v>
       </c>
       <c r="G86" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3581,23 +3581,23 @@
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C87" s="14" t="n">
-        <v>3871.5</v>
+        <v>1724.4</v>
       </c>
       <c r="D87" s="14" t="n">
-        <v>3692.46</v>
+        <v>1659.38</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>3471.85</v>
+        <v>1557.95</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>3235.69</v>
+        <v>1419.03</v>
       </c>
       <c r="G87" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3609,610 +3609,470 @@
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C88" s="14" t="n">
-        <v>79.89</v>
+        <v>597.9</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>77.56</v>
+        <v>550.23</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>75.05</v>
+        <v>519.8</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>79.34</v>
+        <v>518.67</v>
       </c>
       <c r="G88" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SJVN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="n">
-        <v>55.65</v>
-      </c>
-      <c r="D89" s="14" t="n">
-        <v>52.62</v>
-      </c>
-      <c r="E89" s="14" t="n">
-        <v>49.21</v>
-      </c>
-      <c r="F89" s="14" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="G89" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>141.15</v>
+      </c>
+      <c r="D89" s="18" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>93.81</v>
+      </c>
+      <c r="F89" s="18" t="n">
+        <v>78.83</v>
+      </c>
+      <c r="G89" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="n">
-        <v>439.25</v>
-      </c>
-      <c r="D90" s="14" t="n">
-        <v>432.38</v>
-      </c>
-      <c r="E90" s="14" t="n">
-        <v>412.12</v>
-      </c>
-      <c r="F90" s="14" t="n">
-        <v>392.04</v>
-      </c>
-      <c r="G90" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="D90" s="18" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F90" s="18" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G90" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B91" s="13" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="n">
-        <v>4182.3</v>
-      </c>
-      <c r="D91" s="14" t="n">
-        <v>3961.76</v>
-      </c>
-      <c r="E91" s="14" t="n">
-        <v>3641.09</v>
-      </c>
-      <c r="F91" s="14" t="n">
-        <v>3306.32</v>
-      </c>
-      <c r="G91" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+      <c r="A91" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="n">
+        <v>9345.5</v>
+      </c>
+      <c r="D91" s="18" t="n">
+        <v>8683.299999999999</v>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>7881.12</v>
+      </c>
+      <c r="F91" s="18" t="n">
+        <v>7705.25</v>
+      </c>
+      <c r="G91" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="n">
-        <v>1712.5</v>
-      </c>
-      <c r="D92" s="14" t="n">
-        <v>1652.53</v>
-      </c>
-      <c r="E92" s="14" t="n">
-        <v>1551.16</v>
-      </c>
-      <c r="F92" s="14" t="n">
-        <v>1422.66</v>
-      </c>
-      <c r="G92" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>TANLA</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>564.8</v>
+      </c>
+      <c r="D92" s="18" t="n">
+        <v>515.7</v>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>486.77</v>
+      </c>
+      <c r="F92" s="18" t="n">
+        <v>516.78</v>
+      </c>
+      <c r="G92" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B93" s="13" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="n">
-        <v>574.1</v>
-      </c>
-      <c r="D93" s="14" t="n">
-        <v>545.21</v>
-      </c>
-      <c r="E93" s="14" t="n">
-        <v>516.62</v>
-      </c>
-      <c r="F93" s="14" t="n">
-        <v>517.12</v>
-      </c>
-      <c r="G93" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>630.95</v>
+      </c>
+      <c r="D93" s="18" t="n">
+        <v>590.29</v>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>584.48</v>
+      </c>
+      <c r="F93" s="18" t="n">
+        <v>628.53</v>
+      </c>
+      <c r="G93" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>TEJASNET</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="n">
+        <v>514.4</v>
+      </c>
+      <c r="D94" s="18" t="n">
+        <v>441.51</v>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>426.56</v>
+      </c>
+      <c r="F94" s="18" t="n">
+        <v>482.29</v>
+      </c>
+      <c r="G94" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="12" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B94" s="17" t="inlineStr">
+      <c r="B95" s="13" t="inlineStr">
         <is>
           <t>AMBER</t>
         </is>
       </c>
-      <c r="C94" s="18" t="n">
-        <v>8842.5</v>
-      </c>
-      <c r="D94" s="18" t="n">
-        <v>7920.18</v>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>7490.02</v>
-      </c>
-      <c r="F94" s="18" t="n">
-        <v>7128.95</v>
-      </c>
-      <c r="G94" s="19">
+      <c r="C95" s="14" t="n">
+        <v>8824.5</v>
+      </c>
+      <c r="D95" s="14" t="n">
+        <v>8006.3</v>
+      </c>
+      <c r="E95" s="14" t="n">
+        <v>7542.35</v>
+      </c>
+      <c r="F95" s="14" t="n">
+        <v>7149.92</v>
+      </c>
+      <c r="G95" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="20" t="inlineStr">
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="16" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B95" s="17" t="inlineStr">
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>CENTURYPLY</t>
         </is>
       </c>
-      <c r="C95" s="18" t="n">
-        <v>799.9</v>
-      </c>
-      <c r="D95" s="18" t="n">
-        <v>774.6900000000001</v>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>754.3099999999999</v>
-      </c>
-      <c r="F95" s="18" t="n">
-        <v>754.98</v>
-      </c>
-      <c r="G95" s="19">
+      <c r="C96" s="14" t="n">
+        <v>795.15</v>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>778.72</v>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v>757.5700000000001</v>
+      </c>
+      <c r="F96" s="14" t="n">
+        <v>755.04</v>
+      </c>
+      <c r="G96" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="20" t="inlineStr">
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="16" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B96" s="17" t="inlineStr">
+      <c r="B97" s="13" t="inlineStr">
         <is>
           <t>CERA</t>
         </is>
       </c>
-      <c r="C96" s="18" t="n">
-        <v>5456.5</v>
-      </c>
-      <c r="D96" s="18" t="n">
-        <v>5250.59</v>
-      </c>
-      <c r="E96" s="18" t="n">
-        <v>5123.82</v>
-      </c>
-      <c r="F96" s="18" t="n">
-        <v>5401.03</v>
-      </c>
-      <c r="G96" s="19">
+      <c r="C97" s="14" t="n">
+        <v>5782</v>
+      </c>
+      <c r="D97" s="14" t="n">
+        <v>5301.2</v>
+      </c>
+      <c r="E97" s="14" t="n">
+        <v>5149.63</v>
+      </c>
+      <c r="F97" s="14" t="n">
+        <v>5414.64</v>
+      </c>
+      <c r="G97" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="20" t="inlineStr">
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="16" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B97" s="17" t="inlineStr">
+      <c r="B98" s="13" t="inlineStr">
         <is>
           <t>CROMPTON</t>
         </is>
       </c>
-      <c r="C97" s="18" t="n">
-        <v>290.75</v>
-      </c>
-      <c r="D97" s="18" t="n">
-        <v>265.85</v>
-      </c>
-      <c r="E97" s="18" t="n">
-        <v>257.09</v>
-      </c>
-      <c r="F97" s="18" t="n">
-        <v>273.46</v>
-      </c>
-      <c r="G97" s="19">
+      <c r="C98" s="14" t="n">
+        <v>293.3</v>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>268.46</v>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v>258.51</v>
+      </c>
+      <c r="F98" s="14" t="n">
+        <v>273.05</v>
+      </c>
+      <c r="G98" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="n">
-        <v>146.24</v>
-      </c>
-      <c r="D98" s="14" t="n">
-        <v>109.54</v>
-      </c>
-      <c r="E98" s="14" t="n">
-        <v>91.88</v>
-      </c>
-      <c r="F98" s="14" t="n">
-        <v>78.39</v>
-      </c>
-      <c r="G98" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="C99" s="14" t="n">
-        <v>11.23</v>
+        <v>4509</v>
       </c>
       <c r="D99" s="14" t="n">
-        <v>10.1</v>
+        <v>4383.18</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>9.949999999999999</v>
+        <v>4296.65</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>9.470000000000001</v>
+        <v>3980.11</v>
       </c>
       <c r="G99" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TITAN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B100" s="13" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C100" s="14" t="n">
-        <v>9498.5</v>
-      </c>
-      <c r="D100" s="14" t="n">
-        <v>8613.6</v>
-      </c>
-      <c r="E100" s="14" t="n">
-        <v>7821.35</v>
-      </c>
-      <c r="F100" s="14" t="n">
-        <v>7697.53</v>
-      </c>
-      <c r="G100" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>CENTRALBK</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="D100" s="18" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="F100" s="18" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="G100" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTRALBK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>TANLA</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="n">
-        <v>574</v>
-      </c>
-      <c r="D101" s="14" t="n">
-        <v>510.53</v>
-      </c>
-      <c r="E101" s="14" t="n">
-        <v>483.58</v>
-      </c>
-      <c r="F101" s="14" t="n">
-        <v>516.24</v>
-      </c>
-      <c r="G101" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
+      <c r="A101" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="D101" s="18" t="n">
+        <v>77.95999999999999</v>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>72.78</v>
+      </c>
+      <c r="F101" s="18" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="G101" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>TATATECH</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C102" s="14" t="n">
-        <v>629.25</v>
+        <v>1050.4</v>
       </c>
       <c r="D102" s="14" t="n">
-        <v>586.01</v>
+        <v>1009.05</v>
       </c>
       <c r="E102" s="14" t="n">
-        <v>582.59</v>
+        <v>981.53</v>
       </c>
       <c r="F102" s="14" t="n">
-        <v>628.76</v>
+        <v>905.38</v>
       </c>
       <c r="G102" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>TEJASNET</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C103" s="14" t="n">
-        <v>533.4</v>
+        <v>297.25</v>
       </c>
       <c r="D103" s="14" t="n">
-        <v>433.84</v>
+        <v>289.61</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>422.98</v>
+        <v>283.71</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>482.41</v>
+        <v>254.45</v>
       </c>
       <c r="G103" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B104" s="17" t="inlineStr">
-        <is>
-          <t>CENTRALBK</t>
-        </is>
-      </c>
-      <c r="C104" s="18" t="n">
-        <v>37.24</v>
-      </c>
-      <c r="D104" s="18" t="n">
-        <v>36.04</v>
-      </c>
-      <c r="E104" s="18" t="n">
-        <v>36.01</v>
-      </c>
-      <c r="F104" s="18" t="n">
-        <v>36.44</v>
-      </c>
-      <c r="G104" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTRALBK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B105" s="17" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="n">
-        <v>85.31</v>
-      </c>
-      <c r="D105" s="18" t="n">
-        <v>77.34</v>
-      </c>
-      <c r="E105" s="18" t="n">
-        <v>72.33</v>
-      </c>
-      <c r="F105" s="18" t="n">
-        <v>63.12</v>
-      </c>
-      <c r="G105" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B106" s="17" t="inlineStr">
-        <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="n">
-        <v>1092</v>
-      </c>
-      <c r="D106" s="18" t="n">
-        <v>1080.18</v>
-      </c>
-      <c r="E106" s="18" t="n">
-        <v>1078.89</v>
-      </c>
-      <c r="F106" s="18" t="n">
-        <v>992.39</v>
-      </c>
-      <c r="G106" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="12" t="inlineStr">
+      <c r="A104" s="16" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B107" s="13" t="inlineStr">
-        <is>
-          <t>AUBANK</t>
-        </is>
-      </c>
-      <c r="C107" s="14" t="n">
-        <v>1032.4</v>
-      </c>
-      <c r="D107" s="14" t="n">
-        <v>1004.69</v>
-      </c>
-      <c r="E107" s="14" t="n">
-        <v>978.72</v>
-      </c>
-      <c r="F107" s="14" t="n">
-        <v>903.8099999999999</v>
-      </c>
-      <c r="G107" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B108" s="13" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="C108" s="14" t="n">
-        <v>297.05</v>
-      </c>
-      <c r="D108" s="14" t="n">
-        <v>288.8</v>
-      </c>
-      <c r="E108" s="14" t="n">
-        <v>283.15</v>
-      </c>
-      <c r="F108" s="14" t="n">
-        <v>254.39</v>
-      </c>
-      <c r="G108" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B109" s="13" t="inlineStr">
+      <c r="B104" s="13" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="C109" s="14" t="n">
-        <v>946.95</v>
-      </c>
-      <c r="D109" s="14" t="n">
-        <v>887.8099999999999</v>
-      </c>
-      <c r="E109" s="14" t="n">
-        <v>872.15</v>
-      </c>
-      <c r="F109" s="14" t="n">
-        <v>851.73</v>
-      </c>
-      <c r="G109" s="15">
+      <c r="C104" s="14" t="n">
+        <v>950.75</v>
+      </c>
+      <c r="D104" s="14" t="n">
+        <v>893.8</v>
+      </c>
+      <c r="E104" s="14" t="n">
+        <v>875.23</v>
+      </c>
+      <c r="F104" s="14" t="n">
+        <v>852.14</v>
+      </c>
+      <c r="G104" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 11-May-2026  18:16</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 12-May-2026  18:32</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>7</v>
@@ -746,13 +746,13 @@
         <v>0.667</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.467</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.578</v>
+        <v>0.5557</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -827,7 +827,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>23</v>
@@ -836,7 +836,7 @@
         <v>22</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.45</v>
+        <v>0.425</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.575</v>
@@ -845,100 +845,100 @@
         <v>0.55</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.525</v>
+        <v>0.5167</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.4667</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -1006,63 +1006,63 @@
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>7</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.467</v>
+        <v>0.25</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.289</v>
+        <v>0.2777</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.2777</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2377,23 +2377,23 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>1340.4</v>
+        <v>1387.7</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>1310.84</v>
+        <v>1231.81</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1184.43</v>
+        <v>1103.41</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>1017.67</v>
+        <v>1012.06</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2405,23 +2405,23 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>1387.7</v>
+        <v>222.03</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>1231.81</v>
+        <v>211.65</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>1103.41</v>
+        <v>187.03</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>1012.06</v>
+        <v>153.27</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>222.03</v>
+        <v>401.35</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>211.65</v>
+        <v>352.48</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>187.03</v>
+        <v>313.55</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>153.27</v>
+        <v>273.79</v>
       </c>
       <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2461,23 +2461,23 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>401.35</v>
+        <v>182.01</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>352.48</v>
+        <v>180.37</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>313.55</v>
+        <v>170.48</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>273.79</v>
+        <v>164.18</v>
       </c>
       <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>182.01</v>
+        <v>858.1</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>180.37</v>
+        <v>810.0700000000001</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>170.48</v>
+        <v>759.25</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>164.18</v>
+        <v>704.16</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2517,23 +2517,23 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
-        <v>858.1</v>
+        <v>464.45</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>810.0700000000001</v>
+        <v>461.6</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>759.25</v>
+        <v>450.4</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>704.16</v>
+        <v>413.33</v>
       </c>
       <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2545,23 +2545,23 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>464.45</v>
+        <v>4432.9</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>461.6</v>
+        <v>4390.45</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>450.4</v>
+        <v>4064.45</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>413.33</v>
+        <v>3287.36</v>
       </c>
       <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2573,23 +2573,23 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>4432.9</v>
+        <v>556.65</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>4390.45</v>
+        <v>551.6900000000001</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>4064.45</v>
+        <v>527.2</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>3287.36</v>
+        <v>506.59</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2601,23 +2601,23 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>556.65</v>
+        <v>329.7</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>551.6900000000001</v>
+        <v>309.59</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>527.2</v>
+        <v>289.28</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>506.59</v>
+        <v>260.87</v>
       </c>
       <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2629,23 +2629,23 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
-        <v>329.7</v>
+        <v>33020</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>309.59</v>
+        <v>31790</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>289.28</v>
+        <v>28438.38</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>260.87</v>
+        <v>22655.05</v>
       </c>
       <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2657,23 +2657,23 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>33020</v>
+        <v>1316.9</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>31790</v>
+        <v>1195.52</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>28438.38</v>
+        <v>1050.31</v>
       </c>
       <c r="F54" s="18" t="n">
-        <v>22655.05</v>
+        <v>863.84</v>
       </c>
       <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2685,23 +2685,23 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C55" s="18" t="n">
-        <v>1316.9</v>
+        <v>53.3</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>1195.52</v>
+        <v>52.89</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>1050.31</v>
+        <v>49.59</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>863.84</v>
+        <v>51.67</v>
       </c>
       <c r="G55" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2713,23 +2713,23 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C56" s="18" t="n">
-        <v>53.3</v>
+        <v>433.2</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>52.89</v>
+        <v>432.77</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>49.59</v>
+        <v>413.85</v>
       </c>
       <c r="F56" s="18" t="n">
-        <v>51.67</v>
+        <v>394.05</v>
       </c>
       <c r="G56" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2741,23 +2741,23 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C57" s="18" t="n">
-        <v>433.2</v>
+        <v>4545.1</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>432.77</v>
+        <v>4078.99</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>413.85</v>
+        <v>3715.6</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>394.05</v>
+        <v>3336.91</v>
       </c>
       <c r="G57" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2769,23 +2769,23 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>4545.1</v>
+        <v>1680.9</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>4078.99</v>
+        <v>1661.43</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>3715.6</v>
+        <v>1562.77</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>3336.91</v>
+        <v>1425.37</v>
       </c>
       <c r="G58" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2797,303 +2797,303 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C59" s="18" t="n">
-        <v>1680.9</v>
+        <v>582.05</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>1661.43</v>
+        <v>553.26</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>1562.77</v>
+        <v>522.25</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>1425.37</v>
+        <v>522.05</v>
       </c>
       <c r="G59" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="n">
-        <v>582.05</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>553.26</v>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>522.25</v>
-      </c>
-      <c r="F60" s="18" t="n">
-        <v>522.05</v>
-      </c>
-      <c r="G60" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="n">
+        <v>1810.9</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>1772.18</v>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>1725.92</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>1678.31</v>
+      </c>
+      <c r="G60" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="n">
-        <v>270.4</v>
-      </c>
-      <c r="D61" s="14" t="n">
-        <v>265.07</v>
-      </c>
-      <c r="E61" s="14" t="n">
-        <v>260.19</v>
-      </c>
-      <c r="F61" s="14" t="n">
-        <v>269.78</v>
-      </c>
-      <c r="G61" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>1624.5</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>1598.16</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>1584.41</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>1610.15</v>
+      </c>
+      <c r="G61" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
-        <v>1026</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>1025.44</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>1008.64</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>1024.17</v>
-      </c>
-      <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>2747.2</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>2726.23</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>2648.42</v>
+      </c>
+      <c r="F62" s="18" t="n">
+        <v>2609.27</v>
+      </c>
+      <c r="G62" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n">
-        <v>655.75</v>
-      </c>
-      <c r="D63" s="14" t="n">
-        <v>624.8099999999999</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>585.61</v>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>564.75</v>
-      </c>
-      <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>585.6</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>556.4299999999999</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>538.73</v>
+      </c>
+      <c r="F63" s="18" t="n">
+        <v>545.9400000000001</v>
+      </c>
+      <c r="G63" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C64" s="18" t="n">
-        <v>1810.9</v>
+        <v>3187.9</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>1772.18</v>
+        <v>2900.51</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>1725.92</v>
+        <v>2711.5</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>1678.31</v>
+        <v>2207.12</v>
       </c>
       <c r="G64" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C65" s="14" t="n">
-        <v>1624.5</v>
+        <v>270.4</v>
       </c>
       <c r="D65" s="14" t="n">
-        <v>1598.16</v>
+        <v>265.07</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>1584.41</v>
+        <v>260.19</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>1610.15</v>
+        <v>269.78</v>
       </c>
       <c r="G65" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C66" s="14" t="n">
-        <v>2747.2</v>
+        <v>655.75</v>
       </c>
       <c r="D66" s="14" t="n">
-        <v>2726.23</v>
+        <v>624.8099999999999</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>2648.42</v>
+        <v>585.61</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>2609.27</v>
+        <v>564.75</v>
       </c>
       <c r="G66" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="n">
-        <v>585.6</v>
-      </c>
-      <c r="D67" s="14" t="n">
-        <v>556.4299999999999</v>
-      </c>
-      <c r="E67" s="14" t="n">
-        <v>538.73</v>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>545.9400000000001</v>
-      </c>
-      <c r="G67" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n">
+        <v>8539.5</v>
+      </c>
+      <c r="D67" s="18" t="n">
+        <v>8057.08</v>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>7581.47</v>
+      </c>
+      <c r="F67" s="18" t="n">
+        <v>7180.9</v>
+      </c>
+      <c r="G67" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="n">
-        <v>3187.9</v>
-      </c>
-      <c r="D68" s="14" t="n">
-        <v>2900.51</v>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v>2711.5</v>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>2207.12</v>
-      </c>
-      <c r="G68" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>CENTURYPLY</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>778.85</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>778.73</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>758.4</v>
+      </c>
+      <c r="F68" s="18" t="n">
+        <v>756.8200000000001</v>
+      </c>
+      <c r="G68" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="C69" s="18" t="n">
-        <v>8539.5</v>
+        <v>6152</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>8057.08</v>
+        <v>5382.23</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>7581.47</v>
+        <v>5189</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>7180.9</v>
+        <v>5512.42</v>
       </c>
       <c r="G69" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3105,190 +3105,134 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="C70" s="18" t="n">
-        <v>778.85</v>
+        <v>290.2</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>778.73</v>
+        <v>270.53</v>
       </c>
       <c r="E70" s="18" t="n">
-        <v>758.4</v>
+        <v>259.75</v>
       </c>
       <c r="F70" s="18" t="n">
-        <v>756.8200000000001</v>
+        <v>274.01</v>
       </c>
       <c r="G70" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>CERA</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="n">
-        <v>6152</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>5382.23</v>
-      </c>
-      <c r="E71" s="18" t="n">
-        <v>5189</v>
-      </c>
-      <c r="F71" s="18" t="n">
-        <v>5512.42</v>
-      </c>
-      <c r="G71" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="n">
+        <v>81.42</v>
+      </c>
+      <c r="D71" s="14" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="E71" s="14" t="n">
+        <v>73.12</v>
+      </c>
+      <c r="F71" s="14" t="n">
+        <v>63.62</v>
+      </c>
+      <c r="G71" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C72" s="18" t="n">
-        <v>290.2</v>
+        <v>1021.4</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>270.53</v>
+        <v>1010.22</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>259.75</v>
+        <v>983.1</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>274.01</v>
+        <v>907.73</v>
       </c>
       <c r="G72" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B73" s="13" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="n">
-        <v>81.42</v>
-      </c>
-      <c r="D73" s="14" t="n">
-        <v>78.29000000000001</v>
-      </c>
-      <c r="E73" s="14" t="n">
-        <v>73.12</v>
-      </c>
-      <c r="F73" s="14" t="n">
-        <v>63.62</v>
-      </c>
-      <c r="G73" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>292.45</v>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>289.88</v>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>284.05</v>
+      </c>
+      <c r="F73" s="18" t="n">
+        <v>255.47</v>
+      </c>
+      <c r="G73" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="20" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="C74" s="18" t="n">
-        <v>1021.4</v>
+        <v>922.3</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>1010.22</v>
+        <v>896.52</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>983.1</v>
+        <v>877.08</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>907.73</v>
+        <v>849.67</v>
       </c>
       <c r="G74" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="n">
-        <v>292.45</v>
-      </c>
-      <c r="D75" s="18" t="n">
-        <v>289.88</v>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>284.05</v>
-      </c>
-      <c r="F75" s="18" t="n">
-        <v>255.47</v>
-      </c>
-      <c r="G75" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B76" s="17" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="n">
-        <v>922.3</v>
-      </c>
-      <c r="D76" s="18" t="n">
-        <v>896.52</v>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>877.08</v>
-      </c>
-      <c r="F76" s="18" t="n">
-        <v>849.67</v>
-      </c>
-      <c r="G76" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 12-May-2026  18:32</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 13-May-2026  18:35</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>18</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.9</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.9167000000000001</v>
+        <v>0.8167</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,304 +703,304 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>11</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.467</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.733</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.711</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.667</v>
+        <v>0.467</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.5557</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.65</v>
+        <v>0.475</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.25</v>
+        <v>0.525</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.5333</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.5333</v>
+        <v>0.3833</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.425</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.575</v>
+        <v>0.333</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.5167</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7</v>
+        <v>0.267</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.4667</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.55</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.45</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>6</v>
-      </c>
       <c r="F13" s="10" t="n">
-        <v>0.333</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.467</v>
+        <v>0.15</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="E14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="F14" s="6" t="n">
-        <v>0.333</v>
+        <v>0.133</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.3053</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1013,7 +1013,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>3</v>
@@ -1022,7 +1022,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>0.25</v>
@@ -1031,38 +1031,38 @@
         <v>0.25</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.2777</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.2</v>
+        <v>0.083</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.4</v>
+        <v>0.083</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.2667</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1075,25 +1075,25 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3064.2</v>
+        <v>3091.7</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2906.26</v>
+        <v>2923.93</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2870.87</v>
+        <v>2879.54</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2729.65</v>
+        <v>2742.39</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>5599.5</v>
+        <v>5496.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>5471.98</v>
+        <v>5474.32</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>5462.99</v>
+        <v>5464.31</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>5409.27</v>
+        <v>5418.93</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1486.6</v>
+        <v>1488.2</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1414.92</v>
+        <v>1421.89</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1347.46</v>
+        <v>1352.98</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1233.01</v>
+        <v>1237.04</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>390.45</v>
+        <v>402.45</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>368.16</v>
+        <v>371.43</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>368.61</v>
+        <v>369.93</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>368.75</v>
+        <v>369.23</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>6714</v>
+        <v>6644</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6464.17</v>
+        <v>6481.3</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>6320.18</v>
+        <v>6332.89</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>6276.22</v>
+        <v>6291.09</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1919.1</v>
+        <v>1872.1</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1796.94</v>
+        <v>1804.1</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1764.87</v>
+        <v>1769.07</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1750.51</v>
+        <v>1751.97</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2347.3</v>
+        <v>729.05</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>2324.69</v>
+        <v>701.8</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>2229.97</v>
+        <v>657.2</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>2010.89</v>
+        <v>583.71</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>JBCHEPHARM</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>755.6</v>
+        <v>2135.3</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>698.9299999999999</v>
+        <v>2082.34</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>654.27</v>
+        <v>2037.14</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>580.76</v>
+        <v>1875.17</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>1535</v>
+        <v>1268</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>1528.02</v>
+        <v>1155.29</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>1510.82</v>
+        <v>1098.63</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>1452.39</v>
+        <v>974.83</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2209.2</v>
+        <v>2378.9</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2076.77</v>
+        <v>2279.28</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2033.13</v>
+        <v>2199.57</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1870.43</v>
+        <v>2263.29</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,23 +1509,23 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1266.8</v>
+        <v>1181.9</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1143.43</v>
+        <v>1118.01</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>1091.72</v>
+        <v>1052.19</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>971.73</v>
+        <v>938.87</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,23 +1537,23 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>2468.8</v>
+        <v>1845.7</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>2268.79</v>
+        <v>1786.59</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>2192.24</v>
+        <v>1755.04</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>2258.13</v>
+        <v>1715.33</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1206</v>
+        <v>4381.9</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>1111.28</v>
+        <v>4273.97</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>1046.9</v>
+        <v>4209.65</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>937.15</v>
+        <v>3900.06</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,107 +1593,107 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>1872.7</v>
+        <v>930.65</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>1780.36</v>
+        <v>923.46</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>1751.34</v>
+        <v>914.76</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>1712.87</v>
+        <v>923.53</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>4517.1</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>4262.61</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>4202.62</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>3895.36</v>
-      </c>
-      <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>2405.2</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>2358.76</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>2230.11</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>2262.98</v>
+      </c>
+      <c r="G17" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>956.95</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>922.71</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>914.11</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>922.05</v>
-      </c>
-      <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>1041.4</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1028.85</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>989.17</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>872.22</v>
+      </c>
+      <c r="G18" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>2500.2</v>
+        <v>564.2</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>2353.87</v>
+        <v>549.11</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>2222.96</v>
+        <v>537.75</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>2260.22</v>
+        <v>444.44</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1705,23 +1705,23 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>572.9</v>
+        <v>641.9</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>547.52</v>
+        <v>603.52</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>536.67</v>
+        <v>583.33</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>443.5</v>
+        <v>536</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1733,23 +1733,23 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>629.1</v>
+        <v>2859.8</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>599.48</v>
+        <v>2660.98</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>580.9400000000001</v>
+        <v>2491.59</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>535.4299999999999</v>
+        <v>2432.55</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1262.6</v>
+        <v>212</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1253.47</v>
+        <v>211.06</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>1226.58</v>
+        <v>205.22</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>1160.96</v>
+        <v>185.68</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,1451 +1789,863 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>3046.2</v>
+        <v>1319.4</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>2640.05</v>
+        <v>1200.96</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>2476.56</v>
+        <v>1051.57</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>2425.73</v>
+        <v>898.39</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>180.72</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>179.08</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>168.95</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>148.43</v>
-      </c>
-      <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>534.15</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>516.83</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>498.61</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>490.83</v>
+      </c>
+      <c r="G24" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>212.08</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>210.97</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>204.95</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>185.6</v>
-      </c>
-      <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>830</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>795.92</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>776.97</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>749.34</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>1329.3</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>1188.49</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>1040.64</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>893.6</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>1468.6</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>1415.49</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>1342.99</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>1265.71</v>
+      </c>
+      <c r="G26" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>10595.5</v>
+        <v>3428.6</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>9983.68</v>
+        <v>3283.41</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>9693.34</v>
+        <v>3081.76</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>9191.139999999999</v>
+        <v>2938.82</v>
       </c>
       <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>1987</v>
+        <v>1253</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>1884.6</v>
+        <v>1162.51</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>1803.43</v>
+        <v>1136.31</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1544.88</v>
+        <v>1131.11</v>
       </c>
       <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>37315</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>36466.85</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>35496.27</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>35436.89</v>
-      </c>
-      <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>1318.2</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>1309.25</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>1193.44</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>1024.11</v>
+      </c>
+      <c r="G29" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>7202.5</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>7192.83</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>7192.21</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>6887.72</v>
-      </c>
-      <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EICHERMOT","Chart 📈")</f>
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>1308</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>1239.07</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1111.44</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>1016.45</v>
+      </c>
+      <c r="G30" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>130.3</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>124.44</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>121.65</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>114.01</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>391.75</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>316.62</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>275.42</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>3613.7</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>3599.54</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>3611.39</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>3472.95</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>180.38</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>170.87</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>164.12</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C33" s="18" t="n">
-        <v>1637.5</v>
+        <v>833.7</v>
       </c>
       <c r="D33" s="18" t="n">
-        <v>1456.96</v>
+        <v>812.3200000000001</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>1457.61</v>
+        <v>762.17</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>1612.94</v>
+        <v>705.98</v>
       </c>
       <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AFFLE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>148.46</v>
+        <v>463.05</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>115.97</v>
+        <v>461.74</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>95.95999999999999</v>
+        <v>450.9</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>80.06</v>
+        <v>413.79</v>
       </c>
       <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C35" s="18" t="n">
-        <v>12.18</v>
+        <v>32265</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>10.4</v>
+        <v>31835.24</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>10.09</v>
+        <v>28588.45</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>9.529999999999999</v>
+        <v>22759.87</v>
       </c>
       <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>9239.5</v>
+        <v>1265.2</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>8736.27</v>
+        <v>1202.16</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>7934.41</v>
+        <v>1058.73</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>7764.93</v>
+        <v>868.8099999999999</v>
       </c>
       <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>4483</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>4117.47</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>3745.69</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>3350.11</v>
+      </c>
+      <c r="G37" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>TRITURBINE</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>560.7</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>553.97</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>523.75</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>521.7</v>
+      </c>
+      <c r="G38" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>TANLA</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>549.5</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>518.92</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>489.23</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>518.45</v>
-      </c>
-      <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>525.4</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>515.01</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>497.16</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>490.75</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>842.55</v>
+        <v>147.78</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>792.33</v>
+        <v>119</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>774.8099999999999</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>749.4</v>
+        <v>80.8</v>
       </c>
       <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>1481.9</v>
+        <v>11.89</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>1409.9</v>
+        <v>10.54</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>1337.86</v>
+        <v>10.16</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>1264.23</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>3489.7</v>
+        <v>9010.5</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>3268.13</v>
+        <v>8762.389999999999</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>3067.6</v>
+        <v>7976.6</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>2928.83</v>
+        <v>7758.59</v>
       </c>
       <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>1271</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>1152.98</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>1131.55</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>1132.12</v>
-      </c>
-      <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>10397</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>10023.05</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>9720.93</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>9205.040000000001</v>
+      </c>
+      <c r="G42" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>501.3</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>490.26</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>467.02</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>467.52</v>
-      </c>
-      <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>1913</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>1887.3</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>1807.73</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>1548.94</v>
+      </c>
+      <c r="G43" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>1387.7</v>
+        <v>36510</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>1231.81</v>
+        <v>36470.96</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1103.41</v>
+        <v>35536.03</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>1012.06</v>
+        <v>35459.13</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>ADANIPOWER</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>222.03</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>211.65</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>187.03</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>153.27</v>
-      </c>
-      <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>8163.5</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>8067.22</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>7604.29</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>7188.81</v>
+      </c>
+      <c r="G45" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>401.35</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>352.48</v>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>313.55</v>
-      </c>
-      <c r="F46" s="18" t="n">
-        <v>273.79</v>
-      </c>
-      <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>5926.5</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>5434.06</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>5217.91</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>5506.38</v>
+      </c>
+      <c r="G46" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>182.01</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>180.37</v>
-      </c>
-      <c r="E47" s="18" t="n">
-        <v>170.48</v>
-      </c>
-      <c r="F47" s="18" t="n">
-        <v>164.18</v>
-      </c>
-      <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>282.05</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>271.63</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>260.62</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>273.73</v>
+      </c>
+      <c r="G47" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>858.1</v>
+        <v>641.8</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>810.0700000000001</v>
+        <v>626.4299999999999</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>759.25</v>
+        <v>587.8200000000001</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>704.16</v>
+        <v>566.01</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="n">
-        <v>464.45</v>
-      </c>
-      <c r="D49" s="18" t="n">
-        <v>461.6</v>
-      </c>
-      <c r="E49" s="18" t="n">
-        <v>450.4</v>
-      </c>
-      <c r="F49" s="18" t="n">
-        <v>413.33</v>
-      </c>
-      <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>567.65</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>557.49</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>539.87</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>546.28</v>
+      </c>
+      <c r="G49" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="n">
-        <v>4432.9</v>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>4390.45</v>
-      </c>
-      <c r="E50" s="18" t="n">
-        <v>4064.45</v>
-      </c>
-      <c r="F50" s="18" t="n">
-        <v>3287.36</v>
-      </c>
-      <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>3156.9</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>2924.92</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>2728.97</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>2214.53</v>
+      </c>
+      <c r="G50" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>556.65</v>
+        <v>490.95</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>551.6900000000001</v>
+        <v>472</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>527.2</v>
+        <v>470.01</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>506.59</v>
+        <v>443</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>329.7</v>
+        <v>294.5</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>309.59</v>
+        <v>287.18</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>289.28</v>
+        <v>280.18</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>260.87</v>
+        <v>255.59</v>
       </c>
       <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>POWERINDIA</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="n">
-        <v>33020</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>31790</v>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>28438.38</v>
-      </c>
-      <c r="F53" s="18" t="n">
-        <v>22655.05</v>
-      </c>
-      <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>SCHNEIDER</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="n">
-        <v>1316.9</v>
-      </c>
-      <c r="D54" s="18" t="n">
-        <v>1195.52</v>
-      </c>
-      <c r="E54" s="18" t="n">
-        <v>1050.31</v>
-      </c>
-      <c r="F54" s="18" t="n">
-        <v>863.84</v>
-      </c>
-      <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="D55" s="18" t="n">
-        <v>52.89</v>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="F55" s="18" t="n">
-        <v>51.67</v>
-      </c>
-      <c r="G55" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="n">
-        <v>433.2</v>
-      </c>
-      <c r="D56" s="18" t="n">
-        <v>432.77</v>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>413.85</v>
-      </c>
-      <c r="F56" s="18" t="n">
-        <v>394.05</v>
-      </c>
-      <c r="G56" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATAPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="n">
-        <v>4545.1</v>
-      </c>
-      <c r="D57" s="18" t="n">
-        <v>4078.99</v>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>3715.6</v>
-      </c>
-      <c r="F57" s="18" t="n">
-        <v>3336.91</v>
-      </c>
-      <c r="G57" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n">
-        <v>1680.9</v>
-      </c>
-      <c r="D58" s="18" t="n">
-        <v>1661.43</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>1562.77</v>
-      </c>
-      <c r="F58" s="18" t="n">
-        <v>1425.37</v>
-      </c>
-      <c r="G58" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="n">
-        <v>582.05</v>
-      </c>
-      <c r="D59" s="18" t="n">
-        <v>553.26</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>522.25</v>
-      </c>
-      <c r="F59" s="18" t="n">
-        <v>522.05</v>
-      </c>
-      <c r="G59" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="n">
-        <v>1810.9</v>
-      </c>
-      <c r="D60" s="14" t="n">
-        <v>1772.18</v>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v>1725.92</v>
-      </c>
-      <c r="F60" s="14" t="n">
-        <v>1678.31</v>
-      </c>
-      <c r="G60" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n">
-        <v>1624.5</v>
-      </c>
-      <c r="D61" s="18" t="n">
-        <v>1598.16</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>1584.41</v>
-      </c>
-      <c r="F61" s="18" t="n">
-        <v>1610.15</v>
-      </c>
-      <c r="G61" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>HDFCAMC</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="n">
-        <v>2747.2</v>
-      </c>
-      <c r="D62" s="18" t="n">
-        <v>2726.23</v>
-      </c>
-      <c r="E62" s="18" t="n">
-        <v>2648.42</v>
-      </c>
-      <c r="F62" s="18" t="n">
-        <v>2609.27</v>
-      </c>
-      <c r="G62" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="n">
-        <v>585.6</v>
-      </c>
-      <c r="D63" s="18" t="n">
-        <v>556.4299999999999</v>
-      </c>
-      <c r="E63" s="18" t="n">
-        <v>538.73</v>
-      </c>
-      <c r="F63" s="18" t="n">
-        <v>545.9400000000001</v>
-      </c>
-      <c r="G63" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="n">
-        <v>3187.9</v>
-      </c>
-      <c r="D64" s="18" t="n">
-        <v>2900.51</v>
-      </c>
-      <c r="E64" s="18" t="n">
-        <v>2711.5</v>
-      </c>
-      <c r="F64" s="18" t="n">
-        <v>2207.12</v>
-      </c>
-      <c r="G64" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="n">
-        <v>270.4</v>
-      </c>
-      <c r="D65" s="14" t="n">
-        <v>265.07</v>
-      </c>
-      <c r="E65" s="14" t="n">
-        <v>260.19</v>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>269.78</v>
-      </c>
-      <c r="G65" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="n">
-        <v>655.75</v>
-      </c>
-      <c r="D66" s="14" t="n">
-        <v>624.8099999999999</v>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>585.61</v>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>564.75</v>
-      </c>
-      <c r="G66" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="n">
-        <v>8539.5</v>
-      </c>
-      <c r="D67" s="18" t="n">
-        <v>8057.08</v>
-      </c>
-      <c r="E67" s="18" t="n">
-        <v>7581.47</v>
-      </c>
-      <c r="F67" s="18" t="n">
-        <v>7180.9</v>
-      </c>
-      <c r="G67" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>CENTURYPLY</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="n">
-        <v>778.85</v>
-      </c>
-      <c r="D68" s="18" t="n">
-        <v>778.73</v>
-      </c>
-      <c r="E68" s="18" t="n">
-        <v>758.4</v>
-      </c>
-      <c r="F68" s="18" t="n">
-        <v>756.8200000000001</v>
-      </c>
-      <c r="G68" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CENTURYPLY","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>CERA</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="n">
-        <v>6152</v>
-      </c>
-      <c r="D69" s="18" t="n">
-        <v>5382.23</v>
-      </c>
-      <c r="E69" s="18" t="n">
-        <v>5189</v>
-      </c>
-      <c r="F69" s="18" t="n">
-        <v>5512.42</v>
-      </c>
-      <c r="G69" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="n">
-        <v>290.2</v>
-      </c>
-      <c r="D70" s="18" t="n">
-        <v>270.53</v>
-      </c>
-      <c r="E70" s="18" t="n">
-        <v>259.75</v>
-      </c>
-      <c r="F70" s="18" t="n">
-        <v>274.01</v>
-      </c>
-      <c r="G70" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="12" t="inlineStr">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>MAHABANK</t>
         </is>
       </c>
-      <c r="C71" s="14" t="n">
-        <v>81.42</v>
-      </c>
-      <c r="D71" s="14" t="n">
-        <v>78.29000000000001</v>
-      </c>
-      <c r="E71" s="14" t="n">
-        <v>73.12</v>
-      </c>
-      <c r="F71" s="14" t="n">
-        <v>63.62</v>
-      </c>
-      <c r="G71" s="15">
+      <c r="C53" s="14" t="n">
+        <v>78.37</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="G53" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>AUBANK</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="n">
-        <v>1021.4</v>
-      </c>
-      <c r="D72" s="18" t="n">
-        <v>1010.22</v>
-      </c>
-      <c r="E72" s="18" t="n">
-        <v>983.1</v>
-      </c>
-      <c r="F72" s="18" t="n">
-        <v>907.73</v>
-      </c>
-      <c r="G72" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="n">
-        <v>292.45</v>
-      </c>
-      <c r="D73" s="18" t="n">
-        <v>289.88</v>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>284.05</v>
-      </c>
-      <c r="F73" s="18" t="n">
-        <v>255.47</v>
-      </c>
-      <c r="G73" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="n">
-        <v>922.3</v>
-      </c>
-      <c r="D74" s="18" t="n">
-        <v>896.52</v>
-      </c>
-      <c r="E74" s="18" t="n">
-        <v>877.08</v>
-      </c>
-      <c r="F74" s="18" t="n">
-        <v>849.67</v>
-      </c>
-      <c r="G74" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 13-May-2026  18:35</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 14-May-2026  17:39</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.8167</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,25 +703,25 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>12</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.467</v>
+        <v>0.8</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.733</v>
+        <v>0.8</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -734,25 +734,25 @@
         <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.467</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.489</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -765,25 +765,25 @@
         <v>40</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>19</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.475</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.525</v>
+        <v>0.55</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4167</v>
+        <v>0.4583</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -796,56 +796,56 @@
         <v>20</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>10</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3833</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>6</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.311</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -858,25 +858,25 @@
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.289</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -889,87 +889,87 @@
         <v>10</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2667</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1</v>
+        <v>0.333</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2333</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>7</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.2</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -982,7 +982,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>4</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0.267</v>
@@ -1000,7 +1000,7 @@
         <v>0.2</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1013,25 +1013,25 @@
         <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1667</v>
+        <v>0.1947</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1044,25 +1044,25 @@
         <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.083</v>
+        <v>0.167</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0.083</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.111</v>
+        <v>0.1943</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3091.7</v>
+        <v>3259.2</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2923.93</v>
+        <v>2973.03</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2879.54</v>
+        <v>2903.61</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2742.39</v>
+        <v>2750.76</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>5496.5</v>
+        <v>5576.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>5474.32</v>
+        <v>5483.03</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>5464.31</v>
+        <v>5468.64</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>5418.93</v>
+        <v>5420.97</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1488.2</v>
+        <v>1510.9</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1421.89</v>
+        <v>1436.89</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1352.98</v>
+        <v>1364.62</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1237.04</v>
+        <v>1242.02</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>402.45</v>
+        <v>419</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>371.43</v>
+        <v>379.94</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>369.93</v>
+        <v>373.65</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>369.23</v>
+        <v>370.88</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>6644</v>
+        <v>1436.7</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6481.3</v>
+        <v>1317.49</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>6332.89</v>
+        <v>1306.52</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>6291.09</v>
+        <v>1395.41</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CIPLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1872.1</v>
+        <v>6921.5</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1804.1</v>
+        <v>6550.34</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1769.07</v>
+        <v>6373.43</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1751.97</v>
+        <v>6313.81</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>729.05</v>
+        <v>1303.6</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>701.8</v>
+        <v>1285.54</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>657.2</v>
+        <v>1275.08</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>583.71</v>
+        <v>1259.26</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2135.3</v>
+        <v>1898.2</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2082.34</v>
+        <v>1816.52</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2037.14</v>
+        <v>1776.97</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1875.17</v>
+        <v>1756.64</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>1268</v>
+        <v>2340.6</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>1155.29</v>
+        <v>2316.88</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>1098.63</v>
+        <v>2237.09</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>974.83</v>
+        <v>2024.18</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2378.9</v>
+        <v>735.3</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2279.28</v>
+        <v>707.28</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2199.57</v>
+        <v>662.95</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2263.29</v>
+        <v>587.88</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,23 +1509,23 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1181.9</v>
+        <v>1583.9</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1118.01</v>
+        <v>1529.99</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>1052.19</v>
+        <v>1513.45</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>938.87</v>
+        <v>1458.63</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,23 +1537,23 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>JBCHEPHARM</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1845.7</v>
+        <v>2137.8</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>1786.59</v>
+        <v>2088.65</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>1755.04</v>
+        <v>2043.24</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1715.33</v>
+        <v>1882.37</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>4381.9</v>
+        <v>1315.5</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>4273.97</v>
+        <v>1181.34</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>4209.65</v>
+        <v>1113.99</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>3900.06</v>
+        <v>982.11</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,163 +1593,163 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>2462.2</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>2307.75</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>2217.7</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>2267.3</v>
+      </c>
+      <c r="G16" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>1204.4</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>1130.88</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>1062.67</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>944.03</v>
+      </c>
+      <c r="G17" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>1863.2</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1797.18</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>1761.91</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>1718.54</v>
+      </c>
+      <c r="G18" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>4403.9</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>4288.23</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>4220.52</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>3909.7</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n">
-        <v>930.65</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>923.46</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>914.76</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>923.53</v>
-      </c>
-      <c r="G16" s="15">
+      <c r="C20" s="14" t="n">
+        <v>991.7</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>931.3200000000001</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>918.7</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>924.5</v>
+      </c>
+      <c r="G20" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
-        <v>2405.2</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>2358.76</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>2230.11</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>2262.98</v>
-      </c>
-      <c r="G17" s="19">
+      <c r="C21" s="18" t="n">
+        <v>2712.9</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>2404.49</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>2259.14</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>2271.47</v>
+      </c>
+      <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>1041.4</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>1028.85</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>989.17</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>872.22</v>
-      </c>
-      <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>HINDCOPPER</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>564.2</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>549.11</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>537.75</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>444.44</v>
-      </c>
-      <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>HINDZINC</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>641.9</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>603.52</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>583.33</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>536</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>RATNAMANI</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>2859.8</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>2660.98</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>2491.59</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>2432.55</v>
-      </c>
-      <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>212</v>
+        <v>1103.3</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>211.06</v>
+        <v>1039.75</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>205.22</v>
+        <v>996.8099999999999</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>185.68</v>
+        <v>877.78</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,862 +1789,1422 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1319.4</v>
+        <v>606.45</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1200.96</v>
+        <v>558.55</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>1051.57</v>
+        <v>542.62</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>898.39</v>
+        <v>448.35</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>534.15</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>516.83</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>498.61</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>490.83</v>
-      </c>
-      <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>669.25</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>615.26</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>589.86</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>539.41</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>830</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>795.92</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>776.97</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>749.34</v>
-      </c>
-      <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>1252.8</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>1239.41</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>1211.47</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>1109.26</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>1468.6</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>1415.49</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>1342.99</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>1265.71</v>
-      </c>
-      <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>1296.9</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>1259.36</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>1232.09</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>1163.04</v>
+      </c>
+      <c r="G26" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>3428.6</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>3283.41</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>3081.76</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>2938.82</v>
-      </c>
-      <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>416.45</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>408.72</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>315.64</v>
+      </c>
+      <c r="G27" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>1253</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>1162.51</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>1136.31</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>1131.11</v>
-      </c>
-      <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>78.23</v>
+      </c>
+      <c r="G28" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>1318.2</v>
+        <v>2888.6</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>1309.25</v>
+        <v>2697.26</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>1193.44</v>
+        <v>2519.93</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>1024.11</v>
+        <v>2443.92</v>
       </c>
       <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>1308</v>
+        <v>199.08</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>1239.07</v>
+        <v>182.67</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>1111.44</v>
+        <v>171.61</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>1016.45</v>
+        <v>150.09</v>
       </c>
       <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>391.75</v>
+        <v>221.13</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>356.22</v>
+        <v>212.76</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>316.62</v>
+        <v>206.39</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>275.42</v>
+        <v>186.84</v>
       </c>
       <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>1367.5</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>1229.9</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>1075.31</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>908.05</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>540.7</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>521.87</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>502.15</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>492.3</v>
+      </c>
+      <c r="G33" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>835</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>802.87</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>781.37</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>750.61</v>
+      </c>
+      <c r="G34" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1459.6</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>1424.3</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>1352.3</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>1269.65</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>3461</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>3314.72</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>3110.53</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>2947.63</v>
+      </c>
+      <c r="G36" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>1228.3</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>1175.02</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>1143.64</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>1133.24</v>
+      </c>
+      <c r="G37" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>505.15</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>491.43</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>470.12</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>468.01</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>180.38</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>170.87</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>164.12</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>1319.1</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>1310.19</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>1198.37</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>1025.93</v>
+      </c>
+      <c r="G39" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>833.7</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>812.3200000000001</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>762.17</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>705.98</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>1414.9</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>1266.81</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>1132.96</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>1024.62</v>
+      </c>
+      <c r="G40" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>463.05</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>461.74</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>450.9</v>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>413.79</v>
-      </c>
-      <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>224.49</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>212.91</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>190.33</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>155.01</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>POWERINDIA</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>32265</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>31835.24</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>28588.45</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>22759.87</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>SCHNEIDER</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>1265.2</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>1202.16</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>1058.73</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>868.8099999999999</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>4483</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>4117.47</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>3745.69</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>3350.11</v>
-      </c>
-      <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="n">
-        <v>560.7</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>553.97</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>523.75</v>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>521.7</v>
-      </c>
-      <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n">
-        <v>147.78</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>119</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>97.98999999999999</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>9010.5</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>8762.389999999999</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>7976.6</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>7758.59</v>
-      </c>
-      <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>10397</v>
+        <v>413.15</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>10023.05</v>
+        <v>365.74</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>9720.93</v>
+        <v>323.69</v>
       </c>
       <c r="F42" s="18" t="n">
-        <v>9205.040000000001</v>
+        <v>278.13</v>
       </c>
       <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="C43" s="18" t="n">
-        <v>1913</v>
+        <v>184.46</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>1887.3</v>
+        <v>180.71</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>1807.73</v>
+        <v>171.74</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>1548.94</v>
+        <v>164.78</v>
       </c>
       <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>36510</v>
+        <v>848.25</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>36470.96</v>
+        <v>818.74</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>35536.03</v>
+        <v>768.75</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>35459.13</v>
+        <v>710.49</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="n">
-        <v>8163.5</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>8067.22</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>7604.29</v>
-      </c>
-      <c r="F45" s="14" t="n">
-        <v>7188.81</v>
-      </c>
-      <c r="G45" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>294.53</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>263.12</v>
+      </c>
+      <c r="G45" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>CERA</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="n">
-        <v>5926.5</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>5434.06</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>5217.91</v>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>5506.38</v>
-      </c>
-      <c r="G46" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>396.3</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>395.06</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>385.91</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>356.79</v>
+      </c>
+      <c r="G46" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="n">
-        <v>282.05</v>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>271.63</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>260.62</v>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>273.73</v>
-      </c>
-      <c r="G47" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>32290</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>31870.77</v>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>28852.57</v>
+      </c>
+      <c r="F47" s="18" t="n">
+        <v>23005.57</v>
+      </c>
+      <c r="G47" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>641.8</v>
+        <v>1315</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>626.4299999999999</v>
+        <v>1219.72</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>587.8200000000001</v>
+        <v>1077.17</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>566.01</v>
+        <v>877.51</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n">
-        <v>567.65</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>557.49</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>539.87</v>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>546.28</v>
-      </c>
-      <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>3693.8</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>3671.75</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>3502.91</v>
+      </c>
+      <c r="F49" s="18" t="n">
+        <v>3259.23</v>
+      </c>
+      <c r="G49" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n">
-        <v>3156.9</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>2924.92</v>
-      </c>
-      <c r="E50" s="14" t="n">
-        <v>2728.97</v>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>2214.53</v>
-      </c>
-      <c r="G50" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="G50" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>490.95</v>
+        <v>4597.7</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>472</v>
+        <v>4200.17</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>470.01</v>
+        <v>3809.28</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>443</v>
+        <v>3381.27</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>294.5</v>
+        <v>578.55</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>287.18</v>
+        <v>557.29</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>280.18</v>
+        <v>527.47</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>255.59</v>
+        <v>524.61</v>
       </c>
       <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
         <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="n">
+        <v>151.59</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>125.07</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>102.18</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>82.45999999999999</v>
+      </c>
+      <c r="G53" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="G54" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="n">
+        <v>422.35</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>411.7</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>420.01</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>412.15</v>
+      </c>
+      <c r="G55" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="n">
+        <v>8904.5</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>8790.24</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>8048.86</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>7783.56</v>
+      </c>
+      <c r="G56" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>1656.1</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>1563.86</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>1550.68</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>1626.75</v>
+      </c>
+      <c r="G57" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>560.4</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>560.2</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>542.4</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>547.9</v>
+      </c>
+      <c r="G58" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>3339.1</v>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>2988.43</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>2770.8</v>
+      </c>
+      <c r="F59" s="18" t="n">
+        <v>2239.8</v>
+      </c>
+      <c r="G59" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>3531.1</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>3476.35</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>3464.83</v>
+      </c>
+      <c r="F60" s="18" t="n">
+        <v>3290.19</v>
+      </c>
+      <c r="G60" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>451.45</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>450.98</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>434.62</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>401.67</v>
+      </c>
+      <c r="G61" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>8288.5</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>8108.39</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>7657.36</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>7217.85</v>
+      </c>
+      <c r="G62" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>5689.5</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>5490.7</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>5258.68</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>5511.1</v>
+      </c>
+      <c r="G63" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="n">
+        <v>288.95</v>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>274.42</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>262.65</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>274.02</v>
+      </c>
+      <c r="G64" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>635.15</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>628.1799999999999</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>591.53</v>
+      </c>
+      <c r="F65" s="18" t="n">
+        <v>568.46</v>
+      </c>
+      <c r="G65" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="n">
+        <v>10451</v>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>10084.4</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>9769.950000000001</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>9231.01</v>
+      </c>
+      <c r="G66" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="n">
+        <v>1948.9</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>1898.22</v>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>1818.48</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>1560.32</v>
+      </c>
+      <c r="G67" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="n">
+        <v>36945</v>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>36502.67</v>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v>35620.65</v>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>35504.84</v>
+      </c>
+      <c r="G68" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="n">
+        <v>126.11</v>
+      </c>
+      <c r="D69" s="14" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="E69" s="14" t="n">
+        <v>122.09</v>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>114.13</v>
+      </c>
+      <c r="G69" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>517.55</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>479.37</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>473.27</v>
+      </c>
+      <c r="F70" s="18" t="n">
+        <v>445.28</v>
+      </c>
+      <c r="G70" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>289.35</v>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>281.63</v>
+      </c>
+      <c r="F71" s="18" t="n">
+        <v>256.83</v>
+      </c>
+      <c r="G71" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="n">
+        <v>907.9</v>
+      </c>
+      <c r="D72" s="14" t="n">
+        <v>896.97</v>
+      </c>
+      <c r="E72" s="14" t="n">
+        <v>879.4400000000001</v>
+      </c>
+      <c r="F72" s="14" t="n">
+        <v>850.52</v>
+      </c>
+      <c r="G72" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B73" s="17" t="inlineStr">
         <is>
           <t>MAHABANK</t>
         </is>
       </c>
-      <c r="C53" s="14" t="n">
-        <v>78.37</v>
-      </c>
-      <c r="D53" s="14" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="E53" s="14" t="n">
-        <v>73.33</v>
-      </c>
-      <c r="F53" s="14" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="G53" s="15">
+      <c r="C73" s="18" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>78.45999999999999</v>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="F73" s="18" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="G73" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 14-May-2026  17:39</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 15-May-2026  17:26</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>12</v>
@@ -712,7 +712,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.8</v>
@@ -721,7 +721,7 @@
         <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.8</v>
+        <v>0.7333</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -734,25 +734,25 @@
         <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.6</v>
+        <v>0.733</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.733</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.511</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -789,63 +789,63 @@
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.4</v>
+        <v>0.3777</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>20</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.35</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -889,22 +889,22 @@
         <v>10</v>
       </c>
       <c r="C11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="E11" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>0.5</v>
-      </c>
       <c r="H11" s="10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I11" s="11" t="n">
         <v>0.3333</v>
@@ -913,94 +913,94 @@
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.333</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>4</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.267</v>
+        <v>0.4</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2223</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1013,7 +1013,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>2</v>
@@ -1022,7 +1022,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>0.167</v>
@@ -1031,7 +1031,7 @@
         <v>0.25</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1947</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1044,25 +1044,25 @@
         <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0.083</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1943</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3259.2</v>
+        <v>3177.2</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2973.03</v>
+        <v>2992.47</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2903.61</v>
+        <v>2914.34</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2750.76</v>
+        <v>2756.04</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>5576.5</v>
+        <v>5486</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>5483.03</v>
+        <v>5483.31</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>5468.64</v>
+        <v>5469.33</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>5420.97</v>
+        <v>5433.94</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1510.9</v>
+        <v>1511.8</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1436.89</v>
+        <v>1444.02</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1364.62</v>
+        <v>1370.39</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1242.02</v>
+        <v>1244.45</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>419</v>
+        <v>430.1</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>379.94</v>
+        <v>384.71</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>373.65</v>
+        <v>375.87</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>370.88</v>
+        <v>371.5</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1436.7</v>
+        <v>1432.1</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1317.49</v>
+        <v>1328.4</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1306.52</v>
+        <v>1311.45</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1395.41</v>
+        <v>1396.37</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CIPLA","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>6921.5</v>
+        <v>6760.5</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>6550.34</v>
+        <v>6570.35</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>6373.43</v>
+        <v>6388.6</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>6313.81</v>
+        <v>6318.17</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1303.6</v>
+        <v>1336.7</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1285.54</v>
+        <v>1290.42</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1275.08</v>
+        <v>1277.5</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1259.26</v>
+        <v>1261.36</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>1898.2</v>
+        <v>1868.3</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>1816.52</v>
+        <v>1821.45</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>1776.97</v>
+        <v>1780.55</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1756.64</v>
+        <v>1757.67</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>2340.6</v>
+        <v>2325.9</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>2316.88</v>
+        <v>2317.74</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>2237.09</v>
+        <v>2240.57</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>2024.18</v>
+        <v>2027.52</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>735.3</v>
+        <v>736.2</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>707.28</v>
+        <v>710.03</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>662.95</v>
+        <v>665.8200000000001</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>587.88</v>
+        <v>590.16</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1583.9</v>
+        <v>1605</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1529.99</v>
+        <v>1537.14</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>1513.45</v>
+        <v>1517.04</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1458.63</v>
+        <v>1459.08</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>2137.8</v>
+        <v>2140.4</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>2088.65</v>
+        <v>2093.58</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>2043.24</v>
+        <v>2047.05</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1882.37</v>
+        <v>1887.07</v>
       </c>
       <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1315.5</v>
+        <v>1323.6</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>1181.34</v>
+        <v>1194.89</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>1113.99</v>
+        <v>1122.21</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>982.11</v>
+        <v>985.3200000000001</v>
       </c>
       <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>2462.2</v>
+        <v>2503</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>2307.75</v>
+        <v>2326.35</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2217.7</v>
+        <v>2228.89</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2267.3</v>
+        <v>2270.08</v>
       </c>
       <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
@@ -1625,16 +1625,16 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1204.4</v>
+        <v>1199.1</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1130.88</v>
+        <v>1137.37</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1062.67</v>
+        <v>1068.02</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>944.03</v>
+        <v>946.23</v>
       </c>
       <c r="G17" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
@@ -1653,16 +1653,16 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>1863.2</v>
+        <v>1878.2</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>1797.18</v>
+        <v>1804.89</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>1761.91</v>
+        <v>1766.47</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1718.54</v>
+        <v>1722.73</v>
       </c>
       <c r="G18" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
@@ -1681,16 +1681,16 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>4403.9</v>
+        <v>4405.7</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>4288.23</v>
+        <v>4299.42</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>4220.52</v>
+        <v>4227.78</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>3909.7</v>
+        <v>3916.27</v>
       </c>
       <c r="G19" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
@@ -1709,16 +1709,16 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>991.7</v>
+        <v>1011.7</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>931.3200000000001</v>
+        <v>938.98</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>918.7</v>
+        <v>922.34</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>924.5</v>
+        <v>925.46</v>
       </c>
       <c r="G20" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>2712.9</v>
+        <v>2716</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>2404.49</v>
+        <v>2434.15</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>2259.14</v>
+        <v>2277.05</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>2271.47</v>
+        <v>2280.66</v>
       </c>
       <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1765,16 +1765,16 @@
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1103.3</v>
+        <v>1067.5</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1039.75</v>
+        <v>1042.4</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>996.8099999999999</v>
+        <v>999.58</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>877.78</v>
+        <v>880.55</v>
       </c>
       <c r="G22" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>606.45</v>
+        <v>570.25</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>558.55</v>
+        <v>559.67</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>542.62</v>
+        <v>543.7</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>448.35</v>
+        <v>449.23</v>
       </c>
       <c r="G23" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>669.25</v>
+        <v>637.8</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>615.26</v>
+        <v>617.4</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>589.86</v>
+        <v>591.74</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>539.41</v>
+        <v>540.54</v>
       </c>
       <c r="G24" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1845,23 +1845,23 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>1252.8</v>
+        <v>1278.8</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>1239.41</v>
+        <v>1261.21</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>1211.47</v>
+        <v>1233.92</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>1109.26</v>
+        <v>1168.2</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1873,23 +1873,23 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>1296.9</v>
+        <v>91.41</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1259.36</v>
+        <v>88.86</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>1232.09</v>
+        <v>85.64</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>1163.04</v>
+        <v>78.36</v>
       </c>
       <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1901,23 +1901,23 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>416.45</v>
+        <v>192.4</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>408.72</v>
+        <v>183.59</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>396.7</v>
+        <v>172.42</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>315.64</v>
+        <v>150.51</v>
       </c>
       <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1929,23 +1929,23 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>93.20999999999999</v>
+        <v>216.84</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>88.59</v>
+        <v>213.15</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>85.40000000000001</v>
+        <v>206.8</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>78.23</v>
+        <v>187.3</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1957,135 +1957,135 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>2888.6</v>
+        <v>1309</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>2697.26</v>
+        <v>1237.44</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>2519.93</v>
+        <v>1084.48</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>2443.92</v>
+        <v>913.12</v>
       </c>
       <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>199.08</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>182.67</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>171.61</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>150.09</v>
-      </c>
-      <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>539.6</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>523.55</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>503.62</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>492.94</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>221.13</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>212.76</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>206.39</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>186.84</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>841.15</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>806.51</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>783.72</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>751.35</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>1367.5</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>1229.9</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>1075.31</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>908.05</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1430.5</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>1424.89</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>1355.37</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>1272.37</v>
+      </c>
+      <c r="G32" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>540.7</v>
+        <v>3499.2</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>521.87</v>
+        <v>3332.29</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>502.15</v>
+        <v>3125.77</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>492.3</v>
+        <v>2954.56</v>
       </c>
       <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>835</v>
+        <v>1234</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>802.87</v>
+        <v>1180.64</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>781.37</v>
+        <v>1147.18</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>750.61</v>
+        <v>1136.43</v>
       </c>
       <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2125,135 +2125,135 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>1459.6</v>
+        <v>503.8</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>1424.3</v>
+        <v>492.61</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>1352.3</v>
+        <v>471.44</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>1269.65</v>
+        <v>468.08</v>
       </c>
       <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>3461</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>3314.72</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>3110.53</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>2947.63</v>
-      </c>
-      <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>1142.6</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>1028.2</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>1228.3</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>1175.02</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>1143.64</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>1133.24</v>
-      </c>
-      <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>221.33</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>213.71</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>191.54</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>155.73</v>
+      </c>
+      <c r="G37" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>505.15</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>491.43</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>470.12</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>468.01</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>398.3</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>326.62</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>279.84</v>
+      </c>
+      <c r="G38" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
-        <v>1319.1</v>
+        <v>838.2</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>1310.19</v>
+        <v>820.59</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>1198.37</v>
+        <v>771.47</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>1025.93</v>
+        <v>712.1900000000001</v>
       </c>
       <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2265,23 +2265,23 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>1414.9</v>
+        <v>462.2</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>1266.81</v>
+        <v>461.16</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>1132.96</v>
+        <v>451.87</v>
       </c>
       <c r="F40" s="18" t="n">
-        <v>1024.62</v>
+        <v>415.87</v>
       </c>
       <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2293,23 +2293,23 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="C41" s="18" t="n">
-        <v>224.49</v>
+        <v>19.54</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>212.91</v>
+        <v>18.58</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>190.33</v>
+        <v>17.62</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>155.01</v>
+        <v>17.05</v>
       </c>
       <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2321,23 +2321,23 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>413.15</v>
+        <v>352.8</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>365.74</v>
+        <v>320.14</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>323.69</v>
+        <v>296.82</v>
       </c>
       <c r="F42" s="18" t="n">
-        <v>278.13</v>
+        <v>264.2</v>
       </c>
       <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2349,23 +2349,23 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C43" s="18" t="n">
-        <v>184.46</v>
+        <v>395.25</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>180.71</v>
+        <v>395.08</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>171.74</v>
+        <v>386.28</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>164.78</v>
+        <v>357.45</v>
       </c>
       <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2377,23 +2377,23 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>848.25</v>
+        <v>32535</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>818.74</v>
+        <v>31934.03</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>768.75</v>
+        <v>28996.93</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>710.49</v>
+        <v>23004.8</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2405,23 +2405,23 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>370.9</v>
+        <v>1264.3</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>316.7</v>
+        <v>1223.97</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>294.53</v>
+        <v>1084.51</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>263.12</v>
+        <v>882.23</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>396.3</v>
+        <v>53.84</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>395.06</v>
+        <v>52.95</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>385.91</v>
+        <v>50.09</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>356.79</v>
+        <v>52.07</v>
       </c>
       <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2461,23 +2461,23 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>32290</v>
+        <v>4500.4</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>31870.77</v>
+        <v>4228.76</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>28852.57</v>
+        <v>3836.39</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>23005.57</v>
+        <v>3394.45</v>
       </c>
       <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2489,723 +2489,527 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>1315</v>
+        <v>606.95</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1219.72</v>
+        <v>562.02</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>1077.17</v>
+        <v>530.59</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>877.51</v>
+        <v>528.78</v>
       </c>
       <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="n">
-        <v>3693.8</v>
-      </c>
-      <c r="D49" s="18" t="n">
-        <v>3671.75</v>
-      </c>
-      <c r="E49" s="18" t="n">
-        <v>3502.91</v>
-      </c>
-      <c r="F49" s="18" t="n">
-        <v>3259.23</v>
-      </c>
-      <c r="G49" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>10377.5</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>10112.31</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>9793.780000000001</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>9260.309999999999</v>
+      </c>
+      <c r="G49" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="n">
-        <v>53.47</v>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="E50" s="18" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="F50" s="18" t="n">
-        <v>51.94</v>
-      </c>
-      <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>1913.1</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>1899.63</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>1822.19</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>1563.79</v>
+      </c>
+      <c r="G50" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="n">
-        <v>4597.7</v>
-      </c>
-      <c r="D51" s="18" t="n">
-        <v>4200.17</v>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>3809.28</v>
-      </c>
-      <c r="F51" s="18" t="n">
-        <v>3381.27</v>
-      </c>
-      <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="n">
+        <v>37740</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>36620.51</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>35703.78</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>35552.44</v>
+      </c>
+      <c r="G51" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="n">
-        <v>578.55</v>
-      </c>
-      <c r="D52" s="18" t="n">
-        <v>557.29</v>
-      </c>
-      <c r="E52" s="18" t="n">
-        <v>527.47</v>
-      </c>
-      <c r="F52" s="18" t="n">
-        <v>524.61</v>
-      </c>
-      <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="n">
+        <v>129.92</v>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>125.24</v>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>114.43</v>
+      </c>
+      <c r="G52" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>HFCL</t>
         </is>
       </c>
-      <c r="C53" s="14" t="n">
-        <v>151.59</v>
-      </c>
-      <c r="D53" s="14" t="n">
-        <v>125.07</v>
-      </c>
-      <c r="E53" s="14" t="n">
-        <v>102.18</v>
-      </c>
-      <c r="F53" s="14" t="n">
-        <v>82.45999999999999</v>
-      </c>
-      <c r="G53" s="15">
+      <c r="C53" s="18" t="n">
+        <v>147.89</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>103.97</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="G53" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>IDEA</t>
         </is>
       </c>
-      <c r="C54" s="14" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>10.97</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="G54" s="15">
+      <c r="C54" s="18" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="F54" s="18" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="G54" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>INDUSTOWER</t>
         </is>
       </c>
-      <c r="C55" s="14" t="n">
-        <v>422.35</v>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>411.7</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>420.01</v>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>412.15</v>
-      </c>
-      <c r="G55" s="15">
+      <c r="C55" s="18" t="n">
+        <v>430.15</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>413.46</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>420.4</v>
+      </c>
+      <c r="F55" s="18" t="n">
+        <v>412.4</v>
+      </c>
+      <c r="G55" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="16" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="C56" s="14" t="n">
-        <v>8904.5</v>
-      </c>
-      <c r="D56" s="14" t="n">
-        <v>8790.24</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>8048.86</v>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>7783.56</v>
-      </c>
-      <c r="G56" s="15">
+      <c r="C56" s="18" t="n">
+        <v>9015</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>8811.639999999999</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>8086.75</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <v>7799.51</v>
+      </c>
+      <c r="G56" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>TATACOMM</t>
         </is>
       </c>
-      <c r="C57" s="14" t="n">
-        <v>1656.1</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>1563.86</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>1550.68</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>1626.75</v>
-      </c>
-      <c r="G57" s="15">
+      <c r="C57" s="18" t="n">
+        <v>1680</v>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>1574.92</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>1555.76</v>
+      </c>
+      <c r="F57" s="18" t="n">
+        <v>1628.19</v>
+      </c>
+      <c r="G57" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="n">
+        <v>8476.5</v>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>8143.45</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>7689.48</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>7234.06</v>
+      </c>
+      <c r="G58" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="n">
+        <v>5635.5</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>5504.49</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>5273.45</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>5511.15</v>
+      </c>
+      <c r="G59" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="n">
+        <v>301.95</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>277.04</v>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>264.19</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>273.97</v>
+      </c>
+      <c r="G60" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>299.95</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>268.47</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>262.31</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>271.61</v>
+      </c>
+      <c r="G61" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>415.75</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>354.18</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>346.71</v>
+      </c>
+      <c r="F62" s="18" t="n">
+        <v>390.22</v>
+      </c>
+      <c r="G62" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>646.65</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>629.9400000000001</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>593.7</v>
+      </c>
+      <c r="F63" s="18" t="n">
+        <v>568.6799999999999</v>
+      </c>
+      <c r="G63" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n">
-        <v>560.4</v>
-      </c>
-      <c r="D58" s="18" t="n">
-        <v>560.2</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>542.4</v>
-      </c>
-      <c r="F58" s="18" t="n">
-        <v>547.9</v>
-      </c>
-      <c r="G58" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C59" s="18" t="n">
-        <v>3339.1</v>
-      </c>
-      <c r="D59" s="18" t="n">
-        <v>2988.43</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>2770.8</v>
-      </c>
-      <c r="F59" s="18" t="n">
-        <v>2239.8</v>
-      </c>
-      <c r="G59" s="19">
+      <c r="C64" s="14" t="n">
+        <v>3391</v>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>3026.77</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>2795.12</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>2251.29</v>
+      </c>
+      <c r="G64" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>MUTHOOTFIN</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="n">
-        <v>3531.1</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>3476.35</v>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>3464.83</v>
-      </c>
-      <c r="F60" s="18" t="n">
-        <v>3290.19</v>
-      </c>
-      <c r="G60" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>PFC</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n">
-        <v>451.45</v>
-      </c>
-      <c r="D61" s="18" t="n">
-        <v>450.98</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>434.62</v>
-      </c>
-      <c r="F61" s="18" t="n">
-        <v>401.67</v>
-      </c>
-      <c r="G61" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PFC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
-        <v>8288.5</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>8108.39</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>7657.36</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>7217.85</v>
-      </c>
-      <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>CERA</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n">
-        <v>5689.5</v>
-      </c>
-      <c r="D63" s="14" t="n">
-        <v>5490.7</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>5258.68</v>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>5511.1</v>
-      </c>
-      <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>288.95</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>274.42</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>262.65</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>274.02</v>
-      </c>
-      <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C65" s="18" t="n">
-        <v>635.15</v>
+        <v>518.3</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>628.1799999999999</v>
+        <v>483.07</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>591.53</v>
+        <v>475.04</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>568.46</v>
+        <v>446.3</v>
       </c>
       <c r="G65" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="n">
-        <v>10451</v>
-      </c>
-      <c r="D66" s="14" t="n">
-        <v>10084.4</v>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>9769.950000000001</v>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>9231.01</v>
-      </c>
-      <c r="G66" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="n">
-        <v>1948.9</v>
-      </c>
-      <c r="D67" s="14" t="n">
-        <v>1898.22</v>
-      </c>
-      <c r="E67" s="14" t="n">
-        <v>1818.48</v>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>1560.32</v>
-      </c>
-      <c r="G67" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="n">
-        <v>36945</v>
-      </c>
-      <c r="D68" s="14" t="n">
-        <v>36502.67</v>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v>35620.65</v>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>35504.84</v>
-      </c>
-      <c r="G68" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="n">
-        <v>126.11</v>
-      </c>
-      <c r="D69" s="14" t="n">
-        <v>124.75</v>
-      </c>
-      <c r="E69" s="14" t="n">
-        <v>122.09</v>
-      </c>
-      <c r="F69" s="14" t="n">
-        <v>114.13</v>
-      </c>
-      <c r="G69" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="n">
-        <v>517.55</v>
-      </c>
-      <c r="D70" s="18" t="n">
-        <v>479.37</v>
-      </c>
-      <c r="E70" s="18" t="n">
-        <v>473.27</v>
-      </c>
-      <c r="F70" s="18" t="n">
-        <v>445.28</v>
-      </c>
-      <c r="G70" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
       </c>
-      <c r="C71" s="18" t="n">
-        <v>300.9</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>289.35</v>
-      </c>
-      <c r="E71" s="18" t="n">
-        <v>281.63</v>
-      </c>
-      <c r="F71" s="18" t="n">
-        <v>256.83</v>
-      </c>
-      <c r="G71" s="19">
+      <c r="C66" s="18" t="n">
+        <v>299.35</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>290.3</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>282.32</v>
+      </c>
+      <c r="F66" s="18" t="n">
+        <v>257.38</v>
+      </c>
+      <c r="G66" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="n">
-        <v>907.9</v>
-      </c>
-      <c r="D72" s="14" t="n">
-        <v>896.97</v>
-      </c>
-      <c r="E72" s="14" t="n">
-        <v>879.4400000000001</v>
-      </c>
-      <c r="F72" s="14" t="n">
-        <v>850.52</v>
-      </c>
-      <c r="G72" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="D73" s="18" t="n">
-        <v>78.45999999999999</v>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>73.78</v>
-      </c>
-      <c r="F73" s="18" t="n">
-        <v>64.05</v>
-      </c>
-      <c r="G73" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 15-May-2026  17:26</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 18-May-2026  18:26</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>19</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.95</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9167000000000001</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,25 +703,25 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>12</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.6</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.7333</v>
+        <v>0.6887000000000001</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -734,25 +734,25 @@
         <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.733</v>
+        <v>0.667</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.622</v>
+        <v>0.5557</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -765,41 +765,41 @@
         <v>40</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>22</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.475</v>
+        <v>0.45</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>0.55</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4583</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>5</v>
@@ -808,106 +808,106 @@
         <v>0.4</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3777</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.35</v>
+        <v>0.267</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3667</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.3333</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -920,56 +920,56 @@
         <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="E13" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="F13" s="10" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G13" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="H13" s="10" t="n">
         <v>0.267</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="I13" s="11" t="n">
         <v>0.2</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>0.2223</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -982,22 +982,22 @@
         <v>10</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.1667</v>
@@ -1050,7 +1050,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0</v>
@@ -1059,10 +1059,10 @@
         <v>0.083</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.25</v>
+        <v>0.083</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.111</v>
+        <v>0.0553</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1075,7 +1075,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0</v>
+        <v>0.0333</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3177.2</v>
+        <v>3214.1</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2992.47</v>
+        <v>3013.58</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2914.34</v>
+        <v>2926.09</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2756.04</v>
+        <v>2763.04</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>5486</v>
+        <v>1500.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>5483.31</v>
+        <v>1449.4</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>5469.33</v>
+        <v>1375.49</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>5433.94</v>
+        <v>1246.09</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1511.8</v>
+        <v>426.25</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1444.02</v>
+        <v>388.67</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1370.39</v>
+        <v>377.84</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1244.45</v>
+        <v>372.3</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>430.1</v>
+        <v>1426.2</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>384.71</v>
+        <v>1337.72</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>375.87</v>
+        <v>1315.95</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>371.5</v>
+        <v>1395.8</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CIPLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1432.1</v>
+        <v>6835</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1328.4</v>
+        <v>6595.56</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1311.45</v>
+        <v>6406.13</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1396.37</v>
+        <v>6353.73</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CIPLA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>6760.5</v>
+        <v>1331.2</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>6570.35</v>
+        <v>1294.3</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>6388.6</v>
+        <v>1279.6</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>6318.17</v>
+        <v>1260.63</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1336.7</v>
+        <v>2156.6</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1290.42</v>
+        <v>1853.37</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1277.5</v>
+        <v>1795.3</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1261.36</v>
+        <v>1763.59</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>1868.3</v>
+        <v>2339.9</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>1821.45</v>
+        <v>2319.85</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>1780.55</v>
+        <v>2244.47</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1757.67</v>
+        <v>2029.92</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>2325.9</v>
+        <v>731.45</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>2317.74</v>
+        <v>712.0700000000001</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>2240.57</v>
+        <v>668.39</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>2027.52</v>
+        <v>592.33</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>736.2</v>
+        <v>1646.3</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>710.03</v>
+        <v>1547.53</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>665.8200000000001</v>
+        <v>1522.11</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>590.16</v>
+        <v>1463.51</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,23 +1509,23 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>JBCHEPHARM</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1605</v>
+        <v>2125.3</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1537.14</v>
+        <v>2096.6</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>1517.04</v>
+        <v>2050.12</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1459.08</v>
+        <v>1891.48</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,23 +1537,23 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>2140.4</v>
+        <v>1327.3</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>2093.58</v>
+        <v>1207.5</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>2047.05</v>
+        <v>1130.25</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1887.07</v>
+        <v>989.03</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1323.6</v>
+        <v>2495.7</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>1194.89</v>
+        <v>2342.48</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>1122.21</v>
+        <v>2239.36</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>985.3200000000001</v>
+        <v>2272.68</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>2503</v>
+        <v>1165.6</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>2326.35</v>
+        <v>1140.06</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2228.89</v>
+        <v>1071.85</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2270.08</v>
+        <v>951.89</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1199.1</v>
+        <v>1905.8</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1137.37</v>
+        <v>1814.5</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1068.02</v>
+        <v>1771.94</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>946.23</v>
+        <v>1723.74</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,23 +1649,23 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>1878.2</v>
+        <v>4393.7</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>1804.89</v>
+        <v>4308.4</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>1766.47</v>
+        <v>4234.29</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1722.73</v>
+        <v>3924.13</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,79 +1677,79 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>4405.7</v>
+        <v>991.1</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>4299.42</v>
+        <v>943.9400000000001</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>4227.78</v>
+        <v>925.04</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>3916.27</v>
+        <v>926.66</v>
       </c>
       <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>1011.7</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>938.98</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>922.34</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>925.46</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>2689.8</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>2458.5</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>2293.24</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>2286.41</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>2716</v>
+        <v>1053.1</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>2434.15</v>
+        <v>1043.42</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>2277.05</v>
+        <v>1001.68</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>2280.66</v>
+        <v>882.02</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1067.5</v>
+        <v>581.15</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1042.4</v>
+        <v>561.71</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>999.58</v>
+        <v>545.17</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>880.55</v>
+        <v>450.45</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>570.25</v>
+        <v>636.5</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>559.67</v>
+        <v>619.22</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>543.7</v>
+        <v>593.49</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>449.23</v>
+        <v>542.08</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,23 +1817,23 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>637.8</v>
+        <v>1292.8</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>617.4</v>
+        <v>1264.22</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>591.74</v>
+        <v>1236.23</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>540.54</v>
+        <v>1167.91</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1845,23 +1845,23 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>1278.8</v>
+        <v>90.14</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>1261.21</v>
+        <v>88.98</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>1233.92</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>1168.2</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1873,23 +1873,23 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>91.41</v>
+        <v>192.73</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>88.86</v>
+        <v>184.46</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>85.64</v>
+        <v>173.22</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>78.36</v>
+        <v>150.88</v>
       </c>
       <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1901,107 +1901,107 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>192.4</v>
+        <v>1297.9</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>183.59</v>
+        <v>1243.19</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>172.42</v>
+        <v>1092.85</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>150.51</v>
+        <v>917.13</v>
       </c>
       <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>216.84</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>213.15</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>206.8</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>187.3</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>541.1</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>525.23</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>505.09</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>493.24</v>
+      </c>
+      <c r="G28" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>1309</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>1237.44</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>1084.48</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>913.12</v>
-      </c>
-      <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>833.75</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>809.11</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>785.6799999999999</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>751.84</v>
+      </c>
+      <c r="G29" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>539.6</v>
+        <v>1431.7</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>523.55</v>
+        <v>1425.54</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>503.62</v>
+        <v>1358.36</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>492.94</v>
+        <v>1274.35</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>841.15</v>
+        <v>3471.4</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>806.51</v>
+        <v>3345.54</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>783.72</v>
+        <v>3139.33</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>751.35</v>
+        <v>2959.61</v>
       </c>
       <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2041,23 +2041,23 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>1430.5</v>
+        <v>1231</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>1424.89</v>
+        <v>1185.43</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>1355.37</v>
+        <v>1150.47</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>1272.37</v>
+        <v>1137.53</v>
       </c>
       <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2069,107 +2069,107 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>3499.2</v>
+        <v>511.5</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>3332.29</v>
+        <v>494.41</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>3125.77</v>
+        <v>473.01</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>2954.56</v>
+        <v>467.54</v>
       </c>
       <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>1234</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>1180.64</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>1147.18</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>1136.43</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>1328.3</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>1311.35</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>1207.43</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>1031.47</v>
+      </c>
+      <c r="G34" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>503.8</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>492.61</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>471.44</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>468.08</v>
-      </c>
-      <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>1369</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>1286.21</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>1151.48</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>1035.37</v>
+      </c>
+      <c r="G35" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>1379</v>
+        <v>219.3</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>1277.5</v>
+        <v>214.24</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>1142.6</v>
+        <v>192.63</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>1028.2</v>
+        <v>156.67</v>
       </c>
       <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2181,23 +2181,23 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
-        <v>221.33</v>
+        <v>395.25</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>213.71</v>
+        <v>371.36</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>191.54</v>
+        <v>329.31</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>155.73</v>
+        <v>280.83</v>
       </c>
       <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2209,23 +2209,23 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
-        <v>398.3</v>
+        <v>462.1</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>368.84</v>
+        <v>461.25</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>326.62</v>
+        <v>452.27</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>279.84</v>
+        <v>416.18</v>
       </c>
       <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2237,23 +2237,23 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
-        <v>838.2</v>
+        <v>4426.8</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>820.59</v>
+        <v>4376.04</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>771.47</v>
+        <v>4116.31</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>712.1900000000001</v>
+        <v>3351.9</v>
       </c>
       <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2265,23 +2265,23 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="C40" s="18" t="n">
-        <v>462.2</v>
+        <v>19.05</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>461.16</v>
+        <v>18.62</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>451.87</v>
+        <v>17.67</v>
       </c>
       <c r="F40" s="18" t="n">
-        <v>415.87</v>
+        <v>17.1</v>
       </c>
       <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2293,23 +2293,23 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C41" s="18" t="n">
-        <v>19.54</v>
+        <v>348.15</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>18.58</v>
+        <v>322.8</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>17.62</v>
+        <v>298.83</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>17.05</v>
+        <v>265.28</v>
       </c>
       <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2321,23 +2321,23 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C42" s="18" t="n">
-        <v>352.8</v>
+        <v>32800</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>320.14</v>
+        <v>32016.51</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>296.82</v>
+        <v>29146.09</v>
       </c>
       <c r="F42" s="18" t="n">
-        <v>264.2</v>
+        <v>23136.88</v>
       </c>
       <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2349,23 +2349,23 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C43" s="18" t="n">
-        <v>395.25</v>
+        <v>53.25</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>395.08</v>
+        <v>52.98</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>386.28</v>
+        <v>50.22</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>357.45</v>
+        <v>52.1</v>
       </c>
       <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NTPC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2377,23 +2377,23 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>32535</v>
+        <v>4393.3</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>31934.03</v>
+        <v>4244.43</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>28996.93</v>
+        <v>3858.23</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>23004.8</v>
+        <v>3411.32</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2405,611 +2405,499 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C45" s="18" t="n">
-        <v>1264.3</v>
+        <v>596.65</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>1223.97</v>
+        <v>565.3099999999999</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>1084.51</v>
+        <v>533.1799999999999</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>882.23</v>
+        <v>528.24</v>
       </c>
       <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>53.84</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>50.09</v>
-      </c>
-      <c r="F46" s="18" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>139.69</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>128.43</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>105.38</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>84.01000000000001</v>
+      </c>
+      <c r="G46" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>4500.4</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>4228.76</v>
-      </c>
-      <c r="E47" s="18" t="n">
-        <v>3836.39</v>
-      </c>
-      <c r="F47" s="18" t="n">
-        <v>3394.45</v>
-      </c>
-      <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="G47" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="n">
-        <v>606.95</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>562.02</v>
-      </c>
-      <c r="E48" s="18" t="n">
-        <v>530.59</v>
-      </c>
-      <c r="F48" s="18" t="n">
-        <v>528.78</v>
-      </c>
-      <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>430.9</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>415.12</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>420.82</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>411.93</v>
+      </c>
+      <c r="G48" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C49" s="14" t="n">
-        <v>10377.5</v>
+        <v>9408.5</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>10112.31</v>
+        <v>8868.49</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>9793.780000000001</v>
+        <v>8138.58</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>9260.309999999999</v>
+        <v>7820.96</v>
       </c>
       <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>1668.4</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>1583.82</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>1560.17</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>1630.9</v>
+      </c>
+      <c r="G50" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n">
-        <v>1913.1</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>1899.63</v>
-      </c>
-      <c r="E50" s="14" t="n">
-        <v>1822.19</v>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>1563.79</v>
-      </c>
-      <c r="G50" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>10198.5</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>10120.52</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>9809.68</v>
+      </c>
+      <c r="F51" s="18" t="n">
+        <v>9311.969999999999</v>
+      </c>
+      <c r="G51" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>BOSCHLTD</t>
         </is>
       </c>
-      <c r="C51" s="14" t="n">
-        <v>37740</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>36620.51</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>35703.78</v>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>35552.44</v>
-      </c>
-      <c r="G51" s="15">
+      <c r="C52" s="18" t="n">
+        <v>37155</v>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>36671.41</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>35760.68</v>
+      </c>
+      <c r="F52" s="18" t="n">
+        <v>35554.4</v>
+      </c>
+      <c r="G52" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>MOTHERSON</t>
         </is>
       </c>
-      <c r="C52" s="14" t="n">
-        <v>129.92</v>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>125.24</v>
-      </c>
-      <c r="E52" s="14" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="F52" s="14" t="n">
-        <v>114.43</v>
-      </c>
-      <c r="G52" s="15">
+      <c r="C53" s="18" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>125.57</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>122.65</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <v>114.79</v>
+      </c>
+      <c r="G53" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="n">
-        <v>147.89</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>103.97</v>
-      </c>
-      <c r="F53" s="18" t="n">
-        <v>83.48</v>
-      </c>
-      <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="D54" s="18" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="E54" s="18" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="F54" s="18" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="n">
+        <v>298.95</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>271.37</v>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>263.75</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>272.29</v>
+      </c>
+      <c r="G54" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>INDUSTOWER</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="n">
-        <v>430.15</v>
-      </c>
-      <c r="D55" s="18" t="n">
-        <v>413.46</v>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>420.4</v>
-      </c>
-      <c r="F55" s="18" t="n">
-        <v>412.4</v>
-      </c>
-      <c r="G55" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="n">
+        <v>392.35</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>357.82</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>388.22</v>
+      </c>
+      <c r="G55" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="n">
-        <v>9015</v>
-      </c>
-      <c r="D56" s="18" t="n">
-        <v>8811.639999999999</v>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>8086.75</v>
-      </c>
-      <c r="F56" s="18" t="n">
-        <v>7799.51</v>
-      </c>
-      <c r="G56" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>630.98</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>595.54</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>568.9400000000001</v>
+      </c>
+      <c r="G56" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C57" s="18" t="n">
-        <v>1680</v>
+        <v>506.05</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>1574.92</v>
+        <v>485.26</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>1555.76</v>
+        <v>476.25</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>1628.19</v>
+        <v>446.93</v>
       </c>
       <c r="G57" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>290.96</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>282.91</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>257.7</v>
+      </c>
+      <c r="G58" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="n">
+        <v>3348.4</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>3057.4</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>2816.82</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>2266.66</v>
+      </c>
+      <c r="G59" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>8476.5</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>8143.45</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>7689.48</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>7234.06</v>
-      </c>
-      <c r="G58" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>5558.5</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>5509.63</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>5284.63</v>
+      </c>
+      <c r="F60" s="18" t="n">
+        <v>5513.44</v>
+      </c>
+      <c r="G60" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>CERA</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n">
-        <v>5635.5</v>
-      </c>
-      <c r="D59" s="14" t="n">
-        <v>5504.49</v>
-      </c>
-      <c r="E59" s="14" t="n">
-        <v>5273.45</v>
-      </c>
-      <c r="F59" s="14" t="n">
-        <v>5511.15</v>
-      </c>
-      <c r="G59" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
         <is>
           <t>CROMPTON</t>
         </is>
       </c>
-      <c r="C60" s="14" t="n">
-        <v>301.95</v>
-      </c>
-      <c r="D60" s="14" t="n">
-        <v>277.04</v>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v>264.19</v>
-      </c>
-      <c r="F60" s="14" t="n">
-        <v>273.97</v>
-      </c>
-      <c r="G60" s="15">
+      <c r="C61" s="18" t="n">
+        <v>293.3</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>278.59</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>265.33</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>276.11</v>
+      </c>
+      <c r="G61" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n">
-        <v>299.95</v>
-      </c>
-      <c r="D61" s="18" t="n">
-        <v>268.47</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>262.31</v>
-      </c>
-      <c r="F61" s="18" t="n">
-        <v>271.61</v>
-      </c>
-      <c r="G61" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="n">
-        <v>415.75</v>
-      </c>
-      <c r="D62" s="18" t="n">
-        <v>354.18</v>
-      </c>
-      <c r="E62" s="18" t="n">
-        <v>346.71</v>
-      </c>
-      <c r="F62" s="18" t="n">
-        <v>390.22</v>
-      </c>
-      <c r="G62" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="n">
-        <v>646.65</v>
-      </c>
-      <c r="D63" s="18" t="n">
-        <v>629.9400000000001</v>
-      </c>
-      <c r="E63" s="18" t="n">
-        <v>593.7</v>
-      </c>
-      <c r="F63" s="18" t="n">
-        <v>568.6799999999999</v>
-      </c>
-      <c r="G63" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>3391</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>3026.77</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>2795.12</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>2251.29</v>
-      </c>
-      <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="n">
-        <v>518.3</v>
-      </c>
-      <c r="D65" s="18" t="n">
-        <v>483.07</v>
-      </c>
-      <c r="E65" s="18" t="n">
-        <v>475.04</v>
-      </c>
-      <c r="F65" s="18" t="n">
-        <v>446.3</v>
-      </c>
-      <c r="G65" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="C66" s="18" t="n">
-        <v>299.35</v>
-      </c>
-      <c r="D66" s="18" t="n">
-        <v>290.3</v>
-      </c>
-      <c r="E66" s="18" t="n">
-        <v>282.32</v>
-      </c>
-      <c r="F66" s="18" t="n">
-        <v>257.38</v>
-      </c>
-      <c r="G66" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>502.55</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>464.26</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>435.24</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>477.47</v>
+      </c>
+      <c r="G62" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 18-May-2026  18:26</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 19-May-2026  14:08</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>19</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.95</v>
@@ -706,7 +706,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>12</v>
@@ -715,13 +715,13 @@
         <v>0.5329999999999999</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.733</v>
+        <v>0.8</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.6887000000000001</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -737,208 +737,208 @@
         <v>9</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.667</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.5557</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F7" s="10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H7" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>0.55</v>
-      </c>
       <c r="I7" s="11" t="n">
-        <v>0.4333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.45</v>
+        <v>0.475</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3667</v>
+        <v>0.4417</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3333</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>6</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2667</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="E12" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -951,56 +951,56 @@
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0.267</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.2</v>
+        <v>0.2447</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1667</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1037,63 +1037,63 @@
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>0.083</v>
-      </c>
       <c r="I16" s="7" t="n">
-        <v>0.0553</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="E17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>0.1</v>
-      </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0333</v>
+        <v>0.0553</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3214.1</v>
+        <v>3248.2</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3013.58</v>
+        <v>3035.92</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2926.09</v>
+        <v>2938.72</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2763.04</v>
+        <v>2767.86</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1500.5</v>
+        <v>1512.8</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1449.4</v>
+        <v>1455.44</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1375.49</v>
+        <v>1380.88</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1246.09</v>
+        <v>1248.74</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>426.25</v>
+        <v>428.15</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>388.67</v>
+        <v>392.43</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>377.84</v>
+        <v>379.82</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>372.3</v>
+        <v>372.85</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1426.2</v>
+        <v>1409.8</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1337.72</v>
+        <v>1344.58</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1315.95</v>
+        <v>1319.63</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1395.8</v>
+        <v>1395.94</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CIPLA","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>6835</v>
+        <v>6912</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6595.56</v>
+        <v>6625.7</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>6406.13</v>
+        <v>6425.97</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>6353.73</v>
+        <v>6359.28</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1331.2</v>
+        <v>1335.2</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1294.3</v>
+        <v>1298.2</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1279.6</v>
+        <v>1281.78</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1260.63</v>
+        <v>1261.37</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2156.6</v>
+        <v>2251.1</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1853.37</v>
+        <v>1891.25</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1795.3</v>
+        <v>1813.17</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1763.59</v>
+        <v>1768.44</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2339.9</v>
+        <v>2405.9</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2319.85</v>
+        <v>2328.04</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2244.47</v>
+        <v>2250.8</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>2029.92</v>
+        <v>2033.66</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>731.45</v>
+        <v>766.45</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>712.0700000000001</v>
+        <v>717.25</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>668.39</v>
+        <v>672.24</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>592.33</v>
+        <v>594.0599999999999</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>1646.3</v>
+        <v>1656.2</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>1547.53</v>
+        <v>1557.88</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>1522.11</v>
+        <v>1527.37</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1463.51</v>
+        <v>1465.43</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>2125.3</v>
+        <v>2171.6</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>2096.6</v>
+        <v>2103.75</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>2050.12</v>
+        <v>2054.88</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1891.48</v>
+        <v>1894.26</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1327.3</v>
+        <v>1344.9</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>1207.5</v>
+        <v>1220.58</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>1130.25</v>
+        <v>1138.67</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>989.03</v>
+        <v>992.5700000000001</v>
       </c>
       <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>2495.7</v>
+        <v>2492.6</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>2342.48</v>
+        <v>2356.78</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>2239.36</v>
+        <v>2249.29</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>2272.68</v>
+        <v>2274.86</v>
       </c>
       <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>1165.6</v>
+        <v>1882.3</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>1140.06</v>
+        <v>1820.96</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>1071.85</v>
+        <v>1776.26</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>951.89</v>
+        <v>1725.32</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1905.8</v>
+        <v>4460.1</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1814.5</v>
+        <v>4322.84</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1771.94</v>
+        <v>4243.14</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1723.74</v>
+        <v>3929.46</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,79 +1649,79 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>4393.7</v>
+        <v>1018.9</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>4308.4</v>
+        <v>951.08</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>4234.29</v>
+        <v>928.72</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>3924.13</v>
+        <v>927.5700000000001</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>991.1</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>943.9400000000001</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>925.04</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>926.66</v>
-      </c>
-      <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>2725</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>2483.88</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>2310.17</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>2290.78</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>2689.8</v>
+        <v>1048.3</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>2458.5</v>
+        <v>1043.88</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>2293.24</v>
+        <v>1003.51</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>2286.41</v>
+        <v>883.6799999999999</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1733,23 +1733,23 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>1053.1</v>
+        <v>569.5</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>1043.42</v>
+        <v>562.45</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>1001.68</v>
+        <v>546.12</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>882.02</v>
+        <v>451.64</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>581.15</v>
+        <v>632.6</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>561.71</v>
+        <v>620.5</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>545.17</v>
+        <v>595.03</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>450.45</v>
+        <v>542.98</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>636.5</v>
+        <v>1285.2</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>619.22</v>
+        <v>1266.22</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>593.49</v>
+        <v>1238.15</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>542.08</v>
+        <v>1169.07</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,23 +1817,23 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>1292.8</v>
+        <v>89.02</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1264.22</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>1236.23</v>
+        <v>85.94</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>1167.91</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1845,23 +1845,23 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>90.14</v>
+        <v>199.05</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>88.98</v>
+        <v>185.85</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>85.81999999999999</v>
+        <v>174.23</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>78.48999999999999</v>
+        <v>151.36</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1873,79 +1873,79 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>192.73</v>
+        <v>1280.7</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>184.46</v>
+        <v>1246.77</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>173.22</v>
+        <v>1100.21</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>150.88</v>
+        <v>920.75</v>
       </c>
       <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>1297.9</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>1243.19</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>1092.85</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>917.13</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>550.45</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>527.63</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>506.87</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>493.81</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>541.1</v>
+        <v>2188.3</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>525.23</v>
+        <v>2129.1</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>505.09</v>
+        <v>2091.49</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>493.24</v>
+        <v>2176.38</v>
       </c>
       <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COLPAL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>833.75</v>
+        <v>831.45</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>809.11</v>
+        <v>811.24</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>785.6799999999999</v>
+        <v>787.47</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>751.84</v>
+        <v>752.63</v>
       </c>
       <c r="G29" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>1431.7</v>
+        <v>1431.4</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>1425.54</v>
+        <v>1426.09</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>1358.36</v>
+        <v>1361.23</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>1274.35</v>
+        <v>1275.92</v>
       </c>
       <c r="G30" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
@@ -2017,16 +2017,16 @@
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>3471.4</v>
+        <v>3599.9</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>3345.54</v>
+        <v>3369.77</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>3139.33</v>
+        <v>3157.39</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>2959.61</v>
+        <v>2965.98</v>
       </c>
       <c r="G31" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
@@ -2045,16 +2045,16 @@
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>1231</v>
+        <v>1210.9</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>1185.43</v>
+        <v>1187.86</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>1150.47</v>
+        <v>1152.84</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>1137.53</v>
+        <v>1138.26</v>
       </c>
       <c r="G32" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
@@ -2073,16 +2073,16 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>511.5</v>
+        <v>514.8</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>494.41</v>
+        <v>496.35</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>473.01</v>
+        <v>474.65</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>467.54</v>
+        <v>468.01</v>
       </c>
       <c r="G33" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
@@ -2092,812 +2092,868 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>1328.3</v>
+        <v>138.17</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>1311.35</v>
+        <v>129.36</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>1207.43</v>
+        <v>106.66</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>1031.47</v>
+        <v>84.55</v>
       </c>
       <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C35" s="18" t="n">
-        <v>1369</v>
+        <v>13.52</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>1286.21</v>
+        <v>11.53</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>1151.48</v>
+        <v>10.68</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>1035.37</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>219.3</v>
+        <v>430.7</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>214.24</v>
+        <v>416.6</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>192.63</v>
+        <v>421.2</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>156.67</v>
+        <v>412.12</v>
       </c>
       <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
-        <v>395.25</v>
+        <v>9646</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>371.36</v>
+        <v>8942.540000000001</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>329.31</v>
+        <v>8197.700000000001</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>280.83</v>
+        <v>7839.12</v>
       </c>
       <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
-        <v>462.1</v>
+        <v>1646.6</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>461.25</v>
+        <v>1589.8</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>452.27</v>
+        <v>1563.56</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>416.18</v>
+        <v>1631.06</v>
       </c>
       <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>668.55</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>611.65</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>595.95</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>637.09</v>
+      </c>
+      <c r="G39" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>1329.5</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>1313.07</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>1212.22</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>1034.44</v>
+      </c>
+      <c r="G40" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>1377.8</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>1294.93</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>1160.36</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>1038.78</v>
+      </c>
+      <c r="G41" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>219.09</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>214.7</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>193.67</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>157.29</v>
+      </c>
+      <c r="G42" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>401.1</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>374.19</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>332.13</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>282.03</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>181.06</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>180.32</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>172.58</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>165.59</v>
+      </c>
+      <c r="G44" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>GVT&amp;D</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n">
-        <v>4426.8</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>4376.04</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>4116.31</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>3351.9</v>
-      </c>
-      <c r="G39" s="19">
+      <c r="C45" s="14" t="n">
+        <v>4385.3</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>4376.92</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>4126.85</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>3362.19</v>
+      </c>
+      <c r="G45" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>JPPOWER</t>
         </is>
       </c>
-      <c r="C40" s="18" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>18.62</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="G40" s="19">
+      <c r="C46" s="14" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="G46" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>NLCINDIA</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>348.15</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>322.8</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>298.83</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>265.28</v>
-      </c>
-      <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>POWERINDIA</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>32800</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>32016.51</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>29146.09</v>
-      </c>
-      <c r="F42" s="18" t="n">
-        <v>23136.88</v>
-      </c>
-      <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>53.25</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>50.22</v>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>4393.3</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>4244.43</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>3858.23</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>3411.32</v>
-      </c>
-      <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>596.65</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>565.3099999999999</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>533.1799999999999</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>528.24</v>
-      </c>
-      <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="n">
-        <v>139.69</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>128.43</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>105.38</v>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>84.01000000000001</v>
-      </c>
-      <c r="G46" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C47" s="14" t="n">
-        <v>12.86</v>
+        <v>358.35</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>11.32</v>
+        <v>326.19</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>10.56</v>
+        <v>301.17</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>9.66</v>
+        <v>266.21</v>
       </c>
       <c r="G47" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>430.9</v>
+        <v>33360</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>415.12</v>
+        <v>32144.46</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>420.82</v>
+        <v>29311.34</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>411.93</v>
+        <v>23238.6</v>
       </c>
       <c r="G48" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C49" s="14" t="n">
-        <v>9408.5</v>
+        <v>1244.7</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>8868.49</v>
+        <v>1223.97</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>8138.58</v>
+        <v>1095.18</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>7820.96</v>
+        <v>891.65</v>
       </c>
       <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C50" s="14" t="n">
-        <v>1668.4</v>
+        <v>4416.6</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>1583.82</v>
+        <v>4260.83</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>1560.17</v>
+        <v>3880.13</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>1630.9</v>
+        <v>3421.32</v>
       </c>
       <c r="G50" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="n">
-        <v>10198.5</v>
-      </c>
-      <c r="D51" s="18" t="n">
-        <v>10120.52</v>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>9809.68</v>
-      </c>
-      <c r="F51" s="18" t="n">
-        <v>9311.969999999999</v>
-      </c>
-      <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>TRITURBINE</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="n">
+        <v>638.05</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>572.24</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>537.29</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>529.34</v>
+      </c>
+      <c r="G51" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>37155</v>
+        <v>294.95</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>36671.41</v>
+        <v>273.62</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>35760.68</v>
+        <v>264.97</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>35554.4</v>
+        <v>272.51</v>
       </c>
       <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
-        <v>128.75</v>
+        <v>394.3</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>125.57</v>
+        <v>361.29</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>122.65</v>
+        <v>350.3</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>114.79</v>
+        <v>388.28</v>
       </c>
       <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n">
-        <v>298.95</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>271.37</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>263.75</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>272.29</v>
-      </c>
-      <c r="G54" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>651.65</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>632.95</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>597.74</v>
+      </c>
+      <c r="F54" s="18" t="n">
+        <v>569.76</v>
+      </c>
+      <c r="G54" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>392.35</v>
+        <v>623.3</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>357.82</v>
+        <v>616.48</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>348.5</v>
+        <v>592.75</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>388.22</v>
+        <v>591.8200000000001</v>
       </c>
       <c r="G55" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C56" s="14" t="n">
-        <v>640.85</v>
+        <v>501.7</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>630.98</v>
+        <v>486.83</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>595.54</v>
+        <v>477.25</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>568.9400000000001</v>
+        <v>447.48</v>
       </c>
       <c r="G56" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="n">
-        <v>506.05</v>
-      </c>
-      <c r="D57" s="18" t="n">
-        <v>485.26</v>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>476.25</v>
-      </c>
-      <c r="F57" s="18" t="n">
-        <v>446.93</v>
-      </c>
-      <c r="G57" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>291.49</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>283.44</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>258.08</v>
+      </c>
+      <c r="G57" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="C58" s="18" t="n">
-        <v>297.2</v>
+        <v>10205</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>290.96</v>
+        <v>10128.56</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>282.91</v>
+        <v>9825.18</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>257.7</v>
+        <v>9320.860000000001</v>
       </c>
       <c r="G58" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>37130</v>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>36715.09</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>35814.38</v>
+      </c>
+      <c r="F59" s="18" t="n">
+        <v>35570.08</v>
+      </c>
+      <c r="G59" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>131.49</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>126.14</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>123</v>
+      </c>
+      <c r="F60" s="18" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="G60" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>520.05</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>469.57</v>
+      </c>
+      <c r="E61" s="14" t="n">
+        <v>438.57</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>477.89</v>
+      </c>
+      <c r="G61" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>5773.5</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>5534.76</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>5303.8</v>
+      </c>
+      <c r="F62" s="18" t="n">
+        <v>5516.02</v>
+      </c>
+      <c r="G62" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>293.6</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>280.02</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>266.44</v>
+      </c>
+      <c r="F63" s="18" t="n">
+        <v>276.28</v>
+      </c>
+      <c r="G63" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C59" s="14" t="n">
-        <v>3348.4</v>
-      </c>
-      <c r="D59" s="14" t="n">
-        <v>3057.4</v>
-      </c>
-      <c r="E59" s="14" t="n">
-        <v>2816.82</v>
-      </c>
-      <c r="F59" s="14" t="n">
-        <v>2266.66</v>
-      </c>
-      <c r="G59" s="15">
+      <c r="C64" s="14" t="n">
+        <v>3414.7</v>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>3091.43</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>2840.27</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>2278.08</v>
+      </c>
+      <c r="G64" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>CERA</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="n">
-        <v>5558.5</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>5509.63</v>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>5284.63</v>
-      </c>
-      <c r="F60" s="18" t="n">
-        <v>5513.44</v>
-      </c>
-      <c r="G60" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n">
-        <v>293.3</v>
-      </c>
-      <c r="D61" s="18" t="n">
-        <v>278.59</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>265.33</v>
-      </c>
-      <c r="F61" s="18" t="n">
-        <v>276.11</v>
-      </c>
-      <c r="G61" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
-        <v>502.55</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>464.26</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>435.24</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>477.47</v>
-      </c>
-      <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 19-May-2026  14:08</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 20-May-2026  13:51</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>19</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.95</v>
@@ -703,7 +703,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>12</v>
@@ -712,7 +712,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.8</v>
@@ -721,215 +721,215 @@
         <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.711</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="D6" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>0.5329999999999999</v>
-      </c>
       <c r="H6" s="6" t="n">
-        <v>0.467</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.5333</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>13</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.65</v>
+        <v>0.325</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.55</v>
+        <v>0.525</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.3</v>
+        <v>0.575</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.5</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.55</v>
+        <v>0.467</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.4417</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3667</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.3113</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.4</v>
@@ -938,7 +938,7 @@
         <v>0.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2667</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -982,25 +982,25 @@
         <v>20</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2333</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1013,7 +1013,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>2</v>
@@ -1022,7 +1022,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>0.167</v>
@@ -1031,7 +1031,7 @@
         <v>0.25</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.139</v>
+        <v>0.1947</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1044,19 +1044,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
@@ -1075,7 +1075,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>1</v>
@@ -1084,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0.083</v>
@@ -1093,7 +1093,7 @@
         <v>0.083</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0553</v>
+        <v>0.083</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3248.2</v>
+        <v>3188.8</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3035.92</v>
+        <v>3050.48</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2938.72</v>
+        <v>2948.53</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2767.86</v>
+        <v>2769.64</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1512.8</v>
+        <v>1517.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1455.44</v>
+        <v>1461.35</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1380.88</v>
+        <v>1386.23</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1248.74</v>
+        <v>1250.25</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>428.15</v>
+        <v>432.7</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>392.43</v>
+        <v>396.26</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>379.82</v>
+        <v>381.89</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>372.85</v>
+        <v>372.7</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1409.8</v>
+        <v>1399.5</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1344.58</v>
+        <v>1349.81</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1319.63</v>
+        <v>1322.76</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1395.94</v>
+        <v>1392.96</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CIPLA","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>6912</v>
+        <v>6893</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6625.7</v>
+        <v>6651.15</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>6425.97</v>
+        <v>6444.28</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>6359.28</v>
+        <v>6354.07</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1335.2</v>
+        <v>1321.9</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1298.2</v>
+        <v>1300.45</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1281.78</v>
+        <v>1283.36</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1261.37</v>
+        <v>1262.4</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2251.1</v>
+        <v>2221.8</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1891.25</v>
+        <v>1922.73</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1813.17</v>
+        <v>1829.2</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1768.44</v>
+        <v>1774.14</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2405.9</v>
+        <v>2379</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2328.04</v>
+        <v>2332.9</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2250.8</v>
+        <v>2255.82</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>2033.66</v>
+        <v>2036.91</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>766.45</v>
+        <v>758.65</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>717.25</v>
+        <v>721.1900000000001</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>672.24</v>
+        <v>675.63</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>594.0599999999999</v>
+        <v>595.5</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>1656.2</v>
+        <v>1646.6</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>1557.88</v>
+        <v>1566.33</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>1527.37</v>
+        <v>1532.05</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1465.43</v>
+        <v>1468.92</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>2171.6</v>
+        <v>2163.6</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>2103.75</v>
+        <v>2109.45</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>2054.88</v>
+        <v>2059.15</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1894.26</v>
+        <v>1900.05</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1344.9</v>
+        <v>1361.1</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>1220.58</v>
+        <v>1233.97</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>1138.67</v>
+        <v>1147.39</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>992.5700000000001</v>
+        <v>995.08</v>
       </c>
       <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>2492.6</v>
+        <v>2583.9</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>2356.78</v>
+        <v>2378.41</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>2249.29</v>
+        <v>2262.41</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>2274.86</v>
+        <v>2276.7</v>
       </c>
       <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>1882.3</v>
+        <v>1156.3</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>1820.96</v>
+        <v>1140.82</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>1776.26</v>
+        <v>1077.39</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>1725.32</v>
+        <v>954.54</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>4460.1</v>
+        <v>1880.3</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>4322.84</v>
+        <v>1826.61</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>4243.14</v>
+        <v>1780.34</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>3929.46</v>
+        <v>1725.04</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,79 +1649,79 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>4429.2</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>4332.97</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>4250.44</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>3929.44</v>
+      </c>
+      <c r="G18" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n">
-        <v>1018.9</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>951.08</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>928.72</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>927.5700000000001</v>
-      </c>
-      <c r="G18" s="15">
+      <c r="C19" s="14" t="n">
+        <v>1040.85</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>959.63</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>933.12</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>926.4299999999999</v>
+      </c>
+      <c r="G19" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n">
-        <v>2725</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>2483.88</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>2310.17</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>2290.78</v>
-      </c>
-      <c r="G19" s="19">
+      <c r="C20" s="18" t="n">
+        <v>2704.8</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>2504.92</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>2325.65</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>2291.7</v>
+      </c>
+      <c r="G20" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>1048.3</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>1043.88</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>1003.51</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>883.6799999999999</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1733,23 +1733,23 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>569.5</v>
+        <v>1085.5</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>562.45</v>
+        <v>1047.84</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>546.12</v>
+        <v>1006.72</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>451.64</v>
+        <v>886.04</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1765,16 +1765,16 @@
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>632.6</v>
+        <v>630.45</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>620.5</v>
+        <v>621.45</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>595.03</v>
+        <v>596.41</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>542.98</v>
+        <v>542.84</v>
       </c>
       <c r="G22" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1285.2</v>
+        <v>1283.2</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1266.22</v>
+        <v>1267.84</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>1238.15</v>
+        <v>1239.91</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>1169.07</v>
+        <v>1169.64</v>
       </c>
       <c r="G23" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
@@ -1817,23 +1817,23 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>89.02</v>
+        <v>199.04</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>88.98999999999999</v>
+        <v>187.11</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>85.94</v>
+        <v>175.2</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>78.59999999999999</v>
+        <v>151.87</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1845,1115 +1845,1143 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>199.05</v>
+        <v>1316.7</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>185.85</v>
+        <v>1253.43</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>174.23</v>
+        <v>1108.7</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>151.36</v>
+        <v>923.6</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>1280.7</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>1246.77</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>1100.21</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>920.75</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>139.34</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>130.31</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>107.94</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G26" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>550.45</v>
+        <v>13.58</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>527.63</v>
+        <v>11.73</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>506.87</v>
+        <v>10.79</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>493.81</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>2188.3</v>
+        <v>427.85</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>2129.1</v>
+        <v>417.67</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>2091.49</v>
+        <v>421.46</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2176.38</v>
+        <v>412.06</v>
       </c>
       <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COLPAL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>831.45</v>
+        <v>9703.5</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>811.24</v>
+        <v>9015.01</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>787.47</v>
+        <v>8256.74</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>752.63</v>
+        <v>7843.17</v>
       </c>
       <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>1431.4</v>
+        <v>1775.6</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>1426.09</v>
+        <v>1607.5</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>1361.23</v>
+        <v>1571.88</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>1275.92</v>
+        <v>1631.75</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NESTLEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>3599.9</v>
+        <v>674.45</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>3369.77</v>
+        <v>617.63</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>3157.39</v>
+        <v>599.03</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>2965.98</v>
+        <v>636.14</v>
       </c>
       <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>1210.9</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>1187.86</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>1152.84</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>1138.26</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>1346.1</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>1316.22</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>1217.47</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>1035.94</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>514.8</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>496.35</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>474.65</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>468.01</v>
-      </c>
-      <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>1363.2</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>1301.44</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>1168.31</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>1039.54</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>138.17</v>
+        <v>220.24</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>129.36</v>
+        <v>215.23</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>106.66</v>
+        <v>194.71</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>84.55</v>
+        <v>157.82</v>
       </c>
       <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C35" s="18" t="n">
-        <v>13.52</v>
+        <v>408.4</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>11.53</v>
+        <v>377.45</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>10.68</v>
+        <v>335.12</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>9.699999999999999</v>
+        <v>283.34</v>
       </c>
       <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>430.7</v>
+        <v>180.65</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>416.6</v>
+        <v>180.35</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>421.2</v>
+        <v>172.9</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>412.12</v>
+        <v>165.86</v>
       </c>
       <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
-        <v>9646</v>
+        <v>853.25</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>8942.540000000001</v>
+        <v>822.6799999999999</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>8197.700000000001</v>
+        <v>777.83</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>7839.12</v>
+        <v>716.61</v>
       </c>
       <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
-        <v>1646.6</v>
+        <v>4679.4</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>1589.8</v>
+        <v>4405.73</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>1563.56</v>
+        <v>4148.52</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>1631.06</v>
+        <v>3371.44</v>
       </c>
       <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>TATATECH</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
-        <v>668.55</v>
+        <v>354.65</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>611.65</v>
+        <v>328.9</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>595.95</v>
+        <v>303.26</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>637.09</v>
+        <v>267.42</v>
       </c>
       <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>1329.5</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>1313.07</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>1212.22</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>1034.44</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>35525</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>32466.41</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>29555.01</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>23352.48</v>
+      </c>
+      <c r="G40" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>1377.8</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>1294.93</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>1160.36</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>1038.78</v>
-      </c>
-      <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>1231.21</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>1103.22</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>894.77</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>ADANIPOWER</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>219.09</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>214.7</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>193.67</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>157.29</v>
-      </c>
-      <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>3696.4</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>3647.12</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>3516.43</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>3282.2</v>
+      </c>
+      <c r="G42" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>401.1</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>374.19</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>332.13</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>282.03</v>
-      </c>
-      <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>4415.1</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>4275.52</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>3901.11</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>3430.29</v>
+      </c>
+      <c r="G43" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="n">
-        <v>181.06</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>180.32</v>
-      </c>
-      <c r="E44" s="14" t="n">
-        <v>172.58</v>
-      </c>
-      <c r="F44" s="14" t="n">
-        <v>165.59</v>
-      </c>
-      <c r="G44" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>TRITURBINE</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>656.55</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>580.27</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>541.97</v>
+      </c>
+      <c r="F44" s="18" t="n">
+        <v>529.36</v>
+      </c>
+      <c r="G44" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C45" s="14" t="n">
-        <v>4385.3</v>
+        <v>530.75</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>4376.92</v>
+        <v>527.9299999999999</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>4126.85</v>
+        <v>507.81</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>3362.19</v>
+        <v>493.47</v>
       </c>
       <c r="G45" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="C46" s="14" t="n">
-        <v>18.84</v>
+        <v>2185.4</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>18.64</v>
+        <v>2134.46</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>17.72</v>
+        <v>2095.16</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>17.12</v>
+        <v>2169.87</v>
       </c>
       <c r="G46" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COLPAL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C47" s="14" t="n">
-        <v>358.35</v>
+        <v>838.45</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>326.19</v>
+        <v>813.83</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>301.17</v>
+        <v>789.47</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>266.21</v>
+        <v>752.47</v>
       </c>
       <c r="G47" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>33360</v>
+        <v>3565.9</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>32144.46</v>
+        <v>3388.45</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>29311.34</v>
+        <v>3173.41</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>23238.6</v>
+        <v>2969.62</v>
       </c>
       <c r="G48" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C49" s="14" t="n">
-        <v>1244.7</v>
+        <v>1208.7</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>1223.97</v>
+        <v>1189.84</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>1095.18</v>
+        <v>1155.03</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>891.65</v>
+        <v>1137.26</v>
       </c>
       <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="C50" s="14" t="n">
-        <v>4416.6</v>
+        <v>514</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>4260.83</v>
+        <v>498.03</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>3880.13</v>
+        <v>476.19</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>3421.32</v>
+        <v>467.28</v>
       </c>
       <c r="G50" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n">
-        <v>638.05</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>572.24</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>537.29</v>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>529.34</v>
-      </c>
-      <c r="G51" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>10462.5</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>10160.37</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>9850.16</v>
+      </c>
+      <c r="F51" s="18" t="n">
+        <v>9309.32</v>
+      </c>
+      <c r="G51" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>294.95</v>
+        <v>36830</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>273.62</v>
+        <v>36726.03</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>264.97</v>
+        <v>35854.2</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>272.51</v>
+        <v>35578.94</v>
       </c>
       <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="20" t="inlineStr">
         <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>132.17</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>126.71</v>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>123.35</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <v>115.03</v>
+      </c>
+      <c r="G53" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="n">
+        <v>541.5</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>476.42</v>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>442.6</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>481.13</v>
+      </c>
+      <c r="G54" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B53" s="17" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>275.28</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>265.99</v>
+      </c>
+      <c r="F55" s="18" t="n">
+        <v>273.27</v>
+      </c>
+      <c r="G55" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>SAREGAMA</t>
         </is>
       </c>
-      <c r="C53" s="18" t="n">
-        <v>394.3</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>361.29</v>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>350.3</v>
-      </c>
-      <c r="F53" s="18" t="n">
-        <v>388.28</v>
-      </c>
-      <c r="G53" s="19">
+      <c r="C56" s="18" t="n">
+        <v>406.5</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>365.6</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <v>389.01</v>
+      </c>
+      <c r="G56" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>TIPSMUSIC</t>
         </is>
       </c>
-      <c r="C54" s="18" t="n">
-        <v>651.65</v>
-      </c>
-      <c r="D54" s="18" t="n">
-        <v>632.95</v>
-      </c>
-      <c r="E54" s="18" t="n">
-        <v>597.74</v>
-      </c>
-      <c r="F54" s="18" t="n">
-        <v>569.76</v>
-      </c>
-      <c r="G54" s="19">
+      <c r="C57" s="18" t="n">
+        <v>659.3</v>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>635.46</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>600.16</v>
+      </c>
+      <c r="F57" s="18" t="n">
+        <v>571</v>
+      </c>
+      <c r="G57" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="n">
-        <v>623.3</v>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>616.48</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>592.75</v>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>591.8200000000001</v>
-      </c>
-      <c r="G55" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="16" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="n">
+        <v>504.4</v>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>478.31</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>448.07</v>
+      </c>
+      <c r="G58" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="n">
-        <v>501.7</v>
-      </c>
-      <c r="D56" s="14" t="n">
-        <v>486.83</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>477.25</v>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>447.48</v>
-      </c>
-      <c r="G56" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
       </c>
-      <c r="C57" s="14" t="n">
-        <v>296.5</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>291.49</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>283.44</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>258.08</v>
-      </c>
-      <c r="G57" s="15">
+      <c r="C59" s="14" t="n">
+        <v>298.3</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>292.13</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>284.02</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>258.69</v>
+      </c>
+      <c r="G59" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n">
-        <v>10205</v>
-      </c>
-      <c r="D58" s="18" t="n">
-        <v>10128.56</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>9825.18</v>
-      </c>
-      <c r="F58" s="18" t="n">
-        <v>9320.860000000001</v>
-      </c>
-      <c r="G58" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="n">
-        <v>37130</v>
-      </c>
-      <c r="D59" s="18" t="n">
-        <v>36715.09</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>35814.38</v>
-      </c>
-      <c r="F59" s="18" t="n">
-        <v>35570.08</v>
-      </c>
-      <c r="G59" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="C60" s="18" t="n">
-        <v>131.49</v>
+        <v>5748.5</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>126.14</v>
+        <v>5555.12</v>
       </c>
       <c r="E60" s="18" t="n">
-        <v>123</v>
+        <v>5321.23</v>
       </c>
       <c r="F60" s="18" t="n">
-        <v>114.95</v>
+        <v>5504.46</v>
       </c>
       <c r="G60" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="n">
-        <v>520.05</v>
-      </c>
-      <c r="D61" s="14" t="n">
-        <v>469.57</v>
-      </c>
-      <c r="E61" s="14" t="n">
-        <v>438.57</v>
-      </c>
-      <c r="F61" s="14" t="n">
-        <v>477.89</v>
-      </c>
-      <c r="G61" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>290.6</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>281.02</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>267.39</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>275.97</v>
+      </c>
+      <c r="G61" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>CERA</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="n">
-        <v>5773.5</v>
-      </c>
-      <c r="D62" s="18" t="n">
-        <v>5534.76</v>
-      </c>
-      <c r="E62" s="18" t="n">
-        <v>5303.8</v>
-      </c>
-      <c r="F62" s="18" t="n">
-        <v>5516.02</v>
-      </c>
-      <c r="G62" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>3441.7</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>3124.79</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>2863.85</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>2287.33</v>
+      </c>
+      <c r="G62" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C63" s="18" t="n">
-        <v>293.6</v>
+        <v>289.9</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>280.02</v>
+        <v>287.08</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>266.44</v>
+        <v>284.04</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>276.28</v>
+        <v>257.67</v>
       </c>
       <c r="G63" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>3414.7</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>3091.43</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>2840.27</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>2278.08</v>
-      </c>
-      <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>897.15</v>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>895.72</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>881.4299999999999</v>
+      </c>
+      <c r="F64" s="18" t="n">
+        <v>852.25</v>
+      </c>
+      <c r="G64" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="D65" s="14" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="G65" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 20-May-2026  13:51</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 21-May-2026  14:27</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>19</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.95</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.9167000000000001</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,19 +703,19 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>12</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.8</v>
+        <v>0.733</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.8</v>
@@ -734,19 +734,19 @@
         <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.3</v>
@@ -758,125 +758,125 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.325</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.525</v>
+        <v>0.6</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.575</v>
+        <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.475</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.467</v>
+        <v>0.325</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.467</v>
+        <v>0.475</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.467</v>
+        <v>0.55</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.467</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="F9" s="10" t="n">
-        <v>0.267</v>
+        <v>0.467</v>
       </c>
       <c r="G9" s="10" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="H9" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="H9" s="10" t="n">
-        <v>0.267</v>
-      </c>
       <c r="I9" s="11" t="n">
-        <v>0.3113</v>
+        <v>0.4447</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.467</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.3</v>
+        <v>0.4003</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -889,56 +889,56 @@
         <v>10</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F12" s="6" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>0.267</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0.2</v>
-      </c>
       <c r="I12" s="7" t="n">
-        <v>0.289</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -957,7 +957,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0.2</v>
@@ -966,134 +966,134 @@
         <v>0.267</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.267</v>
+        <v>0.4</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.2447</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="F14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.15</v>
+        <v>0.083</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2167</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.167</v>
+        <v>0.1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1947</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.3</v>
+        <v>0.083</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.083</v>
+        <v>0.2</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.083</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3188.8</v>
+        <v>3149.2</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3050.48</v>
+        <v>3059.89</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2948.53</v>
+        <v>2956.4</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2769.64</v>
+        <v>2776.61</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1517.5</v>
+        <v>5501.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1461.35</v>
+        <v>5478.89</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1386.23</v>
+        <v>5469.34</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1250.25</v>
+        <v>5443.3</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>432.7</v>
+        <v>1546.7</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>396.26</v>
+        <v>1469.48</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>381.89</v>
+        <v>1392.53</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>372.7</v>
+        <v>1254.22</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1399.5</v>
+        <v>430.85</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1349.81</v>
+        <v>399.56</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1322.76</v>
+        <v>383.81</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1392.96</v>
+        <v>373.95</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CIPLA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>6893</v>
+        <v>1401.9</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6651.15</v>
+        <v>1354.77</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>6444.28</v>
+        <v>1325.86</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>6354.07</v>
+        <v>1395.32</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CIPLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1321.9</v>
+        <v>6858</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1300.45</v>
+        <v>6670.85</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1283.36</v>
+        <v>6460.5</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1262.4</v>
+        <v>6367.3</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2221.8</v>
+        <v>1318.5</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1922.73</v>
+        <v>1302.17</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1829.2</v>
+        <v>1284.74</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1774.14</v>
+        <v>1263</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2379</v>
+        <v>2331</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2332.9</v>
+        <v>1961.61</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2255.82</v>
+        <v>1848.88</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>2036.91</v>
+        <v>1785.68</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>758.65</v>
+        <v>2393</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>721.1900000000001</v>
+        <v>2338.62</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>675.63</v>
+        <v>2261.2</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>595.5</v>
+        <v>2040.77</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>1646.6</v>
+        <v>764.2</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>1566.33</v>
+        <v>725.29</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>1532.05</v>
+        <v>679.1</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1468.92</v>
+        <v>597.89</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,23 +1509,23 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>2163.6</v>
+        <v>1637</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>2109.45</v>
+        <v>1573.06</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>2059.15</v>
+        <v>1536.16</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1900.05</v>
+        <v>1471.76</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,23 +1537,23 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>JBCHEPHARM</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1361.1</v>
+        <v>2178.9</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>1233.97</v>
+        <v>2116.06</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>1147.39</v>
+        <v>2063.84</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>995.08</v>
+        <v>1900.25</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>2583.9</v>
+        <v>1351</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>2378.41</v>
+        <v>1245.11</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>2262.41</v>
+        <v>1155.38</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>2276.7</v>
+        <v>998.9299999999999</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>1156.3</v>
+        <v>2514.1</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>1140.82</v>
+        <v>2391.33</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>1077.39</v>
+        <v>2272.28</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>954.54</v>
+        <v>2277.58</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1880.3</v>
+        <v>1174.3</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1826.61</v>
+        <v>1144.01</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1780.34</v>
+        <v>1081.19</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1725.04</v>
+        <v>958.65</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,23 +1649,23 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>4429.2</v>
+        <v>1891.3</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>4332.97</v>
+        <v>1832.77</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>4250.44</v>
+        <v>1784.69</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>3929.44</v>
+        <v>1728.64</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,79 +1677,79 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>4469.2</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>4345.95</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>4259.02</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>3938.68</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
-        <v>1040.85</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>959.63</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>933.12</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>926.4299999999999</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="C20" s="14" t="n">
+        <v>1036.45</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>966.95</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>937.17</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>928.04</v>
+      </c>
+      <c r="G20" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="C20" s="18" t="n">
-        <v>2704.8</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>2504.92</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>2325.65</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>2291.7</v>
-      </c>
-      <c r="G20" s="19">
+      <c r="C21" s="18" t="n">
+        <v>2697.6</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>2523.27</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>2340.23</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>2295.64</v>
+      </c>
+      <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>1085.5</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>1047.84</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>1006.72</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>886.04</v>
-      </c>
-      <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>630.45</v>
+        <v>1099.3</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>621.45</v>
+        <v>1052.75</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>596.41</v>
+        <v>1010.35</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>542.84</v>
+        <v>888.1900000000001</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1283.2</v>
+        <v>628.05</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1267.84</v>
+        <v>622.0700000000001</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>1239.91</v>
+        <v>597.66</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>1169.64</v>
+        <v>544.22</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,23 +1817,23 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>199.04</v>
+        <v>1281.3</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>187.11</v>
+        <v>1269.12</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>175.2</v>
+        <v>1241.54</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>151.87</v>
+        <v>1169.79</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1845,107 +1845,107 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>406.4</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>406.28</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>397.74</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>320.53</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>196.53</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>188.01</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>176.04</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>152.51</v>
+      </c>
+      <c r="G26" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n">
-        <v>1316.7</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>1253.43</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>1108.7</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>923.6</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="C27" s="18" t="n">
+        <v>1330.2</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>1260.74</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>1117.39</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>927.49</v>
+      </c>
+      <c r="G27" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>HFCL</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
-        <v>139.34</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>130.31</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>107.94</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>84.79000000000001</v>
-      </c>
-      <c r="G26" s="15">
+      <c r="C28" s="14" t="n">
+        <v>141.75</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>109.27</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="G28" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>10.79</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>INDUSTOWER</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>427.85</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>417.67</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>421.46</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>412.06</v>
-      </c>
-      <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1957,23 +1957,23 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>9703.5</v>
+        <v>13.62</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>9015.01</v>
+        <v>11.91</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>8256.74</v>
+        <v>10.91</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>7843.17</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1985,23 +1985,23 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>1775.6</v>
+        <v>431.8</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>1607.5</v>
+        <v>419.02</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>1571.88</v>
+        <v>421.87</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>1631.75</v>
+        <v>412.38</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2013,974 +2013,1114 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>9730.5</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>9083.15</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>8314.530000000001</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>7857.79</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1896.3</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>1635</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>1584.6</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>1636.84</v>
+      </c>
+      <c r="G32" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
           <t>TATATECH</t>
         </is>
       </c>
-      <c r="C31" s="14" t="n">
-        <v>674.45</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>617.63</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>599.03</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>636.14</v>
-      </c>
-      <c r="G31" s="15">
+      <c r="C33" s="14" t="n">
+        <v>664.1</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>622.0599999999999</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>601.58</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>637.53</v>
+      </c>
+      <c r="G33" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>1346.1</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>1316.22</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>1217.47</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>1035.94</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>1363.2</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>1301.44</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>1168.31</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>1039.54</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>220.24</v>
+        <v>1654.4</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>215.23</v>
+        <v>1642.09</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>194.71</v>
+        <v>1617.01</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>157.82</v>
+        <v>1627.6</v>
       </c>
       <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="C35" s="18" t="n">
-        <v>408.4</v>
+        <v>1795.7</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>377.45</v>
+        <v>1758.27</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>335.12</v>
+        <v>1731.26</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>283.34</v>
+        <v>1691.09</v>
       </c>
       <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>541.5</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>482.62</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>446.48</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>483.33</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>180.65</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>180.35</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>172.9</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>165.86</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CESC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>1342.2</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>1318.69</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>1222.36</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>1039.19</v>
+      </c>
+      <c r="G37" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>1358.2</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>1306.84</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>1175.76</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>1043.74</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>219.33</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>215.62</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>195.68</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>158.35</v>
+      </c>
+      <c r="G39" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>408.15</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>380.37</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>337.98</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>284.83</v>
+      </c>
+      <c r="G40" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>CGPOWER</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n">
-        <v>853.25</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>822.6799999999999</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>777.83</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>716.61</v>
-      </c>
-      <c r="G37" s="19">
+      <c r="C41" s="14" t="n">
+        <v>864.9</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>826.7</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>781.25</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>718.33</v>
+      </c>
+      <c r="G41" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>GVT&amp;D</t>
         </is>
       </c>
-      <c r="C38" s="18" t="n">
-        <v>4679.4</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>4405.73</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>4148.52</v>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>3371.44</v>
-      </c>
-      <c r="G38" s="19">
+      <c r="C42" s="14" t="n">
+        <v>4794.6</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>4442.76</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>4173.86</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>3389.72</v>
+      </c>
+      <c r="G42" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>548.45</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>538.6799999999999</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>526.99</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>509.93</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>NLCINDIA</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n">
-        <v>354.65</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>328.9</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>303.26</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>267.42</v>
-      </c>
-      <c r="G39" s="19">
+      <c r="C44" s="14" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>330.96</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>305.12</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>268.13</v>
+      </c>
+      <c r="G44" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>POWERINDIA</t>
         </is>
       </c>
-      <c r="C40" s="18" t="n">
-        <v>35525</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>32466.41</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>29555.01</v>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>23352.48</v>
-      </c>
-      <c r="G40" s="19">
+      <c r="C45" s="14" t="n">
+        <v>36450</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>32845.8</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>29825.43</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>23541.32</v>
+      </c>
+      <c r="G45" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>SCHNEIDER</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>1231.21</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>1103.22</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>894.77</v>
-      </c>
-      <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>3696.4</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>3647.12</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>3516.43</v>
-      </c>
-      <c r="F42" s="18" t="n">
-        <v>3282.2</v>
-      </c>
-      <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>THERMAX</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>4415.1</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>4275.52</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>3901.11</v>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>3430.29</v>
-      </c>
-      <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>656.55</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>580.27</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>541.97</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>529.36</v>
-      </c>
-      <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="n">
-        <v>530.75</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>527.9299999999999</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>507.81</v>
-      </c>
-      <c r="F45" s="14" t="n">
-        <v>493.47</v>
-      </c>
-      <c r="G45" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C46" s="14" t="n">
-        <v>2185.4</v>
+        <v>1325.3</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>2134.46</v>
+        <v>1240.17</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>2095.16</v>
+        <v>1111.93</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>2169.87</v>
+        <v>899.97</v>
       </c>
       <c r="G46" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COLPAL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C47" s="14" t="n">
-        <v>838.45</v>
+        <v>3720.6</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>813.83</v>
+        <v>3654.12</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>789.47</v>
+        <v>3524.45</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>752.47</v>
+        <v>3300.09</v>
       </c>
       <c r="G47" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>3565.9</v>
+        <v>4575</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>3388.45</v>
+        <v>4304.05</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>3173.41</v>
+        <v>3927.53</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>2969.62</v>
+        <v>3445.07</v>
       </c>
       <c r="G48" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>TRITURBINE</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>705.6</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>592.21</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>548.38</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>530.29</v>
+      </c>
+      <c r="G49" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n">
-        <v>1208.7</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>1189.84</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>1155.03</v>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>1137.26</v>
-      </c>
-      <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>537.45</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>528.83</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>508.97</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>494.16</v>
+      </c>
+      <c r="G50" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n">
-        <v>514</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>498.03</v>
-      </c>
-      <c r="E50" s="14" t="n">
-        <v>476.19</v>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>467.28</v>
-      </c>
-      <c r="G50" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>10462.5</v>
+        <v>831.85</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>10160.37</v>
+        <v>815.54</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>9850.16</v>
+        <v>791.14</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>9309.32</v>
+        <v>753.71</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>36830</v>
+        <v>3571.9</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>36726.03</v>
+        <v>3405.92</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>35854.2</v>
+        <v>3189.03</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>35578.94</v>
+        <v>2965.57</v>
       </c>
       <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
-        <v>132.17</v>
+        <v>1194.9</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>126.71</v>
+        <v>1190.33</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>123.35</v>
+        <v>1156.59</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>115.03</v>
+        <v>1138.67</v>
       </c>
       <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n">
-        <v>541.5</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>476.42</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>442.6</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>481.13</v>
-      </c>
-      <c r="G54" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>519.85</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>500.11</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>477.91</v>
+      </c>
+      <c r="F54" s="18" t="n">
+        <v>467.71</v>
+      </c>
+      <c r="G54" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="n">
+        <v>727.85</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>692.54</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>681.8099999999999</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>719.65</v>
+      </c>
+      <c r="G55" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="n">
+        <v>638.1</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>618.04</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>595.2</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>591.4400000000001</v>
+      </c>
+      <c r="G56" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>503.5</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>489.93</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>479.3</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>448.88</v>
+      </c>
+      <c r="G57" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="n">
+        <v>295.85</v>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>292.49</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>284.49</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>259.02</v>
+      </c>
+      <c r="G58" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B55" s="17" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>NAZARA</t>
         </is>
       </c>
-      <c r="C55" s="18" t="n">
-        <v>291.05</v>
-      </c>
-      <c r="D55" s="18" t="n">
-        <v>275.28</v>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>265.99</v>
-      </c>
-      <c r="F55" s="18" t="n">
-        <v>273.27</v>
-      </c>
-      <c r="G55" s="19">
+      <c r="C59" s="18" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>276.22</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>266.75</v>
+      </c>
+      <c r="F59" s="18" t="n">
+        <v>273.46</v>
+      </c>
+      <c r="G59" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="20" t="inlineStr">
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>SAREGAMA</t>
         </is>
       </c>
-      <c r="C56" s="18" t="n">
-        <v>406.5</v>
-      </c>
-      <c r="D56" s="18" t="n">
-        <v>365.6</v>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>352.5</v>
-      </c>
-      <c r="F56" s="18" t="n">
-        <v>389.01</v>
-      </c>
-      <c r="G56" s="19">
+      <c r="C60" s="18" t="n">
+        <v>406.4</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>369.48</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>354.61</v>
+      </c>
+      <c r="F60" s="18" t="n">
+        <v>389.07</v>
+      </c>
+      <c r="G60" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="n">
-        <v>659.3</v>
-      </c>
-      <c r="D57" s="18" t="n">
-        <v>635.46</v>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>600.16</v>
-      </c>
-      <c r="F57" s="18" t="n">
-        <v>571</v>
-      </c>
-      <c r="G57" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>504.4</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>488.5</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>478.31</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>448.07</v>
-      </c>
-      <c r="G58" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n">
-        <v>298.3</v>
-      </c>
-      <c r="D59" s="14" t="n">
-        <v>292.13</v>
-      </c>
-      <c r="E59" s="14" t="n">
-        <v>284.02</v>
-      </c>
-      <c r="F59" s="14" t="n">
-        <v>258.69</v>
-      </c>
-      <c r="G59" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>CERA</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="n">
-        <v>5748.5</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>5555.12</v>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>5321.23</v>
-      </c>
-      <c r="F60" s="18" t="n">
-        <v>5504.46</v>
-      </c>
-      <c r="G60" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="20" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C61" s="18" t="n">
-        <v>290.6</v>
+        <v>658.85</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>281.02</v>
+        <v>637.6900000000001</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>267.39</v>
+        <v>602.46</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>275.97</v>
+        <v>572.89</v>
       </c>
       <c r="G61" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="12" t="inlineStr">
         <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>10667</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>10208.62</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>9882.200000000001</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>9332.639999999999</v>
+      </c>
+      <c r="G62" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>1898.8</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>1894.66</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>1831.34</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>1574.95</v>
+      </c>
+      <c r="G63" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="n">
+        <v>137</v>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>127.69</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>123.89</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>115.38</v>
+      </c>
+      <c r="G64" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>CERA</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>5788</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>5577.3</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>5339.54</v>
+      </c>
+      <c r="F65" s="18" t="n">
+        <v>5513.89</v>
+      </c>
+      <c r="G65" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>291.85</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>282.06</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>268.34</v>
+      </c>
+      <c r="F66" s="18" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="G66" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="n">
+        <v>899.95</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>896.12</v>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>882.16</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>851.72</v>
+      </c>
+      <c r="G67" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>2727.9</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>2698.34</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>2655.2</v>
+      </c>
+      <c r="F68" s="18" t="n">
+        <v>2625.26</v>
+      </c>
+      <c r="G68" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C62" s="14" t="n">
-        <v>3441.7</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>3124.79</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>2863.85</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>2287.33</v>
-      </c>
-      <c r="G62" s="15">
+      <c r="C69" s="18" t="n">
+        <v>3322.8</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>3143.65</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>2881.85</v>
+      </c>
+      <c r="F69" s="18" t="n">
+        <v>2298.23</v>
+      </c>
+      <c r="G69" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="n">
-        <v>289.9</v>
-      </c>
-      <c r="D63" s="18" t="n">
-        <v>287.08</v>
-      </c>
-      <c r="E63" s="18" t="n">
-        <v>284.04</v>
-      </c>
-      <c r="F63" s="18" t="n">
-        <v>257.67</v>
-      </c>
-      <c r="G63" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="n">
-        <v>897.15</v>
-      </c>
-      <c r="D64" s="18" t="n">
-        <v>895.72</v>
-      </c>
-      <c r="E64" s="18" t="n">
-        <v>881.4299999999999</v>
-      </c>
-      <c r="F64" s="18" t="n">
-        <v>852.25</v>
-      </c>
-      <c r="G64" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="12" t="inlineStr">
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>MAHABANK</t>
         </is>
       </c>
-      <c r="C65" s="14" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="D65" s="14" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="E65" s="14" t="n">
-        <v>74.44</v>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="G65" s="15">
+      <c r="C70" s="14" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="D70" s="14" t="n">
+        <v>78.53</v>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>74.65000000000001</v>
+      </c>
+      <c r="F70" s="14" t="n">
+        <v>64.81999999999999</v>
+      </c>
+      <c r="G70" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 21-May-2026  14:27</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 22-May-2026  13:42</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -706,7 +706,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>12</v>
@@ -715,13 +715,13 @@
         <v>0.467</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.733</v>
+        <v>0.667</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.6446999999999999</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -734,25 +734,25 @@
         <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.55</v>
+        <v>0.5167</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -765,25 +765,25 @@
         <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>5</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>6</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G7" s="10" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>0.6</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -796,7 +796,7 @@
         <v>40</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>19</v>
@@ -805,7 +805,7 @@
         <v>22</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.325</v>
+        <v>0.375</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.475</v>
@@ -814,7 +814,7 @@
         <v>0.55</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -827,7 +827,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>7</v>
@@ -836,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.467</v>
@@ -845,7 +845,7 @@
         <v>0.4</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.4447</v>
+        <v>0.4223</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -858,7 +858,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>7</v>
@@ -867,7 +867,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.467</v>
@@ -876,162 +876,162 @@
         <v>0.267</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.4003</v>
+        <v>0.3779999999999999</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.4</v>
+        <v>0.3553</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.311</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.289</v>
+        <v>0.3167</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.083</v>
+        <v>0.267</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1667</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.1</v>
+        <v>0.167</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1667</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1050,7 +1050,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0.083</v>
@@ -1059,10 +1059,10 @@
         <v>0.083</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.083</v>
+        <v>0.167</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.083</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1075,19 +1075,19 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3149.2</v>
+        <v>3107.5</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3059.89</v>
+        <v>3064.42</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2956.4</v>
+        <v>2962.32</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2776.61</v>
+        <v>2774.62</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>5501.5</v>
+        <v>430.25</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>5478.89</v>
+        <v>402.48</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>5469.34</v>
+        <v>385.63</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>5443.3</v>
+        <v>373.89</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1546.7</v>
+        <v>1399.2</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1469.48</v>
+        <v>1359</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1392.53</v>
+        <v>1328.74</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1254.22</v>
+        <v>1394.23</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CIPLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>430.85</v>
+        <v>6887</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>399.56</v>
+        <v>6691.44</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>383.81</v>
+        <v>6477.23</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>373.95</v>
+        <v>6371.31</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1401.9</v>
+        <v>1307.2</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1354.77</v>
+        <v>1302.65</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1325.86</v>
+        <v>1285.62</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1395.32</v>
+        <v>1263.23</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CIPLA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>6858</v>
+        <v>2334</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>6670.85</v>
+        <v>1997.08</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>6460.5</v>
+        <v>1867.9</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>6367.3</v>
+        <v>1789.1</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1318.5</v>
+        <v>751.95</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1302.17</v>
+        <v>727.83</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1284.74</v>
+        <v>681.96</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1263</v>
+        <v>599.29</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2331</v>
+        <v>1602.1</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>1961.61</v>
+        <v>1575.83</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>1848.88</v>
+        <v>1538.75</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1785.68</v>
+        <v>1470.7</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>JBCHEPHARM</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>2393</v>
+        <v>2192.6</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>2338.62</v>
+        <v>2123.35</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>2261.2</v>
+        <v>2068.89</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>2040.77</v>
+        <v>1904.32</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>764.2</v>
+        <v>1343.5</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>725.29</v>
+        <v>1254.48</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>679.1</v>
+        <v>1162.75</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>597.89</v>
+        <v>1001.84</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,23 +1509,23 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1637</v>
+        <v>2479.4</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1573.06</v>
+        <v>2399.72</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>1536.16</v>
+        <v>2280.4</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1471.76</v>
+        <v>2271.95</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,23 +1537,23 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>2178.9</v>
+        <v>1169.7</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>2116.06</v>
+        <v>1146.46</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>2063.84</v>
+        <v>1084.66</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1900.25</v>
+        <v>960.89</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JBCHEPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1351</v>
+        <v>1844.6</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>1245.11</v>
+        <v>1833.9</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>1155.38</v>
+        <v>1787.04</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>998.9299999999999</v>
+        <v>1728.73</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>2514.1</v>
+        <v>4486.2</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>2391.33</v>
+        <v>4359.3</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2272.28</v>
+        <v>4267.92</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2277.58</v>
+        <v>3937.86</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1621,135 +1621,135 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1174.3</v>
+        <v>1038.95</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1144.01</v>
+        <v>973.8</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1081.19</v>
+        <v>941.16</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>958.65</v>
+        <v>930.27</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATCOPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>1891.3</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>1832.77</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>1784.69</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>1728.64</v>
-      </c>
-      <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNPHARMA","Chart 📈")</f>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>2717.3</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>2541.75</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>2355.02</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>2298.78</v>
+      </c>
+      <c r="G18" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>4469.2</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>4345.95</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>4259.02</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>3938.68</v>
-      </c>
-      <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>1109.2</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>1058.12</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>1014.23</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>889.29</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>1036.45</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>966.95</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>937.17</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>928.04</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>632.25</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>623.04</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>599.01</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>545.12</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>2697.6</v>
+        <v>1285.5</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>2523.27</v>
+        <v>1270.68</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>2340.23</v>
+        <v>1243.26</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>2295.64</v>
+        <v>1171.33</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1099.3</v>
+        <v>409.25</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1052.75</v>
+        <v>406.57</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>1010.35</v>
+        <v>398.19</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>888.1900000000001</v>
+        <v>321.66</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>628.05</v>
+        <v>201.21</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>622.0700000000001</v>
+        <v>189.26</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>597.66</v>
+        <v>177.03</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>544.22</v>
+        <v>153.06</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,135 +1817,135 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>1281.3</v>
+        <v>1277.5</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1269.12</v>
+        <v>1262.33</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>1241.54</v>
+        <v>1123.67</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>1169.79</v>
+        <v>930.42</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>NATIONALUM</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>406.4</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>406.28</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>397.74</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>320.53</v>
-      </c>
-      <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NATIONALUM","Chart 📈")</f>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>148.21</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>133</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>85.86</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>196.53</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>188.01</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>176.04</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>152.51</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="G26" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>1330.2</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>1260.74</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>1117.39</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>927.49</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>432.05</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>420.26</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>422.27</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>412.25</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>141.75</v>
+        <v>9525</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>131.4</v>
+        <v>9125.23</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>109.27</v>
+        <v>8362</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>85.28</v>
+        <v>7867.34</v>
       </c>
       <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1957,23 +1957,23 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>13.62</v>
+        <v>1964</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>11.91</v>
+        <v>1666.34</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>10.91</v>
+        <v>1599.48</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>9.779999999999999</v>
+        <v>1640.32</v>
       </c>
       <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1985,219 +1985,219 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>431.8</v>
+        <v>671.35</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>419.02</v>
+        <v>626.75</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>421.87</v>
+        <v>604.3099999999999</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>412.38</v>
+        <v>638.4</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>9730.5</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>9083.15</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>8314.530000000001</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>7857.79</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>1659.6</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>1643.76</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>1618.68</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>1627.6</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>1896.3</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>1635</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>1584.6</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>1636.84</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>1790.3</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>1761.32</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>1733.57</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>1689.99</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>664.1</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>622.0599999999999</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>601.58</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>637.53</v>
-      </c>
-      <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>552.85</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>489.31</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>450.65</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>481.98</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>1654.4</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>1642.09</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>1617.01</v>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>1627.6</v>
-      </c>
-      <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>1367.9</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>1323.38</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>1228.07</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>1043.03</v>
+      </c>
+      <c r="G34" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>1795.7</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>1758.27</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>1731.26</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>1691.09</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1362.3</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>1312.12</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>1183.07</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>1046.04</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>541.5</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>482.62</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>446.48</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>483.33</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>219.32</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>215.97</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>196.6</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>159</v>
+      </c>
+      <c r="G36" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>1342.2</v>
+        <v>408.55</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>1318.69</v>
+        <v>383.06</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>1222.36</v>
+        <v>340.75</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1039.19</v>
+        <v>286.07</v>
       </c>
       <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENSOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2209,23 +2209,23 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C38" s="14" t="n">
-        <v>1358.2</v>
+        <v>865.7</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>1306.84</v>
+        <v>830.41</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>1175.76</v>
+        <v>784.5599999999999</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1043.74</v>
+        <v>719.99</v>
       </c>
       <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2237,23 +2237,23 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>219.33</v>
+        <v>4849.5</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>215.62</v>
+        <v>4481.5</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>195.68</v>
+        <v>4200.36</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>158.35</v>
+        <v>3404.94</v>
       </c>
       <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2265,23 +2265,23 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>408.15</v>
+        <v>18.76</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>380.37</v>
+        <v>18.62</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>337.98</v>
+        <v>17.81</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>284.83</v>
+        <v>17.14</v>
       </c>
       <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JPPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2293,23 +2293,23 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>864.9</v>
+        <v>551.25</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>826.7</v>
+        <v>539.88</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>781.25</v>
+        <v>527.9400000000001</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>718.33</v>
+        <v>509.94</v>
       </c>
       <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2321,23 +2321,23 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>4794.6</v>
+        <v>344.65</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>4442.76</v>
+        <v>332.26</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>4173.86</v>
+        <v>306.67</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>3389.72</v>
+        <v>268.96</v>
       </c>
       <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2349,23 +2349,23 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C43" s="14" t="n">
-        <v>548.45</v>
+        <v>35555</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>538.6799999999999</v>
+        <v>33103.82</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>526.99</v>
+        <v>30050.15</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>509.93</v>
+        <v>23719.86</v>
       </c>
       <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWENERGY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2377,23 +2377,23 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="C44" s="14" t="n">
-        <v>350.5</v>
+        <v>1307.6</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>330.96</v>
+        <v>1246.59</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>305.12</v>
+        <v>1119.6</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>268.13</v>
+        <v>904.35</v>
       </c>
       <c r="G44" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NLCINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2405,23 +2405,23 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C45" s="14" t="n">
-        <v>36450</v>
+        <v>3811.7</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>32845.8</v>
+        <v>3669.12</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>29825.43</v>
+        <v>3535.71</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>23541.32</v>
+        <v>3306.32</v>
       </c>
       <c r="G45" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C46" s="14" t="n">
-        <v>1325.3</v>
+        <v>53.75</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>1240.17</v>
+        <v>53</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>1111.93</v>
+        <v>50.64</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>899.97</v>
+        <v>52.1</v>
       </c>
       <c r="G46" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUZLON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2461,23 +2461,23 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="C47" s="14" t="n">
-        <v>3720.6</v>
+        <v>4454.6</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>3654.12</v>
+        <v>4318.38</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>3524.45</v>
+        <v>3948.21</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>3300.09</v>
+        <v>3459.59</v>
       </c>
       <c r="G47" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2489,79 +2489,79 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>4575</v>
+        <v>706.95</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>4304.05</v>
+        <v>603.13</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>3927.53</v>
+        <v>554.6</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>3445.07</v>
+        <v>531.83</v>
       </c>
       <c r="G48" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:THERMAX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>TRITURBINE</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n">
-        <v>705.6</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>592.21</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>548.38</v>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>530.29</v>
-      </c>
-      <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TRITURBINE","Chart 📈")</f>
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>535.1</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>529.4299999999999</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>509.99</v>
+      </c>
+      <c r="F49" s="18" t="n">
+        <v>494.67</v>
+      </c>
+      <c r="G49" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>537.45</v>
+        <v>824.45</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>528.83</v>
+        <v>816.39</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>508.97</v>
+        <v>792.4400000000001</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>494.16</v>
+        <v>753.49</v>
       </c>
       <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2573,23 +2573,23 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
-        <v>831.85</v>
+        <v>3561.1</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>815.54</v>
+        <v>3420.7</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>791.14</v>
+        <v>3203.62</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>753.71</v>
+        <v>2974.39</v>
       </c>
       <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2601,23 +2601,23 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C52" s="18" t="n">
-        <v>3571.9</v>
+        <v>1191.8</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>3405.92</v>
+        <v>1190.47</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>3189.03</v>
+        <v>1157.97</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>2965.57</v>
+        <v>1138.22</v>
       </c>
       <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2629,79 +2629,79 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="C53" s="18" t="n">
-        <v>1194.9</v>
+        <v>539.45</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>1190.33</v>
+        <v>503.86</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>1156.59</v>
+        <v>480.32</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>1138.67</v>
+        <v>467.64</v>
       </c>
       <c r="G53" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACONSUM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="n">
-        <v>519.85</v>
-      </c>
-      <c r="D54" s="18" t="n">
-        <v>500.11</v>
-      </c>
-      <c r="E54" s="18" t="n">
-        <v>477.91</v>
-      </c>
-      <c r="F54" s="18" t="n">
-        <v>467.71</v>
-      </c>
-      <c r="G54" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VBL","Chart 📈")</f>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="n">
+        <v>724.45</v>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>695.58</v>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>683.48</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>717.95</v>
+      </c>
+      <c r="G54" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>727.85</v>
+        <v>652.8</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>692.54</v>
+        <v>621.35</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>681.8099999999999</v>
+        <v>597.45</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>719.65</v>
+        <v>591.61</v>
       </c>
       <c r="G55" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2713,387 +2713,387 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C56" s="14" t="n">
-        <v>638.1</v>
+        <v>499.75</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>618.04</v>
+        <v>490.86</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>595.2</v>
+        <v>480.1</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>591.4400000000001</v>
+        <v>448.73</v>
       </c>
       <c r="G56" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="n">
-        <v>503.5</v>
-      </c>
-      <c r="D57" s="14" t="n">
-        <v>489.93</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>479.3</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>448.88</v>
-      </c>
-      <c r="G57" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>10549.5</v>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>10241.08</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>9908.370000000001</v>
+      </c>
+      <c r="F57" s="18" t="n">
+        <v>9348.43</v>
+      </c>
+      <c r="G57" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>295.85</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>292.49</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>284.49</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>259.02</v>
-      </c>
-      <c r="G58" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ONGC","Chart 📈")</f>
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>1897.7</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>1894.95</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>1833.94</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>1579.04</v>
+      </c>
+      <c r="G58" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>136.18</v>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>124.37</v>
+      </c>
+      <c r="F59" s="18" t="n">
+        <v>115.58</v>
+      </c>
+      <c r="G59" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>NAZARA</t>
         </is>
       </c>
-      <c r="C59" s="18" t="n">
-        <v>285.2</v>
-      </c>
-      <c r="D59" s="18" t="n">
-        <v>276.22</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>266.75</v>
-      </c>
-      <c r="F59" s="18" t="n">
-        <v>273.46</v>
-      </c>
-      <c r="G59" s="19">
+      <c r="C60" s="14" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>276.92</v>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>267.4</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>273.61</v>
+      </c>
+      <c r="G60" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>SAREGAMA</t>
         </is>
       </c>
-      <c r="C60" s="18" t="n">
-        <v>406.4</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>369.48</v>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>354.61</v>
-      </c>
-      <c r="F60" s="18" t="n">
-        <v>389.07</v>
-      </c>
-      <c r="G60" s="19">
+      <c r="C61" s="14" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>372.61</v>
+      </c>
+      <c r="E61" s="14" t="n">
+        <v>356.48</v>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>389.32</v>
+      </c>
+      <c r="G61" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>TIPSMUSIC</t>
         </is>
       </c>
-      <c r="C61" s="18" t="n">
-        <v>658.85</v>
-      </c>
-      <c r="D61" s="18" t="n">
-        <v>637.6900000000001</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>602.46</v>
-      </c>
-      <c r="F61" s="18" t="n">
-        <v>572.89</v>
-      </c>
-      <c r="G61" s="19">
+      <c r="C62" s="14" t="n">
+        <v>681.05</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>641.8200000000001</v>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v>605.54</v>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>575.89</v>
+      </c>
+      <c r="G62" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n">
-        <v>10667</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>10208.62</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>9882.200000000001</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>9332.639999999999</v>
-      </c>
-      <c r="G62" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n">
-        <v>1898.8</v>
-      </c>
-      <c r="D63" s="14" t="n">
-        <v>1894.66</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>1831.34</v>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>1574.95</v>
-      </c>
-      <c r="G63" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHARATFORG","Chart 📈")</f>
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>1285.4</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>1270.73</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>1282.74</v>
+      </c>
+      <c r="F63" s="18" t="n">
+        <v>1255.55</v>
+      </c>
+      <c r="G63" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>137</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>127.69</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>123.89</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>115.38</v>
-      </c>
-      <c r="G64" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>2738.7</v>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>2702.18</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>2658.47</v>
+      </c>
+      <c r="F64" s="18" t="n">
+        <v>2625.14</v>
+      </c>
+      <c r="G64" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>3269.9</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>3155.67</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>2897.07</v>
+      </c>
+      <c r="F65" s="18" t="n">
+        <v>2307.89</v>
+      </c>
+      <c r="G65" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B65" s="17" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>CERA</t>
         </is>
       </c>
-      <c r="C65" s="18" t="n">
-        <v>5788</v>
-      </c>
-      <c r="D65" s="18" t="n">
-        <v>5577.3</v>
-      </c>
-      <c r="E65" s="18" t="n">
-        <v>5339.54</v>
-      </c>
-      <c r="F65" s="18" t="n">
-        <v>5513.89</v>
-      </c>
-      <c r="G65" s="19">
+      <c r="C66" s="14" t="n">
+        <v>5708</v>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>5589.75</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>5353.99</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>5515.16</v>
+      </c>
+      <c r="G66" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CERA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="20" t="inlineStr">
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>CROMPTON</t>
         </is>
       </c>
-      <c r="C66" s="18" t="n">
-        <v>291.85</v>
-      </c>
-      <c r="D66" s="18" t="n">
-        <v>282.06</v>
-      </c>
-      <c r="E66" s="18" t="n">
-        <v>268.34</v>
-      </c>
-      <c r="F66" s="18" t="n">
-        <v>276.4</v>
-      </c>
-      <c r="G66" s="19">
+      <c r="C67" s="14" t="n">
+        <v>294.75</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>283.26</v>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>269.38</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>276.33</v>
+      </c>
+      <c r="G67" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CROMPTON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="n">
-        <v>899.95</v>
-      </c>
-      <c r="D67" s="14" t="n">
-        <v>896.12</v>
-      </c>
-      <c r="E67" s="14" t="n">
-        <v>882.16</v>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>851.72</v>
-      </c>
-      <c r="G67" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C68" s="18" t="n">
-        <v>2727.9</v>
+        <v>287.2</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>2698.34</v>
+        <v>286.81</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>2655.2</v>
+        <v>284.16</v>
       </c>
       <c r="F68" s="18" t="n">
-        <v>2625.26</v>
+        <v>258.47</v>
       </c>
       <c r="G68" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCAMC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="C69" s="18" t="n">
-        <v>3322.8</v>
+        <v>910.15</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>3143.65</v>
+        <v>897.46</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>2881.85</v>
+        <v>883.25</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>2298.23</v>
+        <v>853.53</v>
       </c>
       <c r="G69" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -3109,16 +3109,16 @@
         </is>
       </c>
       <c r="C70" s="14" t="n">
-        <v>79.76000000000001</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="D70" s="14" t="n">
-        <v>78.53</v>
+        <v>78.67</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>74.65000000000001</v>
+        <v>74.86</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>64.81999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G70" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 22-May-2026  13:42</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 25-May-2026  14:11</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>18</v>
@@ -684,199 +684,199 @@
         <v>0.8</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.9</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.85</v>
+        <v>0.8667</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.467</v>
+        <v>0.9</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.6446999999999999</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>10</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.75</v>
+        <v>0.467</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.5167</v>
+        <v>0.6446999999999999</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G7" s="10" t="n">
         <v>0.7</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>0.5</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.5</v>
+        <v>0.6333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.375</v>
+        <v>0.667</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.475</v>
+        <v>0.667</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.4667</v>
+        <v>0.578</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>6</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.467</v>
+        <v>0.6</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.4223</v>
+        <v>0.5167</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.467</v>
+        <v>0.525</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.267</v>
+        <v>0.55</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.4917</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -889,25 +889,25 @@
         <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.467</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.3553</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -920,149 +920,149 @@
         <v>10</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.4</v>
+        <v>0.583</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.3167</v>
+        <v>0.3887</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.267</v>
+        <v>0.4</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.289</v>
+        <v>0.3777</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.167</v>
+        <v>0.267</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.2223</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.083</v>
+        <v>0.333</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.083</v>
+        <v>0.333</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.111</v>
+        <v>0.3053</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1075,7 +1075,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>1</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0.1</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0667</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3107.5</v>
+        <v>3081.5</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3064.42</v>
+        <v>3066.05</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2962.32</v>
+        <v>2967</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2774.62</v>
+        <v>2779.2</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>430.25</v>
+        <v>430.05</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>402.48</v>
+        <v>405.11</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>385.63</v>
+        <v>387.37</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>373.89</v>
+        <v>374.39</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BIOCON","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1399.2</v>
+        <v>1413.9</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1359</v>
+        <v>13